--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">SSIM!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">인형나라!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="568">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>423</t>
+    <t>422</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>4경 784조 1696억 5789만</t>
+    <t>4경 2203조 6052억 4725만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,36 +101,39 @@
     <t>자유이용껀</t>
   </si>
   <si>
+    <t>2026.09.13</t>
+  </si>
+  <si>
+    <t>인형나라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B8%ED%98%95%EB%82%98%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>Scania 25</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 1501조 7441억 8574만</t>
+  </si>
+  <si>
+    <t>Server.74 since 2026.01.27</t>
+  </si>
+  <si>
+    <t>최영교</t>
+  </si>
+  <si>
     <t>2026.09.12</t>
   </si>
   <si>
-    <t>인형나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B8%ED%98%95%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
-  </si>
-  <si>
-    <t>424</t>
-  </si>
-  <si>
-    <t>8위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>4경 446조 6640억 8825만</t>
-  </si>
-  <si>
-    <t>Server.74 since 2026.01.27</t>
-  </si>
-  <si>
-    <t>최영교</t>
-  </si>
-  <si>
     <t>86서버</t>
   </si>
   <si>
@@ -143,10 +146,10 @@
     <t>430</t>
   </si>
   <si>
-    <t>4위</t>
-  </si>
-  <si>
-    <t>3경 9778조 1390억 8518만</t>
+    <t>5위</t>
+  </si>
+  <si>
+    <t>4경 127조 5543억 5704만</t>
   </si>
   <si>
     <t>길갑문의 PSG서포터즈, 김로케 귓 (길컨 진심, 길토벌 200위권! 귓)</t>
@@ -164,13 +167,13 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>465</t>
+    <t>466</t>
   </si>
   <si>
     <t>9위</t>
   </si>
   <si>
-    <t>3경 4644조 4735억 5757만</t>
+    <t>3경 4802조 1167억 4071만</t>
   </si>
   <si>
     <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
@@ -188,7 +191,7 @@
     <t>Scania 60</t>
   </si>
   <si>
-    <t>386</t>
+    <t>390</t>
   </si>
   <si>
     <t>2위</t>
@@ -197,7 +200,7 @@
     <t>Lv.8</t>
   </si>
   <si>
-    <t>4경 8075조 6026억 3323만</t>
+    <t>4경 8229조 4306억 6791만</t>
   </si>
   <si>
     <t>길드 콘텐츠 필수 [ 50조 이상 가입 및 대기 문의 : 김또느 ]</t>
@@ -248,7 +251,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>7821조 3447억 6057만</t>
+    <t>7906조 7238억 2174만</t>
   </si>
   <si>
     <t>2</t>
@@ -266,12 +269,27 @@
     <t>112</t>
   </si>
   <si>
-    <t>5155조 6881억 7704만</t>
+    <t>5275조 6486억 443만</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3109조 3775억 1324만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>두향</t>
   </si>
   <si>
@@ -281,10 +299,10 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>3101조 2376억 7222만</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>3106조 3758억 3080만</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -299,22 +317,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>2865조 9570억 7559만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>2753조 9468억 6201만</t>
+    <t>2878조 5956억 6653만</t>
   </si>
   <si>
     <t>6</t>
@@ -341,7 +344,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>1963조 2114억 1325만</t>
+    <t>2095조 8298억 2089만</t>
   </si>
   <si>
     <t>8</t>
@@ -353,7 +356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>1786조 5313억 8270만</t>
+    <t>1816조 5376억 7272만</t>
   </si>
   <si>
     <t>9</t>
@@ -365,7 +368,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1503조 1643억 4957만</t>
+    <t>1537조 2505억 2514만</t>
   </si>
   <si>
     <t>10</t>
@@ -377,7 +380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>1319조 8767억 4330만</t>
+    <t>1353조 6552억 288만</t>
   </si>
   <si>
     <t>11</t>
@@ -473,7 +476,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>694조 6504억 2714만</t>
+    <t>725조 3107억 9252만</t>
   </si>
   <si>
     <t>18</t>
@@ -485,7 +488,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>678조 2459억 5928만</t>
+    <t>703조 4068억 5130만</t>
   </si>
   <si>
     <t>19</t>
@@ -527,19 +530,31 @@
     <t>22</t>
   </si>
   <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>396조 506억 4801만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>플로우00</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>355조 2112억 2687만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>371조 9523억 1021만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -551,18 +566,6 @@
     <t>343조 8712억 3221만</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>323조 9883억 2289만</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -572,7 +575,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>301조 5726억 7737만</t>
+    <t>301조 7207억 2277만</t>
   </si>
   <si>
     <t>26</t>
@@ -587,66 +590,54 @@
     <t>108</t>
   </si>
   <si>
-    <t>249조 5499억 3789만</t>
+    <t>260조 9371억 8629만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>245조 4488억 8737만</t>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>194조 4027억 9180만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>194조 4027억 9180만</t>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>193조 4998억 774만</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>193조 4998억 774만</t>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>186조 7994억 7947만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>186조 7994억 7947만</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
     <t>꼬북빵야</t>
   </si>
   <si>
@@ -674,6 +665,15 @@
     <t>3245조 684억 6500만</t>
   </si>
   <si>
+    <t>괴챠반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
+  </si>
+  <si>
+    <t>3204조 8824억 2626만</t>
+  </si>
+  <si>
     <t>유놈</t>
   </si>
   <si>
@@ -683,15 +683,6 @@
     <t>2621조 4061억 2859만</t>
   </si>
   <si>
-    <t>괴챠반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
-  </si>
-  <si>
-    <t>2488조 481억 9277만</t>
-  </si>
-  <si>
     <t>꿀꿀맛</t>
   </si>
   <si>
@@ -707,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A7%A4%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
   </si>
   <si>
-    <t>1938조 4838억 8336만</t>
+    <t>2146조 5713억 9703만</t>
   </si>
   <si>
     <t>윤꼬밍</t>
@@ -716,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
   </si>
   <si>
-    <t>1796조 5969억 3375만</t>
+    <t>1830조 1454억 192만</t>
   </si>
   <si>
     <t>사오토메란마</t>
@@ -743,6 +734,15 @@
     <t>1152조 7813억 2778만</t>
   </si>
   <si>
+    <t>Pakachu9999</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
+  </si>
+  <si>
+    <t>1111조 2237억 7409만</t>
+  </si>
+  <si>
     <t>구엉이</t>
   </si>
   <si>
@@ -752,22 +752,13 @@
     <t>1052조 5398억 161만</t>
   </si>
   <si>
-    <t>Pakachu9999</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
-  </si>
-  <si>
-    <t>1019조 2014억 6464만</t>
-  </si>
-  <si>
     <t>잉글리쉬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B8%80%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>947조 1064억 8139만</t>
+    <t>981조 8306억 6598만</t>
   </si>
   <si>
     <t>혁바</t>
@@ -776,7 +767,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EB%B0%94</t>
   </si>
   <si>
-    <t>765조 2301억 796만</t>
+    <t>773조 9543억 1435만</t>
   </si>
   <si>
     <t>똥땅이횽</t>
@@ -785,7 +776,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
   </si>
   <si>
-    <t>726조 7815억 3539만</t>
+    <t>727조 1015억 2662만</t>
+  </si>
+  <si>
+    <t>범지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
+  </si>
+  <si>
+    <t>720조 6461억 5197만</t>
   </si>
   <si>
     <t>디메트로돈</t>
@@ -797,13 +797,13 @@
     <t>704조 9735억 7649만</t>
   </si>
   <si>
-    <t>범지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
-  </si>
-  <si>
-    <t>677조 1258억 4414만</t>
+    <t>솖이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>646조 56억 5787만</t>
   </si>
   <si>
     <t>뜨머푸</t>
@@ -812,16 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A8%B8%ED%91%B8</t>
   </si>
   <si>
-    <t>638조 9776억 5630만</t>
-  </si>
-  <si>
-    <t>솖이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>613조 9069억 282만</t>
+    <t>642조 2231억 9071만</t>
   </si>
   <si>
     <t>혜미니현미니</t>
@@ -839,7 +830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
   </si>
   <si>
-    <t>537조 4762억 3361만</t>
+    <t>567조 398억 7136만</t>
   </si>
   <si>
     <t>옆구리두방</t>
@@ -848,7 +839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%86%EA%B5%AC%EB%A6%AC%EB%91%90%EB%B0%A9</t>
   </si>
   <si>
-    <t>501조 9627억 4648만</t>
+    <t>511조 7625억 5353만</t>
   </si>
   <si>
     <t>쀏뀱쪍</t>
@@ -860,7 +851,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>407조 3232억 4984만</t>
+    <t>425조 2685억 1641만</t>
   </si>
   <si>
     <t>양쿼카</t>
@@ -899,13 +890,22 @@
     <t>330조 108억 9811만</t>
   </si>
   <si>
+    <t>돼짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>306조 3982억 4727만</t>
+  </si>
+  <si>
     <t>젤로젤리</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%A4%EB%A1%9C%EC%A0%A4%EB%A6%AC</t>
   </si>
   <si>
-    <t>292조 7357억 1384만</t>
+    <t>304조 3439억 3321만</t>
   </si>
   <si>
     <t>여덟시</t>
@@ -914,16 +914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
   </si>
   <si>
-    <t>279조 215억 6523만</t>
-  </si>
-  <si>
-    <t>돼짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>276조 9550억 6552만</t>
+    <t>282조 2270억 1691만</t>
   </si>
   <si>
     <t>이슬러버</t>
@@ -950,7 +941,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%EB%A1%9C</t>
   </si>
   <si>
-    <t>2991조 4776억 1168만</t>
+    <t>2997조 5305억 8714만</t>
+  </si>
+  <si>
+    <t>웅잉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>2588조 5656억 334만</t>
   </si>
   <si>
     <t>보급중대장</t>
@@ -959,16 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%B8%89%EC%A4%91%EB%8C%80%EC%9E%A5</t>
   </si>
   <si>
-    <t>2379조 8797억 59만</t>
-  </si>
-  <si>
-    <t>웅잉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>2359조 5750억 9407만</t>
+    <t>2387조 4334억 2228만</t>
   </si>
   <si>
     <t>델타시그마</t>
@@ -977,7 +968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
   </si>
   <si>
-    <t>2305조 5919억 4927만</t>
+    <t>2305조 7344억 9898만</t>
   </si>
   <si>
     <t>엉쫀</t>
@@ -989,6 +980,15 @@
     <t>1538조 6264억 5877만</t>
   </si>
   <si>
+    <t>으눼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
+  </si>
+  <si>
+    <t>1277조 2019억 9720만</t>
+  </si>
+  <si>
     <t>돼왕다람쥐</t>
   </si>
   <si>
@@ -998,13 +998,13 @@
     <t>1271조 2353억 7233만</t>
   </si>
   <si>
-    <t>으눼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
-  </si>
-  <si>
-    <t>1241조 6927억 7291만</t>
+    <t>용이a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
+  </si>
+  <si>
+    <t>1218조 9701억 7071만</t>
   </si>
   <si>
     <t>꼴뱅이a</t>
@@ -1013,7 +1013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%B1%85%EC%9D%B4a</t>
   </si>
   <si>
-    <t>1151조 5780억 2484만</t>
+    <t>1173조 8793억 7383만</t>
   </si>
   <si>
     <t>벽그림</t>
@@ -1025,22 +1025,13 @@
     <t>1139조 6050억 2424만</t>
   </si>
   <si>
-    <t>용이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1107조 6996억 41만</t>
-  </si>
-  <si>
     <t>간장아비</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%84%EC%9E%A5%EC%95%84%EB%B9%84</t>
   </si>
   <si>
-    <t>1010조 7682억 3946만</t>
+    <t>1051조 1655억 8445만</t>
   </si>
   <si>
     <t>요금표</t>
@@ -1049,7 +1040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B8%88%ED%91%9C</t>
   </si>
   <si>
-    <t>890조 874억 9082만</t>
+    <t>950조 2372억 5448만</t>
   </si>
   <si>
     <t>무과키</t>
@@ -1067,7 +1058,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
   </si>
   <si>
-    <t>726조 1821억 7870만</t>
+    <t>759조 4295억 7205만</t>
+  </si>
+  <si>
+    <t>하랸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
+  </si>
+  <si>
+    <t>656조 3944억 7494만</t>
   </si>
   <si>
     <t>에누마</t>
@@ -1085,22 +1085,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
   </si>
   <si>
-    <t>648조 2755억 487만</t>
+    <t>648조 3728억 7491만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=PSG%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>642조 2451억 4957만</t>
-  </si>
-  <si>
-    <t>하랸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
-  </si>
-  <si>
-    <t>637조 2617억 1451만</t>
+    <t>642조 5254억 2415만</t>
   </si>
   <si>
     <t>뭉게뭉게구름</t>
@@ -1109,7 +1100,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%EA%B2%8C%EB%AD%89%EA%B2%8C%EA%B5%AC%EB%A6%84</t>
   </si>
   <si>
-    <t>580조 5716억 5734만</t>
+    <t>581조 8316억 4015만</t>
   </si>
   <si>
     <t>서피비치</t>
@@ -1118,7 +1109,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%94%BC%EB%B9%84%EC%B9%98</t>
   </si>
   <si>
-    <t>541조 4286억 5441만</t>
+    <t>545조 8117억 859만</t>
+  </si>
+  <si>
+    <t>주식하자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
+  </si>
+  <si>
+    <t>481조 5286억 3200만</t>
   </si>
   <si>
     <t>김로케</t>
@@ -1127,16 +1127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%9C%EC%BC%80</t>
   </si>
   <si>
-    <t>432조 4661억 8744만</t>
-  </si>
-  <si>
-    <t>주식하자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
-  </si>
-  <si>
-    <t>423조 8075억 1323만</t>
+    <t>434조 3053억 2526만</t>
   </si>
   <si>
     <t>소심한섀도어</t>
@@ -1145,7 +1136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%8B%AC%ED%95%9C%EC%84%80%EB%8F%84%EC%96%B4</t>
   </si>
   <si>
-    <t>312조 286억 277만</t>
+    <t>368조 5948억 3216만</t>
   </si>
   <si>
     <t>전포동포동이</t>
@@ -1154,7 +1145,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8F%AC%EB%8F%99%ED%8F%AC%EB%8F%99%EC%9D%B4</t>
   </si>
   <si>
-    <t>263조 6702억 9488만</t>
+    <t>270조 5475억 634만</t>
+  </si>
+  <si>
+    <t>경춘선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
+  </si>
+  <si>
+    <t>225조 6213억 6343만</t>
   </si>
   <si>
     <t>01260227</t>
@@ -1166,15 +1166,6 @@
     <t>225조 5898억 9585만</t>
   </si>
   <si>
-    <t>경춘선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
-  </si>
-  <si>
-    <t>222조 4682억 7154만</t>
-  </si>
-  <si>
     <t>8623</t>
   </si>
   <si>
@@ -1184,7 +1175,7 @@
     <t>107</t>
   </si>
   <si>
-    <t>200조 262억 8993만</t>
+    <t>200조 1543억 7550만</t>
   </si>
   <si>
     <t>수비맨디</t>
@@ -1205,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>3802조 7381억 6519만</t>
+    <t>3850조 9115억 6840만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1223,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>2756조 7174억 7789만</t>
+    <t>2769조 1351억 2419만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -1250,7 +1241,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>1572조 8351억 8686만</t>
+    <t>1666조 7737억 1182만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1558조 7056억 5039만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1259,7 +1259,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>1481조 8535억 8791만</t>
+    <t>1513조 9876억 9384만</t>
+  </si>
+  <si>
+    <t>해달잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
+  </si>
+  <si>
+    <t>1433조 2212억 1888만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1271,31 +1280,13 @@
     <t>1425조 8545억 3978만</t>
   </si>
   <si>
-    <t>해달잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1414조 3671억 6148만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1404조 81억 6682만</t>
-  </si>
-  <si>
     <t>포빅</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>1109조 6445억 6827만</t>
+    <t>1133조 8432억 4587만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1304,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1090조 5914억 4890만</t>
+    <t>1112조 2357억 5917만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1313,7 +1304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1061조 984억 2887만</t>
+    <t>1063조 3039억 629만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1322,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>945조 8418억 9477만</t>
+    <t>998조 7244억 213만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1331,7 +1322,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
   </si>
   <si>
-    <t>877조 4595억 3995만</t>
+    <t>979조 1950억 779만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1340,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>828조 8581억 5678만</t>
+    <t>830조 9149억 3633만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1349,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>782조 4301억 7616만</t>
+    <t>817조 5104억 6557만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1358,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>755조 95억 4540만</t>
+    <t>780조 1642억 9657만</t>
   </si>
   <si>
     <t>박금쪽</t>
@@ -1367,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
   </si>
   <si>
-    <t>659조 9535억 8019만</t>
+    <t>664조 8222억 7460만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1376,7 +1367,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>640조 9662억 5280만</t>
+    <t>641조 4638억 3097만</t>
+  </si>
+  <si>
+    <t>파이리양말</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
+  </si>
+  <si>
+    <t>641조 3051억 2877만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1385,7 +1385,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>623조 7481억 4062만</t>
+    <t>640조 5014억 9379만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1397,22 +1397,13 @@
     <t>565조 9188억 2581만</t>
   </si>
   <si>
-    <t>파이리양말</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
-  </si>
-  <si>
-    <t>543조 5701억 8517만</t>
-  </si>
-  <si>
     <t>성률</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>540조 151억 8933만</t>
+    <t>541조 1722억 1710만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1421,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
   </si>
   <si>
-    <t>500조 2607억 5801만</t>
+    <t>536조 1307억 2693만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1442,22 +1433,22 @@
     <t>448조 3203억 7107만</t>
   </si>
   <si>
+    <t>하비엔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
+  </si>
+  <si>
+    <t>272조 8228억 5047만</t>
+  </si>
+  <si>
     <t>채구링</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>250조 4135억 3385만</t>
-  </si>
-  <si>
-    <t>하비엔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
-  </si>
-  <si>
-    <t>246조 9868억 6461만</t>
+    <t>253조 655억 8729만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1466,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>206조 9561억 1406만</t>
+    <t>208조 2112억 3656만</t>
   </si>
   <si>
     <t>주식회사서영</t>
@@ -1493,13 +1484,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EA%B7%B8%EB%9F%AC%EC%A7%84%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>2206조 2476억 1352만</t>
+    <t>2303조 8444억 3203만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%90%EB%8A%90</t>
   </si>
   <si>
-    <t>1809조 6213억 5911만</t>
+    <t>1967조 6666억 7859만</t>
+  </si>
+  <si>
+    <t>부산철거</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%EC%B2%A0%EA%B1%B0</t>
+  </si>
+  <si>
+    <t>577조 7457억 312만</t>
   </si>
   <si>
     <t>베네치얀</t>
@@ -1508,16 +1508,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%84%A4%EC%B9%98%EC%96%80</t>
   </si>
   <si>
-    <t>528조 798억 8090만</t>
-  </si>
-  <si>
-    <t>부산철거</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%EC%B2%A0%EA%B1%B0</t>
-  </si>
-  <si>
-    <t>507조 519억 8708만</t>
+    <t>533조 2970억 3238만</t>
+  </si>
+  <si>
+    <t>갸렌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B8%EB%A0%8C</t>
+  </si>
+  <si>
+    <t>347조 4015억 7971만</t>
   </si>
   <si>
     <t>태양o</t>
@@ -1526,16 +1526,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%96%91o</t>
   </si>
   <si>
-    <t>313조 6956억 6747만</t>
-  </si>
-  <si>
-    <t>갸렌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B8%EB%A0%8C</t>
-  </si>
-  <si>
-    <t>308조 1011억 14만</t>
+    <t>324조 7719억 4290만</t>
   </si>
   <si>
     <t>꺆뜎</t>
@@ -1544,7 +1535,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%86%EB%9C%8E</t>
   </si>
   <si>
-    <t>252조 1018억 2702만</t>
+    <t>256조 9970억 813만</t>
   </si>
   <si>
     <t>효설빈</t>
@@ -1553,7 +1544,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%84%A4%EB%B9%88</t>
   </si>
   <si>
-    <t>248조 1851억 5878만</t>
+    <t>254조 6373억 9561만</t>
   </si>
   <si>
     <t>모우모우우</t>
@@ -1562,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%9A%B0%EB%AA%A8%EC%9A%B0%EC%9A%B0</t>
   </si>
   <si>
-    <t>243조 3433억 1597만</t>
+    <t>249조 5633억 6327만</t>
   </si>
   <si>
     <t>봄여름한겨울</t>
@@ -1571,7 +1562,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%97%AC%EB%A6%84%ED%95%9C%EA%B2%A8%EC%9A%B8</t>
   </si>
   <si>
-    <t>230조 9250억 2536만</t>
+    <t>248조 4947억 8591만</t>
   </si>
   <si>
     <t>1지옥참마도1</t>
@@ -1580,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=1%EC%A7%80%EC%98%A5%EC%B0%B8%EB%A7%88%EB%8F%841</t>
   </si>
   <si>
-    <t>227조 9462억 5023만</t>
+    <t>240조 7601억 443만</t>
   </si>
   <si>
     <t>곰세마리당</t>
@@ -1592,22 +1583,22 @@
     <t>219조 5525억 5510만</t>
   </si>
   <si>
+    <t>하숩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%A9</t>
+  </si>
+  <si>
+    <t>213조 64억 4384만</t>
+  </si>
+  <si>
     <t>토느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8A%90</t>
   </si>
   <si>
-    <t>187조 9926억 7161만</t>
-  </si>
-  <si>
-    <t>하숩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%A9</t>
-  </si>
-  <si>
-    <t>176조 227억 6709만</t>
+    <t>193조 7969억 7930만</t>
   </si>
   <si>
     <t>행복하길바래</t>
@@ -1616,7 +1607,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%89%EB%B3%B5%ED%95%98%EA%B8%B8%EB%B0%94%EB%9E%98</t>
   </si>
   <si>
-    <t>156조 5769억 4891만</t>
+    <t>156조 9362억 6516만</t>
+  </si>
+  <si>
+    <t>당근이니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B7%BC%EC%9D%B4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>148조 5665억 550만</t>
   </si>
   <si>
     <t>미허</t>
@@ -1625,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%ED%97%88</t>
   </si>
   <si>
-    <t>144조 3116억 8011만</t>
+    <t>148조 4819억 2363만</t>
   </si>
   <si>
     <t>동그리미</t>
@@ -1634,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EA%B7%B8%EB%A6%AC%EB%AF%B8</t>
   </si>
   <si>
-    <t>140조 3466억 3142만</t>
+    <t>143조 2694억 7698만</t>
   </si>
   <si>
     <t>허상하</t>
@@ -1646,13 +1646,13 @@
     <t>122조 9589억 1010만</t>
   </si>
   <si>
-    <t>당근이니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B7%BC%EC%9D%B4%EB%8B%88</t>
-  </si>
-  <si>
-    <t>118조 26억 7386만</t>
+    <t>명지사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>84조 2901억 7452만</t>
   </si>
   <si>
     <t>최경무</t>
@@ -1661,16 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B2%BD%EB%AC%B4</t>
   </si>
   <si>
-    <t>77조 5542억 4718만</t>
-  </si>
-  <si>
-    <t>명지사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>75조 2507억 7831만</t>
+    <t>78조 522억 1252만</t>
   </si>
   <si>
     <t>앙설</t>
@@ -1682,7 +1673,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>62조 331억 6860만</t>
+    <t>63조 8457억 5091만</t>
   </si>
   <si>
     <t>진떡</t>
@@ -1691,7 +1682,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EB%96%A1</t>
   </si>
   <si>
-    <t>60조 298억 7637만</t>
+    <t>61조 2140억 4733만</t>
   </si>
   <si>
     <t>해적왕정우짱</t>
@@ -1700,7 +1691,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A0%81%EC%99%95%EC%A0%95%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>50조 4961억 739만</t>
+    <t>52조 502억 6634만</t>
   </si>
   <si>
     <t>비단나비</t>
@@ -1709,7 +1700,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%8B%A8%EB%82%98%EB%B9%84</t>
   </si>
   <si>
-    <t>44조 7349억 707만</t>
+    <t>49조 4046억 4806만</t>
   </si>
   <si>
     <t>태양0</t>
@@ -1718,7 +1709,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%96%910</t>
   </si>
   <si>
-    <t>37조 4061억 1893만</t>
+    <t>45조 9846억 5148만</t>
   </si>
   <si>
     <t>마동턱</t>
@@ -1739,7 +1730,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 3162억 3676만</t>
+    <t>30조 2992억 4964만</t>
   </si>
 </sst>
 </file>
@@ -2238,30 +2229,30 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
@@ -2270,39 +2261,39 @@
         <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2311,57 +2302,57 @@
         <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2379,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2396,28 +2387,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2428,28 +2419,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2460,28 +2451,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2492,28 +2483,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2524,25 +2515,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>90</v>
@@ -2568,16 +2559,16 @@
         <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2588,28 +2579,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2620,28 +2611,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2652,28 +2643,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2684,28 +2675,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2716,28 +2707,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2748,28 +2739,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2780,28 +2771,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2812,28 +2803,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2844,7 +2835,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>23</v>
@@ -2853,19 +2844,19 @@
         <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2876,28 +2867,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2908,28 +2899,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2940,28 +2931,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2972,28 +2963,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3004,28 +2995,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3036,28 +3027,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3068,28 +3059,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3100,28 +3091,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3132,28 +3123,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3164,28 +3155,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3196,28 +3187,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3228,28 +3219,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3260,28 +3251,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>134</v>
+        <v>191</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3292,28 +3283,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>194</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3324,28 +3315,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3356,67 +3347,35 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3448,7 +3407,6 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
-    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3474,28 +3432,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3506,31 +3464,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3538,31 +3496,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3570,31 +3528,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>200</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3602,31 +3560,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>203</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3637,28 +3595,28 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3666,31 +3624,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3698,31 +3656,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3730,31 +3688,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3762,7 +3720,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>33</v>
@@ -3771,22 +3729,22 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3794,31 +3752,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3826,31 +3784,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3858,31 +3816,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3890,31 +3848,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3922,31 +3880,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3954,31 +3912,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3986,31 +3944,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4018,31 +3976,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4050,31 +4008,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4082,31 +4040,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>194</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4114,31 +4072,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4146,31 +4104,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4178,31 +4136,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4210,31 +4168,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>277</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4242,31 +4200,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4274,31 +4232,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4306,31 +4264,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4338,31 +4296,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4370,31 +4328,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4402,31 +4360,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4434,31 +4392,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4519,28 +4477,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4548,962 +4506,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>350</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>350</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>355</v>
+        <v>42</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>355</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>134</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>125</v>
+        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>385</v>
-      </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5564,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5593,962 +5551,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>276</v>
+        <v>200</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>384</v>
+        <v>169</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -6609,28 +6567,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6638,962 +6596,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>168</v>
+        <v>381</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>384</v>
+        <v>169</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>276</v>
+        <v>121</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>273</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>185</v>
+        <v>381</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>389</v>
+        <v>186</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>203</v>
+        <v>135</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>551</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>570</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="인형나라" sheetId="3" r:id="rId3"/>
-    <sheet name="86서버" sheetId="4" r:id="rId4"/>
+    <sheet name="86서버" sheetId="3" r:id="rId3"/>
+    <sheet name="인형나라" sheetId="4" r:id="rId4"/>
     <sheet name="눈별" sheetId="5" r:id="rId5"/>
     <sheet name="SSIM" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'86서버'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'86서버'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">SSIM!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">인형나라!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">인형나라!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="565">
   <si>
     <t>guild_name</t>
   </si>
@@ -104,6 +104,36 @@
     <t>2026.09.13</t>
   </si>
   <si>
+    <t>86서버</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=86%EC%84%9C%EB%B2%84</t>
+  </si>
+  <si>
+    <t>Scania 33</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>5위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 127조 5543억 5704만</t>
+  </si>
+  <si>
+    <t>길갑문의 PSG서포터즈, 김로케 귓 (길컨 진심, 길토벌 200위권! 귓)</t>
+  </si>
+  <si>
+    <t>PSG서포터즈</t>
+  </si>
+  <si>
+    <t>2026.09.12</t>
+  </si>
+  <si>
     <t>인형나라</t>
   </si>
   <si>
@@ -119,9 +149,6 @@
     <t>8위</t>
   </si>
   <si>
-    <t>30명</t>
-  </si>
-  <si>
     <t>4경 1501조 7441억 8574만</t>
   </si>
   <si>
@@ -131,33 +158,6 @@
     <t>최영교</t>
   </si>
   <si>
-    <t>2026.09.12</t>
-  </si>
-  <si>
-    <t>86서버</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=86%EC%84%9C%EB%B2%84</t>
-  </si>
-  <si>
-    <t>Scania 33</t>
-  </si>
-  <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>5위</t>
-  </si>
-  <si>
-    <t>4경 127조 5543억 5704만</t>
-  </si>
-  <si>
-    <t>길갑문의 PSG서포터즈, 김로케 귓 (길컨 진심, 길토벌 200위권! 귓)</t>
-  </si>
-  <si>
-    <t>PSG서포터즈</t>
-  </si>
-  <si>
     <t>눈별</t>
   </si>
   <si>
@@ -251,7 +251,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>7906조 7238억 2174만</t>
+    <t>8232조 3835억 8286만</t>
   </si>
   <si>
     <t>2</t>
@@ -269,12 +269,45 @@
     <t>112</t>
   </si>
   <si>
-    <t>5275조 6486억 443만</t>
+    <t>5286조 3617억 27만</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>두향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3428조 96억 9692만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>3164조 1968억 5216만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>몽호</t>
   </si>
   <si>
@@ -284,40 +317,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>3109조 3775억 1324만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>두향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>3106조 3758억 3080만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>2878조 5956억 6653만</t>
+    <t>3155조 7739억 8662만</t>
   </si>
   <si>
     <t>6</t>
@@ -329,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>2490조 7844억 7914만</t>
+    <t>2712조 6401억 5428만</t>
   </si>
   <si>
     <t>7</t>
@@ -344,7 +344,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>2095조 8298억 2089만</t>
+    <t>2262조 57억 2121만</t>
   </si>
   <si>
     <t>8</t>
@@ -356,7 +356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>1816조 5376억 7272만</t>
+    <t>1975조 9326억 3392만</t>
   </si>
   <si>
     <t>9</t>
@@ -368,7 +368,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1537조 2505억 2514만</t>
+    <t>1650조 4569억 6002만</t>
   </si>
   <si>
     <t>10</t>
@@ -380,7 +380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>1353조 6552억 288만</t>
+    <t>1367조 1278억 9128만</t>
   </si>
   <si>
     <t>11</t>
@@ -428,6 +428,21 @@
     <t>14</t>
   </si>
   <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>934조 1730억 4089만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
@@ -440,21 +455,6 @@
     <t>918조 9796억 5248만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>893조 7791억 2578만</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>863조 8591억 6792만</t>
+    <t>886조 8406억 7534만</t>
   </si>
   <si>
     <t>17</t>
@@ -476,7 +476,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>725조 3107억 9252만</t>
+    <t>823조 2725억 3337만</t>
   </si>
   <si>
     <t>18</t>
@@ -488,114 +488,129 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>703조 4068억 5130만</t>
+    <t>747조 6479억 4857만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>막차탄토끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%89%EC%B0%A8%ED%83%84%ED%86%A0%EB%81%BC</t>
-  </si>
-  <si>
-    <t>642조 4043억 3477만</t>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>619조 9042억 7800만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>576조 9303억 7005만</t>
+    <t>팡대지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
+  </si>
+  <si>
+    <t>440조 2371억 788만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>팡대지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
-  </si>
-  <si>
-    <t>440조 2371억 788만</t>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>418조 2231억 6534만</t>
   </si>
   <si>
     <t>22</t>
   </si>
   <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>396조 506억 4801만</t>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>372조 5745억 3012만</t>
   </si>
   <si>
     <t>23</t>
   </si>
   <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>371조 9523억 1021만</t>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>352조 5575억 4369만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>343조 8712억 3221만</t>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>312조 7168억 9611만</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>301조 7207억 2277만</t>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>298조 2305억 9860만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>260조 9371억 8629만</t>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>206조 9922억 631만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>203조 4743억 4374만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>꾸르꾸르</t>
   </si>
   <si>
@@ -608,7 +623,7 @@
     <t>194조 4027억 9180만</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -617,34 +632,286 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>193조 4998억 774만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>186조 7994억 7947만</t>
+    <t>194조 2882억 2735만</t>
+  </si>
+  <si>
+    <t>이슬러버</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%8A%AC%EB%9F%AC%EB%B2%84</t>
+  </si>
+  <si>
+    <t>1경 552조 7143억 6609만</t>
+  </si>
+  <si>
+    <t>이지카이트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%B9%B4%EC%9D%B4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>3729조 1405억 2328만</t>
+  </si>
+  <si>
+    <t>연평로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3198조 7466억 2254만</t>
+  </si>
+  <si>
+    <t>웅잉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>2634조 5725억 4764만</t>
+  </si>
+  <si>
+    <t>델타시그마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>2421조 5885억 2686만</t>
+  </si>
+  <si>
+    <t>보급중대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%B8%89%EC%A4%91%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2420조 9915억 1983만</t>
+  </si>
+  <si>
+    <t>엉쫀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%89%EC%AB%80</t>
+  </si>
+  <si>
+    <t>1538조 6264억 5877만</t>
+  </si>
+  <si>
+    <t>돼왕다람쥐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%99%95%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
+  </si>
+  <si>
+    <t>1331조 7687억 4986만</t>
+  </si>
+  <si>
+    <t>으눼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
+  </si>
+  <si>
+    <t>1303조 6370억 3012만</t>
+  </si>
+  <si>
+    <t>용이a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
+  </si>
+  <si>
+    <t>1274조 7989억 8529만</t>
+  </si>
+  <si>
+    <t>꼴뱅이a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%B1%85%EC%9D%B4a</t>
+  </si>
+  <si>
+    <t>1220조 88억 2860만</t>
+  </si>
+  <si>
+    <t>벽그림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EA%B7%B8%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>1139조 6050억 2424만</t>
+  </si>
+  <si>
+    <t>간장아비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%84%EC%9E%A5%EC%95%84%EB%B9%84</t>
+  </si>
+  <si>
+    <t>1051조 1655억 8445만</t>
+  </si>
+  <si>
+    <t>요금표</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B8%88%ED%91%9C</t>
+  </si>
+  <si>
+    <t>1023조 6329억 7081만</t>
+  </si>
+  <si>
+    <t>무과키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%ED%82%A4</t>
+  </si>
+  <si>
+    <t>909조 1425억 7163만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=PSG%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>822조 630억 5826만</t>
+  </si>
+  <si>
+    <t>뉴비i</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
+  </si>
+  <si>
+    <t>806조 4518억 8822만</t>
+  </si>
+  <si>
+    <t>에누마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%88%84%EB%A7%88</t>
+  </si>
+  <si>
+    <t>679조 1299억 6562만</t>
+  </si>
+  <si>
+    <t>하랸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
+  </si>
+  <si>
+    <t>669조 1047억 1333만</t>
+  </si>
+  <si>
+    <t>한콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>648조 3728억 7491만</t>
+  </si>
+  <si>
+    <t>뭉게뭉게구름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%EA%B2%8C%EB%AD%89%EA%B2%8C%EA%B5%AC%EB%A6%84</t>
+  </si>
+  <si>
+    <t>599조 6164억 6024만</t>
+  </si>
+  <si>
+    <t>서피비치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%94%BC%EB%B9%84%EC%B9%98</t>
+  </si>
+  <si>
+    <t>568조 5290억 8259만</t>
+  </si>
+  <si>
+    <t>주식하자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
+  </si>
+  <si>
+    <t>507조 5595억 3068만</t>
+  </si>
+  <si>
+    <t>김로케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%9C%EC%BC%80</t>
+  </si>
+  <si>
+    <t>435조 1555억 7407만</t>
+  </si>
+  <si>
+    <t>소심한섀도어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%8B%AC%ED%95%9C%EC%84%80%EB%8F%84%EC%96%B4</t>
+  </si>
+  <si>
+    <t>369조 315억 2947만</t>
+  </si>
+  <si>
+    <t>전포동포동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8F%AC%EB%8F%99%ED%8F%AC%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>270조 5475억 634만</t>
+  </si>
+  <si>
+    <t>경춘선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
+  </si>
+  <si>
+    <t>250조 5658억 4896만</t>
+  </si>
+  <si>
+    <t>01260227</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=01260227</t>
+  </si>
+  <si>
+    <t>225조 5898억 9585만</t>
+  </si>
+  <si>
+    <t>8623</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=8623</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>213조 2429억 7608만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>178조 7593억 2042만</t>
+    <t>수비맨디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%84%EB%A7%A8%EB%94%94</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>163조 1505억 9073만</t>
   </si>
   <si>
     <t>글쟈</t>
@@ -656,6 +923,15 @@
     <t>1경 447조 5129억 7199만</t>
   </si>
   <si>
+    <t>괴챠반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
+  </si>
+  <si>
+    <t>3779조 9660억 4199만</t>
+  </si>
+  <si>
     <t>명동이</t>
   </si>
   <si>
@@ -665,15 +941,6 @@
     <t>3245조 684억 6500만</t>
   </si>
   <si>
-    <t>괴챠반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
-  </si>
-  <si>
-    <t>3204조 8824억 2626만</t>
-  </si>
-  <si>
     <t>유놈</t>
   </si>
   <si>
@@ -692,22 +959,22 @@
     <t>2386조 8932억 4753만</t>
   </si>
   <si>
+    <t>윤꼬밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>2156조 1091억 1210만</t>
+  </si>
+  <si>
     <t>디매트로돈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A7%A4%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
   </si>
   <si>
-    <t>2146조 5713억 9703만</t>
-  </si>
-  <si>
-    <t>윤꼬밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>1830조 1454억 192만</t>
+    <t>2148조 7069억 2080만</t>
   </si>
   <si>
     <t>사오토메란마</t>
@@ -722,7 +989,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%98%81%EA%B5%90</t>
   </si>
   <si>
-    <t>1405조 9567억 7448만</t>
+    <t>1495조 9351억 651만</t>
   </si>
   <si>
     <t>김훈한</t>
@@ -740,7 +1007,7 @@
     <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
   </si>
   <si>
-    <t>1111조 2237억 7409만</t>
+    <t>1142조 2566억 8130만</t>
   </si>
   <si>
     <t>구엉이</t>
@@ -758,7 +1025,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B8%80%EB%A6%AC%EC%89%AC</t>
   </si>
   <si>
-    <t>981조 8306억 6598만</t>
+    <t>1022조 5383억 5173만</t>
+  </si>
+  <si>
+    <t>똥땅이횽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
+  </si>
+  <si>
+    <t>776조 7613억 8822만</t>
   </si>
   <si>
     <t>혁바</t>
@@ -767,16 +1043,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EB%B0%94</t>
   </si>
   <si>
-    <t>773조 9543억 1435만</t>
-  </si>
-  <si>
-    <t>똥땅이횽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
-  </si>
-  <si>
-    <t>727조 1015억 2662만</t>
+    <t>775조 4786억 1213만</t>
   </si>
   <si>
     <t>범지</t>
@@ -785,7 +1052,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
   </si>
   <si>
-    <t>720조 6461억 5197만</t>
+    <t>753조 791억 3550만</t>
   </si>
   <si>
     <t>디메트로돈</t>
@@ -803,7 +1070,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
   </si>
   <si>
-    <t>646조 56억 5787만</t>
+    <t>681조 4944억 9400만</t>
   </si>
   <si>
     <t>뜨머푸</t>
@@ -812,7 +1079,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A8%B8%ED%91%B8</t>
   </si>
   <si>
-    <t>642조 2231억 9071만</t>
+    <t>666조 9853억 6246만</t>
+  </si>
+  <si>
+    <t>오우솃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
+  </si>
+  <si>
+    <t>623조 4349억 2383만</t>
   </si>
   <si>
     <t>혜미니현미니</t>
@@ -821,16 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%AF%B8%EB%8B%88%ED%98%84%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>574조 9893억 7196만</t>
-  </si>
-  <si>
-    <t>오우솃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
-  </si>
-  <si>
-    <t>567조 398억 7136만</t>
+    <t>588조 1465억 3109만</t>
   </si>
   <si>
     <t>옆구리두방</t>
@@ -851,7 +1118,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>425조 2685억 1641만</t>
+    <t>477조 4769억 4575만</t>
   </si>
   <si>
     <t>양쿼카</t>
@@ -860,7 +1127,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%BF%BC%EC%B9%B4</t>
   </si>
   <si>
-    <t>385조 6741억 4044만</t>
+    <t>390조 3037억 2972만</t>
+  </si>
+  <si>
+    <t>정섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>384조 5653억 9771만</t>
   </si>
   <si>
     <t>니누고</t>
@@ -872,15 +1148,6 @@
     <t>377조 4506억 6398만</t>
   </si>
   <si>
-    <t>정섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>363조 2721억 3766만</t>
-  </si>
-  <si>
     <t>연속기</t>
   </si>
   <si>
@@ -890,13 +1157,22 @@
     <t>330조 108억 9811만</t>
   </si>
   <si>
+    <t>여덟시</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>313조 7265억 4684만</t>
+  </si>
+  <si>
     <t>돼짱</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
   </si>
   <si>
-    <t>306조 3982억 4727만</t>
+    <t>307조 5404억 2549만</t>
   </si>
   <si>
     <t>젤로젤리</t>
@@ -908,304 +1184,19 @@
     <t>304조 3439억 3321만</t>
   </si>
   <si>
-    <t>여덟시</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>282조 2270억 1691만</t>
-  </si>
-  <si>
-    <t>이슬러버</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%8A%AC%EB%9F%AC%EB%B2%84</t>
-  </si>
-  <si>
-    <t>9900조 3364억 5634만</t>
-  </si>
-  <si>
-    <t>이지카이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%B9%B4%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>3194조 7837억 5105만</t>
-  </si>
-  <si>
-    <t>연평로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>2997조 5305억 8714만</t>
-  </si>
-  <si>
-    <t>웅잉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>2588조 5656억 334만</t>
-  </si>
-  <si>
-    <t>보급중대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%B8%89%EC%A4%91%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2387조 4334억 2228만</t>
-  </si>
-  <si>
-    <t>델타시그마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>2305조 7344억 9898만</t>
-  </si>
-  <si>
-    <t>엉쫀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%89%EC%AB%80</t>
-  </si>
-  <si>
-    <t>1538조 6264억 5877만</t>
-  </si>
-  <si>
-    <t>으눼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
-  </si>
-  <si>
-    <t>1277조 2019억 9720만</t>
-  </si>
-  <si>
-    <t>돼왕다람쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%99%95%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
-  </si>
-  <si>
-    <t>1271조 2353억 7233만</t>
-  </si>
-  <si>
-    <t>용이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1218조 9701억 7071만</t>
-  </si>
-  <si>
-    <t>꼴뱅이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%B1%85%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1173조 8793억 7383만</t>
-  </si>
-  <si>
-    <t>벽그림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EA%B7%B8%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>1139조 6050억 2424만</t>
-  </si>
-  <si>
-    <t>간장아비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%84%EC%9E%A5%EC%95%84%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1051조 1655억 8445만</t>
-  </si>
-  <si>
-    <t>요금표</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B8%88%ED%91%9C</t>
-  </si>
-  <si>
-    <t>950조 2372억 5448만</t>
-  </si>
-  <si>
-    <t>무과키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%ED%82%A4</t>
-  </si>
-  <si>
-    <t>841조 8633억 5226만</t>
-  </si>
-  <si>
-    <t>뉴비i</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
-  </si>
-  <si>
-    <t>759조 4295억 7205만</t>
-  </si>
-  <si>
-    <t>하랸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
-  </si>
-  <si>
-    <t>656조 3944억 7494만</t>
-  </si>
-  <si>
-    <t>에누마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%88%84%EB%A7%88</t>
-  </si>
-  <si>
-    <t>652조 126억 9685만</t>
-  </si>
-  <si>
-    <t>한콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>648조 3728억 7491만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=PSG%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>642조 5254억 2415만</t>
-  </si>
-  <si>
-    <t>뭉게뭉게구름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%EA%B2%8C%EB%AD%89%EA%B2%8C%EA%B5%AC%EB%A6%84</t>
-  </si>
-  <si>
-    <t>581조 8316억 4015만</t>
-  </si>
-  <si>
-    <t>서피비치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%94%BC%EB%B9%84%EC%B9%98</t>
-  </si>
-  <si>
-    <t>545조 8117억 859만</t>
-  </si>
-  <si>
-    <t>주식하자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
-  </si>
-  <si>
-    <t>481조 5286억 3200만</t>
-  </si>
-  <si>
-    <t>김로케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%9C%EC%BC%80</t>
-  </si>
-  <si>
-    <t>434조 3053억 2526만</t>
-  </si>
-  <si>
-    <t>소심한섀도어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%8B%AC%ED%95%9C%EC%84%80%EB%8F%84%EC%96%B4</t>
-  </si>
-  <si>
-    <t>368조 5948억 3216만</t>
-  </si>
-  <si>
-    <t>전포동포동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8F%AC%EB%8F%99%ED%8F%AC%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>270조 5475억 634만</t>
-  </si>
-  <si>
-    <t>경춘선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
-  </si>
-  <si>
-    <t>225조 6213억 6343만</t>
-  </si>
-  <si>
-    <t>01260227</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=01260227</t>
-  </si>
-  <si>
-    <t>225조 5898억 9585만</t>
-  </si>
-  <si>
-    <t>8623</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=8623</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>200조 1543억 7550만</t>
-  </si>
-  <si>
-    <t>수비맨디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%84%EB%A7%A8%EB%94%94</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>149조 8169억 979만</t>
+    <t>우니아파요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>5708조 2885억 4200만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>3850조 9115억 6840만</t>
-  </si>
-  <si>
-    <t>우니아파요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>3578조 6164억 9960만</t>
+    <t>4080조 5012억 4862만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -1214,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>2769조 1351억 2419만</t>
+    <t>2938조 3489억 2905만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -1232,7 +1223,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>1811조 1534억 6055만</t>
+    <t>1952조 1184억 721만</t>
+  </si>
+  <si>
+    <t>종꿀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
+  </si>
+  <si>
+    <t>1871조 7826억 9063만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -1250,16 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
   </si>
   <si>
-    <t>1558조 7056억 5039만</t>
-  </si>
-  <si>
-    <t>종꿀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
-  </si>
-  <si>
-    <t>1513조 9876억 9384만</t>
+    <t>1609조 611억 3837만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1268,7 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
   </si>
   <si>
-    <t>1433조 2212억 1888만</t>
+    <t>1575조 8408억 837만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1277,7 +1268,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>1425조 8545억 3978만</t>
+    <t>1428조 1274억 3869만</t>
+  </si>
+  <si>
+    <t>세월이야속해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1220조 3790억 5343만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1286,16 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>1133조 8432억 4587만</t>
-  </si>
-  <si>
-    <t>세월이야속해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1112조 2357억 5917만</t>
+    <t>1153조 3828억 7253만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1304,7 +1295,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1063조 3039억 629만</t>
+    <t>1087조 1012억 5122만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1313,7 +1304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>998조 7244억 213만</t>
+    <t>1007조 6958억 4699만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1331,7 +1322,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>830조 9149억 3633만</t>
+    <t>925조 4898억 5127만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1340,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>817조 5104억 6557만</t>
+    <t>848조 2555억 9974만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1349,7 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>780조 1642억 9657만</t>
+    <t>793조 9488억 1111만</t>
   </si>
   <si>
     <t>박금쪽</t>
@@ -1358,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
   </si>
   <si>
-    <t>664조 8222억 7460만</t>
+    <t>738조 5839억 1620만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1367,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>641조 4638억 3097만</t>
+    <t>713조 6537억 5559만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1376,7 +1367,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>641조 3051억 2877만</t>
+    <t>699조 842억 792만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1385,7 +1376,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>640조 5014억 9379만</t>
+    <t>640조 6003억 3635만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1394,7 +1385,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
   </si>
   <si>
-    <t>565조 9188억 2581만</t>
+    <t>601조 4919억 9329만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1403,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>541조 1722억 1710만</t>
+    <t>568조 9858억 9869만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1412,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
   </si>
   <si>
-    <t>536조 1307억 2693만</t>
+    <t>544조 7027억 9531만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1421,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>490조 7529억 916만</t>
+    <t>525조 6479억 4753만</t>
   </si>
   <si>
     <t>계니규니</t>
@@ -1430,7 +1421,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>448조 3203억 7107만</t>
+    <t>468조 5687억 6869만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1439,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>272조 8228억 5047만</t>
+    <t>283조 5698억 2300만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1457,7 +1448,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>208조 2112억 3656만</t>
+    <t>225조 9114억 655만</t>
   </si>
   <si>
     <t>주식회사서영</t>
@@ -1466,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%9A%8C%EC%82%AC%EC%84%9C%EC%98%81</t>
   </si>
   <si>
-    <t>3경 5330조 9057억 933만</t>
+    <t>4경 2039조 4141억 5612만</t>
   </si>
   <si>
     <t>블루펀치</t>
@@ -1484,13 +1475,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EA%B7%B8%EB%9F%AC%EC%A7%84%EB%AA%A8%EC%9E%90</t>
   </si>
   <si>
-    <t>2303조 8444억 3203만</t>
+    <t>2409조 1879억 6004만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%90%EB%8A%90</t>
   </si>
   <si>
-    <t>1967조 6666억 7859만</t>
+    <t>1972조 3426억 1900만</t>
   </si>
   <si>
     <t>부산철거</t>
@@ -1499,7 +1490,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EC%82%B0%EC%B2%A0%EA%B1%B0</t>
   </si>
   <si>
-    <t>577조 7457억 312만</t>
+    <t>610조 561억 3804만</t>
   </si>
   <si>
     <t>베네치얀</t>
@@ -1508,7 +1499,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%84%A4%EC%B9%98%EC%96%80</t>
   </si>
   <si>
-    <t>533조 2970억 3238만</t>
+    <t>582조 7749억 7591만</t>
   </si>
   <si>
     <t>갸렌</t>
@@ -1517,7 +1508,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%B8%EB%A0%8C</t>
   </si>
   <si>
-    <t>347조 4015억 7971만</t>
+    <t>369조 3823억 41만</t>
   </si>
   <si>
     <t>태양o</t>
@@ -1526,7 +1517,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%96%91o</t>
   </si>
   <si>
-    <t>324조 7719억 4290만</t>
+    <t>358조 2882억 6663만</t>
+  </si>
+  <si>
+    <t>효설빈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%84%A4%EB%B9%88</t>
+  </si>
+  <si>
+    <t>283조 4488억 434만</t>
   </si>
   <si>
     <t>꺆뜎</t>
@@ -1535,16 +1535,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%86%EB%9C%8E</t>
   </si>
   <si>
-    <t>256조 9970억 813만</t>
-  </si>
-  <si>
-    <t>효설빈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%84%A4%EB%B9%88</t>
-  </si>
-  <si>
-    <t>254조 6373억 9561만</t>
+    <t>277조 150억 2527만</t>
+  </si>
+  <si>
+    <t>봄여름한겨울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%97%AC%EB%A6%84%ED%95%9C%EA%B2%A8%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>263조 3974억 2990만</t>
   </si>
   <si>
     <t>모우모우우</t>
@@ -1556,13 +1556,13 @@
     <t>249조 5633억 6327만</t>
   </si>
   <si>
-    <t>봄여름한겨울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%97%AC%EB%A6%84%ED%95%9C%EA%B2%A8%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>248조 4947억 8591만</t>
+    <t>곰세마리당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EC%84%B8%EB%A7%88%EB%A6%AC%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>246조 6743억 4568만</t>
   </si>
   <si>
     <t>1지옥참마도1</t>
@@ -1574,22 +1574,13 @@
     <t>240조 7601억 443만</t>
   </si>
   <si>
-    <t>곰세마리당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EC%84%B8%EB%A7%88%EB%A6%AC%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>219조 5525억 5510만</t>
-  </si>
-  <si>
     <t>하숩</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%A9</t>
   </si>
   <si>
-    <t>213조 64억 4384만</t>
+    <t>229조 7785억 210만</t>
   </si>
   <si>
     <t>토느</t>
@@ -1598,7 +1589,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8A%90</t>
   </si>
   <si>
-    <t>193조 7969억 7930만</t>
+    <t>194조 9697억 5521만</t>
   </si>
   <si>
     <t>행복하길바래</t>
@@ -1607,7 +1598,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%89%EB%B3%B5%ED%95%98%EA%B8%B8%EB%B0%94%EB%9E%98</t>
   </si>
   <si>
-    <t>156조 9362억 6516만</t>
+    <t>167조 140억 1348만</t>
+  </si>
+  <si>
+    <t>미허</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%ED%97%88</t>
+  </si>
+  <si>
+    <t>158조 8375억 3882만</t>
   </si>
   <si>
     <t>당근이니</t>
@@ -1616,16 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B7%BC%EC%9D%B4%EB%8B%88</t>
   </si>
   <si>
-    <t>148조 5665억 550만</t>
-  </si>
-  <si>
-    <t>미허</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%ED%97%88</t>
-  </si>
-  <si>
-    <t>148조 4819억 2363만</t>
+    <t>158조 7854억 5352만</t>
   </si>
   <si>
     <t>동그리미</t>
@@ -1634,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EA%B7%B8%EB%A6%AC%EB%AF%B8</t>
   </si>
   <si>
-    <t>143조 2694억 7698만</t>
+    <t>153조 4101억 5656만</t>
   </si>
   <si>
     <t>허상하</t>
@@ -1643,7 +1634,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%83%81%ED%95%98</t>
   </si>
   <si>
-    <t>122조 9589억 1010만</t>
+    <t>145조 3356억 22만</t>
+  </si>
+  <si>
+    <t>최경무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B2%BD%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>87조 5400억 7895만</t>
   </si>
   <si>
     <t>명지사나이</t>
@@ -1652,16 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EC%82%AC%EB%82%98%EC%9D%B4</t>
   </si>
   <si>
-    <t>84조 2901억 7452만</t>
-  </si>
-  <si>
-    <t>최경무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B2%BD%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>78조 522억 1252만</t>
+    <t>87조 4900억 9590만</t>
   </si>
   <si>
     <t>앙설</t>
@@ -1673,7 +1664,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>63조 8457억 5091만</t>
+    <t>79조 6202억 1077만</t>
   </si>
   <si>
     <t>진떡</t>
@@ -1682,7 +1673,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EB%96%A1</t>
   </si>
   <si>
-    <t>61조 2140억 4733만</t>
+    <t>65조 3925억 5974만</t>
   </si>
   <si>
     <t>해적왕정우짱</t>
@@ -1709,7 +1700,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%96%910</t>
   </si>
   <si>
-    <t>45조 9846억 5148만</t>
+    <t>48조 7529억 2500만</t>
   </si>
   <si>
     <t>마동턱</t>
@@ -1718,7 +1709,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%99%ED%84%B1</t>
   </si>
   <si>
-    <t>31조 9321억 6342만</t>
+    <t>34조 3164억 8910만</t>
   </si>
   <si>
     <t>웅나공듀</t>
@@ -1730,7 +1721,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>30조 2992억 4964만</t>
+    <t>34조 1260억 7845만</t>
   </si>
 </sst>
 </file>
@@ -2370,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2498,13 +2489,13 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2515,28 +2506,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2547,22 +2538,22 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>95</v>
@@ -2658,7 +2649,7 @@
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>79</v>
@@ -2690,7 +2681,7 @@
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>79</v>
@@ -2838,16 +2829,16 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>135</v>
@@ -2870,16 +2861,16 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>140</v>
@@ -2946,7 +2937,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>79</v>
@@ -3010,7 +3001,7 @@
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
@@ -3077,10 +3068,10 @@
         <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3091,25 +3082,25 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>170</v>
@@ -3138,10 +3129,10 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>174</v>
@@ -3173,7 +3164,7 @@
         <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>178</v>
@@ -3202,13 +3193,13 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3219,25 +3210,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>187</v>
@@ -3269,7 +3260,7 @@
         <v>191</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>192</v>
@@ -3298,13 +3289,13 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3315,25 +3306,25 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>200</v>
+        <v>72</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>201</v>
@@ -3342,40 +3333,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3406,7 +3365,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3419,7 +3377,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -3467,25 +3425,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>135</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -3499,25 +3457,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -3531,25 +3489,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -3560,28 +3518,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -3592,28 +3550,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -3627,13 +3585,13 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
@@ -3642,10 +3600,10 @@
         <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -3659,13 +3617,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -3677,7 +3635,7 @@
         <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -3691,25 +3649,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -3723,25 +3681,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>226</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -3755,25 +3713,25 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -3787,25 +3745,25 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -3819,25 +3777,25 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -3851,13 +3809,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -3866,10 +3824,10 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -3883,25 +3841,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -3915,25 +3873,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -3947,25 +3905,25 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>250</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>250</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -3979,13 +3937,13 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -3994,10 +3952,10 @@
         <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4011,25 +3969,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>191</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4043,25 +4001,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4075,13 +4033,13 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -4093,7 +4051,7 @@
         <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4107,25 +4065,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>200</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4136,28 +4094,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4171,25 +4129,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4203,25 +4161,25 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4235,25 +4193,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4264,28 +4222,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4299,25 +4257,25 @@
         <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4331,25 +4289,25 @@
         <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4360,28 +4318,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>126</v>
+        <v>287</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -4392,28 +4350,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -4464,11 +4422,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4512,25 +4470,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -4544,25 +4502,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>300</v>
-      </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4576,25 +4534,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4605,28 +4563,28 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4637,28 +4595,28 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4672,25 +4630,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4704,13 +4662,13 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -4719,10 +4677,10 @@
         <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4736,25 +4694,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>318</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4768,25 +4726,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4800,25 +4758,25 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4832,25 +4790,25 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4864,25 +4822,25 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4896,13 +4854,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -4911,10 +4869,10 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4928,25 +4886,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4960,25 +4918,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4992,25 +4950,25 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -5024,25 +4982,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>346</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -5056,25 +5014,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>89</v>
+        <v>196</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -5088,25 +5046,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -5120,25 +5078,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -5152,25 +5110,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -5181,28 +5139,28 @@
         <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -5216,22 +5174,22 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="H24" s="2" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>363</v>
@@ -5260,10 +5218,10 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>366</v>
@@ -5292,7 +5250,7 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>126</v>
@@ -5309,7 +5267,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>370</v>
@@ -5324,10 +5282,10 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>372</v>
@@ -5356,10 +5314,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>191</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>375</v>
@@ -5388,10 +5346,10 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>378</v>
@@ -5405,7 +5363,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>379</v>
@@ -5420,13 +5378,13 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>381</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>382</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -5437,28 +5395,28 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -5557,25 +5515,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>385</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>191</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -5589,25 +5547,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>390</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>71</v>
+        <v>139</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -5621,25 +5579,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -5650,28 +5608,28 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -5682,28 +5640,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -5717,25 +5675,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -5749,25 +5707,25 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -5781,25 +5739,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -5813,13 +5771,13 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -5828,10 +5786,10 @@
         <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -5845,25 +5803,25 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -5877,25 +5835,25 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>273</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -5909,25 +5867,25 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>362</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -5941,13 +5899,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -5959,7 +5917,7 @@
         <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -5973,25 +5931,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6005,25 +5963,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6037,25 +5995,25 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6069,25 +6027,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -6101,13 +6059,13 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
@@ -6119,7 +6077,7 @@
         <v>79</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6133,25 +6091,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6165,13 +6123,13 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
@@ -6183,7 +6141,7 @@
         <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6197,13 +6155,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -6215,7 +6173,7 @@
         <v>104</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6226,28 +6184,28 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>104</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6261,25 +6219,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6293,25 +6251,25 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6325,13 +6283,13 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
@@ -6340,10 +6298,10 @@
         <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6354,16 +6312,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
@@ -6375,7 +6333,7 @@
         <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6389,25 +6347,25 @@
         <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6421,13 +6379,13 @@
         <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -6436,10 +6394,10 @@
         <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -6450,28 +6408,28 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -6482,16 +6440,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>71</v>
@@ -6503,7 +6461,7 @@
         <v>126</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -6558,7 +6516,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6602,25 +6560,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6634,25 +6592,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6666,25 +6624,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6695,7 +6653,7 @@
         <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>59</v>
@@ -6704,19 +6662,19 @@
         <v>59</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6727,16 +6685,16 @@
         <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
@@ -6745,10 +6703,10 @@
         <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6762,25 +6720,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6794,25 +6752,25 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6826,13 +6784,13 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -6841,10 +6799,10 @@
         <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6858,13 +6816,13 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
@@ -6873,10 +6831,10 @@
         <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>186</v>
+        <v>293</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6890,13 +6848,13 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -6905,10 +6863,10 @@
         <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>386</v>
+        <v>182</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6922,25 +6880,25 @@
         <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>273</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6954,25 +6912,25 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>362</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6986,13 +6944,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
@@ -7001,10 +6959,10 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -7018,13 +6976,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -7033,10 +6991,10 @@
         <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -7050,13 +7008,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -7065,10 +7023,10 @@
         <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -7082,25 +7040,25 @@
         <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -7114,13 +7072,13 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
@@ -7129,10 +7087,10 @@
         <v>121</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>381</v>
+        <v>182</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7146,25 +7104,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>121</v>
+        <v>362</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>386</v>
+        <v>293</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7178,25 +7136,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>273</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>386</v>
+        <v>293</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7210,25 +7168,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7242,13 +7200,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
@@ -7257,10 +7215,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7271,28 +7229,28 @@
         <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7306,25 +7264,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>381</v>
+        <v>287</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7338,25 +7296,25 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7370,25 +7328,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7399,28 +7357,28 @@
         <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>273</v>
+        <v>362</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>386</v>
+        <v>293</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7434,25 +7392,25 @@
         <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7466,13 +7424,13 @@
         <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>71</v>
@@ -7481,10 +7439,10 @@
         <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -7495,28 +7453,28 @@
         <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -7527,28 +7485,28 @@
         <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>566</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -10,24 +10,24 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="86서버" sheetId="3" r:id="rId3"/>
-    <sheet name="인형나라" sheetId="4" r:id="rId4"/>
-    <sheet name="눈별" sheetId="5" r:id="rId5"/>
+    <sheet name="눈별" sheetId="4" r:id="rId4"/>
+    <sheet name="인형나라" sheetId="5" r:id="rId5"/>
     <sheet name="SSIM" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'86서버'!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">SSIM!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">눈별!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">인형나라!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">인형나라!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="564">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>422</t>
+    <t>404</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>4경 2203조 6052억 4725만</t>
+    <t>4경 7274조 1168억 2294만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.13</t>
+    <t>2026.09.16</t>
   </si>
   <si>
     <t>86서버</t>
@@ -113,7 +113,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>430</t>
+    <t>443</t>
   </si>
   <si>
     <t>5위</t>
@@ -134,6 +134,30 @@
     <t>2026.09.12</t>
   </si>
   <si>
+    <t>눈별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>9위</t>
+  </si>
+  <si>
+    <t>3경 4802조 1167억 4071만</t>
+  </si>
+  <si>
+    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
+  </si>
+  <si>
+    <t>심신삐약자</t>
+  </si>
+  <si>
     <t>인형나라</t>
   </si>
   <si>
@@ -143,7 +167,7 @@
     <t>Scania 25</t>
   </si>
   <si>
-    <t>424</t>
+    <t>438</t>
   </si>
   <si>
     <t>8위</t>
@@ -158,30 +182,6 @@
     <t>최영교</t>
   </si>
   <si>
-    <t>눈별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>466</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>3경 4802조 1167억 4071만</t>
-  </si>
-  <si>
-    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
-  </si>
-  <si>
-    <t>심신삐약자</t>
-  </si>
-  <si>
     <t>SSIM</t>
   </si>
   <si>
@@ -191,7 +191,7 @@
     <t>Scania 60</t>
   </si>
   <si>
-    <t>390</t>
+    <t>325</t>
   </si>
   <si>
     <t>2위</t>
@@ -200,1288 +200,1300 @@
     <t>Lv.8</t>
   </si>
   <si>
-    <t>4경 8229조 4306억 6791만</t>
+    <t>7경 3068조 2890억 6047만</t>
   </si>
   <si>
     <t>길드 콘텐츠 필수 [ 50조 이상 가입 및 대기 문의 : 김또느 ]</t>
   </si>
   <si>
+    <t>토느</t>
+  </si>
+  <si>
+    <t>member_rank_in_guild</t>
+  </si>
+  <si>
+    <t>nickname</t>
+  </si>
+  <si>
+    <t>character_key</t>
+  </si>
+  <si>
+    <t>character_url</t>
+  </si>
+  <si>
+    <t>is_master</t>
+  </si>
+  <si>
+    <t>job_name</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>combat_power</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>8515조 3583억 4706만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>5522조 7382억 506만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>두향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3815조 5213억 6600만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>3301조 3852억 4361만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3217조 3423억 2146만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>3010조 3664억 6363만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>2720조 2809억 9602만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2062조 3576억 7889만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>1718조 1326억 9702만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>1508조 7420억 3377만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>1480조 3201억 3941만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1178조 4809억 5968만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>972조 2153억 1957만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>968조 1677억 2361만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>933조 4008억 6223만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>918조 9796억 5248만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>834조 9225억 8951만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>747조 6479억 4857만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>712조 5098억 2176만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>팡대지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
+  </si>
+  <si>
+    <t>498조 2303억 4062만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>419조 7074억 9119만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>385조 9337억 8532만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>355조 5354억 60만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>328조 1595억 1568만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>325조 8411억 2940만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>216조 9694억 4877만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>206조 9922억 631만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>203조 4743억 4374만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>194조 4027억 9180만</t>
+  </si>
+  <si>
+    <t>이슬러버</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%8A%AC%EB%9F%AC%EB%B2%84</t>
+  </si>
+  <si>
+    <t>1경 763조 7057억 4323만</t>
+  </si>
+  <si>
+    <t>이지카이트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%B9%B4%EC%9D%B4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>3923조 6107억 7357만</t>
+  </si>
+  <si>
+    <t>연평로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3431조 9270억 4534만</t>
+  </si>
+  <si>
+    <t>웅잉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>2749조 440억 826만</t>
+  </si>
+  <si>
+    <t>델타시그마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
+  </si>
+  <si>
+    <t>2462조 8942억 8430만</t>
+  </si>
+  <si>
+    <t>보급중대장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%B8%89%EC%A4%91%EB%8C%80%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2428조 5616억 1111만</t>
+  </si>
+  <si>
+    <t>엉쫀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%89%EC%AB%80</t>
+  </si>
+  <si>
+    <t>1538조 6264억 5877만</t>
+  </si>
+  <si>
+    <t>벽그림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EA%B7%B8%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>1425조 7402억 2493만</t>
+  </si>
+  <si>
+    <t>돼왕다람쥐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%99%95%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
+  </si>
+  <si>
+    <t>1418조 7554억 2776만</t>
+  </si>
+  <si>
+    <t>용이a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
+  </si>
+  <si>
+    <t>1368조 2073억 1181만</t>
+  </si>
+  <si>
+    <t>으눼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
+  </si>
+  <si>
+    <t>1303조 6370억 3012만</t>
+  </si>
+  <si>
+    <t>꼴뱅이a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%B1%85%EC%9D%B4a</t>
+  </si>
+  <si>
+    <t>1224조 7550억 489만</t>
+  </si>
+  <si>
+    <t>간장아비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%84%EC%9E%A5%EC%95%84%EB%B9%84</t>
+  </si>
+  <si>
+    <t>1105조 2813억 7771만</t>
+  </si>
+  <si>
+    <t>요금표</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B8%88%ED%91%9C</t>
+  </si>
+  <si>
+    <t>1065조 6741억 1673만</t>
+  </si>
+  <si>
+    <t>무과키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%ED%82%A4</t>
+  </si>
+  <si>
+    <t>952조 2692억 5801만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=PSG%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>861조 9309억 5785만</t>
+  </si>
+  <si>
+    <t>뉴비i</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
+  </si>
+  <si>
+    <t>836조 8008억 5889만</t>
+  </si>
+  <si>
+    <t>에누마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%88%84%EB%A7%88</t>
+  </si>
+  <si>
+    <t>679조 1299억 6562만</t>
+  </si>
+  <si>
+    <t>하랸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
+  </si>
+  <si>
+    <t>669조 9044억 4671만</t>
+  </si>
+  <si>
+    <t>한콩순</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
+  </si>
+  <si>
+    <t>648조 3728억 7491만</t>
+  </si>
+  <si>
+    <t>뭉게뭉게구름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%EA%B2%8C%EB%AD%89%EA%B2%8C%EA%B5%AC%EB%A6%84</t>
+  </si>
+  <si>
+    <t>623조 6091억 8857만</t>
+  </si>
+  <si>
+    <t>서피비치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%94%BC%EB%B9%84%EC%B9%98</t>
+  </si>
+  <si>
+    <t>619조 1203억 114만</t>
+  </si>
+  <si>
+    <t>주식하자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
+  </si>
+  <si>
+    <t>507조 5595억 3068만</t>
+  </si>
+  <si>
+    <t>김로케</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%9C%EC%BC%80</t>
+  </si>
+  <si>
+    <t>472조 7958억 396만</t>
+  </si>
+  <si>
+    <t>소심한섀도어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%8B%AC%ED%95%9C%EC%84%80%EB%8F%84%EC%96%B4</t>
+  </si>
+  <si>
+    <t>439조 8683억 7255만</t>
+  </si>
+  <si>
+    <t>경춘선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
+  </si>
+  <si>
+    <t>274조 3647억 3191만</t>
+  </si>
+  <si>
+    <t>전포동포동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8F%AC%EB%8F%99%ED%8F%AC%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>270조 5475억 634만</t>
+  </si>
+  <si>
+    <t>01260227</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=01260227</t>
+  </si>
+  <si>
+    <t>225조 5898억 9585만</t>
+  </si>
+  <si>
+    <t>8623</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=8623</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>213조 2429억 7608만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>수비맨디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%84%EB%A7%A8%EB%94%94</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>185조 5885억 6989만</t>
+  </si>
+  <si>
+    <t>우니아파요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>5708조 2885억 4200만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
+  </si>
+  <si>
+    <t>4401조 6419억 9884만</t>
+  </si>
+  <si>
+    <t>도하리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2938조 3489억 2905만</t>
+  </si>
+  <si>
+    <t>죽창당일개통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
+  </si>
+  <si>
+    <t>2365조 5050억 9154만</t>
+  </si>
+  <si>
+    <t>유수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>2074조 9869억 3212만</t>
+  </si>
+  <si>
+    <t>종꿀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
+  </si>
+  <si>
+    <t>1939조 2480억 9380만</t>
+  </si>
+  <si>
+    <t>해달잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
+  </si>
+  <si>
+    <t>1716조 4568억 5714만</t>
+  </si>
+  <si>
+    <t>이용하다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1666조 7737억 1182만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1609조 611억 3837만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>1428조 1274억 3869만</t>
+  </si>
+  <si>
+    <t>세월이야속해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1250조 1932억 1235만</t>
+  </si>
+  <si>
+    <t>포빅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1170조 8638억 6605만</t>
+  </si>
+  <si>
+    <t>덩개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>1158조 2062억 32만</t>
+  </si>
+  <si>
+    <t>여자둘남자둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
+  </si>
+  <si>
+    <t>1089조 3517억 5160만</t>
+  </si>
+  <si>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1007조 6958억 4699만</t>
+  </si>
+  <si>
+    <t>MangCI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
+  </si>
+  <si>
+    <t>925조 4898억 5127만</t>
+  </si>
+  <si>
+    <t>예타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
+  </si>
+  <si>
+    <t>849조 4153억 3018만</t>
+  </si>
+  <si>
+    <t>모르페우스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>795조 7079억 8803만</t>
+  </si>
+  <si>
+    <t>박금쪽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
+  </si>
+  <si>
+    <t>778조 1005억 2919만</t>
+  </si>
+  <si>
+    <t>파이리양말</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
+  </si>
+  <si>
+    <t>733조 7738억 4806만</t>
+  </si>
+  <si>
+    <t>티에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>713조 6537억 5559만</t>
+  </si>
+  <si>
+    <t>지존짱창남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
+  </si>
+  <si>
+    <t>674조 8831억 5472만</t>
+  </si>
+  <si>
+    <t>작업치료사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
+  </si>
+  <si>
+    <t>605조 2191억 6874만</t>
+  </si>
+  <si>
+    <t>히어로호걸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
+  </si>
+  <si>
+    <t>599조 5583억 4223만</t>
+  </si>
+  <si>
+    <t>성률</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
+  </si>
+  <si>
+    <t>583조 592억 9081만</t>
+  </si>
+  <si>
+    <t>감화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
+  </si>
+  <si>
+    <t>529조 2335억 1065만</t>
+  </si>
+  <si>
+    <t>계니규니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>495조 7843억 4910만</t>
+  </si>
+  <si>
+    <t>하비엔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
+  </si>
+  <si>
+    <t>291조 5289억 8208만</t>
+  </si>
+  <si>
+    <t>채구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>266조 6983억 9920만</t>
+  </si>
+  <si>
+    <t>신탄보우짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>231조 8325억 2801만</t>
+  </si>
+  <si>
+    <t>글쟈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%80%EC%9F%88</t>
+  </si>
+  <si>
+    <t>1경 447조 5129억 7199만</t>
+  </si>
+  <si>
+    <t>괴챠반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
+  </si>
+  <si>
+    <t>3779조 9660억 4199만</t>
+  </si>
+  <si>
+    <t>명동이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EB%8F%99%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3245조 684억 6500만</t>
+  </si>
+  <si>
+    <t>유놈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%86%88</t>
+  </si>
+  <si>
+    <t>2691조 9569억 2682만</t>
+  </si>
+  <si>
+    <t>윤꼬밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>2390조 9787억 2469만</t>
+  </si>
+  <si>
+    <t>꿀꿀맛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EB%A7%9B</t>
+  </si>
+  <si>
+    <t>2386조 8932억 4753만</t>
+  </si>
+  <si>
+    <t>디매트로돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A7%A4%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
+  </si>
+  <si>
+    <t>2148조 7069억 2080만</t>
+  </si>
+  <si>
+    <t>사오토메란마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%98%A4%ED%86%A0%EB%A9%94%EB%9E%80%EB%A7%88</t>
+  </si>
+  <si>
+    <t>1768조 8881억 9922만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%98%81%EA%B5%90</t>
+  </si>
+  <si>
+    <t>1495조 9351억 651만</t>
+  </si>
+  <si>
+    <t>김훈한</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%9B%88%ED%95%9C</t>
+  </si>
+  <si>
+    <t>1277조 5140억 7129만</t>
+  </si>
+  <si>
+    <t>Pakachu9999</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
+  </si>
+  <si>
+    <t>1142조 3030억 7681만</t>
+  </si>
+  <si>
+    <t>구엉이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EC%97%89%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1052조 5398억 161만</t>
+  </si>
+  <si>
+    <t>잉글리쉬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B8%80%EB%A6%AC%EC%89%AC</t>
+  </si>
+  <si>
+    <t>1033조 9964억 3444만</t>
+  </si>
+  <si>
+    <t>뜨머푸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A8%B8%ED%91%B8</t>
+  </si>
+  <si>
+    <t>863조 3471억 8490만</t>
+  </si>
+  <si>
+    <t>혁바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EB%B0%94</t>
+  </si>
+  <si>
+    <t>825조 4211억 3052만</t>
+  </si>
+  <si>
+    <t>똥땅이횽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
+  </si>
+  <si>
+    <t>802조 3218억 1161만</t>
+  </si>
+  <si>
+    <t>범지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
+  </si>
+  <si>
+    <t>778조 7201억 5721만</t>
+  </si>
+  <si>
+    <t>디메트로돈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A9%94%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
+  </si>
+  <si>
+    <t>714조 7621억 4089만</t>
+  </si>
+  <si>
+    <t>솖이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>681조 4944억 9400만</t>
+  </si>
+  <si>
+    <t>오우솃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
+  </si>
+  <si>
+    <t>666조 2832억 2541만</t>
+  </si>
+  <si>
+    <t>혜미니현미니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%AF%B8%EB%8B%88%ED%98%84%EB%AF%B8%EB%8B%88</t>
+  </si>
+  <si>
+    <t>597조 3899억 2395만</t>
+  </si>
+  <si>
+    <t>옆구리두방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%86%EA%B5%AC%EB%A6%AC%EB%91%90%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>531조 4391억 9363만</t>
+  </si>
+  <si>
+    <t>쀏뀱쪍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%80%8F%EB%80%B1%EC%AA%8D</t>
+  </si>
+  <si>
+    <t>477조 4769억 4575만</t>
+  </si>
+  <si>
+    <t>양쿼카</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%BF%BC%EC%B9%B4</t>
+  </si>
+  <si>
+    <t>390조 3037억 2972만</t>
+  </si>
+  <si>
+    <t>정섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>384조 5653억 9771만</t>
+  </si>
+  <si>
+    <t>니누고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%88%84%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>377조 4506억 6398만</t>
+  </si>
+  <si>
+    <t>연속기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%86%8D%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>330조 108억 9811만</t>
+  </si>
+  <si>
+    <t>젤로젤리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%A4%EB%A1%9C%EC%A0%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>322조 9565억 646만</t>
+  </si>
+  <si>
+    <t>돼짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>322조 8292억 813만</t>
+  </si>
+  <si>
+    <t>여덟시</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>318조 4244억 6173만</t>
+  </si>
+  <si>
+    <t>주식회사서영</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%9A%8C%EC%82%AC%EC%84%9C%EC%98%81</t>
+  </si>
+  <si>
+    <t>5경 8603조 2478억 2951만</t>
+  </si>
+  <si>
+    <t>블루펀치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%94%EB%A3%A8%ED%8E%80%EC%B9%98</t>
+  </si>
+  <si>
+    <t>4135조 8792억 9596만</t>
+  </si>
+  <si>
+    <t>찌그러진모자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EA%B7%B8%EB%9F%AC%EC%A7%84%EB%AA%A8%EC%9E%90</t>
+  </si>
+  <si>
+    <t>2630조 7259억 1578만</t>
+  </si>
+  <si>
     <t>김또느</t>
   </si>
   <si>
-    <t>member_rank_in_guild</t>
-  </si>
-  <si>
-    <t>nickname</t>
-  </si>
-  <si>
-    <t>character_key</t>
-  </si>
-  <si>
-    <t>character_url</t>
-  </si>
-  <si>
-    <t>is_master</t>
-  </si>
-  <si>
-    <t>job_name</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>combat_power</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8232조 3835억 8286만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>5286조 3617억 27만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>두향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3428조 96억 9692만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>3164조 1968억 5216만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>3155조 7739억 8662만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>2712조 6401억 5428만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2262조 57억 2121만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1975조 9326억 3392만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>1650조 4569억 6002만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>1367조 1278억 9128만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>1273조 5227억 6113만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1098조 3013억 5091만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>972조 2153억 1957만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>934조 1730억 4089만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>918조 9796억 5248만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>886조 8406억 7534만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>823조 2725억 3337만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>정태준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
-  </si>
-  <si>
-    <t>747조 6479억 4857만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>619조 9042억 7800만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>팡대지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
-  </si>
-  <si>
-    <t>440조 2371억 788만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>418조 2231억 6534만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>372조 5745억 3012만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>352조 5575억 4369만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>312조 7168억 9611만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>298조 2305억 9860만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>206조 9922억 631만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>203조 4743억 4374만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>194조 4027억 9180만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>194조 2882억 2735만</t>
-  </si>
-  <si>
-    <t>이슬러버</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%8A%AC%EB%9F%AC%EB%B2%84</t>
-  </si>
-  <si>
-    <t>1경 552조 7143억 6609만</t>
-  </si>
-  <si>
-    <t>이지카이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%B9%B4%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>3729조 1405억 2328만</t>
-  </si>
-  <si>
-    <t>연평로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3198조 7466억 2254만</t>
-  </si>
-  <si>
-    <t>웅잉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>2634조 5725억 4764만</t>
-  </si>
-  <si>
-    <t>델타시그마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>2421조 5885억 2686만</t>
-  </si>
-  <si>
-    <t>보급중대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%B8%89%EC%A4%91%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2420조 9915억 1983만</t>
-  </si>
-  <si>
-    <t>엉쫀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%89%EC%AB%80</t>
-  </si>
-  <si>
-    <t>1538조 6264억 5877만</t>
-  </si>
-  <si>
-    <t>돼왕다람쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%99%95%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
-  </si>
-  <si>
-    <t>1331조 7687억 4986만</t>
-  </si>
-  <si>
-    <t>으눼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
-  </si>
-  <si>
-    <t>1303조 6370억 3012만</t>
-  </si>
-  <si>
-    <t>용이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1274조 7989억 8529만</t>
-  </si>
-  <si>
-    <t>꼴뱅이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%B1%85%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1220조 88억 2860만</t>
-  </si>
-  <si>
-    <t>벽그림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EA%B7%B8%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>1139조 6050억 2424만</t>
-  </si>
-  <si>
-    <t>간장아비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%84%EC%9E%A5%EC%95%84%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1051조 1655억 8445만</t>
-  </si>
-  <si>
-    <t>요금표</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B8%88%ED%91%9C</t>
-  </si>
-  <si>
-    <t>1023조 6329억 7081만</t>
-  </si>
-  <si>
-    <t>무과키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%ED%82%A4</t>
-  </si>
-  <si>
-    <t>909조 1425억 7163만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=PSG%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>822조 630억 5826만</t>
-  </si>
-  <si>
-    <t>뉴비i</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
-  </si>
-  <si>
-    <t>806조 4518억 8822만</t>
-  </si>
-  <si>
-    <t>에누마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%88%84%EB%A7%88</t>
-  </si>
-  <si>
-    <t>679조 1299억 6562만</t>
-  </si>
-  <si>
-    <t>하랸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
-  </si>
-  <si>
-    <t>669조 1047억 1333만</t>
-  </si>
-  <si>
-    <t>한콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>648조 3728억 7491만</t>
-  </si>
-  <si>
-    <t>뭉게뭉게구름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%EA%B2%8C%EB%AD%89%EA%B2%8C%EA%B5%AC%EB%A6%84</t>
-  </si>
-  <si>
-    <t>599조 6164억 6024만</t>
-  </si>
-  <si>
-    <t>서피비치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%94%BC%EB%B9%84%EC%B9%98</t>
-  </si>
-  <si>
-    <t>568조 5290억 8259만</t>
-  </si>
-  <si>
-    <t>주식하자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
-  </si>
-  <si>
-    <t>507조 5595억 3068만</t>
-  </si>
-  <si>
-    <t>김로케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%9C%EC%BC%80</t>
-  </si>
-  <si>
-    <t>435조 1555억 7407만</t>
-  </si>
-  <si>
-    <t>소심한섀도어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%8B%AC%ED%95%9C%EC%84%80%EB%8F%84%EC%96%B4</t>
-  </si>
-  <si>
-    <t>369조 315억 2947만</t>
-  </si>
-  <si>
-    <t>전포동포동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8F%AC%EB%8F%99%ED%8F%AC%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>270조 5475억 634만</t>
-  </si>
-  <si>
-    <t>경춘선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
-  </si>
-  <si>
-    <t>250조 5658억 4896만</t>
-  </si>
-  <si>
-    <t>01260227</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=01260227</t>
-  </si>
-  <si>
-    <t>225조 5898억 9585만</t>
-  </si>
-  <si>
-    <t>8623</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=8623</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>213조 2429억 7608만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>수비맨디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%84%EB%A7%A8%EB%94%94</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>163조 1505억 9073만</t>
-  </si>
-  <si>
-    <t>글쟈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%80%EC%9F%88</t>
-  </si>
-  <si>
-    <t>1경 447조 5129억 7199만</t>
-  </si>
-  <si>
-    <t>괴챠반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
-  </si>
-  <si>
-    <t>3779조 9660억 4199만</t>
-  </si>
-  <si>
-    <t>명동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3245조 684억 6500만</t>
-  </si>
-  <si>
-    <t>유놈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%86%88</t>
-  </si>
-  <si>
-    <t>2621조 4061억 2859만</t>
-  </si>
-  <si>
-    <t>꿀꿀맛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EB%A7%9B</t>
-  </si>
-  <si>
-    <t>2386조 8932억 4753만</t>
-  </si>
-  <si>
-    <t>윤꼬밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>2156조 1091억 1210만</t>
-  </si>
-  <si>
-    <t>디매트로돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A7%A4%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
-  </si>
-  <si>
-    <t>2148조 7069억 2080만</t>
-  </si>
-  <si>
-    <t>사오토메란마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%98%A4%ED%86%A0%EB%A9%94%EB%9E%80%EB%A7%88</t>
-  </si>
-  <si>
-    <t>1707조 4498억 8759만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%98%81%EA%B5%90</t>
-  </si>
-  <si>
-    <t>1495조 9351억 651만</t>
-  </si>
-  <si>
-    <t>김훈한</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%9B%88%ED%95%9C</t>
-  </si>
-  <si>
-    <t>1152조 7813억 2778만</t>
-  </si>
-  <si>
-    <t>Pakachu9999</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
-  </si>
-  <si>
-    <t>1142조 2566억 8130만</t>
-  </si>
-  <si>
-    <t>구엉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EC%97%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1052조 5398억 161만</t>
-  </si>
-  <si>
-    <t>잉글리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B8%80%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1022조 5383억 5173만</t>
-  </si>
-  <si>
-    <t>똥땅이횽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
-  </si>
-  <si>
-    <t>776조 7613억 8822만</t>
-  </si>
-  <si>
-    <t>혁바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EB%B0%94</t>
-  </si>
-  <si>
-    <t>775조 4786억 1213만</t>
-  </si>
-  <si>
-    <t>범지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
-  </si>
-  <si>
-    <t>753조 791억 3550만</t>
-  </si>
-  <si>
-    <t>디메트로돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A9%94%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
-  </si>
-  <si>
-    <t>704조 9735억 7649만</t>
-  </si>
-  <si>
-    <t>솖이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>681조 4944억 9400만</t>
-  </si>
-  <si>
-    <t>뜨머푸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A8%B8%ED%91%B8</t>
-  </si>
-  <si>
-    <t>666조 9853억 6246만</t>
-  </si>
-  <si>
-    <t>오우솃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
-  </si>
-  <si>
-    <t>623조 4349억 2383만</t>
-  </si>
-  <si>
-    <t>혜미니현미니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%AF%B8%EB%8B%88%ED%98%84%EB%AF%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>588조 1465억 3109만</t>
-  </si>
-  <si>
-    <t>옆구리두방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%86%EA%B5%AC%EB%A6%AC%EB%91%90%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>511조 7625억 5353만</t>
-  </si>
-  <si>
-    <t>쀏뀱쪍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%80%8F%EB%80%B1%EC%AA%8D</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>477조 4769억 4575만</t>
-  </si>
-  <si>
-    <t>양쿼카</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%BF%BC%EC%B9%B4</t>
-  </si>
-  <si>
-    <t>390조 3037억 2972만</t>
-  </si>
-  <si>
-    <t>정섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>384조 5653억 9771만</t>
-  </si>
-  <si>
-    <t>니누고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%88%84%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>377조 4506억 6398만</t>
-  </si>
-  <si>
-    <t>연속기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%86%8D%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>330조 108억 9811만</t>
-  </si>
-  <si>
-    <t>여덟시</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>313조 7265억 4684만</t>
-  </si>
-  <si>
-    <t>돼짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>307조 5404억 2549만</t>
-  </si>
-  <si>
-    <t>젤로젤리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%A4%EB%A1%9C%EC%A0%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>304조 3439억 3321만</t>
-  </si>
-  <si>
-    <t>우니아파요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>5708조 2885억 4200만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
-  </si>
-  <si>
-    <t>4080조 5012억 4862만</t>
-  </si>
-  <si>
-    <t>도하리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2938조 3489억 2905만</t>
-  </si>
-  <si>
-    <t>죽창당일개통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
-  </si>
-  <si>
-    <t>2365조 5050억 9154만</t>
-  </si>
-  <si>
-    <t>유수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>1952조 1184억 721만</t>
-  </si>
-  <si>
-    <t>종꿀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
-  </si>
-  <si>
-    <t>1871조 7826억 9063만</t>
-  </si>
-  <si>
-    <t>이용하다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1666조 7737억 1182만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1609조 611억 3837만</t>
-  </si>
-  <si>
-    <t>해달잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1575조 8408억 837만</t>
-  </si>
-  <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1428조 1274억 3869만</t>
-  </si>
-  <si>
-    <t>세월이야속해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1220조 3790억 5343만</t>
-  </si>
-  <si>
-    <t>포빅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
-  </si>
-  <si>
-    <t>1153조 3828억 7253만</t>
-  </si>
-  <si>
-    <t>여자둘남자둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
-  </si>
-  <si>
-    <t>1087조 1012억 5122만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1007조 6958억 4699만</t>
-  </si>
-  <si>
-    <t>덩개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>979조 1950억 779만</t>
-  </si>
-  <si>
-    <t>MangCI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
-  </si>
-  <si>
-    <t>925조 4898억 5127만</t>
-  </si>
-  <si>
-    <t>예타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
-  </si>
-  <si>
-    <t>848조 2555억 9974만</t>
-  </si>
-  <si>
-    <t>모르페우스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>793조 9488억 1111만</t>
-  </si>
-  <si>
-    <t>박금쪽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
-  </si>
-  <si>
-    <t>738조 5839억 1620만</t>
-  </si>
-  <si>
-    <t>티에이치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
-  </si>
-  <si>
-    <t>713조 6537억 5559만</t>
-  </si>
-  <si>
-    <t>파이리양말</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
-  </si>
-  <si>
-    <t>699조 842억 792만</t>
-  </si>
-  <si>
-    <t>지존짱창남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
-  </si>
-  <si>
-    <t>640조 6003억 3635만</t>
-  </si>
-  <si>
-    <t>작업치료사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
-  </si>
-  <si>
-    <t>601조 4919억 9329만</t>
-  </si>
-  <si>
-    <t>성률</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
-  </si>
-  <si>
-    <t>568조 9858억 9869만</t>
-  </si>
-  <si>
-    <t>히어로호걸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
-  </si>
-  <si>
-    <t>544조 7027억 9531만</t>
-  </si>
-  <si>
-    <t>감화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
-  </si>
-  <si>
-    <t>525조 6479억 4753만</t>
-  </si>
-  <si>
-    <t>계니규니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>468조 5687억 6869만</t>
-  </si>
-  <si>
-    <t>하비엔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
-  </si>
-  <si>
-    <t>283조 5698억 2300만</t>
-  </si>
-  <si>
-    <t>채구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>253조 655억 8729만</t>
-  </si>
-  <si>
-    <t>신탄보우짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>225조 9114억 655만</t>
-  </si>
-  <si>
-    <t>주식회사서영</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%9A%8C%EC%82%AC%EC%84%9C%EC%98%81</t>
-  </si>
-  <si>
-    <t>4경 2039조 4141억 5612만</t>
-  </si>
-  <si>
-    <t>블루펀치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B8%94%EB%A3%A8%ED%8E%80%EC%B9%98</t>
-  </si>
-  <si>
-    <t>4135조 8792억 9596만</t>
-  </si>
-  <si>
-    <t>찌그러진모자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%8C%EA%B7%B8%EB%9F%AC%EC%A7%84%EB%AA%A8%EC%9E%90</t>
-  </si>
-  <si>
-    <t>2409조 1879억 6004만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%98%90%EB%8A%90</t>
   </si>
   <si>
-    <t>1972조 3426억 1900만</t>
+    <t>2015조 7183억 7524만</t>
+  </si>
+  <si>
+    <t>베네치얀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%84%A4%EC%B9%98%EC%96%80</t>
+  </si>
+  <si>
+    <t>623조 5767억 7676만</t>
   </si>
   <si>
     <t>부산철거</t>
@@ -1493,22 +1505,13 @@
     <t>610조 561억 3804만</t>
   </si>
   <si>
-    <t>베네치얀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%84%A4%EC%B9%98%EC%96%80</t>
-  </si>
-  <si>
-    <t>582조 7749억 7591만</t>
-  </si>
-  <si>
     <t>갸렌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%B8%EB%A0%8C</t>
   </si>
   <si>
-    <t>369조 3823억 41만</t>
+    <t>390조 451억 476만</t>
   </si>
   <si>
     <t>태양o</t>
@@ -1520,13 +1523,31 @@
     <t>358조 2882억 6663만</t>
   </si>
   <si>
+    <t>봄여름한겨울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%97%AC%EB%A6%84%ED%95%9C%EA%B2%A8%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>342조 8072억 3454만</t>
+  </si>
+  <si>
     <t>효설빈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%84%A4%EB%B9%88</t>
   </si>
   <si>
-    <t>283조 4488억 434만</t>
+    <t>325조 6400억 1276만</t>
+  </si>
+  <si>
+    <t>곰세마리당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EC%84%B8%EB%A7%88%EB%A6%AC%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>322조 3816억 1640만</t>
   </si>
   <si>
     <t>꺆뜎</t>
@@ -1535,16 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BA%86%EB%9C%8E</t>
   </si>
   <si>
-    <t>277조 150억 2527만</t>
-  </si>
-  <si>
-    <t>봄여름한겨울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%84%EC%97%AC%EB%A6%84%ED%95%9C%EA%B2%A8%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>263조 3974억 2990만</t>
+    <t>287조 1291억 162만</t>
   </si>
   <si>
     <t>모우모우우</t>
@@ -1553,16 +1565,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%9A%B0%EB%AA%A8%EC%9A%B0%EC%9A%B0</t>
   </si>
   <si>
-    <t>249조 5633억 6327만</t>
-  </si>
-  <si>
-    <t>곰세마리당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EC%84%B8%EB%A7%88%EB%A6%AC%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>246조 6743억 4568만</t>
+    <t>265조 1793억 4789만</t>
+  </si>
+  <si>
+    <t>하숩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%A9</t>
+  </si>
+  <si>
+    <t>265조 144억 8746만</t>
   </si>
   <si>
     <t>1지옥참마도1</t>
@@ -1574,22 +1586,10 @@
     <t>240조 7601억 443만</t>
   </si>
   <si>
-    <t>하숩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%A9</t>
-  </si>
-  <si>
-    <t>229조 7785억 210만</t>
-  </si>
-  <si>
-    <t>토느</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8A%90</t>
   </si>
   <si>
-    <t>194조 9697억 5521만</t>
+    <t>204조 1079억 9340만</t>
   </si>
   <si>
     <t>행복하길바래</t>
@@ -1598,7 +1598,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%96%89%EB%B3%B5%ED%95%98%EA%B8%B8%EB%B0%94%EB%9E%98</t>
   </si>
   <si>
-    <t>167조 140억 1348만</t>
+    <t>187조 7817억 8995만</t>
+  </si>
+  <si>
+    <t>당근이니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B7%BC%EC%9D%B4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>172조 1354억 3765만</t>
   </si>
   <si>
     <t>미허</t>
@@ -1607,16 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%ED%97%88</t>
   </si>
   <si>
-    <t>158조 8375억 3882만</t>
-  </si>
-  <si>
-    <t>당근이니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%B9%EA%B7%BC%EC%9D%B4%EB%8B%88</t>
-  </si>
-  <si>
-    <t>158조 7854억 5352만</t>
+    <t>167조 9240억 9924만</t>
   </si>
   <si>
     <t>동그리미</t>
@@ -1625,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%99%EA%B7%B8%EB%A6%AC%EB%AF%B8</t>
   </si>
   <si>
-    <t>153조 4101억 5656만</t>
+    <t>163조 3524억 5774만</t>
   </si>
   <si>
     <t>허상하</t>
@@ -1637,22 +1637,22 @@
     <t>145조 3356억 22만</t>
   </si>
   <si>
+    <t>명지사나이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EC%82%AC%EB%82%98%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>105조 3608억 2990만</t>
+  </si>
+  <si>
     <t>최경무</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B2%BD%EB%AC%B4</t>
   </si>
   <si>
-    <t>87조 5400억 7895만</t>
-  </si>
-  <si>
-    <t>명지사나이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EC%82%AC%EB%82%98%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>87조 4900억 9590만</t>
+    <t>89조 835억 2500만</t>
   </si>
   <si>
     <t>앙설</t>
@@ -1661,19 +1661,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%99%EC%84%A4</t>
   </si>
   <si>
+    <t>81조 778억 6734만</t>
+  </si>
+  <si>
+    <t>진떡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EB%96%A1</t>
+  </si>
+  <si>
     <t>105</t>
   </si>
   <si>
-    <t>79조 6202억 1077만</t>
-  </si>
-  <si>
-    <t>진떡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EB%96%A1</t>
-  </si>
-  <si>
-    <t>65조 3925억 5974만</t>
+    <t>76조 8305억 3124만</t>
   </si>
   <si>
     <t>해적왕정우짱</t>
@@ -1682,7 +1682,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A0%81%EC%99%95%EC%A0%95%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>52조 502억 6634만</t>
+    <t>57조 2769억 3563만</t>
   </si>
   <si>
     <t>비단나비</t>
@@ -1691,7 +1691,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%8B%A8%EB%82%98%EB%B9%84</t>
   </si>
   <si>
-    <t>49조 4046억 4806만</t>
+    <t>52조 2864억 1269만</t>
   </si>
   <si>
     <t>태양0</t>
@@ -1700,7 +1700,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%96%910</t>
   </si>
   <si>
-    <t>48조 7529억 2500만</t>
+    <t>51조 4431억 9277만</t>
   </si>
   <si>
     <t>마동턱</t>
@@ -1709,7 +1709,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%99%ED%84%B1</t>
   </si>
   <si>
-    <t>34조 3164억 8910만</t>
+    <t>51조 1280억 9147만</t>
   </si>
   <si>
     <t>웅나공듀</t>
@@ -1718,10 +1718,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EB%82%98%EA%B3%B5%EB%93%80</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>34조 1260억 7845만</t>
+    <t>46조 7146억 8831만</t>
   </si>
 </sst>
 </file>
@@ -2343,7 +2340,7 @@
         <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2585,13 +2582,13 @@
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2602,25 +2599,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>105</v>
@@ -2713,13 +2710,13 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2730,22 +2727,22 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>79</v>
@@ -2777,7 +2774,7 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>126</v>
@@ -2812,7 +2809,7 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>131</v>
@@ -2844,7 +2841,7 @@
         <v>135</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>136</v>
@@ -2861,25 +2858,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>140</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2890,22 +2887,22 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>126</v>
@@ -2972,7 +2969,7 @@
         <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -3097,7 +3094,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>165</v>
@@ -3225,7 +3222,7 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>182</v>
@@ -3257,13 +3254,13 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>182</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3274,28 +3271,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>182</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3306,22 +3303,22 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>182</v>
@@ -3469,7 +3466,7 @@
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>79</v>
@@ -3501,10 +3498,10 @@
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>210</v>
@@ -3533,10 +3530,10 @@
         <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>213</v>
@@ -3565,7 +3562,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>79</v>
@@ -3614,7 +3611,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>220</v>
@@ -3632,7 +3629,7 @@
         <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>222</v>
@@ -3664,7 +3661,7 @@
         <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>225</v>
@@ -3696,7 +3693,7 @@
         <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>228</v>
@@ -3728,7 +3725,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>231</v>
@@ -3742,7 +3739,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>232</v>
@@ -3757,7 +3754,7 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>79</v>
@@ -3789,10 +3786,10 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>237</v>
@@ -3853,10 +3850,10 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>243</v>
@@ -3902,7 +3899,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>33</v>
@@ -3914,10 +3911,10 @@
         <v>247</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>126</v>
@@ -4013,7 +4010,7 @@
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
@@ -4077,10 +4074,10 @@
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>263</v>
@@ -4176,7 +4173,7 @@
         <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>272</v>
@@ -4205,7 +4202,7 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>126</v>
@@ -4237,10 +4234,10 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>278</v>
@@ -4269,10 +4266,10 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>281</v>
@@ -4286,7 +4283,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>282</v>
@@ -4301,7 +4298,7 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>165</v>
@@ -4318,7 +4315,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>285</v>
@@ -4333,7 +4330,7 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>287</v>
@@ -4422,11 +4419,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4482,7 +4479,7 @@
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
@@ -4502,25 +4499,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4534,25 +4531,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4566,13 +4563,13 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
@@ -4581,10 +4578,10 @@
         <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4598,25 +4595,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4630,25 +4627,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4659,28 +4656,28 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4694,25 +4691,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>317</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4726,22 +4723,22 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>318</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>318</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>320</v>
@@ -4770,10 +4767,10 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>323</v>
@@ -4787,7 +4784,7 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -4802,10 +4799,10 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>326</v>
@@ -4834,13 +4831,13 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>329</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4854,25 +4851,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4886,25 +4883,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4918,25 +4915,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4947,28 +4944,28 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4982,25 +4979,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -5014,25 +5011,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -5046,25 +5043,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -5078,25 +5075,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -5110,25 +5107,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -5142,25 +5139,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -5174,22 +5171,22 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>363</v>
@@ -5218,10 +5215,10 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>366</v>
@@ -5250,7 +5247,7 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>126</v>
@@ -5285,7 +5282,7 @@
         <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>372</v>
@@ -5314,7 +5311,7 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>126</v>
@@ -5331,7 +5328,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>376</v>
@@ -5346,7 +5343,7 @@
         <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>165</v>
@@ -5363,7 +5360,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>379</v>
@@ -5378,10 +5375,10 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>381</v>
@@ -5467,11 +5464,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5527,7 +5524,7 @@
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>90</v>
+        <v>144</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>73</v>
@@ -5547,25 +5544,25 @@
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>388</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>388</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -5579,25 +5576,25 @@
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -5611,13 +5608,13 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>71</v>
@@ -5626,10 +5623,10 @@
         <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -5643,25 +5640,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -5675,25 +5672,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -5704,28 +5701,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -5739,25 +5736,25 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>78</v>
+        <v>135</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -5771,22 +5768,22 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>408</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>408</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>409</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>410</v>
@@ -5815,10 +5812,10 @@
         <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>104</v>
+        <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>413</v>
@@ -5832,7 +5829,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>414</v>
@@ -5847,10 +5844,10 @@
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>416</v>
@@ -5879,10 +5876,10 @@
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>362</v>
+        <v>117</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>419</v>
@@ -5914,7 +5911,7 @@
         <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>422</v>
@@ -5943,10 +5940,10 @@
         <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>425</v>
@@ -5975,10 +5972,10 @@
         <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>196</v>
+        <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>428</v>
@@ -5992,7 +5989,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>429</v>
@@ -6007,10 +6004,10 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>431</v>
@@ -6039,10 +6036,10 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>434</v>
@@ -6074,7 +6071,7 @@
         <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>437</v>
@@ -6103,10 +6100,10 @@
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>440</v>
@@ -6135,10 +6132,10 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>121</v>
+        <v>195</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>443</v>
@@ -6170,7 +6167,7 @@
         <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>446</v>
@@ -6199,10 +6196,10 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>449</v>
@@ -6231,10 +6228,10 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>452</v>
@@ -6263,7 +6260,7 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>126</v>
@@ -6295,10 +6292,10 @@
         <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>458</v>
@@ -6330,7 +6327,7 @@
         <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>461</v>
@@ -6359,7 +6356,7 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>126</v>
@@ -6376,7 +6373,7 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>465</v>
@@ -6394,7 +6391,7 @@
         <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>467</v>
@@ -6408,7 +6405,7 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>468</v>
@@ -6423,10 +6420,10 @@
         <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>470</v>
@@ -6455,10 +6452,10 @@
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>473</v>
@@ -6572,16 +6569,16 @@
         <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6604,7 +6601,7 @@
         <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>79</v>
@@ -6613,7 +6610,7 @@
         <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6645,7 +6642,7 @@
         <v>482</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6656,28 +6653,28 @@
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>59</v>
+        <v>483</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>59</v>
+        <v>483</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6688,28 +6685,28 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6720,28 +6717,28 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>191</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6749,31 +6746,31 @@
         <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>182</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6784,13 +6781,13 @@
         <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>71</v>
@@ -6802,10 +6799,10 @@
         <v>165</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6816,28 +6813,28 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>293</v>
+        <v>165</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6848,13 +6845,13 @@
         <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>71</v>
@@ -6863,13 +6860,13 @@
         <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>182</v>
+        <v>293</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6877,31 +6874,31 @@
         <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>165</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6912,28 +6909,28 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6944,28 +6941,28 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>329</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6976,13 +6973,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>71</v>
@@ -6991,13 +6988,13 @@
         <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>182</v>
+        <v>287</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7008,13 +7005,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>71</v>
@@ -7023,13 +7020,13 @@
         <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7037,22 +7034,22 @@
         <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>518</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>518</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>519</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>165</v>
@@ -7061,7 +7058,7 @@
         <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7084,7 +7081,7 @@
         <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>182</v>
@@ -7093,7 +7090,7 @@
         <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7116,7 +7113,7 @@
         <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>362</v>
+        <v>117</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>293</v>
@@ -7125,7 +7122,7 @@
         <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7148,7 +7145,7 @@
         <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>121</v>
+        <v>329</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>293</v>
@@ -7157,7 +7154,7 @@
         <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7180,16 +7177,16 @@
         <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>287</v>
+        <v>182</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7221,7 +7218,7 @@
         <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7244,7 +7241,7 @@
         <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>191</v>
+        <v>144</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>287</v>
@@ -7253,7 +7250,7 @@
         <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7276,7 +7273,7 @@
         <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>287</v>
@@ -7285,7 +7282,7 @@
         <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7308,16 +7305,16 @@
         <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>545</v>
-      </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7328,28 +7325,28 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>548</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7372,7 +7369,7 @@
         <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>293</v>
@@ -7381,7 +7378,7 @@
         <v>551</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7404,16 +7401,16 @@
         <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>554</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7421,7 +7418,7 @@
         <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>555</v>
@@ -7439,13 +7436,13 @@
         <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>557</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7453,7 +7450,7 @@
         <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>558</v>
@@ -7471,13 +7468,13 @@
         <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>544</v>
+        <v>293</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>560</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7500,16 +7497,16 @@
         <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>362</v>
+        <v>329</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>564</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -9,23 +9,25 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="86서버" sheetId="3" r:id="rId3"/>
-    <sheet name="인형나라" sheetId="4" r:id="rId4"/>
+    <sheet name="지존길드" sheetId="3" r:id="rId3"/>
+    <sheet name="버번" sheetId="4" r:id="rId4"/>
     <sheet name="눈별" sheetId="5" r:id="rId5"/>
+    <sheet name="TopOfTop" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'86서버'!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TopOfTop!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">버번!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">인형나라!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="564">
   <si>
     <t>guild_name</t>
   </si>
@@ -78,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>428</t>
+    <t>426</t>
   </si>
   <si>
     <t>13위</t>
@@ -90,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>4경 7274조 1168억 2294만</t>
+    <t>4경 9072조 6890억 7407만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -99,61 +101,58 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.16</t>
-  </si>
-  <si>
-    <t>86서버</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=86%EC%84%9C%EB%B2%84</t>
-  </si>
-  <si>
-    <t>Scania 33</t>
-  </si>
-  <si>
-    <t>433</t>
-  </si>
-  <si>
-    <t>4위</t>
+    <t>2026.09.18</t>
+  </si>
+  <si>
+    <t>지존길드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>11위</t>
   </si>
   <si>
     <t>30명</t>
   </si>
   <si>
-    <t>4경 5973조 774억 3337만</t>
-  </si>
-  <si>
-    <t>길갑문의 PSG서포터즈, 김로케 귓 (길컨 진심, 길토벌 200위권! 귓)</t>
-  </si>
-  <si>
-    <t>PSG서포터즈</t>
-  </si>
-  <si>
-    <t>2026.09.17</t>
-  </si>
-  <si>
-    <t>인형나라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B8%ED%98%95%EB%82%98%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>Scania 25</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>7위</t>
-  </si>
-  <si>
-    <t>4경 4864조 4638억 7136만</t>
-  </si>
-  <si>
-    <t>Server.74 since 2026.01.27</t>
-  </si>
-  <si>
-    <t>최영교</t>
+    <t>4경 5576조 5195억 8399만</t>
+  </si>
+  <si>
+    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
+  </si>
+  <si>
+    <t>지존순찌</t>
+  </si>
+  <si>
+    <t>버번</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B2%84%EB%B2%88</t>
+  </si>
+  <si>
+    <t>Scania 1</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>29위</t>
+  </si>
+  <si>
+    <t>4경 128조 7878억 9119만</t>
+  </si>
+  <si>
+    <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
+  </si>
+  <si>
+    <t>망충둘기</t>
   </si>
   <si>
     <t>눈별</t>
@@ -165,13 +164,13 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>457</t>
+    <t>453</t>
   </si>
   <si>
     <t>9위</t>
   </si>
   <si>
-    <t>4경 1081조 9841억 1301만</t>
+    <t>4경 2302조 5872억 8127만</t>
   </si>
   <si>
     <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
@@ -180,6 +179,30 @@
     <t>심신삐약자</t>
   </si>
   <si>
+    <t>TopOfTop</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>4경 1747조 7735억 7464만</t>
+  </si>
+  <si>
+    <t>길컨 1등만</t>
+  </si>
+  <si>
+    <t>복어띰</t>
+  </si>
+  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -222,7 +245,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8515조 3583억 4706만</t>
+    <t>8558조 231억 7162만</t>
   </si>
   <si>
     <t>2</t>
@@ -237,85 +260,85 @@
     <t>비숍</t>
   </si>
   <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>5571조 2990억 750만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>두향</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>4268조 343억 8957만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>몽호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>3674조 8409억 1914만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>3334조 8639억 6043만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>3314조 3423억 3688만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
     <t>112</t>
   </si>
   <si>
-    <t>5522조 7382억 506만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>두향</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%90%ED%96%A5</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3815조 5213억 6600만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>3301조 3852억 4361만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>몽호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%ED%98%B8</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>3217조 3423억 2146만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>3010조 3664억 6363만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>2720조 2809억 9602만</t>
+    <t>2794조 5874억 3077만</t>
   </si>
   <si>
     <t>8</t>
@@ -327,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2062조 3576억 7889만</t>
+    <t>2062조 5674억 3493만</t>
   </si>
   <si>
     <t>9</t>
@@ -339,12 +362,24 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1718조 1326억 9702만</t>
+    <t>1738조 4910억 368만</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>1576조 8511억 519만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -357,18 +392,6 @@
     <t>1508조 7420억 3377만</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>1480조 3201억 3941만</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -387,6 +410,21 @@
     <t>13</t>
   </si>
   <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1045조 9073억 3017만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>채무조정</t>
   </si>
   <si>
@@ -396,21 +434,6 @@
     <t>972조 2153억 1957만</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>968조 1677억 2361만</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
@@ -420,7 +443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>933조 4008억 6223만</t>
+    <t>942조 6419억 6063만</t>
   </si>
   <si>
     <t>16</t>
@@ -435,7 +458,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>918조 9796억 5248만</t>
+    <t>925조 2980억 4556만</t>
   </si>
   <si>
     <t>17</t>
@@ -447,7 +470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>834조 9225억 8951만</t>
+    <t>838조 1381억 1843만</t>
   </si>
   <si>
     <t>18</t>
@@ -471,7 +494,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>712조 5098억 2176만</t>
+    <t>738조 8585억 6928만</t>
   </si>
   <si>
     <t>20</t>
@@ -483,7 +506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>498조 2303억 4062만</t>
+    <t>539조 3853억 2223만</t>
   </si>
   <si>
     <t>21</t>
@@ -498,7 +521,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>419조 7074억 9119만</t>
+    <t>460조 1881억 9462만</t>
   </si>
   <si>
     <t>22</t>
@@ -510,7 +533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>385조 9337억 8532만</t>
+    <t>386조 4288억 9793만</t>
   </si>
   <si>
     <t>23</t>
@@ -522,12 +545,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>355조 5354억 60만</t>
+    <t>372조 6896억 8563만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>354조 6601억 9194만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>박준우2</t>
   </si>
   <si>
@@ -537,21 +575,6 @@
     <t>328조 1595억 1568만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>325조 8411억 2940만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -561,12 +584,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>216조 9694억 4877만</t>
+    <t>222조 5602억 4740만</t>
   </si>
   <si>
     <t>27</t>
   </si>
   <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>215조 3909억 7501만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>꼬북빵야</t>
   </si>
   <si>
@@ -576,21 +614,6 @@
     <t>206조 9922억 631만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>203조 4743억 4374만</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
@@ -606,553 +629,562 @@
     <t>194조 4027억 9180만</t>
   </si>
   <si>
-    <t>이슬러버</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%8A%AC%EB%9F%AC%EB%B2%84</t>
-  </si>
-  <si>
-    <t>1경 763조 7057억 4323만</t>
-  </si>
-  <si>
-    <t>이지카이트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%B9%B4%EC%9D%B4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>3923조 6107억 7357만</t>
-  </si>
-  <si>
-    <t>연평로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%ED%8F%89%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3762조 9402억 3082만</t>
-  </si>
-  <si>
-    <t>웅잉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%EC%9E%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>2749조 440억 826만</t>
-  </si>
-  <si>
-    <t>보급중대장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%B8%89%EC%A4%91%EB%8C%80%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2594조 8020억 428만</t>
-  </si>
-  <si>
-    <t>델타시그마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%ED%83%80%EC%8B%9C%EA%B7%B8%EB%A7%88</t>
-  </si>
-  <si>
-    <t>2462조 8942억 8430만</t>
-  </si>
-  <si>
-    <t>엉쫀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%89%EC%AB%80</t>
-  </si>
-  <si>
-    <t>1538조 6264억 5877만</t>
-  </si>
-  <si>
-    <t>벽그림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%BD%EA%B7%B8%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>1425조 7402억 2493만</t>
-  </si>
-  <si>
-    <t>돼왕다람쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%99%95%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
-  </si>
-  <si>
-    <t>1421조 3107억 1308만</t>
-  </si>
-  <si>
-    <t>용이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1415조 2977억 397만</t>
-  </si>
-  <si>
-    <t>으눼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EB%88%BC</t>
-  </si>
-  <si>
-    <t>1387조 2451억 3182만</t>
-  </si>
-  <si>
-    <t>꼴뱅이a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%B4%EB%B1%85%EC%9D%B4a</t>
-  </si>
-  <si>
-    <t>1227조 7196억 7541만</t>
-  </si>
-  <si>
-    <t>간장아비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%84%EC%9E%A5%EC%95%84%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1105조 2813억 7771만</t>
-  </si>
-  <si>
-    <t>요금표</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B8%88%ED%91%9C</t>
-  </si>
-  <si>
-    <t>1065조 6741억 1673만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=PSG%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1018조 5521억 6601만</t>
-  </si>
-  <si>
-    <t>무과키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EA%B3%BC%ED%82%A4</t>
-  </si>
-  <si>
-    <t>982조 7422억 2268만</t>
-  </si>
-  <si>
-    <t>뭉게뭉게구름</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AD%89%EA%B2%8C%EB%AD%89%EA%B2%8C%EA%B5%AC%EB%A6%84</t>
-  </si>
-  <si>
-    <t>956조 5555억 3439만</t>
-  </si>
-  <si>
-    <t>뉴비i</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%89%B4%EB%B9%84i</t>
-  </si>
-  <si>
-    <t>871조 4532억 6094만</t>
-  </si>
-  <si>
-    <t>하랸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%9E%B8</t>
-  </si>
-  <si>
-    <t>714조 3668억 7689만</t>
-  </si>
-  <si>
-    <t>에누마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EB%88%84%EB%A7%88</t>
-  </si>
-  <si>
-    <t>679조 1299억 6562만</t>
-  </si>
-  <si>
-    <t>한콩순</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%BD%A9%EC%88%9C</t>
-  </si>
-  <si>
-    <t>648조 3728억 7491만</t>
-  </si>
-  <si>
-    <t>서피비치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%94%BC%EB%B9%84%EC%B9%98</t>
-  </si>
-  <si>
-    <t>620조 6766억 8014만</t>
-  </si>
-  <si>
-    <t>주식하자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%8B%9D%ED%95%98%EC%9E%90</t>
-  </si>
-  <si>
-    <t>507조 5595억 3068만</t>
-  </si>
-  <si>
-    <t>김로케</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EB%A1%9C%EC%BC%80</t>
-  </si>
-  <si>
-    <t>474조 3118억 1293만</t>
-  </si>
-  <si>
-    <t>소심한섀도어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%8B%AC%ED%95%9C%EC%84%80%EB%8F%84%EC%96%B4</t>
-  </si>
-  <si>
-    <t>440조 1008억 3423만</t>
-  </si>
-  <si>
-    <t>경춘선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B6%98%EC%84%A0</t>
-  </si>
-  <si>
-    <t>293조 4853억 9281만</t>
-  </si>
-  <si>
-    <t>전포동포동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%8F%AC%EB%8F%99%ED%8F%AC%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>270조 5475억 634만</t>
-  </si>
-  <si>
-    <t>8623</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=8623</t>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>6757조 5035억 879만</t>
+  </si>
+  <si>
+    <t>협의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+  </si>
+  <si>
+    <t>4151조 7828억 7756만</t>
+  </si>
+  <si>
+    <t>포항엄석대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
+  </si>
+  <si>
+    <t>3857조 9291억 1450만</t>
+  </si>
+  <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>2486조 9079억 1586만</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2263조 1140억 8844만</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>2259조 1663억 8382만</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>1951조 5767억 8833만</t>
+  </si>
+  <si>
+    <t>댜니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1738조 4296억 7283만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>1545조 4817억 4956만</t>
+  </si>
+  <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>1482조 8951억 781만</t>
+  </si>
+  <si>
+    <t>파울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>1419조 9260억 2582만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>1400조 9926억 8431만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1395조 8897억 1304만</t>
+  </si>
+  <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1391조 2010억 3776만</t>
+  </si>
+  <si>
+    <t>짱잘자쿨냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
+  </si>
+  <si>
+    <t>1027조 6078억 1748만</t>
+  </si>
+  <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>971조 5267억 8902만</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>952조 8262억 4047만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>940조 3059억 3341만</t>
+  </si>
+  <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>882조 7278억 5282만</t>
+  </si>
+  <si>
+    <t>마갤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
+  </si>
+  <si>
+    <t>826조 8046억 9936만</t>
+  </si>
+  <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>824조 2609억 4999만</t>
+  </si>
+  <si>
+    <t>냐은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
+  </si>
+  <si>
+    <t>810조 1567억 9854만</t>
+  </si>
+  <si>
+    <t>오옹나이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>787조 4728억 4596만</t>
+  </si>
+  <si>
+    <t>전산봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
+  </si>
+  <si>
+    <t>647조 9759억 4435만</t>
+  </si>
+  <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>584조 3143억 9077만</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>562조 3497억 5522만</t>
+  </si>
+  <si>
+    <t>태코찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>547조 9327억 8104만</t>
+  </si>
+  <si>
+    <t>유플러스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>482조 8831억 8288만</t>
+  </si>
+  <si>
+    <t>진성팔퀴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%84%B1%ED%8C%94%ED%80%B4</t>
+  </si>
+  <si>
+    <t>347조 5732억 9309만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>빵후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
+  </si>
+  <si>
+    <t>277조 36억 4103만</t>
+  </si>
+  <si>
+    <t>강댜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%8C%9C</t>
+  </si>
+  <si>
+    <t>1경 2621조 8500억 3719만</t>
+  </si>
+  <si>
+    <t>빵녕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EB%85%95</t>
+  </si>
+  <si>
+    <t>8707조 3775억 5909만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>7386조 3251억 3475만</t>
+  </si>
+  <si>
+    <t>실프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>1036조 7000억 1875만</t>
+  </si>
+  <si>
+    <t>냠늄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EB%8A%84</t>
+  </si>
+  <si>
+    <t>914조 4728억 6800만</t>
+  </si>
+  <si>
+    <t>페레로로쉐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
+  </si>
+  <si>
+    <t>903조 3164억 5030만</t>
+  </si>
+  <si>
+    <t>보호소</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%ED%98%B8%EC%86%8C</t>
+  </si>
+  <si>
+    <t>821조 5481억 8761만</t>
+  </si>
+  <si>
+    <t>쮸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>749조 536억 6358만</t>
+  </si>
+  <si>
+    <t>더대충</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
+  </si>
+  <si>
+    <t>653조 5119억 7611만</t>
+  </si>
+  <si>
+    <t>그복</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
+  </si>
+  <si>
+    <t>610조 6680억 423만</t>
+  </si>
+  <si>
+    <t>갈매기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%A4%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>606조 1185억 6714만</t>
+  </si>
+  <si>
+    <t>끼꼬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BC%EA%BC%AC</t>
+  </si>
+  <si>
+    <t>572조 1815억 1954만</t>
+  </si>
+  <si>
+    <t>더적당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>495조 9027억 7374만</t>
+  </si>
+  <si>
+    <t>주사고모</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%82%AC%EA%B3%A0%EB%AA%A8</t>
+  </si>
+  <si>
+    <t>484조 4320억 4123만</t>
+  </si>
+  <si>
+    <t>사랑해제명</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
+  </si>
+  <si>
+    <t>404조 8443억 181만</t>
+  </si>
+  <si>
+    <t>꿀꿀이의모험</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
+  </si>
+  <si>
+    <t>397조 4887억 1580만</t>
+  </si>
+  <si>
+    <t>시루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>350조 2268억 4588만</t>
+  </si>
+  <si>
+    <t>퍄딤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
+  </si>
+  <si>
+    <t>335조 291억 9859만</t>
+  </si>
+  <si>
+    <t>냥찐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
+  </si>
+  <si>
+    <t>327조 9016억 7369만</t>
+  </si>
+  <si>
+    <t>환불스토리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>309조 839억 2801만</t>
+  </si>
+  <si>
+    <t>달디달고나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%94%94%EB%8B%AC%EA%B3%A0%EB%82%98</t>
   </si>
   <si>
     <t>107</t>
   </si>
   <si>
-    <t>232조 3059억 5172만</t>
-  </si>
-  <si>
-    <t>01260227</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=01260227</t>
-  </si>
-  <si>
-    <t>225조 5898억 9585만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>수비맨디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EB%B9%84%EB%A7%A8%EB%94%94</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
+    <t>254조 547억 5073만</t>
+  </si>
+  <si>
+    <t>소동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%99</t>
+  </si>
+  <si>
+    <t>191조 2004억 9982만</t>
+  </si>
+  <si>
+    <t>초코파베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>181조 8114억 810만</t>
+  </si>
+  <si>
+    <t>취란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
+  </si>
+  <si>
+    <t>164조 6094억 9117만</t>
+  </si>
+  <si>
+    <t>한굥굥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EA%B5%A5%EA%B5%A5</t>
+  </si>
+  <si>
+    <t>158조 6868억 2419만</t>
+  </si>
+  <si>
+    <t>키류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%A5%98</t>
+  </si>
+  <si>
+    <t>154조 7796억 7587만</t>
+  </si>
+  <si>
+    <t>해졍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
   </si>
   <si>
     <t>106</t>
   </si>
   <si>
-    <t>193조 4344억 8021만</t>
-  </si>
-  <si>
-    <t>글쟈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%80%EC%9F%88</t>
-  </si>
-  <si>
-    <t>1경 447조 5129억 7199만</t>
-  </si>
-  <si>
-    <t>괴챠반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%B4%EC%B1%A0%EB%B0%98</t>
-  </si>
-  <si>
-    <t>3779조 9660억 4199만</t>
-  </si>
-  <si>
-    <t>명동이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EB%8F%99%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>3245조 684억 6500만</t>
-  </si>
-  <si>
-    <t>유놈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EB%86%88</t>
-  </si>
-  <si>
-    <t>2901조 3152억 7649만</t>
-  </si>
-  <si>
-    <t>윤꼬밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%BC%AC%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>2442조 2280억 1960만</t>
-  </si>
-  <si>
-    <t>꿀꿀맛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EB%A7%9B</t>
-  </si>
-  <si>
-    <t>2386조 8932억 4753만</t>
-  </si>
-  <si>
-    <t>디매트로돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A7%A4%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
-  </si>
-  <si>
-    <t>2148조 7069억 2080만</t>
-  </si>
-  <si>
-    <t>사오토메란마</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%98%A4%ED%86%A0%EB%A9%94%EB%9E%80%EB%A7%88</t>
-  </si>
-  <si>
-    <t>1774조 6336억 8068만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%98%81%EA%B5%90</t>
-  </si>
-  <si>
-    <t>1545조 4241억 7527만</t>
-  </si>
-  <si>
-    <t>김훈한</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%9B%88%ED%95%9C</t>
-  </si>
-  <si>
-    <t>1277조 5140억 7129만</t>
-  </si>
-  <si>
-    <t>Pakachu9999</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pakachu9999</t>
-  </si>
-  <si>
-    <t>1170조 6269억 1345만</t>
-  </si>
-  <si>
-    <t>잉글리쉬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EA%B8%80%EB%A6%AC%EC%89%AC</t>
-  </si>
-  <si>
-    <t>1088조 6995억 8142만</t>
-  </si>
-  <si>
-    <t>구엉이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EC%97%89%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1052조 5398억 161만</t>
-  </si>
-  <si>
-    <t>혁바</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%81%EB%B0%94</t>
-  </si>
-  <si>
-    <t>911조 8265억 3396만</t>
-  </si>
-  <si>
-    <t>뜨머푸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A8%B8%ED%91%B8</t>
-  </si>
-  <si>
-    <t>908조 7006억 19만</t>
-  </si>
-  <si>
-    <t>똥땅이횽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%95%85%EC%9D%B4%ED%9A%BD</t>
-  </si>
-  <si>
-    <t>802조 6731억 4848만</t>
-  </si>
-  <si>
-    <t>범지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%94%EC%A7%80</t>
-  </si>
-  <si>
-    <t>781조 6878억 6641만</t>
-  </si>
-  <si>
-    <t>디메트로돈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EB%A9%94%ED%8A%B8%EB%A1%9C%EB%8F%88</t>
-  </si>
-  <si>
-    <t>717조 6625억 1513만</t>
-  </si>
-  <si>
-    <t>솖이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%96%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>681조 4944억 9400만</t>
-  </si>
-  <si>
-    <t>오우솃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%9A%B0%EC%86%83</t>
-  </si>
-  <si>
-    <t>670조 1352억 9136만</t>
-  </si>
-  <si>
-    <t>혜미니현미니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EB%AF%B8%EB%8B%88%ED%98%84%EB%AF%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>608조 9879억 5844만</t>
-  </si>
-  <si>
-    <t>옆구리두방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%86%EA%B5%AC%EB%A6%AC%EB%91%90%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>531조 4391억 9363만</t>
-  </si>
-  <si>
-    <t>쀏뀱쪍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%80%8F%EB%80%B1%EC%AA%8D</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>505조 9352억 9899만</t>
-  </si>
-  <si>
-    <t>양쿼카</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%BF%BC%EC%B9%B4</t>
-  </si>
-  <si>
-    <t>400조 8688억 8723만</t>
-  </si>
-  <si>
-    <t>정섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>395조 8262억 1923만</t>
-  </si>
-  <si>
-    <t>니누고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%88%84%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>377조 4506억 6398만</t>
-  </si>
-  <si>
-    <t>연속기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EC%86%8D%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>330조 108억 9811만</t>
-  </si>
-  <si>
-    <t>돼짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%BC%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>328조 9701억 828만</t>
-  </si>
-  <si>
-    <t>여덟시</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8D%9F%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>325조 4906억 6808만</t>
-  </si>
-  <si>
-    <t>젤로젤리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%A4%EB%A1%9C%EC%A0%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>324조 1743억 5857만</t>
+    <t>111조 8873억 4670만</t>
+  </si>
+  <si>
+    <t>홍뎐잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
+  </si>
+  <si>
+    <t>108조 188억 1551만</t>
+  </si>
+  <si>
+    <t>꾸륭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%AD</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>104조 3404억 5034만</t>
+  </si>
+  <si>
+    <t>허숖</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%88%96</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>11조 3651억 6359만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1167,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>4539조 9051억 8255만</t>
+    <t>4717조 132억 3526만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -1176,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>2938조 3489억 2905만</t>
+    <t>3087조 4263억 7700만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -1194,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2079조 7509억 3154만</t>
+    <t>2290조 6260억 850만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1203,7 +1235,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>1939조 2480억 9380만</t>
+    <t>1970조 805억 6214만</t>
+  </si>
+  <si>
+    <t>이용하다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1746조 878억 9551만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1215,15 +1256,6 @@
     <t>1745조 1553억 5425만</t>
   </si>
   <si>
-    <t>이용하다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1700조 3358억 9824만</t>
-  </si>
-  <si>
     <t>여니워니</t>
   </si>
   <si>
@@ -1248,7 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1271조 7223억 3526만</t>
+    <t>1290조 7158억 985만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1257,7 +1289,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>1263조 5827억 4578만</t>
+    <t>1264조 7840억 4564만</t>
+  </si>
+  <si>
+    <t>MangCI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
+  </si>
+  <si>
+    <t>1225조 1705억 7084만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1275,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1137조 3913억 8758만</t>
+    <t>1141조 7336억 7187만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1284,16 +1325,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>1007조 6958억 4699만</t>
-  </si>
-  <si>
-    <t>MangCI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
-  </si>
-  <si>
-    <t>933조 1513억 6241만</t>
+    <t>1064조 8130억 8425만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1302,7 +1334,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>904조 8447억 7095만</t>
+    <t>916조 2790억 7128만</t>
+  </si>
+  <si>
+    <t>파이리양말</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
+  </si>
+  <si>
+    <t>811조 6711억 3670만</t>
+  </si>
+  <si>
+    <t>박금쪽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
+  </si>
+  <si>
+    <t>801조 7928억 6181만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1311,25 +1361,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>795조 7079억 8803만</t>
-  </si>
-  <si>
-    <t>박금쪽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
-  </si>
-  <si>
-    <t>778조 2437억 4643만</t>
-  </si>
-  <si>
-    <t>파이리양말</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
-  </si>
-  <si>
-    <t>733조 7966억 7796만</t>
+    <t>798조 1805억 5995만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1338,7 +1370,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>713조 6537억 5559만</t>
+    <t>758조 4177억 6625만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1347,7 +1379,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>674조 8831억 5472만</t>
+    <t>674조 9889억 4718만</t>
+  </si>
+  <si>
+    <t>성률</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
+  </si>
+  <si>
+    <t>629조 871억 5026만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1368,15 +1409,6 @@
     <t>599조 5583억 4223만</t>
   </si>
   <si>
-    <t>성률</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
-  </si>
-  <si>
-    <t>597조 2265억 6671만</t>
-  </si>
-  <si>
     <t>감화</t>
   </si>
   <si>
@@ -1392,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>495조 7843억 4910만</t>
+    <t>512조 4058억 7504만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1401,7 +1433,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>321조 1205억 2630만</t>
+    <t>330조 1725억 5296만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1410,7 +1442,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>270조 3755억 3902만</t>
+    <t>279조 240억 539만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1419,7 +1451,274 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>231조 8325억 2801만</t>
+    <t>238조 7342억 9660만</t>
+  </si>
+  <si>
+    <t>가겠습니다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>6383조 3476억 9123만</t>
+  </si>
+  <si>
+    <t>라카도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
+  </si>
+  <si>
+    <t>3957조 457억 9506만</t>
+  </si>
+  <si>
+    <t>미우맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
+  </si>
+  <si>
+    <t>2880조 5219억 5377만</t>
+  </si>
+  <si>
+    <t>롤대신해야지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>2840조 4162억 3948만</t>
+  </si>
+  <si>
+    <t>개종망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>2334조 6051억 8010만</t>
+  </si>
+  <si>
+    <t>gorystalLOVE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
+  </si>
+  <si>
+    <t>2107조 2460억 3000만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
+  </si>
+  <si>
+    <t>1926조 3126억 1612만</t>
+  </si>
+  <si>
+    <t>명지동꿀주먹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
+  </si>
+  <si>
+    <t>1896조 858억 7186만</t>
+  </si>
+  <si>
+    <t>커튼월</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
+  </si>
+  <si>
+    <t>1877조 135억 5251만</t>
+  </si>
+  <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>1868조 4029억 725만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>1549조 8843억 6126만</t>
+  </si>
+  <si>
+    <t>Judge99</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
+  </si>
+  <si>
+    <t>1436조 1270억 3584만</t>
+  </si>
+  <si>
+    <t>도리토스치즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
+  </si>
+  <si>
+    <t>981조 9247억 4194만</t>
+  </si>
+  <si>
+    <t>커럭트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>861조 4774억 5611만</t>
+  </si>
+  <si>
+    <t>지낌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>854조 6861억 572만</t>
+  </si>
+  <si>
+    <t>옥슈쓔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
+  </si>
+  <si>
+    <t>751조 7302억 6614만</t>
+  </si>
+  <si>
+    <t>무동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>741조 9354억 8078만</t>
+  </si>
+  <si>
+    <t>양룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>704조 9101억 2541만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>689조 5155억 5815만</t>
+  </si>
+  <si>
+    <t>또띠야칩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
+  </si>
+  <si>
+    <t>619조 2760억 9659만</t>
+  </si>
+  <si>
+    <t>gorystal</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
+  </si>
+  <si>
+    <t>563조 6969억 640만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>562조 3032억 9117만</t>
+  </si>
+  <si>
+    <t>파파존스맛나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
+  </si>
+  <si>
+    <t>524조 3731억 3025만</t>
+  </si>
+  <si>
+    <t>뀨꾸룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>496조 215억 2581만</t>
+  </si>
+  <si>
+    <t>복룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>491조 9289억 8094만</t>
+  </si>
+  <si>
+    <t>률율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>472조 2483억 5171만</t>
+  </si>
+  <si>
+    <t>짜상무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>437조 8805억 3207만</t>
+  </si>
+  <si>
+    <t>매리골드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>351조 7316억 1310만</t>
+  </si>
+  <si>
+    <t>원종일짱유나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>329조 5045억 2043만</t>
+  </si>
+  <si>
+    <t>문배동육칼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
+  </si>
+  <si>
+    <t>255조 6196억 5729만</t>
   </si>
 </sst>
 </file>
@@ -1782,7 +2081,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -1918,30 +2217,30 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
@@ -1950,39 +2249,39 @@
         <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -1991,25 +2290,67 @@
         <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M6" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M5"/>
+  <autoFilter ref="A1:M6"/>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1"/>
     <hyperlink ref="B3" r:id="rId2"/>
     <hyperlink ref="B4" r:id="rId3"/>
     <hyperlink ref="B5" r:id="rId4"/>
+    <hyperlink ref="B6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2034,28 +2375,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2066,28 +2407,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2098,28 +2439,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2130,28 +2471,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2162,28 +2503,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2194,28 +2535,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2226,28 +2567,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2258,28 +2599,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2290,28 +2631,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2322,28 +2663,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2354,28 +2695,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2386,28 +2727,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2418,28 +2759,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2450,28 +2791,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2482,28 +2823,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2514,28 +2855,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2546,7 +2887,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>23</v>
@@ -2555,19 +2896,19 @@
         <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2578,28 +2919,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2610,28 +2951,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2642,28 +2983,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2674,28 +3015,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -2706,28 +3047,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2738,28 +3079,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2770,28 +3111,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -2802,28 +3143,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -2834,28 +3175,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -2866,28 +3207,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -2898,28 +3239,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -2930,28 +3271,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -2962,28 +3303,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3037,7 +3378,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3046,28 +3387,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3078,31 +3419,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3110,31 +3451,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3142,31 +3483,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3174,31 +3515,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3206,31 +3547,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3238,31 +3579,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3270,31 +3611,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3302,31 +3643,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3334,31 +3675,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3366,31 +3707,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3398,31 +3739,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3430,31 +3771,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3462,31 +3803,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>77</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3494,31 +3835,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3526,31 +3867,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>243</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3558,31 +3899,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3590,31 +3931,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3622,31 +3963,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3654,31 +3995,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3686,31 +4027,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -3718,31 +4059,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -3750,31 +4091,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3782,31 +4123,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -3814,31 +4155,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -3846,31 +4187,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>135</v>
+        <v>274</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -3878,31 +4219,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -3910,31 +4251,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -3942,31 +4283,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>108</v>
+        <v>284</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>275</v>
+        <v>124</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -3974,31 +4315,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>135</v>
+        <v>274</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4006,31 +4347,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>283</v>
+        <v>189</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>284</v>
+        <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4078,11 +4419,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4091,28 +4432,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4120,962 +4461,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>292</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>292</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>191</v>
+        <v>129</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>42</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>220</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>186</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>191</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>354</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>91</v>
+        <v>354</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>353</v>
+        <v>198</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>91</v>
+        <v>354</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>354</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>156</v>
+        <v>354</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>117</v>
+        <v>373</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>117</v>
+        <v>373</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>156</v>
+        <v>380</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>117</v>
+        <v>384</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -5136,28 +5477,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5165,31 +5506,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5197,31 +5538,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5229,31 +5570,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5261,31 +5602,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5293,31 +5634,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5325,31 +5666,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5357,31 +5698,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5389,31 +5730,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5421,31 +5762,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5453,31 +5794,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5485,31 +5826,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5517,31 +5858,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>353</v>
+        <v>220</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5549,31 +5890,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5581,31 +5922,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5613,31 +5954,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5645,31 +5986,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5677,31 +6018,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5709,31 +6050,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5741,31 +6082,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5773,31 +6114,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5805,31 +6146,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5837,31 +6178,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5869,31 +6210,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>353</v>
+        <v>198</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5901,31 +6242,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5933,31 +6274,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>191</v>
+        <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5965,31 +6306,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5997,31 +6338,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6029,31 +6370,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6061,31 +6402,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6093,31 +6434,1076 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J31"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G31" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>117</v>
+        <v>163</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>464</v>
+        <v>563</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TopOfTop!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">버번!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">버번!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="568">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>426</t>
+    <t>428</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>4경 9072조 6890억 7407만</t>
+    <t>4경 9478조 6064억 3410만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.18</t>
+    <t>2026.09.19</t>
   </si>
   <si>
     <t>지존길드</t>
@@ -122,7 +122,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>4경 5576조 5195억 8399만</t>
+    <t>4경 6445조 2840억 90만</t>
   </si>
   <si>
     <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
@@ -140,13 +140,13 @@
     <t>Scania 1</t>
   </si>
   <si>
-    <t>465</t>
+    <t>464</t>
   </si>
   <si>
     <t>29위</t>
   </si>
   <si>
-    <t>4경 128조 7878억 9119만</t>
+    <t>4경 1205조 5828억 6809만</t>
   </si>
   <si>
     <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
@@ -164,13 +164,13 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>453</t>
+    <t>450</t>
   </si>
   <si>
     <t>9위</t>
   </si>
   <si>
-    <t>4경 2302조 5872억 8127만</t>
+    <t>4경 3461조 3653억 7046만</t>
   </si>
   <si>
     <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
@@ -191,10 +191,7 @@
     <t>456</t>
   </si>
   <si>
-    <t>8위</t>
-  </si>
-  <si>
-    <t>4경 1747조 7735억 7464만</t>
+    <t>4경 2296조 1640억 9507만</t>
   </si>
   <si>
     <t>길컨 1등만</t>
@@ -245,7 +242,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8558조 231억 7162만</t>
+    <t>8570조 3175억 8447만</t>
   </si>
   <si>
     <t>2</t>
@@ -278,7 +275,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4268조 343억 8957만</t>
+    <t>4344조 479억 3534만</t>
   </si>
   <si>
     <t>4</t>
@@ -338,7 +335,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2794조 5874억 3077만</t>
+    <t>2838조 8556억 6943만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +347,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2062조 5674억 3493만</t>
+    <t>2125조 1120억 4939만</t>
   </si>
   <si>
     <t>9</t>
@@ -374,7 +371,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>1576조 8511억 519만</t>
+    <t>1606조 9335억 6930만</t>
   </si>
   <si>
     <t>11</t>
@@ -401,49 +398,49 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
+    <t>1178조 4809억 5968만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1101조 795억 6833만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>972조 2153억 1957만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
     <t>110</t>
   </si>
   <si>
-    <t>1178조 4809억 5968만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1045조 9073억 3017만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>972조 2153억 1957만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>942조 6419억 6063만</t>
+    <t>971조 2607억 4284만</t>
   </si>
   <si>
     <t>16</t>
@@ -458,7 +455,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>925조 2980억 4556만</t>
+    <t>926조 4709억 657만</t>
   </si>
   <si>
     <t>17</t>
@@ -518,100 +515,100 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
+    <t>485조 354억 533만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>391조 5629억 3601만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>384조 814억 6223만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>356조 443억 1139만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
     <t>109</t>
   </si>
   <si>
-    <t>460조 1881억 9462만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>386조 4288억 9793만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>372조 6896억 8563만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>354조 6601억 9194만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>328조 1595억 1568만</t>
+    <t>329조 8887억 57만</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>240조 453억 6127만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>226조 9385억 6222만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>아르미느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>222조 5602억 4740만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>215조 3909억 7501만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>206조 9922억 631만</t>
+    <t>224조 7388억 729만</t>
   </si>
   <si>
     <t>29</t>
@@ -626,7 +623,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>194조 4027억 9180만</t>
+    <t>198조 8873억 6281만</t>
   </si>
   <si>
     <t>지존쫀파</t>
@@ -644,7 +641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>4151조 7828억 7756만</t>
+    <t>4158조 8546억 7008만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -653,7 +650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>3857조 9291억 1450만</t>
+    <t>3872조 369억 891만</t>
   </si>
   <si>
     <t>타개</t>
@@ -662,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2486조 9079억 1586만</t>
+    <t>2495조 7634억 7223만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -671,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2263조 1140억 8844만</t>
+    <t>2269조 2449억 6902만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -692,7 +689,16 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>1951조 5767억 8833만</t>
+    <t>2004조 2057억 1924만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1888조 3627억 818만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -701,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1738조 4296억 7283만</t>
+    <t>1739조 5479억 2768만</t>
   </si>
   <si>
     <t>뿡쓰</t>
@@ -710,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>1545조 4817억 4956만</t>
+    <t>1707조 2709억 6232만</t>
   </si>
   <si>
     <t>온백</t>
@@ -719,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1482조 8951억 781만</t>
+    <t>1491조 2311억 2507만</t>
   </si>
   <si>
     <t>파울</t>
@@ -728,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1419조 9260억 2582만</t>
+    <t>1425조 4762억 1692만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -740,15 +746,6 @@
     <t>1400조 9926억 8431만</t>
   </si>
   <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1395조 8897억 1304만</t>
-  </si>
-  <si>
     <t>마카롱롱</t>
   </si>
   <si>
@@ -773,7 +770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>971조 5267억 8902만</t>
+    <t>978조 3640억 5389만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -782,13 +779,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>952조 8262억 4047만</t>
+    <t>956조 6204억 8172만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>940조 3059억 3341만</t>
+    <t>951조 2060억 9725만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -842,7 +839,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>647조 9759억 4435만</t>
+    <t>671조 6340억 2972만</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>627조 8627억 9090만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -857,15 +863,6 @@
     <t>584조 3143억 9077만</t>
   </si>
   <si>
-    <t>Doham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Doham</t>
-  </si>
-  <si>
-    <t>562조 3497억 5522만</t>
-  </si>
-  <si>
     <t>태코찡</t>
   </si>
   <si>
@@ -914,7 +911,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%8C%9C</t>
   </si>
   <si>
-    <t>1경 2621조 8500억 3719만</t>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 3830조 247억 1451만</t>
   </si>
   <si>
     <t>빵녕</t>
@@ -929,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>7386조 3251억 3475만</t>
+    <t>7438조 93억 33만</t>
   </si>
   <si>
     <t>실프</t>
@@ -938,7 +938,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%ED%94%84</t>
   </si>
   <si>
-    <t>1036조 7000억 1875만</t>
+    <t>1103조 6547억 6039만</t>
+  </si>
+  <si>
+    <t>페레로로쉐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
+  </si>
+  <si>
+    <t>916조 3382억 84만</t>
   </si>
   <si>
     <t>냠늄</t>
@@ -950,15 +959,6 @@
     <t>914조 4728억 6800만</t>
   </si>
   <si>
-    <t>페레로로쉐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
-  </si>
-  <si>
-    <t>903조 3164억 5030만</t>
-  </si>
-  <si>
     <t>보호소</t>
   </si>
   <si>
@@ -983,7 +983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
   </si>
   <si>
-    <t>653조 5119억 7611만</t>
+    <t>682조 4662억 121만</t>
   </si>
   <si>
     <t>그복</t>
@@ -992,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
   </si>
   <si>
-    <t>610조 6680억 423만</t>
+    <t>627조 737억 1156만</t>
   </si>
   <si>
     <t>갈매기</t>
@@ -1037,7 +1037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
   </si>
   <si>
-    <t>404조 8443억 181만</t>
+    <t>406조 4561억 2332만</t>
   </si>
   <si>
     <t>꿀꿀이의모험</t>
@@ -1046,7 +1046,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
   </si>
   <si>
-    <t>397조 4887억 1580만</t>
+    <t>406조 2065억 2769만</t>
   </si>
   <si>
     <t>시루</t>
@@ -1064,7 +1064,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
   </si>
   <si>
-    <t>335조 291억 9859만</t>
+    <t>336조 3283억 9339만</t>
   </si>
   <si>
     <t>냥찐</t>
@@ -1082,7 +1082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>309조 839억 2801만</t>
+    <t>325조 2816억 7514만</t>
   </si>
   <si>
     <t>달디달고나</t>
@@ -1103,7 +1103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%99</t>
   </si>
   <si>
-    <t>191조 2004억 9982만</t>
+    <t>200조 5776억 5527만</t>
   </si>
   <si>
     <t>초코파베</t>
@@ -1112,7 +1112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
   </si>
   <si>
-    <t>181조 8114억 810만</t>
+    <t>185조 5073억 8187만</t>
   </si>
   <si>
     <t>취란</t>
@@ -1121,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
   </si>
   <si>
-    <t>164조 6094억 9117만</t>
+    <t>165조 1601억 7427만</t>
   </si>
   <si>
     <t>한굥굥</t>
@@ -1142,24 +1142,33 @@
     <t>154조 7796억 7587만</t>
   </si>
   <si>
+    <t>홀인원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%80%EC%9D%B8%EC%9B%90</t>
+  </si>
+  <si>
+    <t>135조 4559억 5225만</t>
+  </si>
+  <si>
     <t>해졍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
   </si>
   <si>
+    <t>111조 8873억 4670만</t>
+  </si>
+  <si>
+    <t>홍뎐잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
+  </si>
+  <si>
     <t>106</t>
   </si>
   <si>
-    <t>111조 8873억 4670만</t>
-  </si>
-  <si>
-    <t>홍뎐잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
-  </si>
-  <si>
     <t>108조 188억 1551만</t>
   </si>
   <si>
@@ -1175,6 +1184,9 @@
     <t>104조 3404억 5034만</t>
   </si>
   <si>
+    <t>31</t>
+  </si>
+  <si>
     <t>허숖</t>
   </si>
   <si>
@@ -1184,7 +1196,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>11조 3651억 6359만</t>
+    <t>11조 4978억 3358만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1199,7 +1211,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>4717조 132억 3526만</t>
+    <t>4746조 7562억 4321만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -1217,7 +1229,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>2365조 5050억 9154만</t>
+    <t>2968조 2308억 2418만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1226,7 +1238,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2290조 6260억 850만</t>
+    <t>2379조 5295억 2981만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1235,7 +1247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>1970조 805억 6214만</t>
+    <t>1977조 3594억 9418만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -1244,7 +1256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>1746조 878억 9551만</t>
+    <t>1754조 6437억 9937만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1271,7 +1283,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>1433조 1544억 4876만</t>
+    <t>1445조 1995억 5130만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1280,7 +1292,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1290조 7158억 985만</t>
+    <t>1356조 3577억 3624만</t>
+  </si>
+  <si>
+    <t>MangCI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
+  </si>
+  <si>
+    <t>1334조 2685억 2601만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1289,16 +1310,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>1264조 7840억 4564만</t>
-  </si>
-  <si>
-    <t>MangCI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
-  </si>
-  <si>
-    <t>1225조 1705억 7084만</t>
+    <t>1286조 4360억 672만</t>
+  </si>
+  <si>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1199조 399억 9927만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1316,16 +1337,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1141조 7336억 7187만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1064조 8130억 8425만</t>
+    <t>1149조 1869억 3725만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1334,7 +1346,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>916조 2790억 7128만</t>
+    <t>946조 8620억 7457만</t>
+  </si>
+  <si>
+    <t>모르페우스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>830조 3018억 68만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1355,22 +1376,13 @@
     <t>801조 7928억 6181만</t>
   </si>
   <si>
-    <t>모르페우스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>798조 1805억 5995만</t>
-  </si>
-  <si>
     <t>티에이치</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>758조 4177억 6625만</t>
+    <t>761조 7841억 1379만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1388,7 +1400,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>629조 871억 5026만</t>
+    <t>631조 1954억 4605만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1442,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>279조 240억 539만</t>
+    <t>282조 2989억 8387만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1469,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>3957조 457억 9506만</t>
+    <t>4182조 7913억 8419만</t>
   </si>
   <si>
     <t>미우맘</t>
@@ -1508,28 +1520,28 @@
     <t>2107조 2460억 3000만</t>
   </si>
   <si>
+    <t>명지동꿀주먹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
+  </si>
+  <si>
+    <t>1949조 4895억 5806만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
   </si>
   <si>
     <t>1926조 3126억 1612만</t>
   </si>
   <si>
-    <t>명지동꿀주먹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
-  </si>
-  <si>
-    <t>1896조 858억 7186만</t>
-  </si>
-  <si>
     <t>커튼월</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>1877조 135억 5251만</t>
+    <t>1884조 7907억 7354만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -1538,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
   </si>
   <si>
-    <t>1868조 4029억 725만</t>
+    <t>1869조 8018억 5318만</t>
   </si>
   <si>
     <t>천요화</t>
@@ -1574,7 +1586,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
   </si>
   <si>
-    <t>861조 4774억 5611만</t>
+    <t>898조 4126억 1299만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -1583,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>854조 6861억 572만</t>
+    <t>860조 6572억 7106만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -1592,7 +1604,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>751조 7302억 6614만</t>
+    <t>757조 5218억 2069만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>747조 1548억 2596만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -1610,16 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
   </si>
   <si>
-    <t>704조 9101억 2541만</t>
-  </si>
-  <si>
-    <t>스툭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
-  </si>
-  <si>
-    <t>689조 5155억 5815만</t>
+    <t>716조 622억 2087만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1628,7 +1640,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>619조 2760억 9659만</t>
+    <t>619조 6821억 9549만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>568조 6411억 7256만</t>
   </si>
   <si>
     <t>gorystal</t>
@@ -1637,16 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>563조 6969억 640만</t>
-  </si>
-  <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>562조 3032억 9117만</t>
+    <t>564조 6366억 6524만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1658,22 +1670,22 @@
     <t>524조 3731억 3025만</t>
   </si>
   <si>
+    <t>복룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>517조 3742억 8410만</t>
+  </si>
+  <si>
     <t>뀨꾸룽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
   </si>
   <si>
-    <t>496조 215억 2581만</t>
-  </si>
-  <si>
-    <t>복룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>491조 9289억 8094만</t>
+    <t>511조 2753억 9030만</t>
   </si>
   <si>
     <t>률율율</t>
@@ -1682,7 +1694,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>472조 2483억 5171만</t>
+    <t>504조 3146억 7645만</t>
   </si>
   <si>
     <t>짜상무</t>
@@ -1691,7 +1703,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
   </si>
   <si>
-    <t>437조 8805억 3207만</t>
+    <t>498조 3734억 6000만</t>
   </si>
   <si>
     <t>매리골드</t>
@@ -1709,7 +1721,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>329조 5045억 2043만</t>
+    <t>330조 9532억 1530만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1718,7 +1730,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>255조 6196억 5729만</t>
+    <t>255조 8046억 4107만</t>
   </si>
 </sst>
 </file>
@@ -2322,7 +2334,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2331,13 +2343,13 @@
         <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2375,28 +2387,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2407,28 +2419,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2439,28 +2451,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2471,28 +2483,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2503,28 +2515,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2535,28 +2547,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2567,28 +2579,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2599,28 +2611,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>103</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2631,28 +2643,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2663,28 +2675,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2695,28 +2707,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2727,28 +2739,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2759,28 +2771,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2791,28 +2803,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2823,28 +2835,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2855,28 +2867,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2887,7 +2899,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>23</v>
@@ -2896,19 +2908,19 @@
         <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2919,28 +2931,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2951,28 +2963,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2983,28 +2995,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3015,28 +3027,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3047,28 +3059,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3079,28 +3091,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3111,28 +3123,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3143,28 +3155,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3175,28 +3187,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3207,28 +3219,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3239,28 +3251,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3271,28 +3283,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3303,28 +3315,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3387,28 +3399,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3419,28 +3431,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3451,28 +3463,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3483,28 +3495,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3515,28 +3527,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3547,28 +3559,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3579,28 +3591,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3611,28 +3623,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3643,28 +3655,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3675,28 +3687,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3707,28 +3719,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>230</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3739,28 +3751,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3771,28 +3783,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3803,28 +3815,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3835,28 +3847,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>242</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3867,28 +3879,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3899,28 +3911,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3931,28 +3943,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3963,7 +3975,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>33</v>
@@ -3972,19 +3984,19 @@
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3995,28 +4007,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>256</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4027,28 +4039,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4059,28 +4071,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>262</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4091,28 +4103,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4123,28 +4135,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4155,28 +4167,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4187,28 +4199,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4219,28 +4231,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="H27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4251,28 +4263,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4283,28 +4295,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4315,28 +4327,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4347,28 +4359,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4414,7 +4426,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4423,7 +4435,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4432,28 +4444,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4464,25 +4476,25 @@
         <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>295</v>
@@ -4496,7 +4508,7 @@
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>296</v>
@@ -4508,13 +4520,13 @@
         <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>298</v>
@@ -4528,7 +4540,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>41</v>
@@ -4540,13 +4552,13 @@
         <v>299</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>300</v>
@@ -4560,7 +4572,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>301</v>
@@ -4572,13 +4584,13 @@
         <v>302</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>303</v>
@@ -4592,7 +4604,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>304</v>
@@ -4604,13 +4616,13 @@
         <v>305</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>306</v>
@@ -4624,7 +4636,7 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>307</v>
@@ -4636,13 +4648,13 @@
         <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>309</v>
@@ -4656,7 +4668,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>310</v>
@@ -4668,13 +4680,13 @@
         <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>312</v>
@@ -4688,7 +4700,7 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>313</v>
@@ -4700,13 +4712,13 @@
         <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>315</v>
@@ -4720,7 +4732,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>316</v>
@@ -4732,13 +4744,13 @@
         <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>318</v>
@@ -4752,7 +4764,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>319</v>
@@ -4764,13 +4776,13 @@
         <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>321</v>
@@ -4784,7 +4796,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>322</v>
@@ -4796,13 +4808,13 @@
         <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>324</v>
@@ -4816,7 +4828,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>325</v>
@@ -4828,13 +4840,13 @@
         <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>327</v>
@@ -4848,7 +4860,7 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>328</v>
@@ -4860,13 +4872,13 @@
         <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>330</v>
@@ -4880,7 +4892,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>331</v>
@@ -4892,13 +4904,13 @@
         <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>333</v>
@@ -4912,7 +4924,7 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>334</v>
@@ -4924,13 +4936,13 @@
         <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>336</v>
@@ -4944,7 +4956,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>337</v>
@@ -4956,13 +4968,13 @@
         <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>339</v>
@@ -4976,7 +4988,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>340</v>
@@ -4988,13 +5000,13 @@
         <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>342</v>
@@ -5008,7 +5020,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>343</v>
@@ -5020,13 +5032,13 @@
         <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>345</v>
@@ -5040,7 +5052,7 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>346</v>
@@ -5052,13 +5064,13 @@
         <v>347</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>348</v>
@@ -5072,7 +5084,7 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>349</v>
@@ -5084,13 +5096,13 @@
         <v>350</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>351</v>
@@ -5104,7 +5116,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>352</v>
@@ -5116,10 +5128,10 @@
         <v>353</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>354</v>
@@ -5136,7 +5148,7 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>356</v>
@@ -5148,10 +5160,10 @@
         <v>357</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>354</v>
@@ -5168,7 +5180,7 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>359</v>
@@ -5180,10 +5192,10 @@
         <v>360</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>354</v>
@@ -5200,7 +5212,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>362</v>
@@ -5212,10 +5224,10 @@
         <v>363</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>354</v>
@@ -5232,7 +5244,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>365</v>
@@ -5244,13 +5256,13 @@
         <v>366</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>367</v>
@@ -5264,7 +5276,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>368</v>
@@ -5276,10 +5288,10 @@
         <v>369</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>354</v>
@@ -5296,7 +5308,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>371</v>
@@ -5308,16 +5320,16 @@
         <v>372</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5328,28 +5340,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5360,28 +5372,28 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5392,35 +5404,67 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="C32" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J32"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5452,6 +5496,7 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
+    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5477,28 +5522,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5509,28 +5554,28 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5541,7 +5586,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>49</v>
@@ -5550,19 +5595,19 @@
         <v>49</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5573,28 +5618,28 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5605,28 +5650,28 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5637,28 +5682,28 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5669,28 +5714,28 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5701,28 +5746,28 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5733,28 +5778,28 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5765,28 +5810,28 @@
         <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5797,28 +5842,28 @@
         <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5829,28 +5874,28 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5861,28 +5906,28 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>220</v>
+        <v>81</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5893,28 +5938,28 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5925,28 +5970,28 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5957,28 +6002,28 @@
         <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5989,28 +6034,28 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6021,28 +6066,28 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6053,28 +6098,28 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6085,28 +6130,28 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6117,28 +6162,28 @@
         <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6149,28 +6194,28 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6181,28 +6226,28 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6213,28 +6258,28 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6245,28 +6290,28 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6277,28 +6322,28 @@
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6309,28 +6354,28 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6341,28 +6386,28 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6373,28 +6418,28 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6405,28 +6450,28 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6437,28 +6482,28 @@
         <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6522,28 +6567,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6554,28 +6599,28 @@
         <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6586,28 +6631,28 @@
         <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6618,28 +6663,28 @@
         <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6650,28 +6695,28 @@
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6682,28 +6727,28 @@
         <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6714,28 +6759,28 @@
         <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6746,28 +6791,28 @@
         <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>497</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>497</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6778,28 +6823,28 @@
         <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>495</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>495</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6810,28 +6855,28 @@
         <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6842,28 +6887,28 @@
         <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6874,28 +6919,28 @@
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6906,28 +6951,28 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6938,28 +6983,28 @@
         <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6970,28 +7015,28 @@
         <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7002,28 +7047,28 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7034,28 +7079,28 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7066,28 +7111,28 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7098,28 +7143,28 @@
         <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>220</v>
+        <v>118</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7130,28 +7175,28 @@
         <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>219</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7162,28 +7207,28 @@
         <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7194,28 +7239,28 @@
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7226,28 +7271,28 @@
         <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7258,28 +7303,28 @@
         <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7290,28 +7335,28 @@
         <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7322,28 +7367,28 @@
         <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7354,28 +7399,28 @@
         <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7386,28 +7431,28 @@
         <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7418,28 +7463,28 @@
         <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7450,28 +7495,28 @@
         <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7482,28 +7527,28 @@
         <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -10,15 +10,15 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="지존길드" sheetId="3" r:id="rId3"/>
-    <sheet name="버번" sheetId="4" r:id="rId4"/>
-    <sheet name="눈별" sheetId="5" r:id="rId5"/>
+    <sheet name="눈별" sheetId="4" r:id="rId4"/>
+    <sheet name="버번" sheetId="5" r:id="rId5"/>
     <sheet name="TopOfTop" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TopOfTop!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">버번!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">눈별!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">버번!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>428</t>
+    <t>426</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>4경 9478조 6064억 3410만</t>
+    <t>5경 26조 6494억 6590만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.19</t>
+    <t>2026.09.20</t>
   </si>
   <si>
     <t>지존길드</t>
@@ -113,7 +113,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>440</t>
+    <t>437</t>
   </si>
   <si>
     <t>11위</t>
@@ -122,7 +122,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>4경 6445조 2840억 90만</t>
+    <t>4경 7116조 5949억 2207만</t>
   </si>
   <si>
     <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
@@ -131,6 +131,30 @@
     <t>지존순찌</t>
   </si>
   <si>
+    <t>눈별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>9위</t>
+  </si>
+  <si>
+    <t>4경 4475조 8641억 4634만</t>
+  </si>
+  <si>
+    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
+  </si>
+  <si>
+    <t>심신삐약자</t>
+  </si>
+  <si>
     <t>버번</t>
   </si>
   <si>
@@ -140,13 +164,13 @@
     <t>Scania 1</t>
   </si>
   <si>
-    <t>464</t>
+    <t>461</t>
   </si>
   <si>
     <t>29위</t>
   </si>
   <si>
-    <t>4경 1205조 5828억 6809만</t>
+    <t>4경 1489조 52억 895만</t>
   </si>
   <si>
     <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
@@ -155,30 +179,6 @@
     <t>망충둘기</t>
   </si>
   <si>
-    <t>눈별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>450</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>4경 3461조 3653억 7046만</t>
-  </si>
-  <si>
-    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
-  </si>
-  <si>
-    <t>심신삐약자</t>
-  </si>
-  <si>
     <t>TopOfTop</t>
   </si>
   <si>
@@ -188,10 +188,10 @@
     <t>Scania 18</t>
   </si>
   <si>
-    <t>456</t>
-  </si>
-  <si>
-    <t>4경 2296조 1640억 9507만</t>
+    <t>454</t>
+  </si>
+  <si>
+    <t>4경 2489조 52억 6614만</t>
   </si>
   <si>
     <t>길컨 1등만</t>
@@ -242,7 +242,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8570조 3175억 8447만</t>
+    <t>8574조 1501억 5135만</t>
   </si>
   <si>
     <t>2</t>
@@ -275,7 +275,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4344조 479억 3534만</t>
+    <t>4349조 3566억 3215만</t>
   </si>
   <si>
     <t>4</t>
@@ -305,7 +305,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>3334조 8639억 6043만</t>
+    <t>3437조 4377억 392만</t>
   </si>
   <si>
     <t>6</t>
@@ -335,7 +335,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2838조 8556억 6943만</t>
+    <t>2839조 1366억 4961만</t>
   </si>
   <si>
     <t>8</t>
@@ -347,31 +347,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2125조 1120억 4939만</t>
+    <t>2125조 3498억 9185만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>1912조 9606억 5811만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>KR#TAKIN9CP37</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1738조 4910억 368만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>1606조 9335억 6930만</t>
+    <t>1808조 1569억 2798만</t>
   </si>
   <si>
     <t>11</t>
@@ -413,7 +413,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1101조 795억 6833만</t>
+    <t>1102조 6798억 2352만</t>
   </si>
   <si>
     <t>14</t>
@@ -515,7 +515,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>485조 354억 533만</t>
+    <t>486조 5354억 4811만</t>
   </si>
   <si>
     <t>22</t>
@@ -527,7 +527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>391조 5629억 3601만</t>
+    <t>398조 4483억 503만</t>
   </si>
   <si>
     <t>23</t>
@@ -545,6 +545,21 @@
     <t>24</t>
   </si>
   <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>380조 192억 2246만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>솔인</t>
   </si>
   <si>
@@ -557,21 +572,6 @@
     <t>356조 443억 1139만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>329조 8887억 57만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -641,7 +641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>4158조 8546억 7008만</t>
+    <t>4245조 3598억 1665만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -650,7 +650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>3872조 369억 891만</t>
+    <t>4022조 9259억 9763만</t>
   </si>
   <si>
     <t>타개</t>
@@ -659,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2495조 7634억 7223만</t>
+    <t>2546조 9231억 8482만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -668,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2269조 2449억 6902만</t>
+    <t>2275조 975억 942만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -689,7 +689,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>2004조 2057억 1924만</t>
+    <t>2083조 2761억 2150만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -701,22 +701,22 @@
     <t>1888조 3627억 818만</t>
   </si>
   <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>1799조 246억 9846만</t>
+  </si>
+  <si>
     <t>댜니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1739조 5479억 2768만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>1707조 2709억 6232만</t>
+    <t>1757조 1363억 1880만</t>
   </si>
   <si>
     <t>온백</t>
@@ -725,7 +725,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1491조 2311억 2507만</t>
+    <t>1491조 3442억 3139만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>1483조 2810억 4011만</t>
   </si>
   <si>
     <t>파울</t>
@@ -734,16 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1425조 4762억 1692만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>1400조 9926억 8431만</t>
+    <t>1431조 346억 5059만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -752,7 +752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1391조 2010억 3776만</t>
+    <t>1426조 665억 2214만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -761,7 +761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
   </si>
   <si>
-    <t>1027조 6078억 1748만</t>
+    <t>1052조 292억 883만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -770,7 +770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>978조 3640억 5389만</t>
+    <t>978조 7832억 9889만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -785,7 +785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>951조 2060억 9725만</t>
+    <t>953조 6362억 3238만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -794,7 +794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>882조 7278억 5282만</t>
+    <t>916조 5073억 5513만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -848,7 +848,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>627조 8627억 9090만</t>
+    <t>628조 6146억 917만</t>
   </si>
   <si>
     <t>고숨도칭</t>
@@ -869,7 +869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>547조 9327억 8104만</t>
+    <t>548조 5072억 4464만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -881,7 +881,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>482조 8831억 8288만</t>
+    <t>486조 1731억 5041만</t>
   </si>
   <si>
     <t>진성팔퀴</t>
@@ -905,6 +905,273 @@
     <t>277조 36억 4103만</t>
   </si>
   <si>
+    <t>우니아파요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>5708조 2885억 4200만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
+  </si>
+  <si>
+    <t>4771조 5982억 458만</t>
+  </si>
+  <si>
+    <t>도하리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>3087조 4263억 7700만</t>
+  </si>
+  <si>
+    <t>죽창당일개통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
+  </si>
+  <si>
+    <t>2968조 2308억 2418만</t>
+  </si>
+  <si>
+    <t>유수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>2381조 5061억 1898만</t>
+  </si>
+  <si>
+    <t>종꿀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
+  </si>
+  <si>
+    <t>1978조 3473억 4408만</t>
+  </si>
+  <si>
+    <t>이용하다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1926조 9793억 4211만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1846조 1184억 4836만</t>
+  </si>
+  <si>
+    <t>해달잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
+  </si>
+  <si>
+    <t>1745조 1553억 5425만</t>
+  </si>
+  <si>
+    <t>세월이야속해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1492조 6491억 5005만</t>
+  </si>
+  <si>
+    <t>포빅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
+  </si>
+  <si>
+    <t>1491조 4503억 8083만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>1447조 7356억 830만</t>
+  </si>
+  <si>
+    <t>MangCI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
+  </si>
+  <si>
+    <t>1334조 2685억 2601만</t>
+  </si>
+  <si>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1199조 399억 9927만</t>
+  </si>
+  <si>
+    <t>여자둘남자둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
+  </si>
+  <si>
+    <t>1189조 5969억 2961만</t>
+  </si>
+  <si>
+    <t>덩개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>1159조 4581억 2176만</t>
+  </si>
+  <si>
+    <t>예타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
+  </si>
+  <si>
+    <t>961조 606억 439만</t>
+  </si>
+  <si>
+    <t>모르페우스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>851조 6091억 6378만</t>
+  </si>
+  <si>
+    <t>티에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>812조 9149억 5760만</t>
+  </si>
+  <si>
+    <t>파이리양말</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
+  </si>
+  <si>
+    <t>811조 6711억 3670만</t>
+  </si>
+  <si>
+    <t>박금쪽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
+  </si>
+  <si>
+    <t>801조 7928억 6181만</t>
+  </si>
+  <si>
+    <t>성률</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
+  </si>
+  <si>
+    <t>688조 5062억 3265만</t>
+  </si>
+  <si>
+    <t>지존짱창남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
+  </si>
+  <si>
+    <t>674조 9889억 4718만</t>
+  </si>
+  <si>
+    <t>히어로호걸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
+  </si>
+  <si>
+    <t>606조 6653억 7985만</t>
+  </si>
+  <si>
+    <t>작업치료사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
+  </si>
+  <si>
+    <t>605조 2191억 6874만</t>
+  </si>
+  <si>
+    <t>계니규니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>547조 8506억 7422만</t>
+  </si>
+  <si>
+    <t>감화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
+  </si>
+  <si>
+    <t>529조 2335억 1065만</t>
+  </si>
+  <si>
+    <t>하비엔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
+  </si>
+  <si>
+    <t>330조 1725억 5296만</t>
+  </si>
+  <si>
+    <t>채구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>282조 2989억 8387만</t>
+  </si>
+  <si>
+    <t>신탄보우짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>244조 307억 43만</t>
+  </si>
+  <si>
     <t>강댜</t>
   </si>
   <si>
@@ -914,7 +1181,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 3830조 247억 1451만</t>
+    <t>1경 3840조 9768억 1685만</t>
   </si>
   <si>
     <t>빵녕</t>
@@ -929,7 +1196,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>7438조 93억 33만</t>
+    <t>7547조 4204억 8633만</t>
   </si>
   <si>
     <t>실프</t>
@@ -938,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%ED%94%84</t>
   </si>
   <si>
-    <t>1103조 6547억 6039만</t>
+    <t>1143조 8935억 713만</t>
   </si>
   <si>
     <t>페레로로쉐</t>
@@ -947,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
   </si>
   <si>
-    <t>916조 3382억 84만</t>
+    <t>919조 4048억 2542만</t>
   </si>
   <si>
     <t>냠늄</t>
@@ -992,7 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
   </si>
   <si>
-    <t>627조 737억 1156만</t>
+    <t>628조 524억 102만</t>
   </si>
   <si>
     <t>갈매기</t>
@@ -1019,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
   </si>
   <si>
-    <t>495조 9027억 7374만</t>
+    <t>503조 4047억 6153만</t>
   </si>
   <si>
     <t>주사고모</t>
@@ -1031,22 +1298,22 @@
     <t>484조 4320억 4123만</t>
   </si>
   <si>
+    <t>꿀꿀이의모험</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
+  </si>
+  <si>
+    <t>429조 425억 426만</t>
+  </si>
+  <si>
     <t>사랑해제명</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
   </si>
   <si>
-    <t>406조 4561억 2332만</t>
-  </si>
-  <si>
-    <t>꿀꿀이의모험</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
-  </si>
-  <si>
-    <t>406조 2065억 2769만</t>
+    <t>415조 618억 657만</t>
   </si>
   <si>
     <t>시루</t>
@@ -1055,7 +1322,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
   </si>
   <si>
-    <t>350조 2268억 4588만</t>
+    <t>364조 9169억 9552만</t>
+  </si>
+  <si>
+    <t>냥찐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
+  </si>
+  <si>
+    <t>359조 1007억 5265만</t>
   </si>
   <si>
     <t>퍄딤</t>
@@ -1064,16 +1340,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
   </si>
   <si>
-    <t>336조 3283억 9339만</t>
-  </si>
-  <si>
-    <t>냥찐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
-  </si>
-  <si>
-    <t>327조 9016억 7369만</t>
+    <t>348조 3483억 1470만</t>
   </si>
   <si>
     <t>환불스토리</t>
@@ -1082,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>325조 2816억 7514만</t>
+    <t>325조 7409억 9992만</t>
   </si>
   <si>
     <t>달디달고나</t>
@@ -1112,7 +1379,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
   </si>
   <si>
-    <t>185조 5073억 8187만</t>
+    <t>191조 7879억 146만</t>
   </si>
   <si>
     <t>취란</t>
@@ -1121,7 +1388,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
   </si>
   <si>
-    <t>165조 1601억 7427만</t>
+    <t>165조 2717억 4130만</t>
   </si>
   <si>
     <t>한굥굥</t>
@@ -1139,7 +1406,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%A5%98</t>
   </si>
   <si>
-    <t>154조 7796억 7587만</t>
+    <t>157조 503억 5410만</t>
   </si>
   <si>
     <t>홀인원</t>
@@ -1148,7 +1415,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%80%EC%9D%B8%EC%9B%90</t>
   </si>
   <si>
-    <t>135조 4559억 5225만</t>
+    <t>141조 7362억 8379만</t>
   </si>
   <si>
     <t>해졍</t>
@@ -1157,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
   </si>
   <si>
-    <t>111조 8873억 4670만</t>
+    <t>113조 231억 4593만</t>
   </si>
   <si>
     <t>홍뎐잉</t>
@@ -1169,7 +1436,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>108조 188억 1551만</t>
+    <t>110조 113억 8431만</t>
   </si>
   <si>
     <t>꾸륭</t>
@@ -1196,274 +1463,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>11조 4978억 3358만</t>
-  </si>
-  <si>
-    <t>우니아파요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>5708조 2885억 4200만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
-  </si>
-  <si>
-    <t>4746조 7562억 4321만</t>
-  </si>
-  <si>
-    <t>도하리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>3087조 4263억 7700만</t>
-  </si>
-  <si>
-    <t>죽창당일개통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
-  </si>
-  <si>
-    <t>2968조 2308억 2418만</t>
-  </si>
-  <si>
-    <t>유수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>2379조 5295억 2981만</t>
-  </si>
-  <si>
-    <t>종꿀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
-  </si>
-  <si>
-    <t>1977조 3594억 9418만</t>
-  </si>
-  <si>
-    <t>이용하다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1754조 6437억 9937만</t>
-  </si>
-  <si>
-    <t>해달잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1745조 1553억 5425만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1609조 611억 3837만</t>
-  </si>
-  <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1445조 1995억 5130만</t>
-  </si>
-  <si>
-    <t>세월이야속해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1356조 3577억 3624만</t>
-  </si>
-  <si>
-    <t>MangCI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
-  </si>
-  <si>
-    <t>1334조 2685억 2601만</t>
-  </si>
-  <si>
-    <t>포빅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
-  </si>
-  <si>
-    <t>1286조 4360억 672만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1199조 399억 9927만</t>
-  </si>
-  <si>
-    <t>덩개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>1158조 2062억 32만</t>
-  </si>
-  <si>
-    <t>여자둘남자둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
-  </si>
-  <si>
-    <t>1149조 1869억 3725만</t>
-  </si>
-  <si>
-    <t>예타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
-  </si>
-  <si>
-    <t>946조 8620억 7457만</t>
-  </si>
-  <si>
-    <t>모르페우스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>830조 3018억 68만</t>
-  </si>
-  <si>
-    <t>파이리양말</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
-  </si>
-  <si>
-    <t>811조 6711억 3670만</t>
-  </si>
-  <si>
-    <t>박금쪽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
-  </si>
-  <si>
-    <t>801조 7928억 6181만</t>
-  </si>
-  <si>
-    <t>티에이치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
-  </si>
-  <si>
-    <t>761조 7841억 1379만</t>
-  </si>
-  <si>
-    <t>지존짱창남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
-  </si>
-  <si>
-    <t>674조 9889억 4718만</t>
-  </si>
-  <si>
-    <t>성률</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
-  </si>
-  <si>
-    <t>631조 1954억 4605만</t>
-  </si>
-  <si>
-    <t>작업치료사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
-  </si>
-  <si>
-    <t>605조 2191억 6874만</t>
-  </si>
-  <si>
-    <t>히어로호걸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
-  </si>
-  <si>
-    <t>599조 5583억 4223만</t>
-  </si>
-  <si>
-    <t>감화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
-  </si>
-  <si>
-    <t>529조 2335억 1065만</t>
-  </si>
-  <si>
-    <t>계니규니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>512조 4058억 7504만</t>
-  </si>
-  <si>
-    <t>하비엔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
-  </si>
-  <si>
-    <t>330조 1725억 5296만</t>
-  </si>
-  <si>
-    <t>채구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>282조 2989억 8387만</t>
-  </si>
-  <si>
-    <t>신탄보우짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>238조 7342억 9660만</t>
+    <t>13조 8819억 7932만</t>
   </si>
   <si>
     <t>가겠습니다</t>
@@ -1481,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4182조 7913억 8419만</t>
+    <t>4190조 9975억 7541만</t>
   </si>
   <si>
     <t>미우맘</t>
@@ -1541,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>1884조 7907억 7354만</t>
+    <t>1897조 3925억 3200만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -1550,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
   </si>
   <si>
-    <t>1869조 8018억 5318만</t>
+    <t>1895조 8505억 4682만</t>
   </si>
   <si>
     <t>천요화</t>
@@ -1577,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>981조 9247억 4194만</t>
+    <t>1002조 9805억 4140만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -1595,7 +1595,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>860조 6572억 7106만</t>
+    <t>869조 4751억 4407만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>799조 5093억 9199만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -1604,16 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>757조 5218억 2069만</t>
-  </si>
-  <si>
-    <t>스툭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
-  </si>
-  <si>
-    <t>747조 1548억 2596만</t>
+    <t>759조 8540억 2464만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -1622,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
   </si>
   <si>
-    <t>741조 9354억 8078만</t>
+    <t>749조 9013억 1505만</t>
   </si>
   <si>
     <t>양룽</t>
@@ -1631,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
   </si>
   <si>
-    <t>716조 622억 2087만</t>
+    <t>717조 1021억 8764만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>619조 6821억 9549만</t>
+    <t>624조 5956억 2794만</t>
   </si>
   <si>
     <t>욧츠</t>
@@ -1676,7 +1676,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>517조 3742억 8410만</t>
+    <t>523조 6569억 9026만</t>
+  </si>
+  <si>
+    <t>률율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>516조 8300억 4193만</t>
   </si>
   <si>
     <t>뀨꾸룽</t>
@@ -1685,16 +1694,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
   </si>
   <si>
-    <t>511조 2753억 9030만</t>
-  </si>
-  <si>
-    <t>률율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>504조 3146억 7645만</t>
+    <t>512조 7290억 8972만</t>
   </si>
   <si>
     <t>짜상무</t>
@@ -1721,7 +1721,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>330조 9532억 1530만</t>
+    <t>337조 1066억 1385만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1730,7 +1730,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>255조 8046억 4107만</t>
+    <t>276조 9043억 2328만</t>
   </si>
 </sst>
 </file>
@@ -2334,7 +2334,7 @@
         <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2690,7 +2690,7 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>101</v>
@@ -2722,7 +2722,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>101</v>
@@ -3170,7 +3170,7 @@
         <v>68</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>174</v>
@@ -3202,7 +3202,7 @@
         <v>68</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>179</v>
@@ -3237,7 +3237,7 @@
         <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>184</v>
@@ -3269,7 +3269,7 @@
         <v>188</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>189</v>
@@ -3301,7 +3301,7 @@
         <v>69</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>193</v>
@@ -3333,7 +3333,7 @@
         <v>197</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>198</v>
@@ -3702,10 +3702,10 @@
         <v>68</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>226</v>
@@ -3734,10 +3734,10 @@
         <v>68</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>229</v>
@@ -3798,10 +3798,10 @@
         <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>235</v>
@@ -3830,10 +3830,10 @@
         <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>238</v>
@@ -4185,7 +4185,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>270</v>
@@ -4249,7 +4249,7 @@
         <v>276</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>277</v>
@@ -4345,7 +4345,7 @@
         <v>276</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>287</v>
@@ -4377,7 +4377,7 @@
         <v>188</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>291</v>
@@ -4426,6 +4426,1051 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J31"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -4435,7 +5480,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4473,19 +5518,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>292</v>
+        <v>381</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>292</v>
+        <v>381</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
+        <v>382</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>68</v>
@@ -4494,10 +5539,10 @@
         <v>75</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>294</v>
+        <v>383</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4505,19 +5550,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>296</v>
+        <v>385</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>296</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>297</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>68</v>
@@ -4529,7 +5574,7 @@
         <v>86</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>298</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4537,19 +5582,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>299</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>140</v>
@@ -4561,7 +5606,7 @@
         <v>86</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>300</v>
+        <v>389</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4569,19 +5614,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>390</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>391</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>68</v>
@@ -4593,7 +5638,7 @@
         <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>303</v>
+        <v>392</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4601,19 +5646,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>393</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>393</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>68</v>
@@ -4625,7 +5670,7 @@
         <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>395</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4633,19 +5678,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>308</v>
+        <v>397</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>68</v>
@@ -4657,7 +5702,7 @@
         <v>136</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>309</v>
+        <v>398</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4665,19 +5710,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>399</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -4689,7 +5734,7 @@
         <v>136</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>401</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4697,19 +5742,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>402</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>68</v>
@@ -4721,7 +5766,7 @@
         <v>96</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>404</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4729,19 +5774,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>405</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>405</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>406</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>68</v>
@@ -4753,7 +5798,7 @@
         <v>96</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>407</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4761,19 +5806,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>408</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>408</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>409</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>68</v>
@@ -4782,10 +5827,10 @@
         <v>75</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>410</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4793,19 +5838,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>411</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>323</v>
+        <v>412</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>68</v>
@@ -4814,10 +5859,10 @@
         <v>75</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>413</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4825,19 +5870,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>68</v>
@@ -4846,10 +5891,10 @@
         <v>141</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>416</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4857,19 +5902,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>417</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>418</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>68</v>
@@ -4878,10 +5923,10 @@
         <v>219</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>419</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4889,19 +5934,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>420</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>420</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>421</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>68</v>
@@ -4910,10 +5955,10 @@
         <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>422</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4921,31 +5966,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4953,31 +5998,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>138</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>426</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>426</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4985,19 +6030,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>68</v>
@@ -5006,10 +6051,10 @@
         <v>75</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>342</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5017,19 +6062,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>68</v>
@@ -5038,10 +6083,10 @@
         <v>75</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>434</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5049,19 +6094,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>435</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>435</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>436</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>68</v>
@@ -5070,10 +6115,10 @@
         <v>75</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>437</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5081,19 +6126,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>155</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>438</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>68</v>
@@ -5102,10 +6147,10 @@
         <v>141</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>440</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5113,19 +6158,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>159</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>441</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>353</v>
+        <v>442</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>68</v>
@@ -5134,10 +6179,10 @@
         <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5145,19 +6190,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>163</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>356</v>
+        <v>445</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>356</v>
+        <v>445</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>357</v>
+        <v>446</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>68</v>
@@ -5166,10 +6211,10 @@
         <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>358</v>
+        <v>447</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5177,19 +6222,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>359</v>
+        <v>448</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>360</v>
+        <v>449</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>68</v>
@@ -5198,10 +6243,10 @@
         <v>197</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>361</v>
+        <v>450</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5209,19 +6254,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>171</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>362</v>
+        <v>451</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>362</v>
+        <v>451</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>363</v>
+        <v>452</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>68</v>
@@ -5230,10 +6275,10 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>364</v>
+        <v>453</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5241,19 +6286,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>365</v>
+        <v>454</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>365</v>
+        <v>454</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>366</v>
+        <v>455</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>68</v>
@@ -5265,7 +6310,7 @@
         <v>174</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>367</v>
+        <v>456</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5273,19 +6318,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>368</v>
+        <v>457</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>368</v>
+        <v>457</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>369</v>
+        <v>458</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>68</v>
@@ -5294,10 +6339,10 @@
         <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>370</v>
+        <v>459</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5305,19 +6350,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>371</v>
+        <v>460</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>371</v>
+        <v>460</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>372</v>
+        <v>461</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>68</v>
@@ -5326,10 +6371,10 @@
         <v>75</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>373</v>
+        <v>462</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5337,19 +6382,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>374</v>
+        <v>463</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>375</v>
+        <v>464</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>68</v>
@@ -5358,10 +6403,10 @@
         <v>81</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>376</v>
+        <v>465</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5369,19 +6414,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>377</v>
+        <v>466</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>377</v>
+        <v>466</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>378</v>
+        <v>467</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>68</v>
@@ -5390,10 +6435,10 @@
         <v>75</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>379</v>
+        <v>468</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>380</v>
+        <v>469</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5401,19 +6446,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>288</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>381</v>
+        <v>470</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>381</v>
+        <v>470</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>382</v>
+        <v>471</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>68</v>
@@ -5422,10 +6467,10 @@
         <v>141</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>383</v>
+        <v>472</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>384</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5433,19 +6478,19 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>385</v>
+        <v>474</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>387</v>
+        <v>476</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>68</v>
@@ -5454,10 +6499,10 @@
         <v>75</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>388</v>
+        <v>477</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>24</v>
@@ -5502,1051 +6547,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J31"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -7094,10 +7094,10 @@
         <v>68</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>197</v>
+        <v>75</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>525</v>
@@ -7126,10 +7126,10 @@
         <v>68</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>197</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>528</v>
@@ -7161,7 +7161,7 @@
         <v>118</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>531</v>
@@ -7321,7 +7321,7 @@
         <v>75</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>546</v>
@@ -7353,7 +7353,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>549</v>
@@ -7385,7 +7385,7 @@
         <v>75</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>552</v>
@@ -7417,7 +7417,7 @@
         <v>75</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>179</v>
+        <v>96</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>555</v>
@@ -7449,7 +7449,7 @@
         <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>558</v>
@@ -7481,7 +7481,7 @@
         <v>283</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>561</v>
@@ -7545,7 +7545,7 @@
         <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>567</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -10,15 +10,15 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="지존길드" sheetId="3" r:id="rId3"/>
-    <sheet name="눈별" sheetId="4" r:id="rId4"/>
-    <sheet name="버번" sheetId="5" r:id="rId5"/>
+    <sheet name="버번" sheetId="4" r:id="rId4"/>
+    <sheet name="눈별" sheetId="5" r:id="rId5"/>
     <sheet name="TopOfTop" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TopOfTop!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">버번!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">버번!$A$1:$J$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="569">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>426</t>
+    <t>423</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>5경 26조 6494억 6590만</t>
+    <t>5경 977조 6346억 6184만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,34 +101,61 @@
     <t>자유이용껀</t>
   </si>
   <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
+    <t>지존길드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>11위</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 7116조 5949억 2207만</t>
+  </si>
+  <si>
+    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
+  </si>
+  <si>
+    <t>지존순찌</t>
+  </si>
+  <si>
     <t>2026.09.20</t>
   </si>
   <si>
-    <t>지존길드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 4</t>
-  </si>
-  <si>
-    <t>437</t>
-  </si>
-  <si>
-    <t>11위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>4경 7116조 5949억 2207만</t>
-  </si>
-  <si>
-    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
-  </si>
-  <si>
-    <t>지존순찌</t>
+    <t>버번</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B2%84%EB%B2%88</t>
+  </si>
+  <si>
+    <t>Scania 1</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>28위</t>
+  </si>
+  <si>
+    <t>4경 2148조 2775억 4593만</t>
+  </si>
+  <si>
+    <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
+  </si>
+  <si>
+    <t>망충둘기</t>
   </si>
   <si>
     <t>눈별</t>
@@ -140,7 +167,7 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>445</t>
+    <t>446</t>
   </si>
   <si>
     <t>9위</t>
@@ -155,30 +182,6 @@
     <t>심신삐약자</t>
   </si>
   <si>
-    <t>버번</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B2%84%EB%B2%88</t>
-  </si>
-  <si>
-    <t>Scania 1</t>
-  </si>
-  <si>
-    <t>461</t>
-  </si>
-  <si>
-    <t>29위</t>
-  </si>
-  <si>
-    <t>4경 1489조 52억 895만</t>
-  </si>
-  <si>
-    <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
-  </si>
-  <si>
-    <t>망충둘기</t>
-  </si>
-  <si>
     <t>TopOfTop</t>
   </si>
   <si>
@@ -260,7 +263,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>5571조 2990억 750만</t>
+    <t>5653조 5717억 7457만</t>
   </si>
   <si>
     <t>3</t>
@@ -275,7 +278,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4349조 3566억 3215만</t>
+    <t>4372조 5502억 487만</t>
   </si>
   <si>
     <t>4</t>
@@ -305,7 +308,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>3437조 4377억 392만</t>
+    <t>3457조 1738억 2160만</t>
   </si>
   <si>
     <t>6</t>
@@ -320,7 +323,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>3314조 3423억 3688만</t>
+    <t>3449조 7647억 9983만</t>
   </si>
   <si>
     <t>7</t>
@@ -335,7 +338,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2839조 1366억 4961만</t>
+    <t>2874조 2412억 858만</t>
   </si>
   <si>
     <t>8</t>
@@ -347,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2125조 3498억 9185만</t>
+    <t>2221조 522억 2603만</t>
   </si>
   <si>
     <t>9</t>
@@ -359,7 +362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>1912조 9606억 5811만</t>
+    <t>2148조 2115억 8443만</t>
   </si>
   <si>
     <t>10</t>
@@ -371,7 +374,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1808조 1569억 2798만</t>
+    <t>1816조 2366억 5588만</t>
   </si>
   <si>
     <t>11</t>
@@ -413,22 +416,40 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1102조 6798억 2352만</t>
+    <t>1122조 9708억 6007만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1073조 846억 3582만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>채무조정</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>972조 2153억 1957만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>975조 2945억 6270만</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>우후</t>
@@ -437,27 +458,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>971조 2607억 4284만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>926조 4709억 657만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -467,31 +470,31 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>838조 1381억 1843만</t>
+    <t>880조 870억 9413만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>795조 3494억 3995만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>정태준</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>747조 6479억 4857만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>738조 8585억 6928만</t>
+    <t>768조 8481억 6863만</t>
   </si>
   <si>
     <t>20</t>
@@ -503,7 +506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>539조 3853억 2223만</t>
+    <t>542조 4030억 8837만</t>
   </si>
   <si>
     <t>21</t>
@@ -515,7 +518,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>486조 5354억 4811만</t>
+    <t>488조 1597억 2966만</t>
   </si>
   <si>
     <t>22</t>
@@ -527,7 +530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>398조 4483억 503만</t>
+    <t>399조 5828억 710만</t>
   </si>
   <si>
     <t>23</t>
@@ -566,25 +569,37 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
+    <t>356조 443억 1139만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>251조 6847억 937만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
     <t>108</t>
   </si>
   <si>
-    <t>356조 443억 1139만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>240조 453억 6127만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>238조 9690억 8905만</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>여눈</t>
@@ -596,19 +611,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>226조 9385억 6222만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>224조 7388억 729만</t>
+    <t>229조 2691억 8890만</t>
   </si>
   <si>
     <t>29</t>
@@ -632,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>6757조 5035억 879만</t>
+    <t>7090조 8613억 3967만</t>
   </si>
   <si>
     <t>협의</t>
@@ -641,7 +644,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>4245조 3598억 1665만</t>
+    <t>4248조 2049억 8602만</t>
   </si>
   <si>
     <t>포항엄석대</t>
@@ -650,7 +653,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4022조 9259억 9763만</t>
+    <t>4023조 8282억 7084만</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>3018조 92억 9575만</t>
   </si>
   <si>
     <t>타개</t>
@@ -659,7 +671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>2546조 9231억 8482만</t>
+    <t>2760조 3858억 7806만</t>
   </si>
   <si>
     <t>포항가자미</t>
@@ -668,16 +680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2275조 975억 942만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>2259조 1663억 8382만</t>
+    <t>2280조 7090억 9755만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -692,22 +695,22 @@
     <t>2083조 2761억 2150만</t>
   </si>
   <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>1984조 4097억 1520만</t>
+  </si>
+  <si>
     <t>변신술사</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>1888조 3627억 818만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>1799조 246억 9846만</t>
+    <t>1959조 4176억 5949만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -716,7 +719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1757조 1363억 1880만</t>
+    <t>1827조 6451억 1194만</t>
   </si>
   <si>
     <t>온백</t>
@@ -725,7 +728,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1491조 3442억 3139만</t>
+    <t>1564조 8407억 4334만</t>
+  </si>
+  <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1522조 9920억 6658만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -743,16 +755,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1431조 346억 5059만</t>
-  </si>
-  <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1426조 665억 2214만</t>
+    <t>1476조 2629억 7936만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -761,7 +764,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
   </si>
   <si>
-    <t>1052조 292억 883만</t>
+    <t>1149조 8047억 287만</t>
   </si>
   <si>
     <t>대좀이</t>
@@ -770,7 +773,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>978조 7832억 9889만</t>
+    <t>1020조 5615억 2958만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -779,13 +782,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>956조 6204억 8172만</t>
+    <t>1011조 9735억 3143만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>953조 6362억 3238만</t>
+    <t>1000조 7988억 1833만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -797,22 +800,22 @@
     <t>916조 5073억 5513만</t>
   </si>
   <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>904조 9847억 9661만</t>
+  </si>
+  <si>
     <t>마갤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>826조 8046억 9936만</t>
-  </si>
-  <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>824조 2609억 4999만</t>
+    <t>892조 9573억 8284만</t>
   </si>
   <si>
     <t>냐은</t>
@@ -869,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>548조 5072억 4464만</t>
+    <t>549조 2888억 2795만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -881,7 +884,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>486조 1731억 5041만</t>
+    <t>487조 1056억 342만</t>
   </si>
   <si>
     <t>진성팔퀴</t>
@@ -905,6 +908,300 @@
     <t>277조 36억 4103만</t>
   </si>
   <si>
+    <t>강댜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%8C%9C</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 3840조 9768억 1685만</t>
+  </si>
+  <si>
+    <t>빵녕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EB%85%95</t>
+  </si>
+  <si>
+    <t>8707조 3775억 5909만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>7662조 5010억 5135만</t>
+  </si>
+  <si>
+    <t>실프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>1184조 7671억 4021만</t>
+  </si>
+  <si>
+    <t>페레로로쉐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
+  </si>
+  <si>
+    <t>1036조 8752억 7753만</t>
+  </si>
+  <si>
+    <t>냠늄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EB%8A%84</t>
+  </si>
+  <si>
+    <t>914조 4728억 6800만</t>
+  </si>
+  <si>
+    <t>보호소</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%ED%98%B8%EC%86%8C</t>
+  </si>
+  <si>
+    <t>873조 2965억 1326만</t>
+  </si>
+  <si>
+    <t>쮸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>789조 3133억 4361만</t>
+  </si>
+  <si>
+    <t>더대충</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
+  </si>
+  <si>
+    <t>758조 1161억 4287만</t>
+  </si>
+  <si>
+    <t>그복</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
+  </si>
+  <si>
+    <t>628조 1496억 8416만</t>
+  </si>
+  <si>
+    <t>갈매기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%A4%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>606조 1185억 6714만</t>
+  </si>
+  <si>
+    <t>끼꼬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%BC%EA%BC%AC</t>
+  </si>
+  <si>
+    <t>572조 1815억 1954만</t>
+  </si>
+  <si>
+    <t>더적당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>543조 7192억 3582만</t>
+  </si>
+  <si>
+    <t>주사고모</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%82%AC%EA%B3%A0%EB%AA%A8</t>
+  </si>
+  <si>
+    <t>484조 4320억 4123만</t>
+  </si>
+  <si>
+    <t>냥찐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
+  </si>
+  <si>
+    <t>447조 2705억 1520만</t>
+  </si>
+  <si>
+    <t>꿀꿀이의모험</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
+  </si>
+  <si>
+    <t>442조 2109억 7988만</t>
+  </si>
+  <si>
+    <t>사랑해제명</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
+  </si>
+  <si>
+    <t>437조 686억 1760만</t>
+  </si>
+  <si>
+    <t>시루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>376조 987억 5368만</t>
+  </si>
+  <si>
+    <t>퍄딤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
+  </si>
+  <si>
+    <t>362조 8177억 721만</t>
+  </si>
+  <si>
+    <t>환불스토리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>345조 3010억 3064만</t>
+  </si>
+  <si>
+    <t>달디달고나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%94%94%EB%8B%AC%EA%B3%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>254조 547억 5073만</t>
+  </si>
+  <si>
+    <t>소동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%99</t>
+  </si>
+  <si>
+    <t>215조 4742억 8912만</t>
+  </si>
+  <si>
+    <t>초코파베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>194조 1738억 924만</t>
+  </si>
+  <si>
+    <t>한굥굥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EA%B5%A5%EA%B5%A5</t>
+  </si>
+  <si>
+    <t>178조 9060억 5660만</t>
+  </si>
+  <si>
+    <t>취란</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
+  </si>
+  <si>
+    <t>165조 9531억 2123만</t>
+  </si>
+  <si>
+    <t>키류</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%A5%98</t>
+  </si>
+  <si>
+    <t>157조 503억 5410만</t>
+  </si>
+  <si>
+    <t>홀인원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%80%EC%9D%B8%EC%9B%90</t>
+  </si>
+  <si>
+    <t>141조 8021억 4517만</t>
+  </si>
+  <si>
+    <t>해졍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
+  </si>
+  <si>
+    <t>130조 5933억 4162만</t>
+  </si>
+  <si>
+    <t>홍뎐잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>110조 113억 8431만</t>
+  </si>
+  <si>
+    <t>꾸륭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%AD</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>104조 3404억 5034만</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>허숖</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%88%96</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>15조 8921억 6046만</t>
+  </si>
+  <si>
     <t>우니아파요</t>
   </si>
   <si>
@@ -917,7 +1214,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>4771조 5982억 458만</t>
+    <t>5205조 7689억 5644만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -926,7 +1223,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>3087조 4263억 7700만</t>
+    <t>3442조 9183억 3290만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -935,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>2968조 2308억 2418만</t>
+    <t>3189조 8770억 5910만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -953,7 +1250,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>1978조 3473억 4408만</t>
+    <t>2055조 9506억 6594만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -962,7 +1259,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>1926조 9793억 4211만</t>
+    <t>2024조 7110억 2189만</t>
   </si>
   <si>
     <t>여니워니</t>
@@ -971,7 +1268,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
   </si>
   <si>
-    <t>1846조 1184억 4836만</t>
+    <t>1933조 7785억 7266만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -989,7 +1286,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1492조 6491억 5005만</t>
+    <t>1649조 1905억 321만</t>
+  </si>
+  <si>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1525조 3861억 8798만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -998,7 +1304,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>1491조 4503억 8083만</t>
+    <t>1513조 1042억 667만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1007,7 +1313,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>1447조 7356억 830만</t>
+    <t>1496조 8790억 6289만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1016,16 +1322,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1334조 2685억 2601만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1199조 399억 9927만</t>
+    <t>1441조 7009억 4746만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1034,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1189조 5969억 2961만</t>
+    <t>1192조 3269억 3492만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1052,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>961조 606억 439만</t>
+    <t>976조 2012억 5957만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1061,7 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>851조 6091억 6378만</t>
+    <t>907조 4904억 4570만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1070,7 +1367,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>812조 9149억 5760만</t>
+    <t>827조 4846억 2932만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1097,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>688조 5062억 3265만</t>
+    <t>724조 3488억 9485만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1106,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>674조 9889억 4718만</t>
+    <t>706조 8416억 9682만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1133,7 +1430,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>547조 8506억 7422만</t>
+    <t>557조 3253억 3055만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1142,7 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>529조 2335억 1065만</t>
+    <t>534조 7838억 2109만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1160,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>282조 2989억 8387만</t>
+    <t>283조 2681억 4711만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1169,301 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>244조 307억 43만</t>
-  </si>
-  <si>
-    <t>강댜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%8C%9C</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>1경 3840조 9768억 1685만</t>
-  </si>
-  <si>
-    <t>빵녕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EB%85%95</t>
-  </si>
-  <si>
-    <t>8707조 3775억 5909만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>7547조 4204억 8633만</t>
-  </si>
-  <si>
-    <t>실프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>1143조 8935억 713만</t>
-  </si>
-  <si>
-    <t>페레로로쉐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
-  </si>
-  <si>
-    <t>919조 4048억 2542만</t>
-  </si>
-  <si>
-    <t>냠늄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A0%EB%8A%84</t>
-  </si>
-  <si>
-    <t>914조 4728억 6800만</t>
-  </si>
-  <si>
-    <t>보호소</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%ED%98%B8%EC%86%8C</t>
-  </si>
-  <si>
-    <t>821조 5481억 8761만</t>
-  </si>
-  <si>
-    <t>쮸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>749조 536억 6358만</t>
-  </si>
-  <si>
-    <t>더대충</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
-  </si>
-  <si>
-    <t>682조 4662억 121만</t>
-  </si>
-  <si>
-    <t>그복</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
-  </si>
-  <si>
-    <t>628조 524억 102만</t>
-  </si>
-  <si>
-    <t>갈매기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%A4%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>606조 1185억 6714만</t>
-  </si>
-  <si>
-    <t>끼꼬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%BC%EA%BC%AC</t>
-  </si>
-  <si>
-    <t>572조 1815억 1954만</t>
-  </si>
-  <si>
-    <t>더적당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>503조 4047억 6153만</t>
-  </si>
-  <si>
-    <t>주사고모</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%82%AC%EA%B3%A0%EB%AA%A8</t>
-  </si>
-  <si>
-    <t>484조 4320억 4123만</t>
-  </si>
-  <si>
-    <t>꿀꿀이의모험</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
-  </si>
-  <si>
-    <t>429조 425억 426만</t>
-  </si>
-  <si>
-    <t>사랑해제명</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
-  </si>
-  <si>
-    <t>415조 618억 657만</t>
-  </si>
-  <si>
-    <t>시루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>364조 9169억 9552만</t>
-  </si>
-  <si>
-    <t>냥찐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
-  </si>
-  <si>
-    <t>359조 1007억 5265만</t>
-  </si>
-  <si>
-    <t>퍄딤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
-  </si>
-  <si>
-    <t>348조 3483억 1470만</t>
-  </si>
-  <si>
-    <t>환불스토리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>325조 7409억 9992만</t>
-  </si>
-  <si>
-    <t>달디달고나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%94%94%EB%8B%AC%EA%B3%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>254조 547억 5073만</t>
-  </si>
-  <si>
-    <t>소동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%99</t>
-  </si>
-  <si>
-    <t>200조 5776억 5527만</t>
-  </si>
-  <si>
-    <t>초코파베</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
-  </si>
-  <si>
-    <t>191조 7879억 146만</t>
-  </si>
-  <si>
-    <t>취란</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
-  </si>
-  <si>
-    <t>165조 2717억 4130만</t>
-  </si>
-  <si>
-    <t>한굥굥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EA%B5%A5%EA%B5%A5</t>
-  </si>
-  <si>
-    <t>158조 6868억 2419만</t>
-  </si>
-  <si>
-    <t>키류</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EB%A5%98</t>
-  </si>
-  <si>
-    <t>157조 503억 5410만</t>
-  </si>
-  <si>
-    <t>홀인원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%80%EC%9D%B8%EC%9B%90</t>
-  </si>
-  <si>
-    <t>141조 7362억 8379만</t>
-  </si>
-  <si>
-    <t>해졍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
-  </si>
-  <si>
-    <t>113조 231억 4593만</t>
-  </si>
-  <si>
-    <t>홍뎐잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%8E%90%EC%9E%89</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>110조 113억 8431만</t>
-  </si>
-  <si>
-    <t>꾸륭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%AD</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>104조 3404억 5034만</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>허숖</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%97%88%EC%88%96</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>13조 8819억 7932만</t>
+    <t>261조 2697억 4490만</t>
   </si>
   <si>
     <t>가겠습니다</t>
@@ -1472,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>6383조 3476억 9123만</t>
+    <t>6657조 9043억 9852만</t>
   </si>
   <si>
     <t>라카도</t>
@@ -1481,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4190조 9975억 7541만</t>
+    <t>4199조 2065억 9938만</t>
   </si>
   <si>
     <t>미우맘</t>
@@ -1520,19 +1523,28 @@
     <t>2107조 2460억 3000만</t>
   </si>
   <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>2088조 9512억 292만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
+  </si>
+  <si>
+    <t>1984조 5821억 5679만</t>
+  </si>
+  <si>
     <t>명지동꿀주먹</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>1949조 4895억 5806만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
-  </si>
-  <si>
-    <t>1926조 3126억 1612만</t>
+    <t>1978조 3946억 2839만</t>
   </si>
   <si>
     <t>커튼월</t>
@@ -1541,16 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>1897조 3925억 3200만</t>
-  </si>
-  <si>
-    <t>DREAMLINER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
-  </si>
-  <si>
-    <t>1895조 8505억 4682만</t>
+    <t>1920조 5014억 456만</t>
   </si>
   <si>
     <t>천요화</t>
@@ -1559,7 +1562,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
   </si>
   <si>
-    <t>1549조 8843억 6126만</t>
+    <t>1674조 5397억 4802만</t>
   </si>
   <si>
     <t>Judge99</t>
@@ -1568,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=Judge99</t>
   </si>
   <si>
-    <t>1436조 1270억 3584만</t>
+    <t>1557조 2266억 9080만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -1577,7 +1580,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1002조 9805억 4140만</t>
+    <t>1071조 1098억 6914만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -1586,7 +1589,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
   </si>
   <si>
-    <t>898조 4126억 1299만</t>
+    <t>917조 5410억 5538만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -1595,7 +1598,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>869조 4751억 4407만</t>
+    <t>910조 5435억 2039만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -1604,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
   </si>
   <si>
-    <t>799조 5093억 9199만</t>
+    <t>852조 4657억 9247만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -1613,7 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>759조 8540억 2464만</t>
+    <t>820조 8492억 573만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -1622,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
   </si>
   <si>
-    <t>749조 9013억 1505만</t>
+    <t>800조 1347억 7699만</t>
   </si>
   <si>
     <t>양룽</t>
@@ -1631,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
   </si>
   <si>
-    <t>717조 1021억 8764만</t>
+    <t>717조 1554억 4791만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1640,7 +1643,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>624조 5956억 2794만</t>
+    <t>673조 8450억 5753만</t>
+  </si>
+  <si>
+    <t>gorystal</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
+  </si>
+  <si>
+    <t>618조 3743억 4409만</t>
   </si>
   <si>
     <t>욧츠</t>
@@ -1649,16 +1661,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
   </si>
   <si>
-    <t>568조 6411억 7256만</t>
-  </si>
-  <si>
-    <t>gorystal</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
-  </si>
-  <si>
-    <t>564조 6366억 6524만</t>
+    <t>604조 3235억 2253만</t>
+  </si>
+  <si>
+    <t>복룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>592조 6696억 2449만</t>
+  </si>
+  <si>
+    <t>뀨꾸룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>568조 967억 7710만</t>
+  </si>
+  <si>
+    <t>률율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>533조 6240억 4226만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1670,33 +1700,6 @@
     <t>524조 3731억 3025만</t>
   </si>
   <si>
-    <t>복룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>523조 6569억 9026만</t>
-  </si>
-  <si>
-    <t>률율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>516조 8300억 4193만</t>
-  </si>
-  <si>
-    <t>뀨꾸룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>512조 7290억 8972만</t>
-  </si>
-  <si>
     <t>짜상무</t>
   </si>
   <si>
@@ -1712,7 +1715,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>351조 7316억 1310만</t>
+    <t>374조 1651억 4635만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -1721,7 +1724,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>337조 1066억 1385만</t>
+    <t>368조 1647억 5873만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1730,7 +1733,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>276조 9043억 2328만</t>
+    <t>282조 2241억 1233만</t>
   </si>
 </sst>
 </file>
@@ -2229,30 +2232,30 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
@@ -2261,13 +2264,13 @@
         <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2275,25 +2278,25 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2302,39 +2305,39 @@
         <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2343,16 +2346,16 @@
         <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2387,28 +2390,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2419,28 +2422,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2451,28 +2454,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2483,28 +2486,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2515,28 +2518,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2547,28 +2550,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2579,28 +2582,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2611,28 +2614,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2643,28 +2646,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2675,28 +2678,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2707,28 +2710,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2739,28 +2742,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2771,28 +2774,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2803,28 +2806,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2835,28 +2838,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>131</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2867,28 +2870,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2899,28 +2902,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2931,28 +2934,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2963,28 +2966,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2995,28 +2998,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>136</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3027,28 +3030,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3059,28 +3062,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3091,28 +3094,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3123,28 +3126,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3155,28 +3158,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3187,25 +3190,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>180</v>
@@ -3231,13 +3234,13 @@
         <v>183</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>184</v>
@@ -3263,13 +3266,13 @@
         <v>187</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>189</v>
@@ -3295,16 +3298,16 @@
         <v>192</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>193</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3315,28 +3318,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3399,28 +3402,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3431,31 +3434,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3463,31 +3466,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3495,31 +3498,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3527,31 +3530,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3559,31 +3562,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3591,31 +3594,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3623,31 +3626,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3655,31 +3658,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3687,31 +3690,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3719,31 +3722,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3751,31 +3754,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3783,31 +3786,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3815,31 +3818,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3847,31 +3850,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3879,31 +3882,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3911,31 +3914,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3943,31 +3946,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3975,7 +3978,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>33</v>
@@ -3984,22 +3987,22 @@
         <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4007,31 +4010,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4039,31 +4042,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4071,31 +4074,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4103,31 +4106,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4135,31 +4138,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4167,31 +4170,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4199,31 +4202,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4234,28 +4237,28 @@
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4266,28 +4269,28 @@
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4298,28 +4301,28 @@
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4327,31 +4330,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4359,31 +4362,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4426,1051 +4429,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J31"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5489,28 +4447,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5518,31 +4476,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>381</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>381</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>382</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>383</v>
+        <v>295</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>384</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5550,31 +4508,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>385</v>
+        <v>297</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>386</v>
+        <v>298</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5582,31 +4540,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>388</v>
+        <v>300</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>389</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5614,31 +4572,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>390</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>390</v>
+        <v>302</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>391</v>
+        <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>392</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5646,31 +4604,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>393</v>
+        <v>305</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>393</v>
+        <v>305</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>394</v>
+        <v>306</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>395</v>
+        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5678,31 +4636,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>396</v>
+        <v>308</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>397</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>398</v>
+        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5710,31 +4668,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>399</v>
+        <v>311</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>399</v>
+        <v>311</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>400</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>401</v>
+        <v>313</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5742,31 +4700,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>314</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>402</v>
+        <v>314</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>403</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>404</v>
+        <v>316</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5774,31 +4732,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>317</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>317</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>406</v>
+        <v>318</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>407</v>
+        <v>319</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5806,31 +4764,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>408</v>
+        <v>320</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>408</v>
+        <v>320</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>410</v>
+        <v>322</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5838,31 +4796,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>323</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>411</v>
+        <v>323</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>412</v>
+        <v>324</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>413</v>
+        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5870,31 +4828,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>414</v>
+        <v>326</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>326</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
+        <v>327</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5902,31 +4860,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>417</v>
+        <v>329</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>418</v>
+        <v>330</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>419</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5934,31 +4892,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>421</v>
+        <v>333</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>422</v>
+        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5966,31 +4924,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>423</v>
+        <v>335</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
+        <v>335</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>424</v>
+        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>425</v>
+        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5998,31 +4956,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>426</v>
+        <v>338</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>426</v>
+        <v>338</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>427</v>
+        <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>428</v>
+        <v>340</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6030,31 +4988,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>341</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>341</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
+        <v>342</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>343</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6062,31 +5020,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>344</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>344</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>346</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6094,31 +5052,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>347</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>347</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>349</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6126,31 +5084,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>350</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>350</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>351</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>352</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6158,31 +5116,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>353</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>353</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>442</v>
+        <v>354</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>444</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6190,31 +5148,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>445</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>445</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>446</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>447</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6222,31 +5180,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>448</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>448</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>449</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>450</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6254,31 +5212,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>451</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>452</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>443</v>
+        <v>175</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>453</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6286,31 +5244,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>454</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>454</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>455</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>174</v>
+        <v>355</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>456</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6318,31 +5276,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>457</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>457</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>458</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>459</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6350,31 +5308,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>460</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>460</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>461</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>462</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6382,31 +5340,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>463</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>463</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>464</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>465</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6414,31 +5372,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>466</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>466</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>467</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>468</v>
+        <v>380</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>469</v>
+        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6446,31 +5404,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>470</v>
+        <v>382</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>470</v>
+        <v>382</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>471</v>
+        <v>383</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>472</v>
+        <v>384</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>473</v>
+        <v>385</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6478,31 +5436,31 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>474</v>
+        <v>386</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>475</v>
+        <v>387</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>475</v>
+        <v>387</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>476</v>
+        <v>388</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>477</v>
+        <v>389</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>478</v>
+        <v>390</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>24</v>
@@ -6547,6 +5505,1051 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J31"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -6567,28 +6570,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6596,962 +6599,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -10,15 +10,15 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="지존길드" sheetId="3" r:id="rId3"/>
-    <sheet name="버번" sheetId="4" r:id="rId4"/>
-    <sheet name="눈별" sheetId="5" r:id="rId5"/>
-    <sheet name="TopOfTop" sheetId="6" r:id="rId6"/>
+    <sheet name="눈별" sheetId="4" r:id="rId4"/>
+    <sheet name="TopOfTop" sheetId="5" r:id="rId5"/>
+    <sheet name="버번" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">TopOfTop!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">버번!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TopOfTop!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">눈별!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">버번!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="565">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,10 +80,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>13위</t>
+    <t>482</t>
+  </si>
+  <si>
+    <t>36위</t>
   </si>
   <si>
     <t>Lv.9</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>5경 977조 6346억 6184만</t>
+    <t>5경 985조 128억 1537만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -113,7 +113,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>437</t>
+    <t>493</t>
   </si>
   <si>
     <t>11위</t>
@@ -122,7 +122,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>4경 7116조 5949억 2207만</t>
+    <t>4경 9428조 9087억 197만</t>
   </si>
   <si>
     <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
@@ -131,7 +131,52 @@
     <t>지존순찌</t>
   </si>
   <si>
-    <t>2026.09.20</t>
+    <t>눈별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>9위</t>
+  </si>
+  <si>
+    <t>4경 6681조 7185억 6799만</t>
+  </si>
+  <si>
+    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
+  </si>
+  <si>
+    <t>심신삐약자</t>
+  </si>
+  <si>
+    <t>TopOfTop</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>4경 4791조 9790억 3201만</t>
+  </si>
+  <si>
+    <t>길컨 1등만</t>
+  </si>
+  <si>
+    <t>복어띰</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
   </si>
   <si>
     <t>버번</t>
@@ -143,13 +188,13 @@
     <t>Scania 1</t>
   </si>
   <si>
-    <t>458</t>
-  </si>
-  <si>
-    <t>28위</t>
-  </si>
-  <si>
-    <t>4경 2148조 2775억 4593만</t>
+    <t>516</t>
+  </si>
+  <si>
+    <t>40위</t>
+  </si>
+  <si>
+    <t>4경 4715조 920억 2401만</t>
   </si>
   <si>
     <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
@@ -158,51 +203,6 @@
     <t>망충둘기</t>
   </si>
   <si>
-    <t>눈별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>4경 4475조 8641억 4634만</t>
-  </si>
-  <si>
-    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
-  </si>
-  <si>
-    <t>심신삐약자</t>
-  </si>
-  <si>
-    <t>TopOfTop</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>454</t>
-  </si>
-  <si>
-    <t>4경 2489조 52억 6614만</t>
-  </si>
-  <si>
-    <t>길컨 1등만</t>
-  </si>
-  <si>
-    <t>복어띰</t>
-  </si>
-  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -245,7 +245,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8574조 1501억 5135만</t>
+    <t>8584조 5435억 7838만</t>
   </si>
   <si>
     <t>2</t>
@@ -263,7 +263,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>5653조 5717억 7457만</t>
+    <t>5940조 6332억 5803만</t>
   </si>
   <si>
     <t>3</t>
@@ -278,7 +278,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4372조 5502억 487만</t>
+    <t>4623조 7121억 3609만</t>
   </si>
   <si>
     <t>4</t>
@@ -308,7 +308,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>3457조 1738억 2160만</t>
+    <t>3465조 2129억 1474만</t>
   </si>
   <si>
     <t>6</t>
@@ -338,7 +338,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2874조 2412억 858만</t>
+    <t>3025조 9889억 5291만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2221조 522억 2603만</t>
+    <t>2359조 2322억 6229만</t>
   </si>
   <si>
     <t>9</t>
@@ -362,7 +362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2148조 2115억 8443만</t>
+    <t>2245조 5311억 5766만</t>
   </si>
   <si>
     <t>10</t>
@@ -395,28 +395,28 @@
     <t>12</t>
   </si>
   <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1242조 4819억 1644만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>1178조 4809억 5968만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1122조 9708억 6007만</t>
+    <t>1203조 7545억 8232만</t>
   </si>
   <si>
     <t>14</t>
@@ -434,31 +434,31 @@
     <t>110</t>
   </si>
   <si>
-    <t>1073조 846억 3582만</t>
+    <t>1095조 9682억 1720만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>1044조 4520억 5545만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>채무조정</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>975조 2945억 6270만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>971조 2607억 4284만</t>
+    <t>1006조 7349억 1730만</t>
   </si>
   <si>
     <t>17</t>
@@ -470,7 +470,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>880조 870억 9413만</t>
+    <t>985조 127억 7456만</t>
   </si>
   <si>
     <t>18</t>
@@ -506,7 +506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>542조 4030억 8837만</t>
+    <t>553조 2855억 2735만</t>
   </si>
   <si>
     <t>21</t>
@@ -524,16 +524,31 @@
     <t>22</t>
   </si>
   <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>433조 5024억 6914만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>플로우00</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>399조 5828억 710만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>400조 9104억 9253만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -542,22 +557,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>384조 814억 6223만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>380조 192억 2246만</t>
+    <t>398조 6540억 7922만</t>
   </si>
   <si>
     <t>25</t>
@@ -596,7 +596,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>238조 9690억 8905만</t>
+    <t>242조 8640억 355만</t>
   </si>
   <si>
     <t>28</t>
@@ -611,7 +611,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>229조 2691억 8890만</t>
+    <t>242조 2437억 5612만</t>
   </si>
   <si>
     <t>29</t>
@@ -635,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>7090조 8613억 3967만</t>
+    <t>7139조 1억 8544만</t>
   </si>
   <si>
     <t>협의</t>
@@ -653,7 +653,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>4023조 8282억 7084만</t>
+    <t>4094조 124억 4985만</t>
   </si>
   <si>
     <t>기뽐</t>
@@ -680,7 +680,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
   </si>
   <si>
-    <t>2280조 7090억 9755만</t>
+    <t>2305조 9264억 9066만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -692,7 +692,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>2083조 2761억 2150만</t>
+    <t>2136조 7914억 7532만</t>
   </si>
   <si>
     <t>뿡쓰</t>
@@ -701,7 +701,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>1984조 4097억 1520만</t>
+    <t>2087조 4929억 3128만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>1978조 8306억 8833만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -710,7 +719,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
   </si>
   <si>
-    <t>1959조 4176억 5949만</t>
+    <t>1965조 4376억 7943만</t>
   </si>
   <si>
     <t>댜니</t>
@@ -728,7 +737,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>1564조 8407억 4334만</t>
+    <t>1583조 4740억 6611만</t>
   </si>
   <si>
     <t>마카롱롱</t>
@@ -740,22 +749,13 @@
     <t>1522조 9920억 6658만</t>
   </si>
   <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>1483조 2810억 4011만</t>
-  </si>
-  <si>
     <t>파울</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1476조 2629억 7936만</t>
+    <t>1493조 6816억 1073만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -773,7 +773,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1020조 5615억 2958만</t>
+    <t>1055조 6697억 1936만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>1043조 7603억 227만</t>
   </si>
   <si>
     <t>모짜리코베르</t>
@@ -782,13 +788,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1011조 9735억 3143만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>1000조 7988억 1833만</t>
+    <t>1024조 1727억 3300만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -797,7 +797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>916조 5073억 5513만</t>
+    <t>971조 7291억 9209만</t>
   </si>
   <si>
     <t>기본이리</t>
@@ -824,7 +824,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>810조 1567억 9854만</t>
+    <t>853조 2126억 6324만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -836,13 +836,25 @@
     <t>787조 4728억 4596만</t>
   </si>
   <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>757조 3035억 7811만</t>
+  </si>
+  <si>
     <t>전산봉</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>671조 6340억 2972만</t>
+    <t>715조 9849억 4353만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -851,19 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>628조 6146억 917만</t>
-  </si>
-  <si>
-    <t>고숨도칭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>584조 3143억 9077만</t>
+    <t>697조 8345억 1043만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>549조 2888억 2795만</t>
+    <t>563조 8436억 6575만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -908,6 +908,540 @@
     <t>277조 36억 4103만</t>
   </si>
   <si>
+    <t>우니아파요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
+  </si>
+  <si>
+    <t>5708조 2885억 4200만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
+  </si>
+  <si>
+    <t>5212조 5789억 2707만</t>
+  </si>
+  <si>
+    <t>도하리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>3493조 4557억 4453만</t>
+  </si>
+  <si>
+    <t>죽창당일개통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
+  </si>
+  <si>
+    <t>3266조 5159억 420만</t>
+  </si>
+  <si>
+    <t>유수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>2442조 7167억 3154만</t>
+  </si>
+  <si>
+    <t>종꿀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
+  </si>
+  <si>
+    <t>2080조 3777억 6799만</t>
+  </si>
+  <si>
+    <t>이용하다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2056조 4022억 8007만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1933조 7785억 7266만</t>
+  </si>
+  <si>
+    <t>해달잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
+  </si>
+  <si>
+    <t>1765조 4495억 1688만</t>
+  </si>
+  <si>
+    <t>세월이야속해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
+  </si>
+  <si>
+    <t>1649조 1905억 321만</t>
+  </si>
+  <si>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1615조 3693억 8331만</t>
+  </si>
+  <si>
+    <t>포빅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
+  </si>
+  <si>
+    <t>1599조 9170억 8901만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>1551조 3914억 3624만</t>
+  </si>
+  <si>
+    <t>MangCI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
+  </si>
+  <si>
+    <t>1441조 7009억 4746만</t>
+  </si>
+  <si>
+    <t>여자둘남자둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
+  </si>
+  <si>
+    <t>1201조 7967억 40만</t>
+  </si>
+  <si>
+    <t>덩개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>1159조 4581억 2176만</t>
+  </si>
+  <si>
+    <t>예타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
+  </si>
+  <si>
+    <t>994조 3272억 3938만</t>
+  </si>
+  <si>
+    <t>모르페우스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>907조 4904억 4570만</t>
+  </si>
+  <si>
+    <t>티에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>854조 7581억 1259만</t>
+  </si>
+  <si>
+    <t>파이리양말</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
+  </si>
+  <si>
+    <t>834조 3598억 3007만</t>
+  </si>
+  <si>
+    <t>박금쪽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
+  </si>
+  <si>
+    <t>801조 7928억 6181만</t>
+  </si>
+  <si>
+    <t>성률</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
+  </si>
+  <si>
+    <t>782조 4064억 8532만</t>
+  </si>
+  <si>
+    <t>지존짱창남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
+  </si>
+  <si>
+    <t>706조 8416억 9682만</t>
+  </si>
+  <si>
+    <t>히어로호걸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
+  </si>
+  <si>
+    <t>612조 8166억 9275만</t>
+  </si>
+  <si>
+    <t>작업치료사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
+  </si>
+  <si>
+    <t>605조 2191억 6874만</t>
+  </si>
+  <si>
+    <t>감화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
+  </si>
+  <si>
+    <t>563조 6908억 7332만</t>
+  </si>
+  <si>
+    <t>계니규니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>561조 2462억 1227만</t>
+  </si>
+  <si>
+    <t>하비엔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
+  </si>
+  <si>
+    <t>354조 1700억 1601만</t>
+  </si>
+  <si>
+    <t>채구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>290조 9709억 9971만</t>
+  </si>
+  <si>
+    <t>신탄보우짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>266조 7771억 8120만</t>
+  </si>
+  <si>
+    <t>가겠습니다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>7012조 8598억 3928만</t>
+  </si>
+  <si>
+    <t>라카도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
+  </si>
+  <si>
+    <t>4508조 6564억 7698만</t>
+  </si>
+  <si>
+    <t>롤대신해야지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>3010조 441억 5351만</t>
+  </si>
+  <si>
+    <t>미우맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
+  </si>
+  <si>
+    <t>2880조 5219억 5377만</t>
+  </si>
+  <si>
+    <t>개종망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>2774조 2722억 1106만</t>
+  </si>
+  <si>
+    <t>gorystalLOVE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
+  </si>
+  <si>
+    <t>2107조 2460억 3000만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
+  </si>
+  <si>
+    <t>2102조 5589억 5859만</t>
+  </si>
+  <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>2088조 9512억 292만</t>
+  </si>
+  <si>
+    <t>명지동꿀주먹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
+  </si>
+  <si>
+    <t>2020조 946억 579만</t>
+  </si>
+  <si>
+    <t>커튼월</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
+  </si>
+  <si>
+    <t>1996조 4869억 4418만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>1688조 5580억 5122만</t>
+  </si>
+  <si>
+    <t>Judge99</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
+  </si>
+  <si>
+    <t>1557조 2266억 9080만</t>
+  </si>
+  <si>
+    <t>도리토스치즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1083조 8247억 6506만</t>
+  </si>
+  <si>
+    <t>커럭트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>917조 5410억 5538만</t>
+  </si>
+  <si>
+    <t>지낌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>910조 5435억 2039만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>852조 4657억 9247만</t>
+  </si>
+  <si>
+    <t>옥슈쓔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
+  </si>
+  <si>
+    <t>820조 8492억 573만</t>
+  </si>
+  <si>
+    <t>무동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>817조 4820억 228만</t>
+  </si>
+  <si>
+    <t>양룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>740조 3045억 100만</t>
+  </si>
+  <si>
+    <t>또띠야칩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
+  </si>
+  <si>
+    <t>673조 8450억 5753만</t>
+  </si>
+  <si>
+    <t>gorystal</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
+  </si>
+  <si>
+    <t>660조 996억 2701만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>647조 3034억 4911만</t>
+  </si>
+  <si>
+    <t>파파존스맛나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
+  </si>
+  <si>
+    <t>622조 9977억 1292만</t>
+  </si>
+  <si>
+    <t>복룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>596조 708억 6773만</t>
+  </si>
+  <si>
+    <t>뀨꾸룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>580조 1477억 3106만</t>
+  </si>
+  <si>
+    <t>짜상무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>567조 446억 7561만</t>
+  </si>
+  <si>
+    <t>률율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>533조 6240억 4226만</t>
+  </si>
+  <si>
+    <t>매리골드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>378조 6204억 9767만</t>
+  </si>
+  <si>
+    <t>원종일짱유나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>368조 5953억 1098만</t>
+  </si>
+  <si>
+    <t>문배동육칼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
+  </si>
+  <si>
+    <t>327조 4344억 9180만</t>
+  </si>
+  <si>
     <t>강댜</t>
   </si>
   <si>
@@ -917,7 +1451,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 3840조 9768억 1685만</t>
+    <t>1경 4216조 2820억 322만</t>
   </si>
   <si>
     <t>빵녕</t>
@@ -926,13 +1460,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EB%85%95</t>
   </si>
   <si>
-    <t>8707조 3775억 5909만</t>
+    <t>1경 467조 3568억 1596만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>7662조 5010억 5135만</t>
+    <t>7770조 1716억 5948만</t>
   </si>
   <si>
     <t>실프</t>
@@ -950,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EB%A0%88%EB%A1%9C%EB%A1%9C%EC%89%90</t>
   </si>
   <si>
-    <t>1036조 8752억 7753만</t>
+    <t>1037조 1618억 7732만</t>
   </si>
   <si>
     <t>냠늄</t>
@@ -968,7 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%ED%98%B8%EC%86%8C</t>
   </si>
   <si>
-    <t>873조 2965억 1326만</t>
+    <t>903조 4530억 4482만</t>
   </si>
   <si>
     <t>쮸르</t>
@@ -977,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>789조 3133억 4361만</t>
+    <t>820조 3411억 5600만</t>
   </si>
   <si>
     <t>더대충</t>
@@ -986,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
   </si>
   <si>
-    <t>758조 1161억 4287만</t>
+    <t>785조 4568억 4635만</t>
   </si>
   <si>
     <t>그복</t>
@@ -995,7 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
   </si>
   <si>
-    <t>628조 1496억 8416만</t>
+    <t>654조 113억 3869만</t>
   </si>
   <si>
     <t>갈매기</t>
@@ -1007,6 +1541,15 @@
     <t>606조 1185억 6714만</t>
   </si>
   <si>
+    <t>더적당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>573조 7669억 9172만</t>
+  </si>
+  <si>
     <t>끼꼬</t>
   </si>
   <si>
@@ -1016,31 +1559,13 @@
     <t>572조 1815억 1954만</t>
   </si>
   <si>
-    <t>더적당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>543조 7192억 3582만</t>
-  </si>
-  <si>
-    <t>주사고모</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%82%AC%EA%B3%A0%EB%AA%A8</t>
-  </si>
-  <si>
-    <t>484조 4320억 4123만</t>
-  </si>
-  <si>
     <t>냥찐</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
   </si>
   <si>
-    <t>447조 2705억 1520만</t>
+    <t>518조 6793억 8787만</t>
   </si>
   <si>
     <t>꿀꿀이의모험</t>
@@ -1049,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
   </si>
   <si>
-    <t>442조 2109억 7988만</t>
+    <t>456조 9713억 8567만</t>
   </si>
   <si>
     <t>사랑해제명</t>
@@ -1058,7 +1583,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
   </si>
   <si>
-    <t>437조 686억 1760만</t>
+    <t>437조 6914억 193만</t>
   </si>
   <si>
     <t>시루</t>
@@ -1067,7 +1592,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
   </si>
   <si>
-    <t>376조 987억 5368만</t>
+    <t>376조 7036억 8882만</t>
   </si>
   <si>
     <t>퍄딤</t>
@@ -1076,7 +1601,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EB%94%A4</t>
   </si>
   <si>
-    <t>362조 8177억 721만</t>
+    <t>365조 2584억 6400만</t>
   </si>
   <si>
     <t>환불스토리</t>
@@ -1085,7 +1610,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>345조 3010억 3064만</t>
+    <t>346조 1419억 5418만</t>
   </si>
   <si>
     <t>달디달고나</t>
@@ -1133,7 +1658,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
   </si>
   <si>
-    <t>165조 9531억 2123만</t>
+    <t>166조 650억 3497만</t>
+  </si>
+  <si>
+    <t>홀인원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%80%EC%9D%B8%EC%9B%90</t>
+  </si>
+  <si>
+    <t>159조 3234억 4352만</t>
   </si>
   <si>
     <t>키류</t>
@@ -1145,22 +1679,13 @@
     <t>157조 503억 5410만</t>
   </si>
   <si>
-    <t>홀인원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%80%EC%9D%B8%EC%9B%90</t>
-  </si>
-  <si>
-    <t>141조 8021억 4517만</t>
-  </si>
-  <si>
     <t>해졍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
   </si>
   <si>
-    <t>130조 5933억 4162만</t>
+    <t>131조 1231억 9174만</t>
   </si>
   <si>
     <t>홍뎐잉</t>
@@ -1172,7 +1697,7 @@
     <t>106</t>
   </si>
   <si>
-    <t>110조 113억 8431만</t>
+    <t>119조 3425억 9122만</t>
   </si>
   <si>
     <t>꾸륭</t>
@@ -1184,10 +1709,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>104조 3404억 5034만</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>116조 2818억 1284만</t>
   </si>
   <si>
     <t>허숖</t>
@@ -1199,541 +1721,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 8921억 6046만</t>
-  </si>
-  <si>
-    <t>우니아파요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
-  </si>
-  <si>
-    <t>5708조 2885억 4200만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
-  </si>
-  <si>
-    <t>5205조 7689억 5644만</t>
-  </si>
-  <si>
-    <t>도하리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>3442조 9183억 3290만</t>
-  </si>
-  <si>
-    <t>죽창당일개통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
-  </si>
-  <si>
-    <t>3189조 8770억 5910만</t>
-  </si>
-  <si>
-    <t>유수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>2381조 5061억 1898만</t>
-  </si>
-  <si>
-    <t>종꿀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
-  </si>
-  <si>
-    <t>2055조 9506억 6594만</t>
-  </si>
-  <si>
-    <t>이용하다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2024조 7110억 2189만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1933조 7785억 7266만</t>
-  </si>
-  <si>
-    <t>해달잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1745조 1553억 5425만</t>
-  </si>
-  <si>
-    <t>세월이야속해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
-  </si>
-  <si>
-    <t>1649조 1905억 321만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1525조 3861억 8798만</t>
-  </si>
-  <si>
-    <t>포빅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
-  </si>
-  <si>
-    <t>1513조 1042억 667만</t>
-  </si>
-  <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1496조 8790억 6289만</t>
-  </si>
-  <si>
-    <t>MangCI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
-  </si>
-  <si>
-    <t>1441조 7009억 4746만</t>
-  </si>
-  <si>
-    <t>여자둘남자둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
-  </si>
-  <si>
-    <t>1192조 3269억 3492만</t>
-  </si>
-  <si>
-    <t>덩개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>1159조 4581억 2176만</t>
-  </si>
-  <si>
-    <t>예타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
-  </si>
-  <si>
-    <t>976조 2012억 5957만</t>
-  </si>
-  <si>
-    <t>모르페우스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>907조 4904억 4570만</t>
-  </si>
-  <si>
-    <t>티에이치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
-  </si>
-  <si>
-    <t>827조 4846억 2932만</t>
-  </si>
-  <si>
-    <t>파이리양말</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
-  </si>
-  <si>
-    <t>811조 6711억 3670만</t>
-  </si>
-  <si>
-    <t>박금쪽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
-  </si>
-  <si>
-    <t>801조 7928억 6181만</t>
-  </si>
-  <si>
-    <t>성률</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
-  </si>
-  <si>
-    <t>724조 3488억 9485만</t>
-  </si>
-  <si>
-    <t>지존짱창남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
-  </si>
-  <si>
-    <t>706조 8416억 9682만</t>
-  </si>
-  <si>
-    <t>히어로호걸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
-  </si>
-  <si>
-    <t>606조 6653억 7985만</t>
-  </si>
-  <si>
-    <t>작업치료사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
-  </si>
-  <si>
-    <t>605조 2191억 6874만</t>
-  </si>
-  <si>
-    <t>계니규니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>557조 3253억 3055만</t>
-  </si>
-  <si>
-    <t>감화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
-  </si>
-  <si>
-    <t>534조 7838억 2109만</t>
-  </si>
-  <si>
-    <t>하비엔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
-  </si>
-  <si>
-    <t>330조 1725억 5296만</t>
-  </si>
-  <si>
-    <t>채구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>283조 2681억 4711만</t>
-  </si>
-  <si>
-    <t>신탄보우짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>261조 2697억 4490만</t>
-  </si>
-  <si>
-    <t>가겠습니다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>6657조 9043억 9852만</t>
-  </si>
-  <si>
-    <t>라카도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
-  </si>
-  <si>
-    <t>4199조 2065억 9938만</t>
-  </si>
-  <si>
-    <t>미우맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
-  </si>
-  <si>
-    <t>2880조 5219억 5377만</t>
-  </si>
-  <si>
-    <t>롤대신해야지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>2840조 4162억 3948만</t>
-  </si>
-  <si>
-    <t>개종망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>2334조 6051억 8010만</t>
-  </si>
-  <si>
-    <t>gorystalLOVE</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
-  </si>
-  <si>
-    <t>2107조 2460억 3000만</t>
-  </si>
-  <si>
-    <t>DREAMLINER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
-  </si>
-  <si>
-    <t>2088조 9512억 292만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
-  </si>
-  <si>
-    <t>1984조 5821억 5679만</t>
-  </si>
-  <si>
-    <t>명지동꿀주먹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
-  </si>
-  <si>
-    <t>1978조 3946억 2839만</t>
-  </si>
-  <si>
-    <t>커튼월</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
-  </si>
-  <si>
-    <t>1920조 5014억 456만</t>
-  </si>
-  <si>
-    <t>천요화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
-  </si>
-  <si>
-    <t>1674조 5397억 4802만</t>
-  </si>
-  <si>
-    <t>Judge99</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
-  </si>
-  <si>
-    <t>1557조 2266억 9080만</t>
-  </si>
-  <si>
-    <t>도리토스치즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1071조 1098억 6914만</t>
-  </si>
-  <si>
-    <t>커럭트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>917조 5410억 5538만</t>
-  </si>
-  <si>
-    <t>지낌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>910조 5435억 2039만</t>
-  </si>
-  <si>
-    <t>스툭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
-  </si>
-  <si>
-    <t>852조 4657억 9247만</t>
-  </si>
-  <si>
-    <t>옥슈쓔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
-  </si>
-  <si>
-    <t>820조 8492억 573만</t>
-  </si>
-  <si>
-    <t>무동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>800조 1347억 7699만</t>
-  </si>
-  <si>
-    <t>양룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>717조 1554억 4791만</t>
-  </si>
-  <si>
-    <t>또띠야칩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
-  </si>
-  <si>
-    <t>673조 8450억 5753만</t>
-  </si>
-  <si>
-    <t>gorystal</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
-  </si>
-  <si>
-    <t>618조 3743억 4409만</t>
-  </si>
-  <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>604조 3235억 2253만</t>
-  </si>
-  <si>
-    <t>복룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>592조 6696억 2449만</t>
-  </si>
-  <si>
-    <t>뀨꾸룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>568조 967억 7710만</t>
-  </si>
-  <si>
-    <t>률율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>533조 6240억 4226만</t>
-  </si>
-  <si>
-    <t>파파존스맛나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
-  </si>
-  <si>
-    <t>524조 3731억 3025만</t>
-  </si>
-  <si>
-    <t>짜상무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>498조 3734억 6000만</t>
-  </si>
-  <si>
-    <t>매리골드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>374조 1651억 4635만</t>
-  </si>
-  <si>
-    <t>원종일짱유나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>368조 1647억 5873만</t>
-  </si>
-  <si>
-    <t>문배동육칼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
-  </si>
-  <si>
-    <t>282조 2241억 1233만</t>
+    <t>16조 3085억 7886만</t>
   </si>
 </sst>
 </file>
@@ -2232,30 +2220,30 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
@@ -2264,13 +2252,13 @@
         <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2278,25 +2266,25 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2305,39 +2293,39 @@
         <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2355,7 +2343,7 @@
         <v>57</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2789,13 +2777,13 @@
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2806,22 +2794,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>97</v>
@@ -2885,10 +2873,10 @@
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -2917,10 +2905,10 @@
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>143</v>
@@ -3109,13 +3097,13 @@
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3126,28 +3114,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>134</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3158,16 +3146,16 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
@@ -3176,7 +3164,7 @@
         <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>176</v>
@@ -3208,7 +3196,7 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>180</v>
@@ -3240,7 +3228,7 @@
         <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>184</v>
@@ -3304,7 +3292,7 @@
         <v>193</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>194</v>
@@ -3458,7 +3446,7 @@
         <v>202</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3490,7 +3478,7 @@
         <v>205</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3522,7 +3510,7 @@
         <v>208</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3554,7 +3542,7 @@
         <v>211</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3586,7 +3574,7 @@
         <v>214</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3618,7 +3606,7 @@
         <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3650,7 +3638,7 @@
         <v>221</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3682,7 +3670,7 @@
         <v>224</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3705,7 +3693,7 @@
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>77</v>
@@ -3714,7 +3702,7 @@
         <v>227</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3737,16 +3725,16 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>230</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3769,7 +3757,7 @@
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>102</v>
@@ -3778,7 +3766,7 @@
         <v>233</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3801,16 +3789,16 @@
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>236</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3818,7 +3806,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>237</v>
@@ -3833,7 +3821,7 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>77</v>
@@ -3842,7 +3830,7 @@
         <v>239</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3874,7 +3862,7 @@
         <v>242</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3906,7 +3894,7 @@
         <v>245</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3938,7 +3926,7 @@
         <v>248</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3949,28 +3937,28 @@
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>76</v>
+        <v>220</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3981,19 +3969,19 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>252</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>97</v>
@@ -4002,7 +3990,7 @@
         <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4034,7 +4022,7 @@
         <v>256</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4066,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4098,7 +4086,7 @@
         <v>262</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4130,7 +4118,7 @@
         <v>265</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4138,7 +4126,7 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>266</v>
@@ -4162,7 +4150,7 @@
         <v>268</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4170,7 +4158,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>269</v>
@@ -4185,16 +4173,16 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>271</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4205,28 +4193,28 @@
         <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4237,28 +4225,28 @@
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>277</v>
+        <v>133</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>278</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4284,13 +4272,13 @@
         <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>281</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4322,7 +4310,7 @@
         <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4345,16 +4333,16 @@
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>288</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -4380,13 +4368,13 @@
         <v>193</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>292</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -4429,7 +4417,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4438,7 +4426,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4476,7 +4464,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>66</v>
@@ -4494,13 +4482,13 @@
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4508,31 +4496,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4540,31 +4528,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>298</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4572,31 +4560,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4604,31 +4592,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4636,31 +4624,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4668,31 +4656,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4700,19 +4688,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -4721,10 +4709,10 @@
         <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4732,31 +4720,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4764,31 +4752,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4796,31 +4784,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4828,31 +4816,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4860,31 +4848,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4892,31 +4880,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4924,19 +4912,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
@@ -4945,10 +4933,10 @@
         <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4956,31 +4944,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>339</v>
-      </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>134</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4988,31 +4976,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5020,19 +5008,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
@@ -5041,10 +5029,10 @@
         <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5052,31 +5040,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>349</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5084,31 +5072,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5116,31 +5104,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5148,31 +5136,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5180,31 +5168,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5212,31 +5200,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5244,31 +5232,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5276,19 +5264,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
@@ -5297,10 +5285,10 @@
         <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>355</v>
+        <v>134</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5308,31 +5296,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5340,31 +5328,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5372,31 +5360,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5404,70 +5392,38 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>384</v>
+        <v>134</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5499,7 +5455,6 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
-    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5512,7 +5467,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -5554,243 +5509,243 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>385</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>385</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>284</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>408</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>408</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -5802,603 +5757,603 @@
         <v>102</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>102</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>102</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>220</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>271</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>134</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>175</v>
+        <v>97</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>220</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
@@ -6410,106 +6365,106 @@
         <v>134</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -6557,11 +6512,11 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6599,19 +6554,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -6620,190 +6575,190 @@
         <v>76</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
+        <v>473</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>486</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>486</v>
+        <v>57</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>102</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
@@ -6812,126 +6767,126 @@
         <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>57</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>57</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>133</v>
+        <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
@@ -6940,318 +6895,318 @@
         <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>119</v>
+        <v>220</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>133</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>220</v>
+        <v>133</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>277</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>97</v>
+        <v>530</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
@@ -7260,62 +7215,62 @@
         <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>530</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>198</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>530</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
@@ -7324,30 +7279,30 @@
         <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
@@ -7356,30 +7311,30 @@
         <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>97</v>
+        <v>530</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
@@ -7388,30 +7343,30 @@
         <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>134</v>
+        <v>530</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
@@ -7420,141 +7375,141 @@
         <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>175</v>
+        <v>530</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>175</v>
+        <v>530</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>284</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>188</v>
+        <v>555</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>97</v>
+        <v>559</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>289</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>198</v>
+        <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>175</v>
+        <v>563</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -10,14 +10,14 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="지존길드" sheetId="3" r:id="rId3"/>
-    <sheet name="눈별" sheetId="4" r:id="rId4"/>
-    <sheet name="TopOfTop" sheetId="5" r:id="rId5"/>
+    <sheet name="TopOfTop" sheetId="4" r:id="rId4"/>
+    <sheet name="눈별" sheetId="5" r:id="rId5"/>
     <sheet name="버번" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">TopOfTop!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">눈별!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TopOfTop!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">버번!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="567">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,10 +80,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>482</t>
-  </si>
-  <si>
-    <t>36위</t>
+    <t>842</t>
+  </si>
+  <si>
+    <t>37위</t>
   </si>
   <si>
     <t>Lv.9</t>
@@ -113,10 +113,10 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>493</t>
-  </si>
-  <si>
-    <t>11위</t>
+    <t>851</t>
+  </si>
+  <si>
+    <t>31위</t>
   </si>
   <si>
     <t>30명</t>
@@ -131,6 +131,33 @@
     <t>지존순찌</t>
   </si>
   <si>
+    <t>TopOfTop</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>897</t>
+  </si>
+  <si>
+    <t>16위</t>
+  </si>
+  <si>
+    <t>4경 4791조 9790억 3201만</t>
+  </si>
+  <si>
+    <t>길컨 1등만</t>
+  </si>
+  <si>
+    <t>복어띰</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
     <t>눈별</t>
   </si>
   <si>
@@ -140,10 +167,10 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>508</t>
-  </si>
-  <si>
-    <t>9위</t>
+    <t>878</t>
+  </si>
+  <si>
+    <t>38위</t>
   </si>
   <si>
     <t>4경 6681조 7185억 6799만</t>
@@ -155,30 +182,6 @@
     <t>심신삐약자</t>
   </si>
   <si>
-    <t>TopOfTop</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>515</t>
-  </si>
-  <si>
-    <t>4경 4791조 9790억 3201만</t>
-  </si>
-  <si>
-    <t>길컨 1등만</t>
-  </si>
-  <si>
-    <t>복어띰</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
     <t>버번</t>
   </si>
   <si>
@@ -188,13 +191,13 @@
     <t>Scania 1</t>
   </si>
   <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>40위</t>
-  </si>
-  <si>
-    <t>4경 4715조 920억 2401만</t>
+    <t>854</t>
+  </si>
+  <si>
+    <t>39위</t>
+  </si>
+  <si>
+    <t>4경 8797조 8949억 1840만</t>
   </si>
   <si>
     <t>오래하실분들같이해요 1일초과 미접시 정리합니다 길드컨텐츠 필참 바랍니다</t>
@@ -203,6 +206,9 @@
     <t>망충둘기</t>
   </si>
   <si>
+    <t>2026.09.23</t>
+  </si>
+  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -245,7 +251,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8584조 5435억 7838만</t>
+    <t>8683조 3042억 8295만</t>
   </si>
   <si>
     <t>2</t>
@@ -263,7 +269,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>5940조 6332억 5803만</t>
+    <t>6014조 3394억 942만</t>
   </si>
   <si>
     <t>3</t>
@@ -278,7 +284,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>4623조 7121억 3609만</t>
+    <t>5946조 1612억 9207만</t>
   </si>
   <si>
     <t>4</t>
@@ -293,7 +299,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>3674조 8409억 1914만</t>
+    <t>3715조 6957억 2132만</t>
   </si>
   <si>
     <t>5</t>
@@ -308,7 +314,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>3465조 2129억 1474만</t>
+    <t>3507조 7653억 9172만</t>
   </si>
   <si>
     <t>6</t>
@@ -323,7 +329,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>3449조 7647억 9983만</t>
+    <t>3449조 8638억 133만</t>
   </si>
   <si>
     <t>7</t>
@@ -338,7 +344,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>3025조 9889억 5291만</t>
+    <t>3260조 9407억 8185만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2359조 2322억 6229만</t>
+    <t>2359조 7550억 1059만</t>
   </si>
   <si>
     <t>9</t>
@@ -362,7 +368,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2245조 5311억 5766만</t>
+    <t>2316조 8153억 3460만</t>
   </si>
   <si>
     <t>10</t>
@@ -374,25 +380,52 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1816조 2366억 5588만</t>
+    <t>1880조 3086억 2917만</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>1825조 2398억 5085만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1561조 8118억 4850만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>야가다</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>1508조 7420억 3377만</t>
   </si>
   <si>
-    <t>12</t>
+    <t>14</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -407,45 +440,18 @@
     <t>1242조 4819억 1644만</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>1203조 7545억 8232만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
+    <t>15</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
     <t>110</t>
   </si>
   <si>
-    <t>1095조 9682억 1720만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
     <t>1044조 4520억 5545만</t>
   </si>
   <si>
@@ -464,16 +470,28 @@
     <t>17</t>
   </si>
   <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>987조 2843억 9824만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>호우기</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>985조 127억 7456만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>986조 551억 8118만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -482,10 +500,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>795조 3494억 3995만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>861조 2835억 6020만</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>정태준</t>
@@ -494,10 +512,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>768조 8481억 6863만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>812조 1715억 4606만</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -506,10 +524,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>553조 2855억 2735만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>559조 6324억 8795만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -518,10 +536,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>488조 1597억 2966만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>500조 9954억 5178만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -536,7 +554,7 @@
     <t>433조 5024억 6914만</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -545,10 +563,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>400조 9104억 9253만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>416조 7357억 5542만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -557,10 +575,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>398조 6540억 7922만</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>403조 6278억 871만</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>솔인</t>
@@ -569,10 +587,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>356조 443억 1139만</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>356조 1852억 8158만</t>
+  </si>
+  <si>
+    <t>27</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -581,10 +599,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
   </si>
   <si>
-    <t>251조 6847억 937만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>275조 6869억 3523만</t>
+  </si>
+  <si>
+    <t>28</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -596,10 +614,10 @@
     <t>108</t>
   </si>
   <si>
-    <t>242조 8640억 355만</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>244조 3551억 7832만</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>여눈</t>
@@ -611,97 +629,94 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>242조 2437억 5612만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+    <t>242조 5850억 8938만</t>
+  </si>
+  <si>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>8162조 1096억 772만</t>
+  </si>
+  <si>
+    <t>협의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+  </si>
+  <si>
+    <t>4402조 1032억 4015만</t>
+  </si>
+  <si>
+    <t>포항엄석대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
+  </si>
+  <si>
+    <t>4094조 124억 4985만</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>3018조 92억 9575만</t>
+  </si>
+  <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>2913조 2571억 3442만</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2408조 7909억 3748만</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>2137조 4087억 8011만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>2118조 7754억 9696만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>198조 8873억 6281만</t>
-  </si>
-  <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>7139조 1억 8544만</t>
-  </si>
-  <si>
-    <t>협의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
-  </si>
-  <si>
-    <t>4248조 2049억 8602만</t>
-  </si>
-  <si>
-    <t>포항엄석대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
-  </si>
-  <si>
-    <t>4094조 124억 4985만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>3018조 92억 9575만</t>
-  </si>
-  <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>2760조 3858억 7806만</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2305조 9264억 9066만</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>2136조 7914억 7532만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2087조 4929억 3128만</t>
+    <t>2096조 8805억 5133만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -713,15 +728,6 @@
     <t>1978조 8306억 8833만</t>
   </si>
   <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>1965조 4376억 7943만</t>
-  </si>
-  <si>
     <t>댜니</t>
   </si>
   <si>
@@ -731,6 +737,15 @@
     <t>1827조 6451억 1194만</t>
   </si>
   <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1588조 266억 9563만</t>
+  </si>
+  <si>
     <t>온백</t>
   </si>
   <si>
@@ -740,22 +755,22 @@
     <t>1583조 4740억 6611만</t>
   </si>
   <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1522조 9920억 6658만</t>
-  </si>
-  <si>
     <t>파울</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1493조 6816억 1073만</t>
+    <t>1575조 8992억 1236만</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1166조 4887억 4672만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -773,22 +788,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1055조 6697억 1936만</t>
+    <t>1068조 7270억 2261만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>1043조 7603억 227만</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1024조 1727억 3300만</t>
+    <t>1049조 1344억 9586만</t>
   </si>
   <si>
     <t>김허덕</t>
@@ -806,7 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>904조 9847억 9661만</t>
+    <t>962조 5525억 4808만</t>
   </si>
   <si>
     <t>마갤</t>
@@ -815,7 +821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>892조 9573억 8284만</t>
+    <t>958조 354억 5369만</t>
   </si>
   <si>
     <t>냐은</t>
@@ -824,7 +830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>853조 2126억 6324만</t>
+    <t>862조 2177억 3466만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -845,7 +851,16 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>757조 3035억 7811만</t>
+    <t>774조 3795억 6668만</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>731조 3900억 9490만</t>
   </si>
   <si>
     <t>전산봉</t>
@@ -854,16 +869,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
   </si>
   <si>
-    <t>715조 9849억 4353만</t>
-  </si>
-  <si>
-    <t>Doham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Doham</t>
-  </si>
-  <si>
-    <t>697조 8345억 1043만</t>
+    <t>716조 1754억 1584만</t>
   </si>
   <si>
     <t>태코찡</t>
@@ -884,7 +890,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>487조 1056억 342만</t>
+    <t>513조 6683억 596만</t>
   </si>
   <si>
     <t>진성팔퀴</t>
@@ -908,6 +914,273 @@
     <t>277조 36억 4103만</t>
   </si>
   <si>
+    <t>가겠습니다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>7363조 6456억 7965만</t>
+  </si>
+  <si>
+    <t>라카도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
+  </si>
+  <si>
+    <t>4642조 6799억 6495만</t>
+  </si>
+  <si>
+    <t>롤대신해야지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>3010조 441억 5351만</t>
+  </si>
+  <si>
+    <t>미우맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
+  </si>
+  <si>
+    <t>2944조 6888억 5738만</t>
+  </si>
+  <si>
+    <t>개종망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>2774조 2722억 1106만</t>
+  </si>
+  <si>
+    <t>명지동꿀주먹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
+  </si>
+  <si>
+    <t>2110조 4594억 9444만</t>
+  </si>
+  <si>
+    <t>gorystalLOVE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
+  </si>
+  <si>
+    <t>2107조 2460억 3000만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
+  </si>
+  <si>
+    <t>2102조 5589억 5859만</t>
+  </si>
+  <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>2088조 9512억 292만</t>
+  </si>
+  <si>
+    <t>커튼월</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
+  </si>
+  <si>
+    <t>2073조 1572억 7673만</t>
+  </si>
+  <si>
+    <t>Judge99</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
+  </si>
+  <si>
+    <t>1871조 9459억 8382만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>1702조 4089억 7976만</t>
+  </si>
+  <si>
+    <t>도리토스치즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1101조 8037억 264만</t>
+  </si>
+  <si>
+    <t>지낌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>929조 6562억 6641만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>926조 8253억 7423만</t>
+  </si>
+  <si>
+    <t>커럭트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>923조 9124억 9450만</t>
+  </si>
+  <si>
+    <t>옥슈쓔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
+  </si>
+  <si>
+    <t>882조 9385억 2064만</t>
+  </si>
+  <si>
+    <t>양룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>856조 3913억 2499만</t>
+  </si>
+  <si>
+    <t>무동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>839조 3372억 8938만</t>
+  </si>
+  <si>
+    <t>또띠야칩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
+  </si>
+  <si>
+    <t>700조 1142억 862만</t>
+  </si>
+  <si>
+    <t>gorystal</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
+  </si>
+  <si>
+    <t>670조 2742억 8324만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>650조 278억 3949만</t>
+  </si>
+  <si>
+    <t>짜상무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>642조 9928억 6971만</t>
+  </si>
+  <si>
+    <t>파파존스맛나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
+  </si>
+  <si>
+    <t>622조 9977억 1292만</t>
+  </si>
+  <si>
+    <t>뀨꾸룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>607조 2543억 4464만</t>
+  </si>
+  <si>
+    <t>복룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>604조 2562억 1967만</t>
+  </si>
+  <si>
+    <t>률율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>533조 6240억 4226만</t>
+  </si>
+  <si>
+    <t>매리골드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>378조 6204억 9767만</t>
+  </si>
+  <si>
+    <t>원종일짱유나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>372조 7777억 7671만</t>
+  </si>
+  <si>
+    <t>문배동육칼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
+  </si>
+  <si>
+    <t>334조 1776억 1349만</t>
+  </si>
+  <si>
     <t>우니아파요</t>
   </si>
   <si>
@@ -920,7 +1193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>5212조 5789억 2707만</t>
+    <t>5443조 3472억 6840만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -929,7 +1202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>3493조 4557억 4453만</t>
+    <t>3802조 2509억 9228만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -938,7 +1211,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3266조 5159억 420만</t>
+    <t>3347조 9436억 1500만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -947,7 +1220,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2442조 7167억 3154만</t>
+    <t>2498조 1000억 4788만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2210조 5639억 7060만</t>
+  </si>
+  <si>
+    <t>이용하다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2174조 9586억 7823만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -956,25 +1247,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>2080조 3777억 6799만</t>
-  </si>
-  <si>
-    <t>이용하다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2056조 4022억 8007만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1933조 7785억 7266만</t>
+    <t>2087조 3274억 6751만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -983,7 +1256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
   </si>
   <si>
-    <t>1765조 4495억 1688만</t>
+    <t>1798조 8570억 3819만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -992,7 +1265,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1649조 1905억 321만</t>
+    <t>1702조 542억 7425만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>1649조 581억 7955만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1001,7 +1283,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>1615조 3693억 8331만</t>
+    <t>1643조 4872억 6754만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1010,16 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>1599조 9170억 8901만</t>
-  </si>
-  <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1551조 3914억 3624만</t>
+    <t>1638조 1855억 1173만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1028,7 +1301,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1441조 7009억 4746만</t>
+    <t>1451조 9418억 545만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1037,7 +1310,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1201조 7967억 40만</t>
+    <t>1220조 8861억 5817만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1055,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>994조 3272억 3938만</t>
+    <t>1078조 1194억 6189만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1064,7 +1337,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>907조 4904억 4570만</t>
+    <t>919조 5977억 4320만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1073,7 +1346,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>854조 7581억 1259만</t>
+    <t>857조 4792억 4510만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1109,7 +1382,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>706조 8416억 9682만</t>
+    <t>722조 8660억 8886만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1118,7 +1391,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
   </si>
   <si>
-    <t>612조 8166억 9275만</t>
+    <t>653조 885억 7543만</t>
+  </si>
+  <si>
+    <t>감화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
+  </si>
+  <si>
+    <t>647조 9162억 3381만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1130,22 +1412,13 @@
     <t>605조 2191억 6874만</t>
   </si>
   <si>
-    <t>감화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
-  </si>
-  <si>
-    <t>563조 6908억 7332만</t>
-  </si>
-  <si>
     <t>계니규니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>561조 2462억 1227만</t>
+    <t>561조 9668억 2613만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1154,7 +1427,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>354조 1700억 1601만</t>
+    <t>357조 8084억 7069만</t>
+  </si>
+  <si>
+    <t>신탄보우짱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
+  </si>
+  <si>
+    <t>319조 5253억 5427만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1163,283 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>290조 9709억 9971만</t>
-  </si>
-  <si>
-    <t>신탄보우짱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
-  </si>
-  <si>
-    <t>266조 7771억 8120만</t>
-  </si>
-  <si>
-    <t>가겠습니다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>7012조 8598억 3928만</t>
-  </si>
-  <si>
-    <t>라카도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
-  </si>
-  <si>
-    <t>4508조 6564억 7698만</t>
-  </si>
-  <si>
-    <t>롤대신해야지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>3010조 441억 5351만</t>
-  </si>
-  <si>
-    <t>미우맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
-  </si>
-  <si>
-    <t>2880조 5219억 5377만</t>
-  </si>
-  <si>
-    <t>개종망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>2774조 2722억 1106만</t>
-  </si>
-  <si>
-    <t>gorystalLOVE</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
-  </si>
-  <si>
-    <t>2107조 2460억 3000만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
-  </si>
-  <si>
-    <t>2102조 5589억 5859만</t>
-  </si>
-  <si>
-    <t>DREAMLINER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
-  </si>
-  <si>
-    <t>2088조 9512억 292만</t>
-  </si>
-  <si>
-    <t>명지동꿀주먹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
-  </si>
-  <si>
-    <t>2020조 946억 579만</t>
-  </si>
-  <si>
-    <t>커튼월</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
-  </si>
-  <si>
-    <t>1996조 4869억 4418만</t>
-  </si>
-  <si>
-    <t>천요화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
-  </si>
-  <si>
-    <t>1688조 5580억 5122만</t>
-  </si>
-  <si>
-    <t>Judge99</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
-  </si>
-  <si>
-    <t>1557조 2266억 9080만</t>
-  </si>
-  <si>
-    <t>도리토스치즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1083조 8247억 6506만</t>
-  </si>
-  <si>
-    <t>커럭트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>917조 5410억 5538만</t>
-  </si>
-  <si>
-    <t>지낌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>910조 5435억 2039만</t>
-  </si>
-  <si>
-    <t>스툭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
-  </si>
-  <si>
-    <t>852조 4657억 9247만</t>
-  </si>
-  <si>
-    <t>옥슈쓔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
-  </si>
-  <si>
-    <t>820조 8492억 573만</t>
-  </si>
-  <si>
-    <t>무동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>817조 4820억 228만</t>
-  </si>
-  <si>
-    <t>양룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>740조 3045억 100만</t>
-  </si>
-  <si>
-    <t>또띠야칩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
-  </si>
-  <si>
-    <t>673조 8450억 5753만</t>
-  </si>
-  <si>
-    <t>gorystal</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
-  </si>
-  <si>
-    <t>660조 996억 2701만</t>
-  </si>
-  <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>647조 3034억 4911만</t>
-  </si>
-  <si>
-    <t>파파존스맛나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
-  </si>
-  <si>
-    <t>622조 9977억 1292만</t>
-  </si>
-  <si>
-    <t>복룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>596조 708억 6773만</t>
-  </si>
-  <si>
-    <t>뀨꾸룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>580조 1477억 3106만</t>
-  </si>
-  <si>
-    <t>짜상무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>567조 446억 7561만</t>
-  </si>
-  <si>
-    <t>률율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>533조 6240억 4226만</t>
-  </si>
-  <si>
-    <t>매리골드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>378조 6204억 9767만</t>
-  </si>
-  <si>
-    <t>원종일짱유나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>368조 5953억 1098만</t>
-  </si>
-  <si>
-    <t>문배동육칼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
-  </si>
-  <si>
-    <t>327조 4344억 9180만</t>
+    <t>293조 5919억 845만</t>
   </si>
   <si>
     <t>강댜</t>
@@ -1451,7 +1457,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 4216조 2820억 322만</t>
+    <t>1경 6336조 4105억 2176만</t>
   </si>
   <si>
     <t>빵녕</t>
@@ -1460,13 +1466,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%EB%85%95</t>
   </si>
   <si>
-    <t>1경 467조 3568억 1596만</t>
+    <t>1경 857조 5808억 4596만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B6%A9%EB%91%98%EA%B8%B0</t>
   </si>
   <si>
-    <t>7770조 1716억 5948만</t>
+    <t>9044조 5156억 5749만</t>
   </si>
   <si>
     <t>실프</t>
@@ -1511,7 +1517,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>820조 3411억 5600만</t>
+    <t>876조 5433억 6568만</t>
   </si>
   <si>
     <t>더대충</t>
@@ -1520,7 +1526,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EB%8C%80%EC%B6%A9</t>
   </si>
   <si>
-    <t>785조 4568억 4635만</t>
+    <t>859조 3819억 8674만</t>
   </si>
   <si>
     <t>그복</t>
@@ -1529,7 +1535,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%B3%B5</t>
   </si>
   <si>
-    <t>654조 113억 3869만</t>
+    <t>672조 8664억 6832만</t>
   </si>
   <si>
     <t>갈매기</t>
@@ -1547,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%94%EC%A0%81%EB%8B%B9</t>
   </si>
   <si>
-    <t>573조 7669억 9172만</t>
+    <t>593조 8281억 8065만</t>
   </si>
   <si>
     <t>끼꼬</t>
@@ -1556,7 +1562,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%BC%EA%BC%AC</t>
   </si>
   <si>
-    <t>572조 1815억 1954만</t>
+    <t>577조 3282억 4734만</t>
   </si>
   <si>
     <t>냥찐</t>
@@ -1565,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%A5%EC%B0%90</t>
   </si>
   <si>
-    <t>518조 6793억 8787만</t>
+    <t>533조 438억 2602만</t>
   </si>
   <si>
     <t>꿀꿀이의모험</t>
@@ -1574,7 +1580,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EA%BF%80%EC%9D%B4%EC%9D%98%EB%AA%A8%ED%97%98</t>
   </si>
   <si>
-    <t>456조 9713억 8567만</t>
+    <t>469조 9974억 1332만</t>
   </si>
   <si>
     <t>사랑해제명</t>
@@ -1583,7 +1589,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%9E%91%ED%95%B4%EC%A0%9C%EB%AA%85</t>
   </si>
   <si>
-    <t>437조 6914억 193만</t>
+    <t>468조 6750억 5243만</t>
   </si>
   <si>
     <t>시루</t>
@@ -1592,7 +1598,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%A3%A8</t>
   </si>
   <si>
-    <t>376조 7036억 8882만</t>
+    <t>383조 2113억 1869만</t>
   </si>
   <si>
     <t>퍄딤</t>
@@ -1610,7 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%8A%A4%ED%86%A0%EB%A6%AC</t>
   </si>
   <si>
-    <t>346조 1419억 5418만</t>
+    <t>355조 2774억 7686만</t>
   </si>
   <si>
     <t>달디달고나</t>
@@ -1631,7 +1637,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%99</t>
   </si>
   <si>
-    <t>215조 4742억 8912만</t>
+    <t>253조 6928억 4279만</t>
   </si>
   <si>
     <t>초코파베</t>
@@ -1640,7 +1646,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%ED%8C%8C%EB%B2%A0</t>
   </si>
   <si>
-    <t>194조 1738억 924만</t>
+    <t>206조 6209억 3299만</t>
   </si>
   <si>
     <t>한굥굥</t>
@@ -1658,7 +1664,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B7%A8%EB%9E%80</t>
   </si>
   <si>
-    <t>166조 650억 3497만</t>
+    <t>171조 8434억 9241만</t>
   </si>
   <si>
     <t>홀인원</t>
@@ -1685,7 +1691,19 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EC%A1%8D</t>
   </si>
   <si>
-    <t>131조 1231억 9174만</t>
+    <t>136조 4932억 1805만</t>
+  </si>
+  <si>
+    <t>꾸륭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%AD</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>128조 8288억 525만</t>
   </si>
   <si>
     <t>홍뎐잉</t>
@@ -1698,18 +1716,6 @@
   </si>
   <si>
     <t>119조 3425억 9122만</t>
-  </si>
-  <si>
-    <t>꾸륭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%AD</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>116조 2818억 1284만</t>
   </si>
   <si>
     <t>허숖</t>
@@ -2261,30 +2267,30 @@
         <v>41</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2293,39 +2299,39 @@
         <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -2334,16 +2340,16 @@
         <v>30</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -2378,28 +2384,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2410,28 +2416,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2442,28 +2448,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2474,28 +2480,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2506,28 +2512,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2538,28 +2544,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2570,28 +2576,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2602,28 +2608,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2634,28 +2640,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2666,28 +2672,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2698,28 +2704,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2730,28 +2736,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2762,28 +2768,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2794,28 +2800,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2826,28 +2832,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2858,28 +2864,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2890,28 +2896,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2922,28 +2928,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2954,28 +2960,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2986,28 +2992,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3018,28 +3024,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3050,28 +3056,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3082,28 +3088,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3114,28 +3120,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3146,28 +3152,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3178,28 +3184,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3210,28 +3216,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3242,28 +3248,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3274,28 +3280,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>193</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3306,28 +3312,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3390,28 +3396,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3422,28 +3428,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3454,28 +3460,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3486,28 +3492,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3518,28 +3524,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3550,28 +3556,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3582,28 +3588,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3614,28 +3620,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3646,28 +3652,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3678,28 +3684,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3710,28 +3716,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3742,28 +3748,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3774,28 +3780,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3806,28 +3812,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3838,28 +3844,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3870,28 +3876,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3902,28 +3908,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3934,28 +3940,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3966,28 +3972,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>251</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3998,28 +4004,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4030,28 +4036,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4062,28 +4068,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4094,28 +4100,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4126,28 +4132,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4158,28 +4164,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4190,28 +4196,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4222,28 +4228,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4254,28 +4260,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4286,28 +4292,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4318,28 +4324,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4350,28 +4356,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4422,7 +4428,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -4435,28 +4441,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4467,31 +4473,31 @@
         <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4499,31 +4505,31 @@
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4531,31 +4537,31 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4563,31 +4569,31 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>286</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4595,31 +4601,31 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4627,31 +4633,31 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4659,31 +4665,31 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4691,31 +4697,31 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4723,31 +4729,31 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4755,31 +4761,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4787,31 +4793,31 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4819,31 +4825,31 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4851,31 +4857,31 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4883,31 +4889,31 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4915,31 +4921,31 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4947,31 +4953,31 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4979,31 +4985,31 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -5011,31 +5017,31 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -5043,31 +5049,31 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -5075,31 +5081,31 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>273</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -5107,31 +5113,31 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>193</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -5139,31 +5145,31 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -5171,31 +5177,31 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>193</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>102</v>
+        <v>173</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -5203,31 +5209,31 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -5235,31 +5241,31 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -5267,31 +5273,31 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -5299,31 +5305,31 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -5331,31 +5337,31 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>76</v>
+        <v>286</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -5363,31 +5369,31 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>188</v>
+        <v>99</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -5395,31 +5401,31 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -5467,7 +5473,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -5480,28 +5486,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5509,962 +5515,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>284</v>
+        <v>94</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>48</v>
+        <v>401</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>401</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>221</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>198</v>
+        <v>126</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>271</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H25" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="I25" s="2" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>221</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>198</v>
+        <v>94</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6516,7 +6522,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6525,28 +6531,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6554,962 +6560,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>134</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="H14" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -123,7 +123,7 @@
     <t>5경 985조 128억 1537만</t>
   </si>
   <si>
-    <t>셀린느2군 IN 300위분들   귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -222,7 +222,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8188조 1,046억 1,273만</t>
+    <t>8188조 1046억 1273만</t>
   </si>
   <si>
     <t>2</t>
@@ -240,7 +240,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>6992조 3,764억 4,633만</t>
+    <t>6992조 3764억 4633만</t>
   </si>
   <si>
     <t>3</t>
@@ -255,7 +255,7 @@
     <t>바이퍼</t>
   </si>
   <si>
-    <t>4402조 1,032억 4,015만</t>
+    <t>4402조 1032억 4015만</t>
   </si>
   <si>
     <t>4</t>
@@ -273,7 +273,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>4094조 124억 4,985만</t>
+    <t>4094조 124억 4985만</t>
   </si>
   <si>
     <t>5</t>
@@ -288,7 +288,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>3303조 6,174억 3,840만</t>
+    <t>3303조 6174억 3840만</t>
   </si>
   <si>
     <t>6</t>
@@ -303,7 +303,7 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>2988조 9,066억 1,886만</t>
+    <t>2988조 9066억 1886만</t>
   </si>
   <si>
     <t>7</t>
@@ -318,7 +318,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2424조 9,978억 2,159만</t>
+    <t>2424조 9978억 2159만</t>
   </si>
   <si>
     <t>8</t>
@@ -333,37 +333,37 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>2269조 6,121억 182만</t>
+    <t>2290조 8654억 1226만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2279조 9226억 7885만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>지존빼앙</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2224조 5,091억 9,296만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>2182조 5,730억 5,749만</t>
+    <t>2224조 5091억 9296만</t>
   </si>
   <si>
     <t>11</t>
@@ -375,7 +375,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
   </si>
   <si>
-    <t>1978조 8,306억 8,833만</t>
+    <t>1978조 8306억 8833만</t>
   </si>
   <si>
     <t>12</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1831조 4,812억 8,418만</t>
+    <t>1831조 4812억 8418만</t>
   </si>
   <si>
     <t>13</t>
@@ -402,7 +402,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>1814조 2,226억 6,845만</t>
+    <t>1814조 2226억 6845만</t>
   </si>
   <si>
     <t>14</t>
@@ -414,7 +414,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
   </si>
   <si>
-    <t>1766조 7,006억 9,923만</t>
+    <t>1766조 7006억 9923만</t>
   </si>
   <si>
     <t>15</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1596조 5,749억 9,080만</t>
+    <t>1596조 5749억 9080만</t>
   </si>
   <si>
     <t>16</t>
@@ -438,7 +438,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1240조 6,809억 9,149만</t>
+    <t>1240조 6809억 9149만</t>
   </si>
   <si>
     <t>17</t>
@@ -450,7 +450,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>1213조 7,003억 6,444만</t>
+    <t>1213조 7003억 6444만</t>
   </si>
   <si>
     <t>18</t>
@@ -465,7 +465,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>1149조 8,047억 287만</t>
+    <t>1149조 8047억 287만</t>
   </si>
   <si>
     <t>19</t>
@@ -477,7 +477,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1091조 9,888억 5,564만</t>
+    <t>1091조 9888억 5564만</t>
   </si>
   <si>
     <t>20</t>
@@ -489,7 +489,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1050조 4,181억 3,112만</t>
+    <t>1050조 4181억 3112만</t>
   </si>
   <si>
     <t>21</t>
@@ -501,7 +501,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1046조 865억 5,975만</t>
+    <t>1046조 865억 5975만</t>
   </si>
   <si>
     <t>22</t>
@@ -513,7 +513,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
   </si>
   <si>
-    <t>1033조 7,202억 5,586만</t>
+    <t>1033조 7202억 5586만</t>
   </si>
   <si>
     <t>23</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1015조 5,704억 3,498만</t>
+    <t>1015조 5704억 3498만</t>
   </si>
   <si>
     <t>24</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>799조 5,234억 8,229만</t>
+    <t>799조 5234억 8229만</t>
   </si>
   <si>
     <t>25</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>796조 5,685억 5,174만</t>
+    <t>796조 5685억 5174만</t>
   </si>
   <si>
     <t>26</t>
@@ -564,7 +564,7 @@
     <t>109</t>
   </si>
   <si>
-    <t>765조 9,289억 1,162만</t>
+    <t>765조 9289억 1162만</t>
   </si>
   <si>
     <t>27</t>
@@ -576,7 +576,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>747조 6,533억 1,496만</t>
+    <t>747조 6533억 1496만</t>
   </si>
   <si>
     <t>28</t>
@@ -588,7 +588,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>665조 2,579억 6,198만</t>
+    <t>665조 2579억 6198만</t>
   </si>
   <si>
     <t>29</t>
@@ -603,7 +603,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>649조 5,527억 6,316만</t>
+    <t>649조 5527억 6316만</t>
   </si>
   <si>
     <t>30</t>
@@ -615,7 +615,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
   </si>
   <si>
-    <t>277조 36억 4,103만</t>
+    <t>277조 36억 4103만</t>
   </si>
   <si>
     <t>김치싸대기</t>
@@ -624,7 +624,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
   </si>
   <si>
-    <t>9713조 4,850억 8,781만</t>
+    <t>9713조 4850억 8781만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -633,7 +633,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>6465조 5,267억 4,688만</t>
+    <t>6465조 5267억 4688만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -642,7 +642,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>3686조 3,442억 6,715만</t>
+    <t>3686조 3442억 6715만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -651,7 +651,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3586조 4,643억 9,612만</t>
+    <t>3586조 4643억 9612만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -660,7 +660,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3469조 8,887억 4,598만</t>
+    <t>3469조 8887억 4598만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2483조 8,452억 3,773만</t>
+    <t>2483조 8452억 3773만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -678,7 +678,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2417조 4,217억 703만</t>
+    <t>2431조 544억 4930만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -687,13 +687,13 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1905조 4,587억 3,879만</t>
+    <t>1905조 4587억 3879만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>1831조 3,912억 3,225만</t>
+    <t>1831조 3912억 3225만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -705,7 +705,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>1825조 2,398억 5,085만</t>
+    <t>1825조 2398억 5085만</t>
   </si>
   <si>
     <t>야가다</t>
@@ -714,7 +714,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
   </si>
   <si>
-    <t>1697조 755억 7,134만</t>
+    <t>1697조 755억 7134만</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -726,7 +726,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1259조 8,128억 5,685만</t>
+    <t>1259조 8128억 5685만</t>
   </si>
   <si>
     <t>우후</t>
@@ -735,7 +735,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1058조 2,431억 2,633만</t>
+    <t>1058조 2431억 2633만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -744,7 +744,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1052조 9,891억 7,693만</t>
+    <t>1052조 9891억 7693만</t>
   </si>
   <si>
     <t>채무조정</t>
@@ -753,7 +753,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1006조 7,349억 1,730만</t>
+    <t>1006조 7349억 1730만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -762,7 +762,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>987조 2,843억 9,824만</t>
+    <t>987조 2843억 9824만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -771,7 +771,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>926조 2,055억 4,066만</t>
+    <t>928조 8138억 6047만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -780,7 +780,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>914조 9,534억 4,237만</t>
+    <t>914조 9534억 4237만</t>
   </si>
   <si>
     <t>정태준</t>
@@ -789,7 +789,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>864조 6,290억 5,998만</t>
+    <t>864조 6290억 5998만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -798,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>560조 1,285억 7,637만</t>
+    <t>560조 1285억 7637만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -807,7 +807,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>532조 1,581억 8,976만</t>
+    <t>532조 1581억 8976만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -816,7 +816,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>459조 5,489억 3,382만</t>
+    <t>459조 5489억 3382만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -825,7 +825,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>420조 8,785억 9,592만</t>
+    <t>420조 8785억 9592만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -834,7 +834,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>410조 5,852억 7,919만</t>
+    <t>410조 5852억 7919만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -843,7 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>372조 4,821억 9,681만</t>
+    <t>372조 4821억 9681만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -852,7 +852,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
   </si>
   <si>
-    <t>275조 6,869억 3,523만</t>
+    <t>275조 6869억 3523만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -861,7 +861,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>249조 9,325억 1,140만</t>
+    <t>249조 9325억 1140만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -873,7 +873,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>245조 4,859억 3,395만</t>
+    <t>245조 4859억 3395만</t>
   </si>
   <si>
     <t>가겠습니다</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>7363조 6,456억 7,965만</t>
+    <t>7363조 6456억 7965만</t>
   </si>
   <si>
     <t>라카도</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4712조 790억 3,428만</t>
+    <t>4712조 790억 3428만</t>
   </si>
   <si>
     <t>롤대신해야지</t>
@@ -900,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
   </si>
   <si>
-    <t>3728조 6,519억 2,880만</t>
+    <t>3728조 6519억 2880만</t>
   </si>
   <si>
     <t>미우맘</t>
@@ -909,7 +909,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
   </si>
   <si>
-    <t>3003조 1,592억 9,722만</t>
+    <t>3003조 1592억 9722만</t>
   </si>
   <si>
     <t>개종망겜</t>
@@ -918,7 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
   </si>
   <si>
-    <t>2774조 2,722억 1,106만</t>
+    <t>2774조 2722억 1106만</t>
   </si>
   <si>
     <t>커튼월</t>
@@ -927,7 +927,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>2479조 6,616억 3,099만</t>
+    <t>2479조 6616억 3099만</t>
   </si>
   <si>
     <t>gorystalLOVE</t>
@@ -936,7 +936,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
   </si>
   <si>
-    <t>2290조 9,695억 1,564만</t>
+    <t>2290조 9695억 1564만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -945,7 +945,7 @@
     <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
   </si>
   <si>
-    <t>2274조 2,104억 2,874만</t>
+    <t>2274조 2104억 2874만</t>
   </si>
   <si>
     <t>명지동꿀주먹</t>
@@ -954,7 +954,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>2258조 2,854억 4,445만</t>
+    <t>2258조 2854억 4445만</t>
   </si>
   <si>
     <t>Judge99</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=Judge99</t>
   </si>
   <si>
-    <t>2185조 696억 5,500만</t>
+    <t>2185조 696억 5500만</t>
   </si>
   <si>
     <t>천요화</t>
@@ -972,13 +972,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
   </si>
   <si>
-    <t>2161조 3,214억 2,617만</t>
+    <t>2161조 3214억 2617만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
   </si>
   <si>
-    <t>2102조 5,589억 5,859만</t>
+    <t>2102조 5589억 5859만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -987,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1400조 5,111억 4,442만</t>
+    <t>1400조 5111억 4442만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -996,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1028조 843억 4,082만</t>
+    <t>1028조 843억 4082만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -1005,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
   </si>
   <si>
-    <t>965조 5,474억 7,452만</t>
+    <t>965조 5474억 7452만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -1014,7 +1014,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>951조 7,711억 3,126만</t>
+    <t>951조 7711억 3126만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -1023,7 +1023,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
   </si>
   <si>
-    <t>923조 9,124억 9,450만</t>
+    <t>923조 9124억 9450만</t>
   </si>
   <si>
     <t>양룽</t>
@@ -1032,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
   </si>
   <si>
-    <t>867조 2,556억 5,423만</t>
+    <t>867조 2556억 5423만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -1041,7 +1041,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
   </si>
   <si>
-    <t>847조 3,200억 1,616만</t>
+    <t>847조 3200억 1616만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1050,7 +1050,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>738조 8,419억 1,124만</t>
+    <t>738조 8419억 1124만</t>
   </si>
   <si>
     <t>욧츠</t>
@@ -1059,7 +1059,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
   </si>
   <si>
-    <t>732조 6,506억 5,328만</t>
+    <t>732조 6506억 5328만</t>
   </si>
   <si>
     <t>gorystal</t>
@@ -1068,7 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>715조 4,194억 1,453만</t>
+    <t>715조 4194억 1453만</t>
   </si>
   <si>
     <t>복룽</t>
@@ -1077,7 +1077,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>710조 5,967억 7,854만</t>
+    <t>710조 5967억 7854만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1086,7 +1086,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
   </si>
   <si>
-    <t>657조 7,522억 2,440만</t>
+    <t>657조 7522억 2440만</t>
   </si>
   <si>
     <t>뀨꾸룽</t>
@@ -1095,7 +1095,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
   </si>
   <si>
-    <t>656조 7,617억 4,920만</t>
+    <t>656조 7617억 4920만</t>
   </si>
   <si>
     <t>짜상무</t>
@@ -1104,7 +1104,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
   </si>
   <si>
-    <t>642조 9,928억 6,971만</t>
+    <t>642조 9928억 6971만</t>
   </si>
   <si>
     <t>률율율</t>
@@ -1113,7 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>547조 1,538억 8,441만</t>
+    <t>547조 1538억 8441만</t>
   </si>
   <si>
     <t>매리골드</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>389조 9,183억 6,640만</t>
+    <t>389조 9183억 6640만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -1131,7 +1131,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>372조 7,777억 7,671만</t>
+    <t>372조 7777억 7671만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1140,13 +1140,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>334조 1,776억 1,349만</t>
+    <t>334조 1776억 1349만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>5731조 3,781억 8,495만</t>
+    <t>5731조 3781억 8495만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1155,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EB%8B%88%EC%95%84%ED%8C%8C%EC%9A%94</t>
   </si>
   <si>
-    <t>5708조 2,885억 4,200만</t>
+    <t>5708조 2885억 4200만</t>
   </si>
   <si>
     <t>도하리</t>
@@ -1164,7 +1164,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
   </si>
   <si>
-    <t>3802조 2,509억 9,228만</t>
+    <t>3802조 2509억 9228만</t>
   </si>
   <si>
     <t>죽창당일개통</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3347조 9,436억 1,500만</t>
+    <t>3347조 9436억 1500만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1182,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2706조 7,527억 6,350만</t>
+    <t>2706조 7527억 6350만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -1191,7 +1191,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2216조 4,022억 554만</t>
+    <t>2216조 4022억 554만</t>
   </si>
   <si>
     <t>여니워니</t>
@@ -1200,7 +1200,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
   </si>
   <si>
-    <t>2210조 5,639억 7,060만</t>
+    <t>2210조 5639억 7060만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1209,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>2204조 873억 8,415만</t>
+    <t>2204조 873억 8415만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1218,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>2094조 3,509억 5,174만</t>
+    <t>2094조 3509억 5174만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
   </si>
   <si>
-    <t>1842조 5,559억 6,212만</t>
+    <t>1842조 5559억 6212만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1236,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1733조 9,308억 7,806만</t>
+    <t>1733조 9308억 7806만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1245,7 +1245,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>1649조 581억 7,955만</t>
+    <t>1649조 581억 7955만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1254,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>1643조 4,872억 6,754만</t>
+    <t>1643조 4872억 6754만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1263,7 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
   </si>
   <si>
-    <t>1532조 7,337억 2,070만</t>
+    <t>1532조 7337억 2070만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1272,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1451조 9,418억 545만</t>
+    <t>1451조 9418억 545만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1281,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1319조 5,858억 7,337만</t>
+    <t>1319조 5858억 7337만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1290,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1098조 1,848억 4,864만</t>
+    <t>1098조 1848억 4864만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1299,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>925조 8,925억 1,529만</t>
+    <t>925조 8925억 1529만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1308,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>902조 2,941억 6,618만</t>
+    <t>902조 2941억 6618만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1317,7 +1317,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>884조 6,876억 1,268만</t>
+    <t>884조 6876억 1268만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1326,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>881조 2,976억 2,492만</t>
+    <t>881조 2976억 2492만</t>
   </si>
   <si>
     <t>박금쪽</t>
@@ -1335,7 +1335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
   </si>
   <si>
-    <t>804조 4,549억 516만</t>
+    <t>804조 4549억 516만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1344,7 +1344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>738조 7,041억 4,433만</t>
+    <t>738조 7041억 4433만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1353,7 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>737조 1,909억 7,080만</t>
+    <t>737조 1909억 7080만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1362,7 +1362,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%96%B4%EB%A1%9C%ED%98%B8%EA%B1%B8</t>
   </si>
   <si>
-    <t>725조 7,659억 853만</t>
+    <t>725조 7659억 853만</t>
   </si>
   <si>
     <t>작업치료사</t>
@@ -1371,7 +1371,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
   </si>
   <si>
-    <t>627조 1,553억 6,314만</t>
+    <t>627조 1553억 6314만</t>
   </si>
   <si>
     <t>계니규니</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>563조 6,801억 7,647만</t>
+    <t>563조 6801억 7647만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1389,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>448조 4,913억 2,823만</t>
+    <t>448조 4913억 2823만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>368조 1,032억 9,070만</t>
+    <t>368조 1032억 9070만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1407,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>310조 1,700억 7,637만</t>
+    <t>310조 1700억 7637만</t>
   </si>
 </sst>
 </file>
@@ -2014,7 +2014,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2326,13 +2326,13 @@
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2343,25 +2343,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>112</v>
@@ -2390,7 +2390,7 @@
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>81</v>
@@ -2553,7 +2553,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>137</v>
@@ -2585,7 +2585,7 @@
         <v>101</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>141</v>
@@ -2649,7 +2649,7 @@
         <v>101</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>150</v>
@@ -2713,7 +2713,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
@@ -2745,7 +2745,7 @@
         <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>162</v>
@@ -2809,7 +2809,7 @@
         <v>124</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>170</v>
@@ -2937,7 +2937,7 @@
         <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>187</v>
@@ -2969,7 +2969,7 @@
         <v>191</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>192</v>
@@ -3058,7 +3058,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3181,7 +3181,7 @@
         <v>91</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>205</v>
@@ -3373,7 +3373,7 @@
         <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>222</v>
@@ -3387,7 +3387,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>223</v>
@@ -3405,7 +3405,7 @@
         <v>225</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>226</v>
@@ -3469,7 +3469,7 @@
         <v>232</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>233</v>
@@ -3565,7 +3565,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>242</v>
@@ -3597,7 +3597,7 @@
         <v>124</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>245</v>
@@ -3658,7 +3658,7 @@
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>178</v>
@@ -3693,7 +3693,7 @@
         <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>254</v>
@@ -4037,7 +4037,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4125,7 +4125,7 @@
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>64</v>
@@ -4366,7 +4366,7 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>310</v>
@@ -4480,7 +4480,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>320</v>
@@ -4512,7 +4512,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>323</v>
@@ -4544,7 +4544,7 @@
         <v>91</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>326</v>
@@ -4573,7 +4573,7 @@
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>145</v>
@@ -4605,7 +4605,7 @@
         <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>96</v>
@@ -4640,7 +4640,7 @@
         <v>101</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>335</v>
@@ -4704,7 +4704,7 @@
         <v>69</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>341</v>
@@ -4736,7 +4736,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>344</v>
@@ -4768,7 +4768,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>347</v>
@@ -4800,7 +4800,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>350</v>
@@ -4864,7 +4864,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>356</v>
@@ -4992,7 +4992,7 @@
         <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>368</v>
@@ -5021,7 +5021,7 @@
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>178</v>
@@ -5082,7 +5082,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5138,7 +5138,7 @@
         <v>140</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>70</v>
@@ -5365,7 +5365,7 @@
         <v>101</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>394</v>
@@ -5411,7 +5411,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>398</v>
@@ -5554,10 +5554,10 @@
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>412</v>
@@ -5621,7 +5621,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>418</v>
@@ -5714,10 +5714,10 @@
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>427</v>
@@ -5749,7 +5749,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>430</v>
@@ -5973,7 +5973,7 @@
         <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>451</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -78,7 +78,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>858</t>
+    <t>864</t>
   </si>
   <si>
     <t>31위</t>
@@ -111,7 +111,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>841</t>
+    <t>845</t>
   </si>
   <si>
     <t>37위</t>
@@ -138,7 +138,7 @@
     <t>Scania 18</t>
   </si>
   <si>
-    <t>894</t>
+    <t>896</t>
   </si>
   <si>
     <t>16위</t>
@@ -165,7 +165,7 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>884</t>
+    <t>885</t>
   </si>
   <si>
     <t>38위</t>
@@ -222,7 +222,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>8188조 1046억 1273만</t>
+    <t>8217조 5797억 1907만</t>
   </si>
   <si>
     <t>2</t>
@@ -240,7 +240,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>6992조 3764억 4633만</t>
+    <t>7449조 4009억 54만</t>
   </si>
   <si>
     <t>3</t>
@@ -303,12 +303,27 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>2988조 9066억 1886만</t>
+    <t>2993조 5억 2522만</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>2465조 3877억 3257만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>포항가자미</t>
   </si>
   <si>
@@ -318,22 +333,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2424조 9978억 2159만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>2290조 8654억 1226만</t>
+    <t>2432조 7584억 4757만</t>
   </si>
   <si>
     <t>9</t>
@@ -363,7 +363,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2224조 5091억 9296만</t>
+    <t>2255조 9124억 1422만</t>
   </si>
   <si>
     <t>11</t>
@@ -387,7 +387,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>1831조 4812억 8418만</t>
+    <t>1833조 7180억 5399만</t>
   </si>
   <si>
     <t>13</t>
@@ -402,7 +402,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>1814조 2226억 6845만</t>
+    <t>1830조 1973억 356만</t>
   </si>
   <si>
     <t>14</t>
@@ -426,7 +426,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
   </si>
   <si>
-    <t>1596조 5749억 9080만</t>
+    <t>1725조 492억 8770만</t>
   </si>
   <si>
     <t>16</t>
@@ -477,7 +477,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1091조 9888억 5564만</t>
+    <t>1101조 5798억 4738만</t>
   </si>
   <si>
     <t>20</t>
@@ -489,7 +489,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1050조 4181억 3112만</t>
+    <t>1050조 6512억 3068만</t>
   </si>
   <si>
     <t>21</t>
@@ -501,7 +501,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
   </si>
   <si>
-    <t>1046조 865억 5975만</t>
+    <t>1047조 2041억 8654만</t>
   </si>
   <si>
     <t>22</t>
@@ -525,7 +525,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
   </si>
   <si>
-    <t>1015조 5704억 3498만</t>
+    <t>1018조 127억 2969만</t>
   </si>
   <si>
     <t>24</t>
@@ -537,7 +537,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>799조 5234억 8229만</t>
+    <t>826조 4642억 7332만</t>
   </si>
   <si>
     <t>25</t>
@@ -549,7 +549,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>796조 5685억 5174만</t>
+    <t>819조 1516억 3816만</t>
   </si>
   <si>
     <t>26</t>
@@ -651,7 +651,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>3586조 4643억 9612만</t>
+    <t>3648조 8531억 6875만</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -660,7 +660,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>3469조 8887억 4598만</t>
+    <t>3531조 2793억 8113만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -669,7 +669,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2483조 8452억 3773만</t>
+    <t>2484조 5237억 5157만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -678,7 +678,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2431조 544억 4930만</t>
+    <t>2443조 1439억 5824만</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>2043조 9656억 4336만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -687,7 +699,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>1905조 4587억 3879만</t>
+    <t>1905조 6059억 8847만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
@@ -696,18 +708,6 @@
     <t>1831조 3912억 3225만</t>
   </si>
   <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>1825조 2398억 5085만</t>
-  </si>
-  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -726,7 +726,25 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1259조 8128억 5685만</t>
+    <t>1265조 7396억 7046만</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1065조 650억 5642만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1062조 1444억 674만</t>
   </si>
   <si>
     <t>우후</t>
@@ -735,25 +753,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>1058조 2431억 2633만</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1052조 9891억 7693만</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>1006조 7349억 1730만</t>
+    <t>1058조 5051억 8293만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -771,7 +771,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
   </si>
   <si>
-    <t>928조 8138억 6047만</t>
+    <t>930조 1939억 3217만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -798,7 +798,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
   </si>
   <si>
-    <t>560조 1285억 7637만</t>
+    <t>560조 3492억 2985만</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -816,7 +816,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
   </si>
   <si>
-    <t>459조 5489억 3382만</t>
+    <t>524조 8468억 7860만</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>440조 6040억 4040만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -825,16 +834,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>420조 8785억 9592만</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>410조 5852억 7919만</t>
+    <t>425조 1582억 57만</t>
   </si>
   <si>
     <t>솔인</t>
@@ -843,7 +843,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>372조 4821억 9681만</t>
+    <t>420조 9657억 7177만</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>325조 1469억 5466만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -861,19 +873,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>249조 9325억 1140만</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>245조 4859억 3395만</t>
+    <t>254조 6783억 7167만</t>
   </si>
   <si>
     <t>가겠습니다</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>7363조 6456억 7965만</t>
+    <t>7433조 909억 8318만</t>
   </si>
   <si>
     <t>라카도</t>
@@ -891,7 +891,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4712조 790억 3428만</t>
+    <t>4934조 5246억 3849만</t>
   </si>
   <si>
     <t>롤대신해야지</t>
@@ -900,7 +900,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
   </si>
   <si>
-    <t>3728조 6519억 2880만</t>
+    <t>3818조 9392억 1956만</t>
+  </si>
+  <si>
+    <t>개종망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>3293조 8550억 2424만</t>
   </si>
   <si>
     <t>미우맘</t>
@@ -909,16 +918,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
   </si>
   <si>
-    <t>3003조 1592억 9722만</t>
-  </si>
-  <si>
-    <t>개종망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>2774조 2722억 1106만</t>
+    <t>3005조 5830억 1775만</t>
   </si>
   <si>
     <t>커튼월</t>
@@ -927,7 +927,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>2479조 6616억 3099만</t>
+    <t>2565조 4727억 9671만</t>
   </si>
   <si>
     <t>gorystalLOVE</t>
@@ -936,7 +936,25 @@
     <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
   </si>
   <si>
-    <t>2290조 9695억 1564만</t>
+    <t>2330조 1458억 535만</t>
+  </si>
+  <si>
+    <t>Judge99</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
+  </si>
+  <si>
+    <t>2311조 2928억 2700만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>2281조 3425억 5886만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -954,31 +972,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>2258조 2854억 4445만</t>
-  </si>
-  <si>
-    <t>Judge99</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
-  </si>
-  <si>
-    <t>2185조 696억 5500만</t>
-  </si>
-  <si>
-    <t>천요화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
-  </si>
-  <si>
-    <t>2161조 3214억 2617만</t>
+    <t>2267조 5467억 7182만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
   </si>
   <si>
-    <t>2102조 5589억 5859만</t>
+    <t>2136조 215억 9493만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -987,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1400조 5111억 4442만</t>
+    <t>1404조 9900억 92만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -996,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1028조 843억 4082만</t>
+    <t>1034조 6450억 3558만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -1032,7 +1032,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
   </si>
   <si>
-    <t>867조 2556억 5423만</t>
+    <t>911조 1863억 1172만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -1041,7 +1041,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
   </si>
   <si>
-    <t>847조 3200억 1616만</t>
+    <t>862조 9057억 2979만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>767조 3552억 915만</t>
+  </si>
+  <si>
+    <t>gorystal</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
+  </si>
+  <si>
+    <t>760조 7239억 7368만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1050,25 +1068,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>738조 8419억 1124만</t>
-  </si>
-  <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>732조 6506억 5328만</t>
-  </si>
-  <si>
-    <t>gorystal</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
-  </si>
-  <si>
-    <t>715조 4194억 1453만</t>
+    <t>741조 519억 8746만</t>
   </si>
   <si>
     <t>복룽</t>
@@ -1077,7 +1077,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>710조 5967억 7854만</t>
+    <t>727조 7112억 1208만</t>
+  </si>
+  <si>
+    <t>뀨꾸룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>665조 3726억 2336만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1089,22 +1098,13 @@
     <t>657조 7522억 2440만</t>
   </si>
   <si>
-    <t>뀨꾸룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>656조 7617억 4920만</t>
-  </si>
-  <si>
     <t>짜상무</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
   </si>
   <si>
-    <t>642조 9928억 6971만</t>
+    <t>645조 4219억 2412만</t>
   </si>
   <si>
     <t>률율율</t>
@@ -1113,7 +1113,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>547조 1538억 8441만</t>
+    <t>603조 203억 6747만</t>
   </si>
   <si>
     <t>매리골드</t>
@@ -1122,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>389조 9183억 6640만</t>
+    <t>390조 4351억 6402만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -1140,13 +1140,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>334조 1776억 1349만</t>
+    <t>357조 700억 5668만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>5731조 3781억 8495만</t>
+    <t>5763조 9414억 4481만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1173,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3347조 9436억 1500만</t>
+    <t>3704조 3415억 6045만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1185,13 +1185,22 @@
     <t>2706조 7527억 6350만</t>
   </si>
   <si>
+    <t>포빅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
+  </si>
+  <si>
+    <t>2278조 4574억 7634만</t>
+  </si>
+  <si>
     <t>이용하다</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2216조 4022억 554만</t>
+    <t>2271조 9010억 9441만</t>
   </si>
   <si>
     <t>여니워니</t>
@@ -1203,15 +1212,6 @@
     <t>2210조 5639억 7060만</t>
   </si>
   <si>
-    <t>포빅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
-  </si>
-  <si>
-    <t>2204조 873억 8415만</t>
-  </si>
-  <si>
     <t>종꿀</t>
   </si>
   <si>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
   </si>
   <si>
-    <t>1842조 5559억 6212만</t>
+    <t>1912조 1890억 2174만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1236,7 +1236,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1733조 9308억 7806만</t>
+    <t>1809조 4618억 4034만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1245,7 +1245,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>1649조 581억 7955만</t>
+    <t>1789조 4899억 2128만</t>
+  </si>
+  <si>
+    <t>MangCI</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
+  </si>
+  <si>
+    <t>1735조 7655억 7172만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1263,16 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
   </si>
   <si>
-    <t>1532조 7337억 2070만</t>
-  </si>
-  <si>
-    <t>MangCI</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MangCI</t>
-  </si>
-  <si>
-    <t>1451조 9418억 545만</t>
+    <t>1535조 6335억 4711만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1281,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1319조 5858억 7337만</t>
+    <t>1339조 9426억 3710만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1290,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1098조 1848억 4864만</t>
+    <t>1141조 3586억 4748만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1299,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>925조 8925억 1529만</t>
+    <t>958조 5088억 2977만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1311,22 +1311,22 @@
     <t>902조 2941억 6618만</t>
   </si>
   <si>
+    <t>티에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>892조 8271억 7980만</t>
+  </si>
+  <si>
     <t>파이리양말</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>884조 6876억 1268만</t>
-  </si>
-  <si>
-    <t>티에이치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
-  </si>
-  <si>
-    <t>881조 2976억 2492만</t>
+    <t>884조 9551억 1696만</t>
   </si>
   <si>
     <t>박금쪽</t>
@@ -1380,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>563조 6801억 7647만</t>
+    <t>602조 5546억 7140만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1389,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>448조 4913억 2823만</t>
+    <t>463조 3921억 4669만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>368조 1032억 9070만</t>
+    <t>376조 2375억 4839만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1407,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>310조 1700억 7637만</t>
+    <t>332조 6910억 8543만</t>
   </si>
 </sst>
 </file>
@@ -2262,10 +2262,10 @@
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>97</v>
@@ -2294,10 +2294,10 @@
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>102</v>
@@ -2358,10 +2358,10 @@
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>112</v>
@@ -2425,7 +2425,7 @@
         <v>91</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>120</v>
@@ -2457,7 +2457,7 @@
         <v>124</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>125</v>
@@ -2489,7 +2489,7 @@
         <v>75</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>129</v>
@@ -2553,7 +2553,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>137</v>
@@ -2582,7 +2582,7 @@
         <v>140</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>107</v>
@@ -2646,7 +2646,7 @@
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>107</v>
@@ -2681,7 +2681,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>154</v>
@@ -2777,7 +2777,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>166</v>
@@ -3245,7 +3245,7 @@
         <v>124</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>211</v>
@@ -3277,7 +3277,7 @@
         <v>91</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>214</v>
@@ -3309,7 +3309,7 @@
         <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>217</v>
@@ -3338,13 +3338,13 @@
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3358,25 +3358,25 @@
         <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>222</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3390,19 +3390,19 @@
         <v>109</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>223</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>223</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>140</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>225</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>107</v>
@@ -3434,10 +3434,10 @@
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>229</v>
@@ -3498,10 +3498,10 @@
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>236</v>
@@ -3533,7 +3533,7 @@
         <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>239</v>
@@ -3562,10 +3562,10 @@
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>242</v>
@@ -3818,7 +3818,7 @@
         <v>62</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>145</v>
@@ -3850,7 +3850,7 @@
         <v>62</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>145</v>
@@ -3914,13 +3914,13 @@
         <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
+        <v>275</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3934,25 +3934,25 @@
         <v>180</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>178</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3966,22 +3966,22 @@
         <v>184</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>281</v>
+        <v>178</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>282</v>
@@ -4160,7 +4160,7 @@
         <v>75</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>291</v>
@@ -4189,10 +4189,10 @@
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>191</v>
+        <v>91</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>294</v>
@@ -4221,10 +4221,10 @@
         <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>91</v>
+        <v>191</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>297</v>
@@ -4256,7 +4256,7 @@
         <v>80</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>300</v>
@@ -4317,10 +4317,10 @@
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>306</v>
@@ -4349,10 +4349,10 @@
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>309</v>
@@ -4381,10 +4381,10 @@
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>312</v>
@@ -4413,10 +4413,10 @@
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>315</v>
@@ -4608,7 +4608,7 @@
         <v>106</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>332</v>
@@ -4637,7 +4637,7 @@
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>107</v>
@@ -4669,7 +4669,7 @@
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>178</v>
@@ -4701,7 +4701,7 @@
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>107</v>
@@ -4765,7 +4765,7 @@
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>107</v>
@@ -4832,7 +4832,7 @@
         <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>178</v>
+        <v>101</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>353</v>
@@ -4864,7 +4864,7 @@
         <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>107</v>
+        <v>178</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>356</v>
@@ -5298,10 +5298,10 @@
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>388</v>
@@ -5330,10 +5330,10 @@
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>391</v>
@@ -5362,10 +5362,10 @@
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>394</v>
@@ -5426,10 +5426,10 @@
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>400</v>
@@ -5461,7 +5461,7 @@
         <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>403</v>
@@ -5493,7 +5493,7 @@
         <v>86</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>406</v>
@@ -5522,10 +5522,10 @@
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>232</v>
+        <v>86</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>409</v>
@@ -5554,10 +5554,10 @@
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>412</v>
@@ -5586,10 +5586,10 @@
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>415</v>
@@ -5621,7 +5621,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>418</v>
@@ -5653,7 +5653,7 @@
         <v>80</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>421</v>
@@ -5685,7 +5685,7 @@
         <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>424</v>
@@ -5746,10 +5746,10 @@
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>220</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>430</v>
@@ -5778,10 +5778,10 @@
         <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>433</v>
@@ -5877,7 +5877,7 @@
         <v>75</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>442</v>
@@ -5938,7 +5938,7 @@
         <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>178</v>
@@ -6069,7 +6069,7 @@
         <v>63</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>460</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="지존길드" sheetId="2" r:id="rId2"/>
-    <sheet name="빅딜" sheetId="3" r:id="rId3"/>
+    <sheet name="빅딜" sheetId="2" r:id="rId2"/>
+    <sheet name="지존길드" sheetId="3" r:id="rId3"/>
     <sheet name="TopOfTop" sheetId="4" r:id="rId4"/>
     <sheet name="눈별" sheetId="5" r:id="rId5"/>
   </sheets>
@@ -17,15 +17,15 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TopOfTop!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">지존길드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="465">
   <si>
     <t>guild_name</t>
   </si>
@@ -66,25 +66,55 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>빅딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>850</t>
+  </si>
+  <si>
+    <t>38위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>5경 985조 128억 1537만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
     <t>지존길드</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 4</t>
   </si>
   <si>
-    <t>864</t>
-  </si>
-  <si>
-    <t>31위</t>
-  </si>
-  <si>
-    <t>Lv.9</t>
+    <t>867</t>
+  </si>
+  <si>
+    <t>30위</t>
   </si>
   <si>
     <t>30명</t>
@@ -99,78 +129,48 @@
     <t>지존순찌</t>
   </si>
   <si>
-    <t>2026.09.21</t>
-  </si>
-  <si>
-    <t>빅딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>845</t>
+    <t>TopOfTop</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>900</t>
+  </si>
+  <si>
+    <t>16위</t>
+  </si>
+  <si>
+    <t>4경 4791조 9790억 3201만</t>
+  </si>
+  <si>
+    <t>길컨 1등만</t>
+  </si>
+  <si>
+    <t>복어띰</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
+    <t>눈별</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
+  </si>
+  <si>
+    <t>Scania 6</t>
+  </si>
+  <si>
+    <t>887</t>
   </si>
   <si>
     <t>37위</t>
   </si>
   <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>5경 985조 128억 1537만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>TopOfTop</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>896</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
-    <t>4경 4791조 9790억 3201만</t>
-  </si>
-  <si>
-    <t>길컨 1등만</t>
-  </si>
-  <si>
-    <t>복어띰</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>눈별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>885</t>
-  </si>
-  <si>
-    <t>38위</t>
-  </si>
-  <si>
     <t>4경 6681조 7185억 6799만</t>
   </si>
   <si>
@@ -207,25 +207,412 @@
     <t>1</t>
   </si>
   <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 8450조 7155억 2134만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>김치싸대기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>1경 30조 3328억 561만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>6509조 1554억 3685만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>3845조 8894억 7995만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>3686조 3442억 6715만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>3555조 7999억 2556만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>2506조 3339억 590만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2455조 5806억 1503만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>2043조 9656억 4336만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1988조 6370억 9907만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>1905조 6059억 8847만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1697조 755억 7134만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1271조 9043억 5495만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1089조 6862억 6567만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1065조 650억 5642만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1058조 5051억 8293만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>997조 8062억 583만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>946조 8208억 9125만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>914조 9534억 4237만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>865조 3240억 427만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>574조 2768억 9948만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>팡대지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
+  </si>
+  <si>
+    <t>560조 3492억 2985만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>532조 1581억 8976만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>524조 8468억 7860만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>443조 7313억 8364만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>428조 3947억 2311만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>325조 6414억 3296만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>275조 6869억 3523만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>262조 3181억 5323만</t>
+  </si>
+  <si>
     <t>지존쫀파</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8217조 5797억 1907만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>8503조 5541억 5588만</t>
   </si>
   <si>
     <t>수텍</t>
@@ -240,10 +627,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>7449조 4009억 54만</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>7454조 6453억 3071만</t>
   </si>
   <si>
     <t>협의</t>
@@ -252,61 +636,43 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
   </si>
   <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
     <t>4402조 1032억 4015만</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>포항엄석대</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
   </si>
   <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
     <t>4094조 124억 4985만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>기뽐</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
     <t>3303조 6174억 3840만</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>타개</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
   </si>
   <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>2993조 5억 2522만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>3031조 6924억 884만</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2505조 3859억 3849만</t>
   </si>
   <si>
     <t>변신술사</t>
@@ -321,40 +687,13 @@
     <t>2465조 3877억 3257만</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2432조 7584억 4757만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>뿡쓰</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2279조 9226억 7885만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>2289조 9844억 4941만</t>
   </si>
   <si>
     <t>지존빼앙</t>
@@ -363,10 +702,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
   </si>
   <si>
-    <t>2255조 9124억 1422만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>2278조 7750억 6763만</t>
+  </si>
+  <si>
+    <t>댜니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1980조 3463억 5910만</t>
   </si>
   <si>
     <t>엘르가든</t>
@@ -378,34 +723,13 @@
     <t>1978조 8306억 8833만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>댜니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1833조 7180억 5399만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>온백</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
   </si>
   <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>1830조 1973억 356만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>1847조 6328억 3638만</t>
   </si>
   <si>
     <t>파울</t>
@@ -417,9 +741,6 @@
     <t>1766조 7006억 9923만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>마카롱롱</t>
   </si>
   <si>
@@ -429,9 +750,6 @@
     <t>1725조 492억 8770만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>모짜리코베르</t>
   </si>
   <si>
@@ -441,19 +759,19 @@
     <t>1240조 6809억 9149만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>1213조 7003억 6444만</t>
   </si>
   <si>
-    <t>18</t>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1211조 7444억 9137만</t>
   </si>
   <si>
     <t>짱잘자쿨냥</t>
@@ -462,27 +780,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>1149조 8047억 287만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1101조 5798억 4738만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>기본이리</t>
   </si>
   <si>
@@ -492,9 +792,6 @@
     <t>1050조 6512억 3068만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>김허덕</t>
   </si>
   <si>
@@ -504,9 +801,6 @@
     <t>1047조 2041억 8654만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>냐은</t>
   </si>
   <si>
@@ -516,9 +810,6 @@
     <t>1033조 7202억 5586만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>마갤</t>
   </si>
   <si>
@@ -528,7 +819,22 @@
     <t>1018조 127억 2969만</t>
   </si>
   <si>
-    <t>24</t>
+    <t>전산봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
+  </si>
+  <si>
+    <t>876조 7240억 1465만</t>
+  </si>
+  <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>847조 1465억 7512만</t>
   </si>
   <si>
     <t>오옹나이스</t>
@@ -537,37 +843,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>826조 4642억 7332만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>고숨도칭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
-  </si>
-  <si>
-    <t>819조 1516억 3816만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>전산봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>765조 9289억 1162만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>839조 5673억 5995만</t>
   </si>
   <si>
     <t>Doham</t>
@@ -579,19 +855,13 @@
     <t>747조 6533억 1496만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
     <t>태코찡</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>665조 2579억 6198만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>702조 8469억 5016만</t>
   </si>
   <si>
     <t>유플러스</t>
@@ -618,264 +888,6 @@
     <t>277조 36억 4103만</t>
   </si>
   <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>9713조 4850억 8781만</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>6465조 5267억 4688만</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>3686조 3442억 6715만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>3648조 8531억 6875만</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>3531조 2793억 8113만</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>2484조 5237억 5157만</t>
-  </si>
-  <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2443조 1439억 5824만</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>2043조 9656억 4336만</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>1905조 6059억 8847만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>1831조 3912억 3225만</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1697조 755억 7134만</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1265조 7396억 7046만</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>1065조 650억 5642만</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1062조 1444억 674만</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>1058조 5051억 8293만</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>987조 2843억 9824만</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>930조 1939억 3217만</t>
-  </si>
-  <si>
-    <t>뽀송히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
-  </si>
-  <si>
-    <t>914조 9534억 4237만</t>
-  </si>
-  <si>
-    <t>정태준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
-  </si>
-  <si>
-    <t>864조 6290억 5998만</t>
-  </si>
-  <si>
-    <t>팡대지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
-  </si>
-  <si>
-    <t>560조 3492억 2985만</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>532조 1581억 8976만</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>524조 8468억 7860만</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>440조 6040억 4040만</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>425조 1582억 57만</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>420조 9657억 7177만</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>325조 1469억 5466만</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>275조 6869억 3523만</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>254조 6783억 7167만</t>
-  </si>
-  <si>
     <t>가겠습니다</t>
   </si>
   <si>
@@ -900,7 +912,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
   </si>
   <si>
-    <t>3818조 9392억 1956만</t>
+    <t>4016조 8249억 1279만</t>
+  </si>
+  <si>
+    <t>미우맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
+  </si>
+  <si>
+    <t>3451조 4519억 580만</t>
   </si>
   <si>
     <t>개종망겜</t>
@@ -912,22 +933,31 @@
     <t>3293조 8550억 2424만</t>
   </si>
   <si>
-    <t>미우맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
-  </si>
-  <si>
-    <t>3005조 5830억 1775만</t>
-  </si>
-  <si>
     <t>커튼월</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>2565조 4727억 9671만</t>
+    <t>2767조 8317억 5892만</t>
+  </si>
+  <si>
+    <t>명지동꿀주먹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
+  </si>
+  <si>
+    <t>2406조 3771억 2303만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>2367조 657억 9217만</t>
   </si>
   <si>
     <t>gorystalLOVE</t>
@@ -936,7 +966,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
   </si>
   <si>
-    <t>2330조 1458억 535만</t>
+    <t>2351조 9875억 2829만</t>
   </si>
   <si>
     <t>Judge99</t>
@@ -945,16 +975,7 @@
     <t>https://mgf.gg/contents/character.php?n=Judge99</t>
   </si>
   <si>
-    <t>2311조 2928억 2700만</t>
-  </si>
-  <si>
-    <t>천요화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
-  </si>
-  <si>
-    <t>2281조 3425억 5886만</t>
+    <t>2336조 2072억 6503만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -966,19 +987,10 @@
     <t>2274조 2104억 2874만</t>
   </si>
   <si>
-    <t>명지동꿀주먹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
-  </si>
-  <si>
-    <t>2267조 5467억 7182만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
   </si>
   <si>
-    <t>2136조 215억 9493만</t>
+    <t>2137조 7737억 719만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -987,7 +999,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1404조 9900억 92만</t>
+    <t>1526조 9634억 6688만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>1075조 4105억 4512만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -996,16 +1017,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1034조 6450억 3558만</t>
-  </si>
-  <si>
-    <t>스툭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
-  </si>
-  <si>
-    <t>965조 5474억 7452만</t>
+    <t>1036조 5839억 2145만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -1014,7 +1026,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>951조 7711억 3126만</t>
+    <t>965조 8239억 6171만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -1026,6 +1038,15 @@
     <t>923조 9124억 9450만</t>
   </si>
   <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>922조 746억 8446만</t>
+  </si>
+  <si>
     <t>양룽</t>
   </si>
   <si>
@@ -1041,16 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
   </si>
   <si>
-    <t>862조 9057억 2979만</t>
-  </si>
-  <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>767조 3552억 915만</t>
+    <t>903조 5254억 9045만</t>
   </si>
   <si>
     <t>gorystal</t>
@@ -1059,7 +1071,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>760조 7239억 7368만</t>
+    <t>779조 2102억 1404만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1068,7 +1080,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>741조 519억 8746만</t>
+    <t>759조 2908억 3261만</t>
   </si>
   <si>
     <t>복룽</t>
@@ -1077,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>727조 7112억 1208만</t>
+    <t>743조 871억 620만</t>
   </si>
   <si>
     <t>뀨꾸룽</t>
@@ -1086,7 +1098,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
   </si>
   <si>
-    <t>665조 3726억 2336만</t>
+    <t>667조 3625억 7101만</t>
+  </si>
+  <si>
+    <t>짜상무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>657조 8734억 7796만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1098,22 +1119,13 @@
     <t>657조 7522억 2440만</t>
   </si>
   <si>
-    <t>짜상무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>645조 4219억 2412만</t>
-  </si>
-  <si>
     <t>률율율</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>603조 203억 6747만</t>
+    <t>642조 104억 5929만</t>
   </si>
   <si>
     <t>매리골드</t>
@@ -1122,7 +1134,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>390조 4351억 6402만</t>
+    <t>395조 8938억 7457만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -1131,7 +1143,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>372조 7777억 7671만</t>
+    <t>394조 4486억 279만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1140,13 +1152,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>357조 700억 5668만</t>
+    <t>362조 1452억 2256만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>5763조 9414억 4481만</t>
+    <t>6256조 513억 9626만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1182,7 +1194,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2706조 7527억 6350만</t>
+    <t>2751조 2086억 7442만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2368조 2509억 3616만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1191,7 +1212,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>2278조 4574억 7634만</t>
+    <t>2297조 9485억 1427만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -1200,16 +1221,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2271조 9010억 9441만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2210조 5639억 7060만</t>
+    <t>2279조 2542억 8978만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1218,7 +1230,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>2094조 3509억 5174만</t>
+    <t>2181조 5872억 8722만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1227,7 +1239,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
   </si>
   <si>
-    <t>1912조 1890억 2174만</t>
+    <t>1934조 8248억 2045만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>1849조 4968억 4237만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1236,16 +1257,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1809조 4618억 4034만</t>
-  </si>
-  <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1789조 4899억 2128만</t>
+    <t>1817조 4953억 3551만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1254,7 +1266,16 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1735조 7655억 7172만</t>
+    <t>1794조 9809억 9810만</t>
+  </si>
+  <si>
+    <t>덩개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>1755조 1937억 6384만</t>
   </si>
   <si>
     <t>자이언트리</t>
@@ -1266,22 +1287,13 @@
     <t>1643조 4872억 6754만</t>
   </si>
   <si>
-    <t>덩개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>1535조 6335억 4711만</t>
-  </si>
-  <si>
     <t>여자둘남자둘</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1339조 9426억 3710만</t>
+    <t>1340조 9970억 8549만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1290,7 +1302,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1141조 3586억 4748만</t>
+    <t>1143조 3991억 9708만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1299,7 +1311,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>958조 5088억 2977만</t>
+    <t>992조 426억 4572만</t>
+  </si>
+  <si>
+    <t>파이리양말</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
+  </si>
+  <si>
+    <t>921조 4895억 8939만</t>
+  </si>
+  <si>
+    <t>박금쪽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
+  </si>
+  <si>
+    <t>921조 387억 931만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1308,7 +1338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%EB%A5%A0</t>
   </si>
   <si>
-    <t>902조 2941억 6618만</t>
+    <t>910조 593억 4871만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1317,25 +1347,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>892조 8271억 7980만</t>
-  </si>
-  <si>
-    <t>파이리양말</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
-  </si>
-  <si>
-    <t>884조 9551억 1696만</t>
-  </si>
-  <si>
-    <t>박금쪽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
-  </si>
-  <si>
-    <t>804조 4549억 516만</t>
+    <t>900조 5793억 8606만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1344,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>738조 7041억 4433만</t>
+    <t>743조 4123억 1320만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1353,7 +1365,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>737조 1909억 7080만</t>
+    <t>740조 1133억 898만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1389,7 +1401,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>463조 3921억 4669만</t>
+    <t>509조 3405억 2279만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1398,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>376조 2375억 4839만</t>
+    <t>376조 7128억 9008만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1407,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>332조 6910억 8543만</t>
+    <t>335조 1093억 5927만</t>
   </si>
 </sst>
 </file>
@@ -1935,7 +1947,7 @@
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>39</v>
@@ -1976,7 +1988,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>48</v>
@@ -2004,6 +2016,1017 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2052,31 +3075,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>61</v>
+        <v>194</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2084,31 +3107,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>196</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2116,31 +3139,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>202</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>76</v>
+        <v>203</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2148,31 +3171,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>79</v>
+        <v>205</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>82</v>
+        <v>206</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2180,31 +3203,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2212,31 +3235,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>89</v>
+        <v>210</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>90</v>
+        <v>211</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>92</v>
+        <v>212</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2244,31 +3267,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>94</v>
+        <v>213</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>95</v>
+        <v>214</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>97</v>
+        <v>215</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2276,31 +3299,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>86</v>
+        <v>218</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>102</v>
+        <v>219</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2308,31 +3331,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>104</v>
+        <v>220</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>105</v>
+        <v>221</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>108</v>
+        <v>222</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2340,31 +3363,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>110</v>
+        <v>223</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>110</v>
+        <v>223</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>111</v>
+        <v>224</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2372,31 +3395,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>114</v>
+        <v>226</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>226</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>115</v>
+        <v>227</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>116</v>
+        <v>228</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2404,31 +3427,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>119</v>
+        <v>230</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2436,31 +3459,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>123</v>
+        <v>233</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>125</v>
+        <v>234</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2468,31 +3491,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>127</v>
+        <v>235</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>128</v>
+        <v>236</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>101</v>
-      </c>
       <c r="I15" s="2" t="s">
-        <v>129</v>
+        <v>237</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2500,31 +3523,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>131</v>
+        <v>238</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>132</v>
+        <v>239</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>133</v>
+        <v>240</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2532,31 +3555,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>135</v>
+        <v>241</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>136</v>
+        <v>242</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>137</v>
+        <v>243</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2564,31 +3587,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>141</v>
+        <v>245</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2596,31 +3619,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>143</v>
+        <v>246</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>144</v>
+        <v>247</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>146</v>
+        <v>248</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2628,31 +3651,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>148</v>
+        <v>249</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>249</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>149</v>
+        <v>250</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>150</v>
+        <v>251</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2660,31 +3683,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>152</v>
+        <v>252</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>153</v>
+        <v>253</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -2692,31 +3715,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>156</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2724,31 +3747,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>161</v>
+        <v>259</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2756,31 +3779,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>164</v>
+        <v>261</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>166</v>
+        <v>263</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -2788,31 +3811,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>168</v>
+        <v>264</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>168</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>169</v>
+        <v>265</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>170</v>
+        <v>266</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -2820,31 +3843,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>172</v>
+        <v>267</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>173</v>
+        <v>268</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -2852,31 +3875,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>177</v>
+        <v>271</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
+        <v>90</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>179</v>
+        <v>272</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -2884,31 +3907,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -2916,31 +3939,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>184</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>185</v>
+        <v>276</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>186</v>
+        <v>277</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>187</v>
+        <v>278</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -2948,31 +3971,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>188</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>189</v>
+        <v>279</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -2980,31 +4003,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>194</v>
+        <v>284</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>194</v>
+        <v>284</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3048,984 +4071,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J29"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
@@ -4081,25 +4126,25 @@
         <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>42</v>
@@ -4113,25 +4158,25 @@
         <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>42</v>
@@ -4145,25 +4190,25 @@
         <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>42</v>
@@ -4177,25 +4222,25 @@
         <v>77</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>91</v>
+        <v>281</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>42</v>
@@ -4206,28 +4251,28 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>191</v>
+        <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>42</v>
@@ -4238,28 +4283,28 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>42</v>
@@ -4270,16 +4315,16 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
@@ -4288,10 +4333,10 @@
         <v>80</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>42</v>
@@ -4302,28 +4347,28 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>220</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>42</v>
@@ -4334,28 +4379,28 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>42</v>
@@ -4366,28 +4411,28 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>42</v>
@@ -4398,16 +4443,16 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
@@ -4416,10 +4461,10 @@
         <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>42</v>
@@ -4430,7 +4475,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>41</v>
@@ -4439,19 +4484,19 @@
         <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>42</v>
@@ -4462,28 +4507,28 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>42</v>
@@ -4494,16 +4539,16 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
@@ -4512,10 +4557,10 @@
         <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>42</v>
@@ -4526,28 +4571,28 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>42</v>
@@ -4558,28 +4603,28 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>42</v>
@@ -4590,28 +4635,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>42</v>
@@ -4622,28 +4667,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>42</v>
@@ -4654,28 +4699,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>178</v>
+        <v>85</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>42</v>
@@ -4686,28 +4731,28 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>42</v>
@@ -4718,28 +4763,28 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>42</v>
@@ -4750,28 +4795,28 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>42</v>
@@ -4782,28 +4827,28 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>42</v>
@@ -4814,28 +4859,28 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>42</v>
@@ -4846,28 +4891,28 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>42</v>
@@ -4881,13 +4926,13 @@
         <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>62</v>
@@ -4896,10 +4941,10 @@
         <v>63</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>42</v>
@@ -4910,28 +4955,28 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>42</v>
@@ -4945,25 +4990,25 @@
         <v>184</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>42</v>
@@ -4977,25 +5022,25 @@
         <v>188</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>42</v>
@@ -5006,28 +5051,28 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>42</v>
@@ -5132,19 +5177,19 @@
         <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5158,25 +5203,25 @@
         <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5190,25 +5235,25 @@
         <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5222,25 +5267,25 @@
         <v>77</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5251,28 +5296,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>232</v>
+        <v>121</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>70</v>
+        <v>199</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5283,28 +5328,28 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5315,28 +5360,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5347,28 +5392,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5379,28 +5424,28 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5411,28 +5456,28 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5443,28 +5488,28 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5475,28 +5520,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5507,28 +5552,28 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>86</v>
+        <v>173</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5539,28 +5584,28 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>232</v>
+        <v>147</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5571,28 +5616,28 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5603,28 +5648,28 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5635,28 +5680,28 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5667,28 +5712,28 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5699,28 +5744,28 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5731,28 +5776,28 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5763,28 +5808,28 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5795,28 +5840,28 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5827,28 +5872,28 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5859,28 +5904,28 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5891,28 +5936,28 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5926,25 +5971,25 @@
         <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>96</v>
+        <v>218</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5955,28 +6000,28 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5990,25 +6035,25 @@
         <v>184</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6022,25 +6067,25 @@
         <v>188</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6051,28 +6096,28 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>275</v>
+        <v>182</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -78,7 +78,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>850</t>
+    <t>851</t>
   </si>
   <si>
     <t>38위</t>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TopOfTop!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="462">
   <si>
     <t>guild_name</t>
   </si>
@@ -78,10 +78,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>851</t>
-  </si>
-  <si>
-    <t>38위</t>
+    <t>863</t>
+  </si>
+  <si>
+    <t>39위</t>
   </si>
   <si>
     <t>Lv.9</t>
@@ -111,7 +111,7 @@
     <t>Scania 4</t>
   </si>
   <si>
-    <t>867</t>
+    <t>877</t>
   </si>
   <si>
     <t>30위</t>
@@ -138,7 +138,7 @@
     <t>Scania 18</t>
   </si>
   <si>
-    <t>900</t>
+    <t>915</t>
   </si>
   <si>
     <t>16위</t>
@@ -165,7 +165,7 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>887</t>
+    <t>898</t>
   </si>
   <si>
     <t>37위</t>
@@ -222,648 +222,639 @@
     <t>116</t>
   </si>
   <si>
-    <t>1경 8450조 7155억 2134만</t>
+    <t>2경 237조 9091억 2548만</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>김치싸대기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%EC%B9%98%EC%8B%B8%EB%8C%80%EA%B8%B0</t>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>7601조 6815억 1984만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>3977조 6444억 4078만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>3924조 2536억 9340만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
     <t>히어로</t>
   </si>
   <si>
+    <t>3762조 2211억 2278만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>퍼퓸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
+  </si>
+  <si>
+    <t>2728조 3700억 7437만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2631조 6453억 5245만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2043조 9656억 4336만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>1989조 7824억 6125만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>1905조 6059억 8847만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>1697조 755억 7134만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1315조 5220억 4669만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>1109조 9165억 9489만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1108조 180억 2351만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1073조 5649억 8462만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1065조 650억 5642만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1035조 3847억 2058만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>1004조 8036억 1662만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>945조 4753억 8997만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>694조 9328억 4347만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>팡대지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
+  </si>
+  <si>
+    <t>575조 1653억 9478만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>551조 4586억 8525만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>538조 1761억 3296만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>465조 5751억 1115만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>435조 2837억 6019만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>326조 4698억 2146만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>275조 6869억 3523만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>270조 8495억 5221만</t>
+  </si>
+  <si>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
     <t>114</t>
   </si>
   <si>
-    <t>1경 30조 3328억 561만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>6509조 1554억 3685만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>3845조 8894억 7995만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>3686조 3442억 6715만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>3555조 7999억 2556만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>2506조 3339억 590만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2455조 5806억 1503만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>2043조 9656억 4336만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>1988조 6370억 9907만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>1905조 6059억 8847만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1697조 755억 7134만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1271조 9043억 5495만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1089조 6862억 6567만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>1065조 650억 5642만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>110</t>
-  </si>
-  <si>
-    <t>1058조 5051억 8293만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>997조 8062억 583만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>946조 8208억 9125만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>뽀송히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>914조 9534억 4237만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>정태준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
-  </si>
-  <si>
-    <t>865조 3240억 427만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>574조 2768억 9948만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>팡대지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
-  </si>
-  <si>
-    <t>560조 3492억 2985만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>532조 1581억 8976만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>524조 8468억 7860만</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>443조 7313억 8364만</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>428조 3947억 2311만</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>325조 6414억 3296만</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>275조 6869억 3523만</t>
+    <t>8623조 4455억 698만</t>
+  </si>
+  <si>
+    <t>수텍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>7468조 2422억 4958만</t>
+  </si>
+  <si>
+    <t>포항엄석대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
+  </si>
+  <si>
+    <t>4453조 8085억 1203만</t>
+  </si>
+  <si>
+    <t>협의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+  </si>
+  <si>
+    <t>4402조 1032억 4015만</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>3303조 6174억 3840만</t>
+  </si>
+  <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>3074조 9670억 3069만</t>
+  </si>
+  <si>
+    <t>댜니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2719조 7474억 1743만</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2581조 6429억 5864만</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>2472조 8689억 2239만</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>2465조 3877억 3257만</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>2441조 2925억 1424만</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>2313조 7071억 7362만</t>
+  </si>
+  <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>2255조 4974억 667만</t>
+  </si>
+  <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1889조 8524억 3410만</t>
+  </si>
+  <si>
+    <t>파울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>1802조 8305억 7088만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>1303조 7925억 4494만</t>
+  </si>
+  <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1293조 7161억 8573만</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1247조 6075억 2806만</t>
+  </si>
+  <si>
+    <t>짱잘자쿨냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
+  </si>
+  <si>
+    <t>1149조 8047억 287만</t>
+  </si>
+  <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1083조 3384억 3846만</t>
+  </si>
+  <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1078조 6352억 6820만</t>
+  </si>
+  <si>
+    <t>냐은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
+  </si>
+  <si>
+    <t>1068조 2571억 1131만</t>
+  </si>
+  <si>
+    <t>마갤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
+  </si>
+  <si>
+    <t>1060조 3768억 2296만</t>
+  </si>
+  <si>
+    <t>전산봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
+  </si>
+  <si>
+    <t>925조 3542억 1411만</t>
+  </si>
+  <si>
+    <t>오옹나이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>883조 1176억 6134만</t>
+  </si>
+  <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>849조 971억 5090만</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>793조 748억 2183만</t>
+  </si>
+  <si>
+    <t>태코찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>775조 1513억 6255만</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>262조 3181억 5323만</t>
-  </si>
-  <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>8503조 5541억 5588만</t>
-  </si>
-  <si>
-    <t>수텍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>7454조 6453억 3071만</t>
-  </si>
-  <si>
-    <t>협의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
-  </si>
-  <si>
-    <t>4402조 1032억 4015만</t>
-  </si>
-  <si>
-    <t>포항엄석대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
-  </si>
-  <si>
-    <t>4094조 124억 4985만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>3303조 6174억 3840만</t>
-  </si>
-  <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>3031조 6924억 884만</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2505조 3859억 3849만</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>2465조 3877억 3257만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2289조 9844억 4941만</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>2278조 7750억 6763만</t>
-  </si>
-  <si>
-    <t>댜니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>1980조 3463억 5910만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>1978조 8306억 8833만</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>1847조 6328억 3638만</t>
-  </si>
-  <si>
-    <t>파울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>1766조 7006억 9923만</t>
-  </si>
-  <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1725조 492억 8770만</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1240조 6809억 9149만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>1213조 7003억 6444만</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1211조 7444억 9137만</t>
-  </si>
-  <si>
-    <t>짱잘자쿨냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
-  </si>
-  <si>
-    <t>1149조 8047억 287만</t>
-  </si>
-  <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1050조 6512억 3068만</t>
-  </si>
-  <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1047조 2041억 8654만</t>
-  </si>
-  <si>
-    <t>냐은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
-  </si>
-  <si>
-    <t>1033조 7202억 5586만</t>
-  </si>
-  <si>
-    <t>마갤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
-  </si>
-  <si>
-    <t>1018조 127억 2969만</t>
-  </si>
-  <si>
-    <t>전산봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
-  </si>
-  <si>
-    <t>876조 7240억 1465만</t>
-  </si>
-  <si>
-    <t>고숨도칭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
-  </si>
-  <si>
-    <t>847조 1465억 7512만</t>
-  </si>
-  <si>
-    <t>오옹나이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>839조 5673억 5995만</t>
-  </si>
-  <si>
-    <t>Doham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Doham</t>
-  </si>
-  <si>
-    <t>747조 6533억 1496만</t>
-  </si>
-  <si>
-    <t>태코찡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
-  </si>
-  <si>
-    <t>702조 8469억 5016만</t>
-  </si>
-  <si>
     <t>유플러스</t>
   </si>
   <si>
@@ -885,7 +876,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
   </si>
   <si>
-    <t>277조 36억 4103만</t>
+    <t>286조 3410억 357만</t>
   </si>
   <si>
     <t>가겠습니다</t>
@@ -894,7 +885,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>7433조 909억 8318만</t>
+    <t>7608조 9145억 6232만</t>
   </si>
   <si>
     <t>라카도</t>
@@ -921,7 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
   </si>
   <si>
-    <t>3451조 4519억 580만</t>
+    <t>3684조 5142억 2036만</t>
   </si>
   <si>
     <t>개종망겜</t>
@@ -939,7 +930,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>2767조 8317억 5892만</t>
+    <t>2834조 1888억 1942만</t>
+  </si>
+  <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>2759조 5197억 9026만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>2753조 8727억 4004만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
+  </si>
+  <si>
+    <t>2644조 703억 3944만</t>
   </si>
   <si>
     <t>명지동꿀주먹</t>
@@ -948,16 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>2406조 3771억 2303만</t>
-  </si>
-  <si>
-    <t>천요화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
-  </si>
-  <si>
-    <t>2367조 657억 9217만</t>
+    <t>2528조 4750억 2397만</t>
   </si>
   <si>
     <t>gorystalLOVE</t>
@@ -978,28 +984,22 @@
     <t>2336조 2072억 6503만</t>
   </si>
   <si>
-    <t>DREAMLINER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
-  </si>
-  <si>
-    <t>2274조 2104억 2874만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
-  </si>
-  <si>
-    <t>2137조 7737억 719만</t>
-  </si>
-  <si>
     <t>도리토스치즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1526조 9634억 6688만</t>
+    <t>1641조 8069억 2741만</t>
+  </si>
+  <si>
+    <t>지낌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1100조 4977억 6561만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -1011,22 +1011,22 @@
     <t>1075조 4105억 4512만</t>
   </si>
   <si>
-    <t>지낌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1036조 5839억 2145만</t>
-  </si>
-  <si>
     <t>옥슈쓔</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>965조 8239억 6171만</t>
+    <t>991조 4376억 1607만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>983조 2121억 6252만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -1038,15 +1038,6 @@
     <t>923조 9124억 9450만</t>
   </si>
   <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>922조 746억 8446만</t>
-  </si>
-  <si>
     <t>양룽</t>
   </si>
   <si>
@@ -1071,7 +1062,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>779조 2102억 1404만</t>
+    <t>790조 9059억 8419만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -1080,7 +1071,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>759조 2908억 3261만</t>
+    <t>775조 9620억 8479만</t>
   </si>
   <si>
     <t>복룽</t>
@@ -1089,7 +1080,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>743조 871억 620만</t>
+    <t>746조 3009억 299만</t>
   </si>
   <si>
     <t>뀨꾸룽</t>
@@ -1098,7 +1089,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
   </si>
   <si>
-    <t>667조 3625억 7101만</t>
+    <t>692조 2460억 8475만</t>
   </si>
   <si>
     <t>짜상무</t>
@@ -1107,7 +1098,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
   </si>
   <si>
-    <t>657조 8734억 7796만</t>
+    <t>665조 2346억 615만</t>
   </si>
   <si>
     <t>파파존스맛나</t>
@@ -1134,7 +1125,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>395조 8938억 7457만</t>
+    <t>414조 6642억 9700만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -1143,7 +1134,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>394조 4486억 279만</t>
+    <t>394조 6210억 2814만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -1158,7 +1149,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>6256조 513억 9626만</t>
+    <t>6457조 5219억 9175만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1170,6 +1161,15 @@
     <t>5708조 2885억 4200만</t>
   </si>
   <si>
+    <t>죽창당일개통</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
+  </si>
+  <si>
+    <t>3917조 2434억 5986만</t>
+  </si>
+  <si>
     <t>도하리</t>
   </si>
   <si>
@@ -1179,15 +1179,6 @@
     <t>3802조 2509억 9228만</t>
   </si>
   <si>
-    <t>죽창당일개통</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
-  </si>
-  <si>
-    <t>3704조 3415억 6045만</t>
-  </si>
-  <si>
     <t>유수달</t>
   </si>
   <si>
@@ -1197,31 +1188,31 @@
     <t>2751조 2086억 7442만</t>
   </si>
   <si>
+    <t>이용하다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2467조 863억 3175만</t>
+  </si>
+  <si>
+    <t>포빅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
+  </si>
+  <si>
+    <t>2417조 9903억 6478만</t>
+  </si>
+  <si>
     <t>여니워니</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
   </si>
   <si>
-    <t>2368조 2509억 3616만</t>
-  </si>
-  <si>
-    <t>포빅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
-  </si>
-  <si>
-    <t>2297조 9485억 1427만</t>
-  </si>
-  <si>
-    <t>이용하다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2279조 2542억 8978만</t>
+    <t>2374조 2205억 8289만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1230,7 +1221,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>2181조 5872억 8722만</t>
+    <t>2274조 8790억 9139만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>2003조 3427억 7484만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1242,15 +1242,6 @@
     <t>1934조 8248억 2045만</t>
   </si>
   <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>1849조 4968억 4237만</t>
-  </si>
-  <si>
     <t>세월이야속해</t>
   </si>
   <si>
@@ -1293,7 +1284,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1340조 9970억 8549만</t>
+    <t>1356조 2717억 3730만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1302,7 +1293,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1143조 3991억 9708만</t>
+    <t>1237조 3127억 5973만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1320,7 +1311,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>921조 4895억 8939만</t>
+    <t>925조 2128억 9053만</t>
   </si>
   <si>
     <t>박금쪽</t>
@@ -1329,7 +1320,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
   </si>
   <si>
-    <t>921조 387억 931만</t>
+    <t>922조 4504억 367만</t>
+  </si>
+  <si>
+    <t>티에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>912조 6534억 4698만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1341,22 +1341,13 @@
     <t>910조 593억 4871만</t>
   </si>
   <si>
-    <t>티에이치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
-  </si>
-  <si>
-    <t>900조 5793억 8606만</t>
-  </si>
-  <si>
     <t>감화</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>743조 4123억 1320만</t>
+    <t>781조 5966억 4318만</t>
   </si>
   <si>
     <t>지존짱창남</t>
@@ -1365,7 +1356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>740조 1133억 898만</t>
+    <t>746조 5284억 1379만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1410,7 +1401,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>376조 7128억 9008만</t>
+    <t>400조 5703억 7489만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1419,7 +1410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>335조 1093억 5927만</t>
+    <t>385조 3941억 429만</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2025,7 +2016,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="22.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2113,13 +2104,13 @@
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2130,16 +2121,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
@@ -2148,10 +2139,10 @@
         <v>63</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2162,28 +2153,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2194,28 +2185,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2226,28 +2217,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2258,28 +2249,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2290,25 +2281,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>99</v>
@@ -2325,22 +2316,22 @@
         <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>103</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>104</v>
@@ -2357,25 +2348,25 @@
         <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>106</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2386,28 +2377,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2418,25 +2409,25 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>117</v>
@@ -2465,10 +2456,10 @@
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>122</v>
@@ -2497,10 +2488,10 @@
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>126</v>
@@ -2529,10 +2520,10 @@
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>130</v>
@@ -2561,13 +2552,13 @@
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2578,28 +2569,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2610,28 +2601,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H19" s="2" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2642,28 +2633,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2674,16 +2665,16 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
@@ -2692,10 +2683,10 @@
         <v>63</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -2706,16 +2697,16 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
@@ -2724,10 +2715,10 @@
         <v>63</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -2738,16 +2729,16 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
@@ -2756,10 +2747,10 @@
         <v>63</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -2770,16 +2761,16 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
@@ -2788,10 +2779,10 @@
         <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -2802,25 +2793,25 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H25" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>169</v>
@@ -2849,13 +2840,13 @@
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -2866,25 +2857,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>178</v>
@@ -2913,13 +2904,13 @@
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>183</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -2930,25 +2921,25 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>187</v>
@@ -2957,40 +2948,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3020,7 +2979,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3081,25 +3039,25 @@
         <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3113,25 +3071,25 @@
         <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3142,28 +3100,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>191</v>
+        <v>103</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3174,28 +3132,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3206,28 +3164,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3238,16 +3196,16 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
@@ -3256,10 +3214,10 @@
         <v>63</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3270,28 +3228,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>173</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3302,28 +3260,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>218</v>
+        <v>168</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3337,25 +3295,25 @@
         <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3369,25 +3327,25 @@
         <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3398,28 +3356,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3430,28 +3388,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3465,25 +3423,25 @@
         <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3497,25 +3455,25 @@
         <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>191</v>
+        <v>63</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3529,25 +3487,25 @@
         <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3561,25 +3519,25 @@
         <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>241</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>217</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3590,28 +3548,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>239</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3622,28 +3580,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>218</v>
+        <v>63</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3654,16 +3612,16 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
@@ -3672,10 +3630,10 @@
         <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3686,16 +3644,16 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
@@ -3704,10 +3662,10 @@
         <v>63</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3718,16 +3676,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
@@ -3736,10 +3694,10 @@
         <v>63</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3750,28 +3708,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3782,16 +3740,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
@@ -3800,10 +3758,10 @@
         <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3814,16 +3772,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>62</v>
@@ -3832,10 +3790,10 @@
         <v>63</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3849,25 +3807,25 @@
         <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>198</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3878,28 +3836,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>69</v>
+        <v>194</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3913,25 +3871,25 @@
         <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3942,16 +3900,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
@@ -3960,10 +3918,10 @@
         <v>63</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3974,28 +3932,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4006,28 +3964,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4126,13 +4084,13 @@
         <v>59</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>62</v>
@@ -4141,10 +4099,10 @@
         <v>63</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>42</v>
@@ -4158,25 +4116,25 @@
         <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>42</v>
@@ -4187,28 +4145,28 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>42</v>
@@ -4219,28 +4177,28 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>42</v>
@@ -4251,16 +4209,16 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>62</v>
@@ -4269,10 +4227,10 @@
         <v>63</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>42</v>
@@ -4283,28 +4241,28 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>42</v>
@@ -4315,28 +4273,28 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>42</v>
@@ -4347,16 +4305,16 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
@@ -4365,10 +4323,10 @@
         <v>63</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>42</v>
@@ -4382,25 +4340,25 @@
         <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>311</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>311</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>42</v>
@@ -4414,25 +4372,25 @@
         <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>42</v>
@@ -4443,28 +4401,28 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>42</v>
@@ -4475,28 +4433,28 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>316</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>316</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>42</v>
@@ -4510,25 +4468,25 @@
         <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>42</v>
@@ -4542,25 +4500,25 @@
         <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>42</v>
@@ -4574,25 +4532,25 @@
         <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>42</v>
@@ -4606,25 +4564,25 @@
         <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>42</v>
@@ -4635,28 +4593,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>147</v>
+        <v>63</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>42</v>
@@ -4667,28 +4625,28 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>42</v>
@@ -4699,28 +4657,28 @@
         <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>42</v>
@@ -4731,28 +4689,28 @@
         <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>42</v>
@@ -4763,16 +4721,16 @@
         <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
@@ -4781,10 +4739,10 @@
         <v>63</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>42</v>
@@ -4795,28 +4753,28 @@
         <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>42</v>
@@ -4827,16 +4785,16 @@
         <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
@@ -4845,10 +4803,10 @@
         <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>42</v>
@@ -4859,16 +4817,16 @@
         <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>62</v>
@@ -4877,10 +4835,10 @@
         <v>63</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>42</v>
@@ -4894,25 +4852,25 @@
         <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>42</v>
@@ -4923,16 +4881,16 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>62</v>
@@ -4941,10 +4899,10 @@
         <v>63</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>42</v>
@@ -4958,13 +4916,13 @@
         <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
@@ -4973,10 +4931,10 @@
         <v>63</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>42</v>
@@ -4987,28 +4945,28 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>42</v>
@@ -5019,16 +4977,16 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>62</v>
@@ -5037,10 +4995,10 @@
         <v>63</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>42</v>
@@ -5051,28 +5009,28 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>42</v>
@@ -5177,19 +5135,19 @@
         <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5203,25 +5161,25 @@
         <v>66</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5232,28 +5190,28 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>173</v>
+        <v>79</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5264,28 +5222,28 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5296,28 +5254,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5328,28 +5286,28 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5360,28 +5318,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5392,28 +5350,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>103</v>
+        <v>63</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5427,25 +5385,25 @@
         <v>100</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5459,25 +5417,25 @@
         <v>105</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>103</v>
+        <v>168</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5488,28 +5446,28 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>173</v>
+        <v>97</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5520,28 +5478,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5555,25 +5513,25 @@
         <v>118</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5587,25 +5545,25 @@
         <v>123</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5619,25 +5577,25 @@
         <v>127</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5651,13 +5609,13 @@
         <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>62</v>
@@ -5666,10 +5624,10 @@
         <v>63</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5680,28 +5638,28 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5712,16 +5670,16 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>62</v>
@@ -5730,10 +5688,10 @@
         <v>63</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5744,16 +5702,16 @@
         <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>62</v>
@@ -5762,10 +5720,10 @@
         <v>63</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5776,28 +5734,28 @@
         <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5808,28 +5766,28 @@
         <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5840,28 +5798,28 @@
         <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>103</v>
+        <v>142</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5872,16 +5830,16 @@
         <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>62</v>
@@ -5890,10 +5848,10 @@
         <v>63</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5904,28 +5862,28 @@
         <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5939,25 +5897,25 @@
         <v>170</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5968,28 +5926,28 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6003,25 +5961,25 @@
         <v>179</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6032,16 +5990,16 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
@@ -6050,10 +6008,10 @@
         <v>63</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6064,16 +6022,16 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>62</v>
@@ -6082,10 +6040,10 @@
         <v>63</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6096,28 +6054,28 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>62</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -8,24 +8,24 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="지존길드" sheetId="3" r:id="rId3"/>
-    <sheet name="TopOfTop" sheetId="4" r:id="rId4"/>
+    <sheet name="지존길드" sheetId="2" r:id="rId2"/>
+    <sheet name="TopOfTop" sheetId="3" r:id="rId3"/>
+    <sheet name="빅딜" sheetId="4" r:id="rId4"/>
     <sheet name="눈별" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TopOfTop!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TopOfTop!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">지존길드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1285" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="467">
   <si>
     <t>guild_name</t>
   </si>
@@ -66,27 +66,84 @@
     <t>data_date</t>
   </si>
   <si>
+    <t>지존길드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>Scania</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>883</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>4경 9428조 9087억 197만</t>
+  </si>
+  <si>
+    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
+  </si>
+  <si>
+    <t>지존순찌</t>
+  </si>
+  <si>
+    <t>2026.09.21</t>
+  </si>
+  <si>
+    <t>TopOfTop</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
+  </si>
+  <si>
+    <t>Scania 18</t>
+  </si>
+  <si>
+    <t>919</t>
+  </si>
+  <si>
+    <t>16위</t>
+  </si>
+  <si>
+    <t>4경 4791조 9790억 3201만</t>
+  </si>
+  <si>
+    <t>길컨 1등만</t>
+  </si>
+  <si>
+    <t>복어띰</t>
+  </si>
+  <si>
+    <t>2026.09.22</t>
+  </si>
+  <si>
     <t>빅딜</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
   </si>
   <si>
-    <t>Scania</t>
-  </si>
-  <si>
     <t>Scania 2</t>
   </si>
   <si>
-    <t>863</t>
+    <t>866</t>
   </si>
   <si>
     <t>39위</t>
   </si>
   <si>
-    <t>Lv.9</t>
-  </si>
-  <si>
     <t>29명</t>
   </si>
   <si>
@@ -99,63 +156,6 @@
     <t>자유이용껀</t>
   </si>
   <si>
-    <t>2026.09.21</t>
-  </si>
-  <si>
-    <t>지존길드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>Scania 4</t>
-  </si>
-  <si>
-    <t>877</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>4경 9428조 9087억 197만</t>
-  </si>
-  <si>
-    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
-  </si>
-  <si>
-    <t>지존순찌</t>
-  </si>
-  <si>
-    <t>TopOfTop</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>915</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
-    <t>4경 4791조 9790억 3201만</t>
-  </si>
-  <si>
-    <t>길컨 1등만</t>
-  </si>
-  <si>
-    <t>복어띰</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
     <t>눈별</t>
   </si>
   <si>
@@ -165,10 +165,7 @@
     <t>Scania 6</t>
   </si>
   <si>
-    <t>898</t>
-  </si>
-  <si>
-    <t>37위</t>
+    <t>907</t>
   </si>
   <si>
     <t>4경 6681조 7185억 6799만</t>
@@ -207,40 +204,706 @@
     <t>1</t>
   </si>
   <si>
+    <t>지존쫀파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>9094조 7371억 4105만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>수텍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>7571조 6718억 4695만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>포항엄석대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>4469조 9154억 1147만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>협의</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+  </si>
+  <si>
+    <t>바이퍼</t>
+  </si>
+  <si>
+    <t>4402조 1032억 4015만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>타개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3686조 6135억 2383만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>기뽐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>3303조 6174억 3840만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>댜니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2840조 4958억 3412만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>포항가자미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2582조 4683억 1990만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>뿡쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>2517조 3409억 1416만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>지존빼앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>2472조 8689억 2239만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>변신술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>2465조 3877억 3257만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>엘르가든</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
+  </si>
+  <si>
+    <t>2313조 7071억 7362만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2287조 747억 2820만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>파울</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
+  </si>
+  <si>
+    <t>1901조 6768억 6078만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>마카롱롱</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
+  </si>
+  <si>
+    <t>1889조 8524억 3410만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>오옹나이스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1379조 1810억 4031만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1328조 7104억 3097만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>1316조 2657억 6833만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1263조 2766억 1030만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>마갤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
+  </si>
+  <si>
+    <t>1200조 1472억 1769만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>짱잘자쿨냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
+  </si>
+  <si>
+    <t>1149조 8047억 287만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1140조 9567억 8620만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>기본이리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1078조 6352억 6820만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>냐은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
+  </si>
+  <si>
+    <t>1068조 2571억 1131만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>전산봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>952조 4188억 521만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>고숨도칭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
+  </si>
+  <si>
+    <t>864조 3912억 902만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>태코찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>845조 9463억 6641만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Doham</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Doham</t>
+  </si>
+  <si>
+    <t>803조 7038억 6082만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>유플러스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>649조 5527억 6316만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>빵후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>355조 5297억 5157만</t>
+  </si>
+  <si>
+    <t>가겠습니다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>7993조 5091억 8323만</t>
+  </si>
+  <si>
+    <t>라카도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
+  </si>
+  <si>
+    <t>4934조 5246억 3849만</t>
+  </si>
+  <si>
+    <t>롤대신해야지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
+  </si>
+  <si>
+    <t>4695조 3427억 8180만</t>
+  </si>
+  <si>
+    <t>미우맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
+  </si>
+  <si>
+    <t>4205조 8562억 7869만</t>
+  </si>
+  <si>
+    <t>개종망겜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
+  </si>
+  <si>
+    <t>3293조 8550억 2424만</t>
+  </si>
+  <si>
+    <t>커튼월</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
+  </si>
+  <si>
+    <t>3051조 2684억 6323만</t>
+  </si>
+  <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>3028조 1159억 9865만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
+  </si>
+  <si>
+    <t>2825조 2016억 7065만</t>
+  </si>
+  <si>
+    <t>천요화</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
+  </si>
+  <si>
+    <t>2812조 7489억 5017만</t>
+  </si>
+  <si>
+    <t>gorystalLOVE</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
+  </si>
+  <si>
+    <t>2740조 1127억 8972만</t>
+  </si>
+  <si>
+    <t>명지동꿀주먹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
+  </si>
+  <si>
+    <t>2558조 6371억 2618만</t>
+  </si>
+  <si>
+    <t>Judge99</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>2454조 646억 3923만</t>
+  </si>
+  <si>
+    <t>도리토스치즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
+  </si>
+  <si>
+    <t>1641조 8069억 2741만</t>
+  </si>
+  <si>
+    <t>지낌이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1197조 1381억 5357만</t>
+  </si>
+  <si>
+    <t>옥슈쓔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
+  </si>
+  <si>
+    <t>1159조 1872억 4556만</t>
+  </si>
+  <si>
+    <t>스툭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
+  </si>
+  <si>
+    <t>1099조 5687억 5690만</t>
+  </si>
+  <si>
+    <t>커럭트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>1059조 2120억 7264만</t>
+  </si>
+  <si>
+    <t>욧츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>983조 2121억 6252만</t>
+  </si>
+  <si>
+    <t>무동동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
+  </si>
+  <si>
+    <t>939조 4385억 160만</t>
+  </si>
+  <si>
+    <t>양룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>911조 1863억 1172만</t>
+  </si>
+  <si>
+    <t>gorystal</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
+  </si>
+  <si>
+    <t>879조 4249억 6660만</t>
+  </si>
+  <si>
+    <t>또띠야칩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
+  </si>
+  <si>
+    <t>802조 5020억 2166만</t>
+  </si>
+  <si>
+    <t>복룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>786조 245억 4746만</t>
+  </si>
+  <si>
+    <t>률율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>740조 7326억 3663만</t>
+  </si>
+  <si>
+    <t>뀨꾸룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>735조 288억 114만</t>
+  </si>
+  <si>
+    <t>파파존스맛나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
+  </si>
+  <si>
+    <t>705조 6030억 8365만</t>
+  </si>
+  <si>
+    <t>짜상무</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
+  </si>
+  <si>
+    <t>690조 8189억 3082만</t>
+  </si>
+  <si>
+    <t>매리골드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
+  </si>
+  <si>
+    <t>451조 3210억 8830만</t>
+  </si>
+  <si>
+    <t>원종일짱유나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>397조 5451억 5417만</t>
+  </si>
+  <si>
+    <t>문배동육칼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
+  </si>
+  <si>
+    <t>379조 4412억 4014만</t>
+  </si>
+  <si>
     <t>아이스꾸임</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
     <t>116</t>
   </si>
   <si>
     <t>2경 237조 9091억 2548만</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>7601조 6815억 1984만</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>7915조 5233억 4019만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -249,13 +912,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>3977조 6444억 4078만</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>4261조 8121억 2145만</t>
   </si>
   <si>
     <t>대방어조아</t>
@@ -264,28 +921,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
   </si>
   <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
     <t>3924조 2536억 9340만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>엘라임</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
   </si>
   <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>3762조 2211억 2278만</t>
-  </si>
-  <si>
-    <t>6</t>
+    <t>3855조 7457억 7793만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -294,10 +939,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
   </si>
   <si>
-    <t>2728조 3700억 7437만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>2845조 5542억 8706만</t>
   </si>
   <si>
     <t>서포터즈</t>
@@ -306,10 +948,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
   </si>
   <si>
-    <t>2631조 6453억 5245만</t>
-  </si>
-  <si>
-    <t>8</t>
+    <t>2746조 3871억 2532만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2284조 2891억 4675만</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>2119조 8987억 8050만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -318,45 +972,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
     <t>2043조 9656억 4336만</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>1989조 7824억 6125만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>1905조 6059억 8847만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -366,9 +984,6 @@
     <t>1697조 755억 7134만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>불보독지</t>
   </si>
   <si>
@@ -378,10 +993,25 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1315조 5220억 4669만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>1322조 8716억 7240만</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1128조 7710억 7257만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1123조 2521억 2655만</t>
   </si>
   <si>
     <t>우후</t>
@@ -390,39 +1020,9 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>110</t>
-  </si>
-  <si>
     <t>1109조 9165억 9489만</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1108조 180억 2351만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>1073조 5649억 8462만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>채무조정</t>
   </si>
   <si>
@@ -432,7 +1032,13 @@
     <t>1065조 650억 5642만</t>
   </si>
   <si>
-    <t>17</t>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>1037조 6022억 9430만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -444,37 +1050,22 @@
     <t>1035조 3847억 2058만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>뽀송히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>109</t>
-  </si>
-  <si>
-    <t>1004조 8036억 1662만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>정태준</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
   </si>
   <si>
-    <t>945조 4753억 8997만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>970조 2899억 6670만</t>
+  </si>
+  <si>
+    <t>라탱호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
+  </si>
+  <si>
+    <t>839조 136억 3753만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -483,10 +1074,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>694조 9328억 4347만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>771조 110억 9890만</t>
+  </si>
+  <si>
+    <t>짤똘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
+  </si>
+  <si>
+    <t>671조 4394억 5627만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -498,9 +1095,6 @@
     <t>575조 1653억 9478만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>민들레꽃</t>
   </si>
   <si>
@@ -510,9 +1104,6 @@
     <t>551조 4586억 8525만</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>박준우2</t>
   </si>
   <si>
@@ -522,22 +1113,13 @@
     <t>538조 1761억 3296만</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
     <t>솔인</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>465조 5751억 1115만</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>467조 3553억 7499만</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -546,10 +1128,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>435조 2837억 6019만</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>445조 8279억 8293만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -561,10 +1140,16 @@
     <t>108</t>
   </si>
   <si>
-    <t>326조 4698억 2146만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>327조 8098억 2654만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>290조 6954억 7448만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -576,580 +1161,10 @@
     <t>275조 6869억 3523만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>바이퍼</t>
-  </si>
-  <si>
-    <t>270조 8495억 5221만</t>
-  </si>
-  <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>8623조 4455억 698만</t>
-  </si>
-  <si>
-    <t>수텍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>7468조 2422억 4958만</t>
-  </si>
-  <si>
-    <t>포항엄석대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
-  </si>
-  <si>
-    <t>4453조 8085억 1203만</t>
-  </si>
-  <si>
-    <t>협의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
-  </si>
-  <si>
-    <t>4402조 1032억 4015만</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
-  </si>
-  <si>
-    <t>3303조 6174억 3840만</t>
-  </si>
-  <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>3074조 9670억 3069만</t>
-  </si>
-  <si>
-    <t>댜니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2719조 7474억 1743만</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>2581조 6429억 5864만</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>2472조 8689억 2239만</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>2465조 3877억 3257만</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>2441조 2925억 1424만</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>2313조 7071억 7362만</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>2255조 4974억 667만</t>
-  </si>
-  <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1889조 8524억 3410만</t>
-  </si>
-  <si>
-    <t>파울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>1802조 8305억 7088만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>1303조 7925억 4494만</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1293조 7161억 8573만</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1247조 6075억 2806만</t>
-  </si>
-  <si>
-    <t>짱잘자쿨냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%9E%98%EC%9E%90%EC%BF%A8%EB%83%A5</t>
-  </si>
-  <si>
-    <t>1149조 8047억 287만</t>
-  </si>
-  <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1083조 3384억 3846만</t>
-  </si>
-  <si>
-    <t>기본이리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1078조 6352억 6820만</t>
-  </si>
-  <si>
-    <t>냐은</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%83%90%EC%9D%80</t>
-  </si>
-  <si>
-    <t>1068조 2571억 1131만</t>
-  </si>
-  <si>
-    <t>마갤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EA%B0%A4</t>
-  </si>
-  <si>
-    <t>1060조 3768억 2296만</t>
-  </si>
-  <si>
-    <t>전산봉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%EC%82%B0%EB%B4%89</t>
-  </si>
-  <si>
-    <t>925조 3542억 1411만</t>
-  </si>
-  <si>
-    <t>오옹나이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>883조 1176억 6134만</t>
-  </si>
-  <si>
-    <t>고숨도칭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
-  </si>
-  <si>
-    <t>849조 971억 5090만</t>
-  </si>
-  <si>
-    <t>Doham</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Doham</t>
-  </si>
-  <si>
-    <t>793조 748억 2183만</t>
-  </si>
-  <si>
-    <t>태코찡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
-  </si>
-  <si>
-    <t>775조 1513억 6255만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>유플러스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%94%8C%EB%9F%AC%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>649조 5527억 6316만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>빵후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%B5%ED%9B%84</t>
-  </si>
-  <si>
-    <t>286조 3410억 357만</t>
-  </si>
-  <si>
-    <t>가겠습니다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>7608조 9145억 6232만</t>
-  </si>
-  <si>
-    <t>라카도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
-  </si>
-  <si>
-    <t>4934조 5246억 3849만</t>
-  </si>
-  <si>
-    <t>롤대신해야지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%A4%EB%8C%80%EC%8B%A0%ED%95%B4%EC%95%BC%EC%A7%80</t>
-  </si>
-  <si>
-    <t>4016조 8249억 1279만</t>
-  </si>
-  <si>
-    <t>미우맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
-  </si>
-  <si>
-    <t>3684조 5142억 2036만</t>
-  </si>
-  <si>
-    <t>개종망겜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%A2%85%EB%A7%9D%EA%B2%9C</t>
-  </si>
-  <si>
-    <t>3293조 8550억 2424만</t>
-  </si>
-  <si>
-    <t>커튼월</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
-  </si>
-  <si>
-    <t>2834조 1888억 1942만</t>
-  </si>
-  <si>
-    <t>DREAMLINER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
-  </si>
-  <si>
-    <t>2759조 5197억 9026만</t>
-  </si>
-  <si>
-    <t>천요화</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%9A%94%ED%99%94</t>
-  </si>
-  <si>
-    <t>2753조 8727억 4004만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
-  </si>
-  <si>
-    <t>2644조 703억 3944만</t>
-  </si>
-  <si>
-    <t>명지동꿀주먹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
-  </si>
-  <si>
-    <t>2528조 4750억 2397만</t>
-  </si>
-  <si>
-    <t>gorystalLOVE</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
-  </si>
-  <si>
-    <t>2351조 9875억 2829만</t>
-  </si>
-  <si>
-    <t>Judge99</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Judge99</t>
-  </si>
-  <si>
-    <t>2336조 2072억 6503만</t>
-  </si>
-  <si>
-    <t>도리토스치즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
-  </si>
-  <si>
-    <t>1641조 8069억 2741만</t>
-  </si>
-  <si>
-    <t>지낌이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1100조 4977억 6561만</t>
-  </si>
-  <si>
-    <t>스툭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
-  </si>
-  <si>
-    <t>1075조 4105억 4512만</t>
-  </si>
-  <si>
-    <t>옥슈쓔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
-  </si>
-  <si>
-    <t>991조 4376억 1607만</t>
-  </si>
-  <si>
-    <t>욧츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>983조 2121억 6252만</t>
-  </si>
-  <si>
-    <t>커럭트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>923조 9124억 9450만</t>
-  </si>
-  <si>
-    <t>양룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>911조 1863억 1172만</t>
-  </si>
-  <si>
-    <t>무동동</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%8F%99%EB%8F%99</t>
-  </si>
-  <si>
-    <t>903조 5254억 9045만</t>
-  </si>
-  <si>
-    <t>gorystal</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=gorystal</t>
-  </si>
-  <si>
-    <t>790조 9059억 8419만</t>
-  </si>
-  <si>
-    <t>또띠야칩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
-  </si>
-  <si>
-    <t>775조 9620억 8479만</t>
-  </si>
-  <si>
-    <t>복룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>746조 3009억 299만</t>
-  </si>
-  <si>
-    <t>뀨꾸룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%80%A8%EA%BE%B8%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>692조 2460억 8475만</t>
-  </si>
-  <si>
-    <t>짜상무</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9C%EC%83%81%EB%AC%B4</t>
-  </si>
-  <si>
-    <t>665조 2346억 615만</t>
-  </si>
-  <si>
-    <t>파파존스맛나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%ED%8C%8C%EC%A1%B4%EC%8A%A4%EB%A7%9B%EB%82%98</t>
-  </si>
-  <si>
-    <t>657조 7522억 2440만</t>
-  </si>
-  <si>
-    <t>률율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>642조 104억 5929만</t>
-  </si>
-  <si>
-    <t>매리골드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
-  </si>
-  <si>
-    <t>414조 6642억 9700만</t>
-  </si>
-  <si>
-    <t>원종일짱유나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>394조 6210억 2814만</t>
-  </si>
-  <si>
-    <t>문배동육칼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
-  </si>
-  <si>
-    <t>362조 1452억 2256만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>6457조 5219억 9175만</t>
+    <t>6476조 5653억 5349만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1161,22 +1176,22 @@
     <t>5708조 2885억 4200만</t>
   </si>
   <si>
+    <t>도하리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>4283조 899억 2017만</t>
+  </si>
+  <si>
     <t>죽창당일개통</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3917조 2434억 5986만</t>
-  </si>
-  <si>
-    <t>도하리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%ED%95%98%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>3802조 2509억 9228만</t>
+    <t>3933조 5360억 7684만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1185,7 +1200,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>2751조 2086억 7442만</t>
+    <t>3324조 7984억 5566만</t>
+  </si>
+  <si>
+    <t>여니워니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2775조 8283억 3908만</t>
   </si>
   <si>
     <t>이용하다</t>
@@ -1194,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2467조 863억 3175만</t>
+    <t>2583조 6801억 5685만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1203,16 +1227,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>2417조 9903억 6478만</t>
-  </si>
-  <si>
-    <t>여니워니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%8B%88%EC%9B%8C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2374조 2205억 8289만</t>
+    <t>2477조 8147억 2572만</t>
+  </si>
+  <si>
+    <t>해달잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2277조 237억 8803만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1230,16 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
   </si>
   <si>
-    <t>2003조 3427억 7484만</t>
-  </si>
-  <si>
-    <t>해달잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%EB%8B%AC%EC%9E%89</t>
-  </si>
-  <si>
-    <t>1934조 8248억 2045만</t>
+    <t>2146조 3238억 3192만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1248,7 +1263,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>1817조 4953억 3551만</t>
+    <t>2068조 7048억 735만</t>
+  </si>
+  <si>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2055조 407억 5244만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1257,7 +1281,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1794조 9809억 9810만</t>
+    <t>1918조 1494억 5161만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1266,16 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A9%EA%B0%9C</t>
   </si>
   <si>
-    <t>1755조 1937억 6384만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1643조 4872억 6754만</t>
+    <t>1899조 6860억 4532만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1284,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1356조 2717억 3730만</t>
+    <t>1675조 5719억 5782만</t>
   </si>
   <si>
     <t>예타</t>
@@ -1293,7 +1308,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1237조 3127억 5973만</t>
+    <t>1237조 8245억 7030만</t>
+  </si>
+  <si>
+    <t>티에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>1156조 440억 654만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1302,7 +1326,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%A5%B4%ED%8E%98%EC%9A%B0%EC%8A%A4</t>
   </si>
   <si>
-    <t>992조 426억 4572만</t>
+    <t>1049조 3531억 5215만</t>
+  </si>
+  <si>
+    <t>박금쪽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
+  </si>
+  <si>
+    <t>1001조 2765억 9574만</t>
+  </si>
+  <si>
+    <t>작업치료사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
+  </si>
+  <si>
+    <t>947조 4009억 563만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1311,25 +1353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>925조 2128억 9053만</t>
-  </si>
-  <si>
-    <t>박금쪽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
-  </si>
-  <si>
-    <t>922조 4504억 367만</t>
-  </si>
-  <si>
-    <t>티에이치</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
-  </si>
-  <si>
-    <t>912조 6534억 4698만</t>
+    <t>935조 4890억 3993만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1356,7 +1380,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>746조 5284억 1379만</t>
+    <t>748조 5004억 9254만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1368,15 +1392,6 @@
     <t>725조 7659억 853만</t>
   </si>
   <si>
-    <t>작업치료사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
-  </si>
-  <si>
-    <t>627조 1553억 6314만</t>
-  </si>
-  <si>
     <t>계니규니</t>
   </si>
   <si>
@@ -1392,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>509조 3405억 2279만</t>
+    <t>595조 341억 9825만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1401,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>400조 5703억 7489만</t>
+    <t>404조 4529억 969만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1410,7 +1425,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>385조 3941억 429만</t>
+    <t>390조 9478억 8266만</t>
   </si>
 </sst>
 </file>
@@ -1897,19 +1912,19 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1938,19 +1953,19 @@
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1973,22 +1988,22 @@
         <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2008,15 +2023,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2025,28 +2041,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2057,28 +2073,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>65</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2089,28 +2105,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2121,22 +2137,22 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>63</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>74</v>
@@ -2165,13 +2181,13 @@
         <v>78</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>80</v>
@@ -2197,16 +2213,16 @@
         <v>83</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2217,28 +2233,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2249,28 +2265,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2281,28 +2297,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2313,28 +2329,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2345,28 +2361,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2377,28 +2393,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2409,28 +2425,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2441,28 +2457,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2473,28 +2489,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>79</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2505,28 +2521,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2537,28 +2553,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2569,28 +2585,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2601,25 +2617,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>144</v>
@@ -2645,13 +2661,13 @@
         <v>147</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>148</v>
@@ -2677,13 +2693,13 @@
         <v>151</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>152</v>
@@ -2709,13 +2725,13 @@
         <v>155</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>156</v>
@@ -2741,13 +2757,13 @@
         <v>159</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>160</v>
@@ -2773,13 +2789,13 @@
         <v>163</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>164</v>
@@ -2805,16 +2821,16 @@
         <v>167</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -2825,25 +2841,25 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>173</v>
@@ -2869,16 +2885,16 @@
         <v>176</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -2889,28 +2905,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -2921,35 +2937,99 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -2979,6 +3059,8 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2991,7 +3073,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
@@ -3004,28 +3086,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3036,31 +3118,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3068,31 +3150,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>194</v>
+        <v>104</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3100,31 +3182,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3135,28 +3217,28 @@
         <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3167,28 +3249,28 @@
         <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3196,31 +3278,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3228,31 +3310,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3260,31 +3342,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>212</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="H9" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3292,31 +3374,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3324,31 +3406,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>217</v>
+        <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3356,31 +3438,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3388,31 +3470,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3420,31 +3502,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3452,31 +3534,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3484,31 +3566,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3516,31 +3598,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3548,31 +3630,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>217</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3580,31 +3662,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3615,28 +3697,28 @@
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3647,28 +3729,28 @@
         <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -3679,28 +3761,28 @@
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -3711,28 +3793,28 @@
         <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -3743,28 +3825,28 @@
         <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -3775,28 +3857,28 @@
         <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -3804,31 +3886,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -3839,28 +3921,28 @@
         <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="I27" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -3868,31 +3950,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="H28" s="2" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -3900,31 +3982,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>63</v>
+        <v>189</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -3932,31 +4014,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -3964,31 +4046,31 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4036,11 +4118,10 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4049,28 +4130,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4081,31 +4162,31 @@
         <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>195</v>
+        <v>288</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4113,31 +4194,31 @@
         <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -4145,31 +4226,31 @@
         <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4180,28 +4261,28 @@
         <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4212,28 +4293,28 @@
         <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4241,31 +4322,31 @@
         <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4273,31 +4354,31 @@
         <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -4305,31 +4386,31 @@
         <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>305</v>
+        <v>42</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>305</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -4337,31 +4418,31 @@
         <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>310</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -4369,31 +4450,31 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I11" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -4401,31 +4482,31 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>230</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -4433,31 +4514,31 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>97</v>
+        <v>321</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -4465,31 +4546,31 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -4497,31 +4578,31 @@
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -4529,31 +4610,31 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -4561,31 +4642,31 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -4593,31 +4674,31 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -4625,31 +4706,31 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -4660,28 +4741,28 @@
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>217</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4692,28 +4773,28 @@
         <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4724,28 +4805,28 @@
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4756,28 +4837,28 @@
         <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>194</v>
+        <v>90</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4788,28 +4869,28 @@
         <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4820,28 +4901,28 @@
         <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>74</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4849,31 +4930,31 @@
         <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4884,28 +4965,28 @@
         <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4913,31 +4994,31 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4945,31 +5026,31 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>278</v>
+        <v>123</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>143</v>
+        <v>370</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4977,31 +5058,31 @@
         <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -5009,31 +5090,31 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -5094,28 +5175,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5126,28 +5207,28 @@
         <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5158,28 +5239,28 @@
         <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5190,28 +5271,28 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5225,25 +5306,25 @@
         <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5257,25 +5338,25 @@
         <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>116</v>
+        <v>321</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5286,28 +5367,28 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5318,28 +5399,28 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5350,28 +5431,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5382,28 +5463,28 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>79</v>
+        <v>230</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5414,28 +5495,28 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5446,28 +5527,28 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5478,28 +5559,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5510,28 +5591,28 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>168</v>
+        <v>321</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5542,28 +5623,28 @@
         <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5574,28 +5655,28 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5606,28 +5687,28 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5638,28 +5719,28 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5670,28 +5751,28 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>63</v>
+        <v>230</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5705,25 +5786,25 @@
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5737,25 +5818,25 @@
         <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5769,25 +5850,25 @@
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5801,25 +5882,25 @@
         <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5833,25 +5914,25 @@
         <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5865,25 +5946,25 @@
         <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5894,28 +5975,28 @@
         <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5929,25 +6010,25 @@
         <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>217</v>
+        <v>123</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5958,28 +6039,28 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5990,28 +6071,28 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6022,28 +6103,28 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>275</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>121</v>
+        <v>172</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6054,28 +6135,28 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>280</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="F31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="H31" s="2" t="s">
-        <v>177</v>
+        <v>370</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TopOfTop!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="464">
   <si>
     <t>guild_name</t>
   </si>
@@ -219,7 +219,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9094조 7371억 4105만</t>
+    <t>9743조 813억 3813만</t>
   </si>
   <si>
     <t>2</t>
@@ -234,7 +234,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>7571조 6718억 4695만</t>
+    <t>7731조 8382억 7567만</t>
   </si>
   <si>
     <t>3</t>
@@ -252,7 +252,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>4469조 9154억 1147만</t>
+    <t>4492조 1878억 3268만</t>
   </si>
   <si>
     <t>4</t>
@@ -285,7 +285,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>3686조 6135억 2383만</t>
+    <t>3689조 8892억 3174만</t>
   </si>
   <si>
     <t>6</t>
@@ -345,7 +345,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>2517조 3409억 1416만</t>
+    <t>2530조 3491억 7461만</t>
   </si>
   <si>
     <t>10</t>
@@ -360,7 +360,7 @@
     <t>캡틴</t>
   </si>
   <si>
-    <t>2472조 8689억 2239만</t>
+    <t>2515조 2382억 6614만</t>
   </si>
   <si>
     <t>11</t>
@@ -399,7 +399,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>2287조 747억 2820만</t>
+    <t>2292조 9975억 215만</t>
   </si>
   <si>
     <t>14</t>
@@ -447,31 +447,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
   </si>
   <si>
-    <t>1328조 7104억 3097만</t>
+    <t>1338조 9567억 2031만</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
+    <t>모짜리코베르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>1337조 9988억 6043만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
   </si>
   <si>
     <t>Y</t>
   </si>
   <si>
-    <t>1316조 2657억 6833만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1263조 2766억 1030만</t>
+    <t>1316조 5131억 3303만</t>
   </si>
   <si>
     <t>20</t>
@@ -489,6 +489,18 @@
     <t>21</t>
   </si>
   <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1173조 7299억 1919만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>짱잘자쿨냥</t>
   </si>
   <si>
@@ -498,18 +510,6 @@
     <t>1149조 8047억 287만</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1140조 9567억 8620만</t>
-  </si>
-  <si>
     <t>23</t>
   </si>
   <si>
@@ -519,7 +519,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%B3%B8%EC%9D%B4%EB%A6%AC</t>
   </si>
   <si>
-    <t>1078조 6352억 6820만</t>
+    <t>1128조 1572억 135만</t>
   </si>
   <si>
     <t>24</t>
@@ -546,7 +546,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>952조 4188억 521만</t>
+    <t>952조 4457억 9458만</t>
   </si>
   <si>
     <t>26</t>
@@ -558,7 +558,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%88%A8%EB%8F%84%EC%B9%AD</t>
   </si>
   <si>
-    <t>864조 3912억 902만</t>
+    <t>879조 345억 6976만</t>
   </si>
   <si>
     <t>27</t>
@@ -570,7 +570,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>845조 9463억 6641만</t>
+    <t>848조 4037억 9866만</t>
   </si>
   <si>
     <t>28</t>
@@ -582,7 +582,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>803조 7038억 6082만</t>
+    <t>806조 785억 6034만</t>
   </si>
   <si>
     <t>29</t>
@@ -621,7 +621,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EA%B2%A0%EC%8A%B5%EB%8B%88%EB%8B%A4</t>
   </si>
   <si>
-    <t>7993조 5091억 8323만</t>
+    <t>7996조 3673억 7488만</t>
+  </si>
+  <si>
+    <t>미우맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
+  </si>
+  <si>
+    <t>5531조 6892억 328만</t>
   </si>
   <si>
     <t>라카도</t>
@@ -630,7 +639,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4934조 5246억 3849만</t>
+    <t>4998조 7308억 5935만</t>
   </si>
   <si>
     <t>롤대신해야지</t>
@@ -642,15 +651,6 @@
     <t>4695조 3427억 8180만</t>
   </si>
   <si>
-    <t>미우맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%9A%B0%EB%A7%98</t>
-  </si>
-  <si>
-    <t>4205조 8562억 7869만</t>
-  </si>
-  <si>
     <t>개종망겜</t>
   </si>
   <si>
@@ -666,7 +666,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>3051조 2684억 6323만</t>
+    <t>3077조 3973억 8600만</t>
   </si>
   <si>
     <t>DREAMLINER</t>
@@ -681,7 +681,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
   </si>
   <si>
-    <t>2825조 2016억 7065만</t>
+    <t>2967조 6832억 6223만</t>
   </si>
   <si>
     <t>천요화</t>
@@ -699,7 +699,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
   </si>
   <si>
-    <t>2740조 1127억 8972만</t>
+    <t>2740조 7867억 7417만</t>
   </si>
   <si>
     <t>명지동꿀주먹</t>
@@ -708,7 +708,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>2558조 6371억 2618만</t>
+    <t>2590조 3931억 9874만</t>
   </si>
   <si>
     <t>Judge99</t>
@@ -720,7 +720,7 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>2454조 646억 3923만</t>
+    <t>2478조 451억 385만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -729,7 +729,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1641조 8069억 2741만</t>
+    <t>1646조 9463억 9910만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -747,7 +747,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>1159조 1872억 4556만</t>
+    <t>1162조 9583억 2280만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -756,7 +756,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%88%AD</t>
   </si>
   <si>
-    <t>1099조 5687억 5690만</t>
+    <t>1123조 8859억 609만</t>
   </si>
   <si>
     <t>커럭트</t>
@@ -765,7 +765,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
   </si>
   <si>
-    <t>1059조 2120억 7264만</t>
+    <t>1070조 4154억 4123만</t>
   </si>
   <si>
     <t>욧츠</t>
@@ -774,7 +774,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A7%EC%B8%A0</t>
   </si>
   <si>
-    <t>983조 2121억 6252만</t>
+    <t>1004조 3060억 9433만</t>
   </si>
   <si>
     <t>무동동</t>
@@ -801,7 +801,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>879조 4249억 6660만</t>
+    <t>898조 3325억 1255만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -810,7 +810,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9D%A0%EC%95%BC%EC%B9%A9</t>
   </si>
   <si>
-    <t>802조 5020억 2166만</t>
+    <t>836조 7862억 1508만</t>
   </si>
   <si>
     <t>복룽</t>
@@ -819,7 +819,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>786조 245억 4746만</t>
+    <t>788조 6231억 1453만</t>
   </si>
   <si>
     <t>률율율</t>
@@ -828,7 +828,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%A0%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>740조 7326억 3663만</t>
+    <t>741조 8129억 6928만</t>
   </si>
   <si>
     <t>뀨꾸룽</t>
@@ -864,7 +864,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>451조 3210억 8830만</t>
+    <t>453조 8280억 6944만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -873,7 +873,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>397조 5451억 5417만</t>
+    <t>423조 6040억 5186만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -882,7 +882,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>379조 4412억 4014만</t>
+    <t>379조 6134억 1592만</t>
   </si>
   <si>
     <t>아이스꾸임</t>
@@ -894,7 +894,7 @@
     <t>116</t>
   </si>
   <si>
-    <t>2경 237조 9091억 2548만</t>
+    <t>2경 255조 6179억 2423만</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -903,7 +903,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>7915조 5233억 4019만</t>
+    <t>7944조 993억 9474만</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>4704조 7804억 542만</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -924,13 +933,13 @@
     <t>3924조 2536억 9340만</t>
   </si>
   <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>3855조 7457억 7793만</t>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2958조 4121억 9385만</t>
   </si>
   <si>
     <t>퍼퓸</t>
@@ -942,19 +951,10 @@
     <t>2845조 5542억 8706만</t>
   </si>
   <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2746조 3871억 2532만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2284조 2891억 4675만</t>
+    <t>2301조 7318억 5637만</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -963,7 +963,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>2119조 8987억 8050만</t>
+    <t>2155조 4511억 6887만</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -993,7 +993,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1322조 8716억 7240만</t>
+    <t>1324조 9226억 3624만</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -1002,7 +1002,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>1128조 7710억 7257만</t>
+    <t>1134조 9932억 8765만</t>
   </si>
   <si>
     <t>호우기</t>
@@ -1011,7 +1011,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
   </si>
   <si>
-    <t>1123조 2521억 2655만</t>
+    <t>1124조 2763억 6571만</t>
   </si>
   <si>
     <t>우후</t>
@@ -1029,7 +1029,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
   </si>
   <si>
-    <t>1065조 650억 5642만</t>
+    <t>1077조 4158억 5356만</t>
   </si>
   <si>
     <t>뽀송히</t>
@@ -1038,7 +1038,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
   </si>
   <si>
-    <t>1037조 6022억 9430만</t>
+    <t>1042조 2381억 369만</t>
   </si>
   <si>
     <t>좀치는형님</t>
@@ -1065,7 +1065,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
   </si>
   <si>
-    <t>839조 136억 3753만</t>
+    <t>878조 9823억 5133만</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -1074,7 +1074,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>771조 110억 9890만</t>
+    <t>789조 2546억 9378만</t>
   </si>
   <si>
     <t>짤똘</t>
@@ -1083,7 +1083,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
   </si>
   <si>
-    <t>671조 4394억 5627만</t>
+    <t>671조 5173억 6638만</t>
   </si>
   <si>
     <t>팡대지</t>
@@ -1101,7 +1101,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>551조 4586억 8525만</t>
+    <t>558조 368억 4937만</t>
   </si>
   <si>
     <t>박준우2</t>
@@ -1119,16 +1119,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
   </si>
   <si>
-    <t>467조 3553억 7499만</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>445조 8279억 8293만</t>
+    <t>468조 4891억 849만</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -1140,7 +1131,7 @@
     <t>108</t>
   </si>
   <si>
-    <t>327조 8098억 2654만</t>
+    <t>337조 7925억 8502만</t>
   </si>
   <si>
     <t>여눈</t>
@@ -1149,7 +1140,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
   </si>
   <si>
-    <t>290조 6954억 7448만</t>
+    <t>292조 9201억 6015만</t>
   </si>
   <si>
     <t>꼬북빵야</t>
@@ -1164,7 +1155,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>6476조 5653억 5349만</t>
+    <t>6501조 2641억 9896만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1191,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3933조 5360억 7684만</t>
+    <t>3944조 2652억 3274만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1218,7 +1209,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2583조 6801억 5685만</t>
+    <t>2601조 2204억 5556만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1227,7 +1218,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>2477조 8147억 2572만</t>
+    <t>2481조 5827억 2891만</t>
+  </si>
+  <si>
+    <t>종꿀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
+  </si>
+  <si>
+    <t>2420조 6677억 6056만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1239,13 +1239,13 @@
     <t>2277조 237억 8803만</t>
   </si>
   <si>
-    <t>종꿀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
-  </si>
-  <si>
-    <t>2274조 8790억 9139만</t>
+    <t>자이언트리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2151조 5238억 6674만</t>
   </si>
   <si>
     <t>시골미남</t>
@@ -1263,16 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>2068조 7048억 735만</t>
-  </si>
-  <si>
-    <t>자이언트리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2055조 407억 5244만</t>
+    <t>2092조 5680억 8366만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1281,7 +1272,16 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1918조 1494억 5161만</t>
+    <t>1988조 3644억 8119만</t>
+  </si>
+  <si>
+    <t>여자둘남자둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
+  </si>
+  <si>
+    <t>1912조 768억 9141만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1293,22 +1293,13 @@
     <t>1899조 6860억 4532만</t>
   </si>
   <si>
-    <t>여자둘남자둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
-  </si>
-  <si>
-    <t>1675조 5719억 5782만</t>
-  </si>
-  <si>
     <t>예타</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1237조 8245억 7030만</t>
+    <t>1291조 2442억 5985만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1317,7 +1308,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>1156조 440억 654만</t>
+    <t>1156조 5866억 1348만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1329,6 +1320,15 @@
     <t>1049조 3531억 5215만</t>
   </si>
   <si>
+    <t>작업치료사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1036조 5240억 221만</t>
+  </si>
+  <si>
     <t>박금쪽</t>
   </si>
   <si>
@@ -1338,22 +1338,13 @@
     <t>1001조 2765억 9574만</t>
   </si>
   <si>
-    <t>작업치료사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%91%EC%97%85%EC%B9%98%EB%A3%8C%EC%82%AC</t>
-  </si>
-  <si>
-    <t>947조 4009억 563만</t>
-  </si>
-  <si>
     <t>파이리양말</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9D%B4%EB%A6%AC%EC%96%91%EB%A7%90</t>
   </si>
   <si>
-    <t>935조 4890억 3993만</t>
+    <t>940조 644억 5296만</t>
   </si>
   <si>
     <t>성률</t>
@@ -1365,22 +1356,22 @@
     <t>910조 593억 4871만</t>
   </si>
   <si>
+    <t>지존짱창남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
+  </si>
+  <si>
+    <t>791조 7059억 4412만</t>
+  </si>
+  <si>
     <t>감화</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>781조 5966억 4318만</t>
-  </si>
-  <si>
-    <t>지존짱창남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
-  </si>
-  <si>
-    <t>748조 5004억 9254만</t>
+    <t>782조 9287억 8838만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1398,7 +1389,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%84%EB%8B%88%EA%B7%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>602조 5546억 7140만</t>
+    <t>641조 721억 8379만</t>
   </si>
   <si>
     <t>신탄보우짱</t>
@@ -1407,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>595조 341억 9825만</t>
+    <t>613조 6005억 7337만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1416,7 +1407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>404조 4529억 969만</t>
+    <t>413조 5874억 3219만</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1425,7 +1416,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>390조 9478억 8266만</t>
+    <t>392조 3486억 9945만</t>
   </si>
 </sst>
 </file>
@@ -2603,7 +2594,7 @@
         <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>140</v>
@@ -2620,19 +2611,19 @@
         <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>143</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>99</v>
@@ -2652,19 +2643,19 @@
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="G20" s="2" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>99</v>
@@ -2731,7 +2722,7 @@
         <v>84</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>156</v>
@@ -3165,10 +3156,10 @@
         <v>61</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>104</v>
+        <v>189</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>201</v>
@@ -3197,10 +3188,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>204</v>
@@ -3229,10 +3220,10 @@
         <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>79</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>207</v>
@@ -3354,7 +3345,7 @@
         <v>217</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>62</v>
@@ -4113,7 +4104,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4241,10 +4232,10 @@
         <v>61</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>295</v>
@@ -4273,10 +4264,10 @@
         <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>298</v>
@@ -4305,7 +4296,7 @@
         <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>85</v>
@@ -4337,10 +4328,10 @@
         <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>304</v>
@@ -4369,10 +4360,10 @@
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>307</v>
@@ -4398,7 +4389,7 @@
         <v>308</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>73</v>
@@ -4692,7 +4683,7 @@
         <v>104</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>337</v>
@@ -5009,13 +5000,13 @@
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>172</v>
+        <v>367</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5029,22 +5020,22 @@
         <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>370</v>
+        <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>371</v>
@@ -5073,7 +5064,7 @@
         <v>61</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>194</v>
@@ -5085,40 +5076,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -5149,7 +5108,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5216,10 +5174,10 @@
         <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>104</v>
@@ -5228,7 +5186,7 @@
         <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5242,13 +5200,13 @@
         <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>61</v>
@@ -5260,7 +5218,7 @@
         <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5274,13 +5232,13 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>61</v>
@@ -5292,7 +5250,7 @@
         <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5306,13 +5264,13 @@
         <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>61</v>
@@ -5324,7 +5282,7 @@
         <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5338,13 +5296,13 @@
         <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>61</v>
@@ -5356,7 +5314,7 @@
         <v>63</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5370,13 +5328,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>61</v>
@@ -5385,10 +5343,10 @@
         <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5402,13 +5360,13 @@
         <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>61</v>
@@ -5420,7 +5378,7 @@
         <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5434,13 +5392,13 @@
         <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>61</v>
@@ -5452,7 +5410,7 @@
         <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5466,25 +5424,25 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5498,25 +5456,25 @@
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>62</v>
+        <v>230</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5530,25 +5488,25 @@
         <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>321</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5562,25 +5520,25 @@
         <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5594,25 +5552,25 @@
         <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>321</v>
+        <v>62</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5626,13 +5584,13 @@
         <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>61</v>
@@ -5644,7 +5602,7 @@
         <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5658,25 +5616,25 @@
         <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5690,25 +5648,25 @@
         <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5722,13 +5680,13 @@
         <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
@@ -5740,7 +5698,7 @@
         <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5754,13 +5712,13 @@
         <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>61</v>
@@ -5772,7 +5730,7 @@
         <v>105</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5786,13 +5744,13 @@
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
@@ -5804,7 +5762,7 @@
         <v>99</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5818,25 +5776,25 @@
         <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5850,25 +5808,25 @@
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5882,13 +5840,13 @@
         <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>61</v>
@@ -5900,7 +5858,7 @@
         <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5914,13 +5872,13 @@
         <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>61</v>
@@ -5932,7 +5890,7 @@
         <v>105</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5946,25 +5904,25 @@
         <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5978,25 +5936,25 @@
         <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6010,13 +5968,13 @@
         <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>61</v>
@@ -6028,7 +5986,7 @@
         <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6042,13 +6000,13 @@
         <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>61</v>
@@ -6060,7 +6018,7 @@
         <v>105</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6074,13 +6032,13 @@
         <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>61</v>
@@ -6089,10 +6047,10 @@
         <v>84</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6106,13 +6064,13 @@
         <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>61</v>
@@ -6124,7 +6082,7 @@
         <v>172</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6138,13 +6096,13 @@
         <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>61</v>
@@ -6153,10 +6111,10 @@
         <v>62</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -9,15 +9,15 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="지존길드" sheetId="2" r:id="rId2"/>
-    <sheet name="TopOfTop" sheetId="3" r:id="rId3"/>
-    <sheet name="빅딜" sheetId="4" r:id="rId4"/>
+    <sheet name="빅딜" sheetId="3" r:id="rId3"/>
+    <sheet name="TopOfTop" sheetId="4" r:id="rId4"/>
     <sheet name="눈별" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TopOfTop!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TopOfTop!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">지존길드!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="465">
   <si>
     <t>guild_name</t>
   </si>
@@ -102,6 +102,33 @@
     <t>2026.09.21</t>
   </si>
   <si>
+    <t>빅딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>866</t>
+  </si>
+  <si>
+    <t>39위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>5경 985조 128억 1537만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
     <t>TopOfTop</t>
   </si>
   <si>
@@ -129,33 +156,6 @@
     <t>2026.09.22</t>
   </si>
   <si>
-    <t>빅딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>866</t>
-  </si>
-  <si>
-    <t>39위</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>5경 985조 128억 1537만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
     <t>눈별</t>
   </si>
   <si>
@@ -219,7 +219,7 @@
     <t>115</t>
   </si>
   <si>
-    <t>9743조 813억 3813만</t>
+    <t>9888조 9654억 14만</t>
   </si>
   <si>
     <t>2</t>
@@ -252,7 +252,7 @@
     <t>114</t>
   </si>
   <si>
-    <t>4492조 1878억 3268만</t>
+    <t>4544조 7861억 2132만</t>
   </si>
   <si>
     <t>4</t>
@@ -285,7 +285,7 @@
     <t>113</t>
   </si>
   <si>
-    <t>3689조 8892억 3174만</t>
+    <t>3694조 4730억 5673만</t>
   </si>
   <si>
     <t>6</t>
@@ -312,7 +312,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>2840조 4958억 3412만</t>
+    <t>2884조 3838억 7409만</t>
   </si>
   <si>
     <t>8</t>
@@ -327,7 +327,7 @@
     <t>112</t>
   </si>
   <si>
-    <t>2582조 4683억 1990만</t>
+    <t>2585조 8424억 4496만</t>
   </si>
   <si>
     <t>9</t>
@@ -345,7 +345,7 @@
     <t>111</t>
   </si>
   <si>
-    <t>2530조 3491억 7461만</t>
+    <t>2533조 6647억 4576만</t>
   </si>
   <si>
     <t>10</t>
@@ -378,6 +378,21 @@
     <t>12</t>
   </si>
   <si>
+    <t>온백</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>2338조 5666억 805만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>엘르가든</t>
   </si>
   <si>
@@ -387,21 +402,6 @@
     <t>2313조 7071억 7362만</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2292조 9975억 215만</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -429,6 +429,18 @@
     <t>16</t>
   </si>
   <si>
+    <t>대좀이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1488조 1251억 1121만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>오옹나이스</t>
   </si>
   <si>
@@ -438,18 +450,6 @@
     <t>1379조 1810억 4031만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1338조 9567억 2031만</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -459,7 +459,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
   </si>
   <si>
-    <t>1337조 9988억 6043만</t>
+    <t>1378조 9632억 3810만</t>
   </si>
   <si>
     <t>19</t>
@@ -471,12 +471,24 @@
     <t>Y</t>
   </si>
   <si>
-    <t>1316조 5131억 3303만</t>
+    <t>1319조 631억 7399만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
+    <t>김허덕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
+  </si>
+  <si>
+    <t>1206조 1272억 7177만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>마갤</t>
   </si>
   <si>
@@ -486,18 +498,6 @@
     <t>1200조 1472억 1769만</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>김허덕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%97%88%EB%8D%95</t>
-  </si>
-  <si>
-    <t>1173조 7299억 1919만</t>
-  </si>
-  <si>
     <t>22</t>
   </si>
   <si>
@@ -546,7 +546,7 @@
     <t>110</t>
   </si>
   <si>
-    <t>952조 4457억 9458만</t>
+    <t>1019조 5372억 3078만</t>
   </si>
   <si>
     <t>26</t>
@@ -570,7 +570,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%BD%94%EC%B0%A1</t>
   </si>
   <si>
-    <t>848조 4037억 9866만</t>
+    <t>850조 4940억 4514만</t>
   </si>
   <si>
     <t>28</t>
@@ -582,7 +582,7 @@
     <t>https://mgf.gg/contents/character.php?n=Doham</t>
   </si>
   <si>
-    <t>806조 785억 6034만</t>
+    <t>822조 168억 4984만</t>
   </si>
   <si>
     <t>29</t>
@@ -615,6 +615,267 @@
     <t>355조 5297억 5157만</t>
   </si>
   <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>2경 321조 1980억 8092만</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>8237조 7144억 4543만</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>5059조 4008억 4197만</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>4261조 8121억 2145만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>3924조 2536억 9340만</t>
+  </si>
+  <si>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>2971조 3297억 316만</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>2586조 1679억 2303만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2301조 7318억 5637만</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>2224조 2393억 3922만</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>2043조 9656억 4336만</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1330조 9299억 4958만</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1139조 3354억 3997만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1124조 2763억 6571만</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>1109조 9165억 9489만</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1081조 8986억 458만</t>
+  </si>
+  <si>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>1050조 6657억 3307만</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1035조 3847억 2058만</t>
+  </si>
+  <si>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>972조 152억 3118만</t>
+  </si>
+  <si>
+    <t>라탱호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
+  </si>
+  <si>
+    <t>881조 7556억 9106만</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>789조 2546억 9378만</t>
+  </si>
+  <si>
+    <t>짤똘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
+  </si>
+  <si>
+    <t>671조 9525억 1752만</t>
+  </si>
+  <si>
+    <t>팡대지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
+  </si>
+  <si>
+    <t>575조 1653억 9478만</t>
+  </si>
+  <si>
+    <t>박준우2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
+  </si>
+  <si>
+    <t>568조 4360억 6361만</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>559조 1192억 5788만</t>
+  </si>
+  <si>
+    <t>솔인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>468조 4891억 849만</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>338조 1338억 8268만</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>328조 9422억 4240만</t>
+  </si>
+  <si>
+    <t>꼬북빵야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
+  </si>
+  <si>
+    <t>275조 6869억 3523만</t>
+  </si>
+  <si>
     <t>가겠습니다</t>
   </si>
   <si>
@@ -639,7 +900,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%B9%B4%EB%8F%84</t>
   </si>
   <si>
-    <t>4998조 7308억 5935만</t>
+    <t>5111조 4615억 812만</t>
   </si>
   <si>
     <t>롤대신해야지</t>
@@ -660,22 +921,22 @@
     <t>3293조 8550억 2424만</t>
   </si>
   <si>
+    <t>DREAMLINER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
+  </si>
+  <si>
+    <t>3252조 7397억 640만</t>
+  </si>
+  <si>
     <t>커튼월</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%8A%BC%EC%9B%94</t>
   </si>
   <si>
-    <t>3077조 3973억 8600만</t>
-  </si>
-  <si>
-    <t>DREAMLINER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=DREAMLINER</t>
-  </si>
-  <si>
-    <t>3028조 1159억 9865만</t>
+    <t>3108조 3375억 7800만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EC%96%B4%EB%9D%B0</t>
@@ -699,7 +960,7 @@
     <t>https://mgf.gg/contents/character.php?n=gorystalLOVE</t>
   </si>
   <si>
-    <t>2740조 7867억 7417만</t>
+    <t>2809조 2348억 295만</t>
   </si>
   <si>
     <t>명지동꿀주먹</t>
@@ -708,7 +969,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%A7%80%EB%8F%99%EA%BF%80%EC%A3%BC%EB%A8%B9</t>
   </si>
   <si>
-    <t>2590조 3931억 9874만</t>
+    <t>2804조 5357억 7451만</t>
   </si>
   <si>
     <t>Judge99</t>
@@ -717,10 +978,7 @@
     <t>https://mgf.gg/contents/character.php?n=Judge99</t>
   </si>
   <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>2478조 451억 385만</t>
+    <t>2602조 520억 3141만</t>
   </si>
   <si>
     <t>도리토스치즈</t>
@@ -729,7 +987,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A6%AC%ED%86%A0%EC%8A%A4%EC%B9%98%EC%A6%88</t>
   </si>
   <si>
-    <t>1646조 9463억 9910만</t>
+    <t>1693조 5870억 434만</t>
   </si>
   <si>
     <t>지낌이</t>
@@ -738,7 +996,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%82%8C%EC%9D%B4</t>
   </si>
   <si>
-    <t>1197조 1381억 5357만</t>
+    <t>1285조 796억 7588만</t>
   </si>
   <si>
     <t>옥슈쓔</t>
@@ -747,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A5%EC%8A%88%EC%93%94</t>
   </si>
   <si>
-    <t>1162조 9583억 2280만</t>
+    <t>1170조 4805억 6265만</t>
   </si>
   <si>
     <t>스툭</t>
@@ -765,7 +1023,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%EB%9F%AD%ED%8A%B8</t>
   </si>
   <si>
-    <t>1070조 4154억 4123만</t>
+    <t>1071조 633억 8410만</t>
   </si>
   <si>
     <t>욧츠</t>
@@ -777,6 +1035,15 @@
     <t>1004조 3060억 9433만</t>
   </si>
   <si>
+    <t>양룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
+  </si>
+  <si>
+    <t>962조 6459억 7591만</t>
+  </si>
+  <si>
     <t>무동동</t>
   </si>
   <si>
@@ -786,22 +1053,13 @@
     <t>939조 4385억 160만</t>
   </si>
   <si>
-    <t>양룽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EB%A3%BD</t>
-  </si>
-  <si>
-    <t>911조 1863억 1172만</t>
-  </si>
-  <si>
     <t>gorystal</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=gorystal</t>
   </si>
   <si>
-    <t>898조 3325억 1255만</t>
+    <t>923조 4464억 1428만</t>
   </si>
   <si>
     <t>또띠야칩</t>
@@ -819,7 +1077,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B5%EB%A3%BD</t>
   </si>
   <si>
-    <t>788조 6231억 1453만</t>
+    <t>829조 5492억 8086만</t>
   </si>
   <si>
     <t>률율율</t>
@@ -864,7 +1122,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A6%AC%EA%B3%A8%EB%93%9C</t>
   </si>
   <si>
-    <t>453조 8280억 6944만</t>
+    <t>477조 6327억 6015만</t>
   </si>
   <si>
     <t>원종일짱유나</t>
@@ -873,7 +1131,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9B%90%EC%A2%85%EC%9D%BC%EC%A7%B1%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>423조 6040억 5186만</t>
+    <t>434조 2061억 6842만</t>
   </si>
   <si>
     <t>문배동육칼</t>
@@ -882,280 +1140,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B0%B0%EB%8F%99%EC%9C%A1%EC%B9%BC</t>
   </si>
   <si>
-    <t>379조 6134억 1592만</t>
-  </si>
-  <si>
-    <t>아이스꾸임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
-  </si>
-  <si>
-    <t>116</t>
-  </si>
-  <si>
-    <t>2경 255조 6179억 2423만</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>7944조 993억 9474만</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>4704조 7804억 542만</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>4261조 8121억 2145만</t>
-  </si>
-  <si>
-    <t>대방어조아</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
-  </si>
-  <si>
-    <t>3924조 2536억 9340만</t>
-  </si>
-  <si>
-    <t>서포터즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
-  </si>
-  <si>
-    <t>2958조 4121억 9385만</t>
-  </si>
-  <si>
-    <t>퍼퓸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8D%BC%ED%93%B8</t>
-  </si>
-  <si>
-    <t>2845조 5542억 8706만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>2301조 7318억 5637만</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>2155조 4511억 6887만</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>2043조 9656억 4336만</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>1697조 755억 7134만</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>1324조 9226억 3624만</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>1134조 9932억 8765만</t>
-  </si>
-  <si>
-    <t>호우기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>1124조 2763억 6571만</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>1109조 9165억 9489만</t>
-  </si>
-  <si>
-    <t>채무조정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
-  </si>
-  <si>
-    <t>1077조 4158억 5356만</t>
-  </si>
-  <si>
-    <t>뽀송히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
-  </si>
-  <si>
-    <t>1042조 2381억 369만</t>
-  </si>
-  <si>
-    <t>좀치는형님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
-  </si>
-  <si>
-    <t>1035조 3847억 2058만</t>
-  </si>
-  <si>
-    <t>정태준</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
-  </si>
-  <si>
-    <t>970조 2899억 6670만</t>
-  </si>
-  <si>
-    <t>라탱호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
-  </si>
-  <si>
-    <t>878조 9823억 5133만</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>789조 2546억 9378만</t>
-  </si>
-  <si>
-    <t>짤똘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
-  </si>
-  <si>
-    <t>671조 5173억 6638만</t>
-  </si>
-  <si>
-    <t>팡대지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%A1%EB%8C%80%EC%A7%80</t>
-  </si>
-  <si>
-    <t>575조 1653억 9478만</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>558조 368억 4937만</t>
-  </si>
-  <si>
-    <t>박준우2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%A4%80%EC%9A%B02</t>
-  </si>
-  <si>
-    <t>538조 1761억 3296만</t>
-  </si>
-  <si>
-    <t>솔인</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%94%EC%9D%B8</t>
-  </si>
-  <si>
-    <t>468조 4891억 849만</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>337조 7925억 8502만</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>292조 9201억 6015만</t>
-  </si>
-  <si>
-    <t>꼬북빵야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BC%AC%EB%B6%81%EB%B9%B5%EC%95%BC</t>
-  </si>
-  <si>
-    <t>275조 6869억 3523만</t>
+    <t>385조 8360억 7882만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%AC%EC%8B%A0%EC%82%90%EC%95%BD%EC%9E%90</t>
   </si>
   <si>
-    <t>6501조 2641억 9896만</t>
+    <t>6530조 3023억 4059만</t>
   </si>
   <si>
     <t>우니아파요</t>
@@ -1182,7 +1173,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BD%EC%B0%BD%EB%8B%B9%EC%9D%BC%EA%B0%9C%ED%86%B5</t>
   </si>
   <si>
-    <t>3944조 2652억 3274만</t>
+    <t>4119조 8252억 9776만</t>
   </si>
   <si>
     <t>유수달</t>
@@ -1191,7 +1182,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>3324조 7984억 5566만</t>
+    <t>3434조 5745억 6656만</t>
   </si>
   <si>
     <t>여니워니</t>
@@ -1209,7 +1200,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9A%A9%ED%95%98%EB%8B%A4</t>
   </si>
   <si>
-    <t>2601조 2204억 5556만</t>
+    <t>2603조 5955억 597만</t>
+  </si>
+  <si>
+    <t>시골미남</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
+  </si>
+  <si>
+    <t>2597조 5226억 3060만</t>
   </si>
   <si>
     <t>포빅</t>
@@ -1218,7 +1218,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EB%B9%85</t>
   </si>
   <si>
-    <t>2481조 5827억 2891만</t>
+    <t>2515조 9073억 7619만</t>
   </si>
   <si>
     <t>종꿀</t>
@@ -1227,7 +1227,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%BF%80</t>
   </si>
   <si>
-    <t>2420조 6677억 6056만</t>
+    <t>2433조 5416억 4572만</t>
   </si>
   <si>
     <t>해달잉</t>
@@ -1245,16 +1245,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9D%B4%EC%96%B8%ED%8A%B8%EB%A6%AC</t>
   </si>
   <si>
-    <t>2151조 5238억 6674만</t>
-  </si>
-  <si>
-    <t>시골미남</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B3%A8%EB%AF%B8%EB%82%A8</t>
-  </si>
-  <si>
-    <t>2146조 3238억 3192만</t>
+    <t>2158조 8353억 6792만</t>
   </si>
   <si>
     <t>세월이야속해</t>
@@ -1263,7 +1254,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EC%9B%94%EC%9D%B4%EC%95%BC%EC%86%8D%ED%95%B4</t>
   </si>
   <si>
-    <t>2092조 5680억 8366만</t>
+    <t>2121조 4771억 1480만</t>
   </si>
   <si>
     <t>MangCI</t>
@@ -1272,7 +1263,7 @@
     <t>https://mgf.gg/contents/character.php?n=MangCI</t>
   </si>
   <si>
-    <t>1988조 3644억 8119만</t>
+    <t>2119조 353억 1969만</t>
   </si>
   <si>
     <t>여자둘남자둘</t>
@@ -1281,7 +1272,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EC%9E%90%EB%91%98%EB%82%A8%EC%9E%90%EB%91%98</t>
   </si>
   <si>
-    <t>1912조 768억 9141만</t>
+    <t>1934조 6567억 6353만</t>
   </si>
   <si>
     <t>덩개</t>
@@ -1299,7 +1290,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%88%ED%83%80</t>
   </si>
   <si>
-    <t>1291조 2442억 5985만</t>
+    <t>1327조 4794억 6540만</t>
   </si>
   <si>
     <t>티에이치</t>
@@ -1308,7 +1299,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%97%90%EC%9D%B4%EC%B9%98</t>
   </si>
   <si>
-    <t>1156조 5866억 1348만</t>
+    <t>1177조 6186억 3929만</t>
   </si>
   <si>
     <t>모르페우스</t>
@@ -1335,7 +1326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EA%B8%88%EC%AA%BD</t>
   </si>
   <si>
-    <t>1001조 2765억 9574만</t>
+    <t>1001조 3815억 6032만</t>
   </si>
   <si>
     <t>파이리양말</t>
@@ -1362,7 +1353,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%A7%B1%EC%B0%BD%EB%82%A8</t>
   </si>
   <si>
-    <t>791조 7059억 4412만</t>
+    <t>821조 467억 7853만</t>
+  </si>
+  <si>
+    <t>이루니아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%A3%A8%EB%8B%88%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>812조 4997억 5789만</t>
   </si>
   <si>
     <t>감화</t>
@@ -1371,7 +1371,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%ED%99%94</t>
   </si>
   <si>
-    <t>782조 9287억 8838만</t>
+    <t>792조 6328억 2368만</t>
   </si>
   <si>
     <t>히어로호걸</t>
@@ -1398,7 +1398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%ED%83%84%EB%B3%B4%EC%9A%B0%EC%A7%B1</t>
   </si>
   <si>
-    <t>613조 6005억 7337만</t>
+    <t>617조 7385억 6931만</t>
   </si>
   <si>
     <t>하비엔</t>
@@ -1407,7 +1407,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%B9%84%EC%97%94</t>
   </si>
   <si>
-    <t>413조 5874억 3219만</t>
+    <t>443조 9421억 1806만</t>
+  </si>
+  <si>
+    <t>31</t>
   </si>
   <si>
     <t>채구링</t>
@@ -1416,7 +1419,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EA%B5%AC%EB%A7%81</t>
   </si>
   <si>
-    <t>392조 3486억 9945만</t>
+    <t>423조 5369억 2218만</t>
   </si>
 </sst>
 </file>
@@ -1903,19 +1906,19 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -1944,19 +1947,19 @@
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -1979,7 +1982,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
@@ -2431,13 +2434,13 @@
         <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2448,25 +2451,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>124</v>
@@ -2559,7 +2562,7 @@
         <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>99</v>
@@ -2591,7 +2594,7 @@
         <v>61</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>99</v>
@@ -3059,6 +3062,984 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="21.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J29"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3106,19 +4087,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>196</v>
+        <v>283</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>196</v>
+        <v>283</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>197</v>
+        <v>284</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>61</v>
@@ -3130,27 +4111,27 @@
         <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>198</v>
+        <v>285</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>199</v>
+        <v>286</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>199</v>
+        <v>286</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>61</v>
@@ -3162,27 +4143,27 @@
         <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>202</v>
+        <v>289</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>203</v>
+        <v>290</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>61</v>
@@ -3194,27 +4175,27 @@
         <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>204</v>
+        <v>291</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>205</v>
+        <v>292</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>206</v>
+        <v>293</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>61</v>
@@ -3226,27 +4207,27 @@
         <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>208</v>
+        <v>295</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>208</v>
+        <v>295</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>209</v>
+        <v>296</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>61</v>
@@ -3258,91 +4239,91 @@
         <v>99</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>210</v>
+        <v>297</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>213</v>
+        <v>300</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>217</v>
+        <v>304</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>147</v>
@@ -3354,27 +4335,27 @@
         <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>218</v>
+        <v>305</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>219</v>
+        <v>306</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>219</v>
+        <v>306</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>220</v>
+        <v>307</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>61</v>
@@ -3386,27 +4367,27 @@
         <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>221</v>
+        <v>308</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>222</v>
+        <v>309</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>222</v>
+        <v>309</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>223</v>
+        <v>310</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>61</v>
@@ -3418,27 +4399,27 @@
         <v>85</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>224</v>
+        <v>311</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>225</v>
+        <v>312</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>225</v>
+        <v>312</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>226</v>
+        <v>313</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>61</v>
@@ -3450,91 +4431,91 @@
         <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>227</v>
+        <v>314</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>228</v>
+        <v>315</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>229</v>
+        <v>316</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>233</v>
+        <v>319</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>234</v>
+        <v>320</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>236</v>
+        <v>322</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>61</v>
@@ -3546,27 +4527,27 @@
         <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>237</v>
+        <v>323</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>238</v>
+        <v>324</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>238</v>
+        <v>324</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>239</v>
+        <v>325</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>61</v>
@@ -3578,27 +4559,27 @@
         <v>105</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>240</v>
+        <v>326</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>241</v>
+        <v>327</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>241</v>
+        <v>327</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>242</v>
+        <v>328</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>61</v>
@@ -3610,27 +4591,27 @@
         <v>105</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>243</v>
+        <v>329</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>244</v>
+        <v>330</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>244</v>
+        <v>330</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>245</v>
+        <v>331</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
@@ -3642,27 +4623,27 @@
         <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>246</v>
+        <v>332</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>247</v>
+        <v>333</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>248</v>
+        <v>334</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>61</v>
@@ -3674,91 +4655,91 @@
         <v>105</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>249</v>
+        <v>335</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>250</v>
+        <v>336</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>250</v>
+        <v>336</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>251</v>
+        <v>337</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>252</v>
+        <v>338</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>253</v>
+        <v>339</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>253</v>
+        <v>339</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>255</v>
+        <v>341</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>256</v>
+        <v>342</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>256</v>
+        <v>342</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>257</v>
+        <v>343</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>61</v>
@@ -3770,27 +4751,27 @@
         <v>105</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>258</v>
+        <v>344</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>259</v>
+        <v>345</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>260</v>
+        <v>346</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>61</v>
@@ -3802,27 +4783,27 @@
         <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>261</v>
+        <v>347</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>262</v>
+        <v>348</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>262</v>
+        <v>348</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>263</v>
+        <v>349</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>61</v>
@@ -3834,27 +4815,27 @@
         <v>105</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>264</v>
+        <v>350</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>266</v>
+        <v>352</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>61</v>
@@ -3866,27 +4847,27 @@
         <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>267</v>
+        <v>353</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>268</v>
+        <v>354</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>61</v>
@@ -3898,27 +4879,27 @@
         <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>270</v>
+        <v>356</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>271</v>
+        <v>357</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>271</v>
+        <v>357</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>272</v>
+        <v>358</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>61</v>
@@ -3930,27 +4911,27 @@
         <v>194</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>273</v>
+        <v>359</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>274</v>
+        <v>360</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>274</v>
+        <v>360</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>275</v>
+        <v>361</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>61</v>
@@ -3962,27 +4943,27 @@
         <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>276</v>
+        <v>362</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>277</v>
+        <v>363</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>277</v>
+        <v>363</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>61</v>
@@ -3994,27 +4975,27 @@
         <v>194</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>279</v>
+        <v>365</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>280</v>
+        <v>366</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>280</v>
+        <v>366</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>281</v>
+        <v>367</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>61</v>
@@ -4026,27 +5007,27 @@
         <v>105</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>282</v>
+        <v>368</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>283</v>
+        <v>369</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>284</v>
+        <v>370</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>61</v>
@@ -4058,10 +5039,10 @@
         <v>194</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -4102,1020 +5083,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="21.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5174,7 +5144,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>147</v>
@@ -5186,7 +5156,7 @@
         <v>63</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5200,13 +5170,13 @@
         <v>65</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>61</v>
@@ -5218,7 +5188,7 @@
         <v>63</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5232,13 +5202,13 @@
         <v>70</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>61</v>
@@ -5250,7 +5220,7 @@
         <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5264,13 +5234,13 @@
         <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>61</v>
@@ -5279,10 +5249,10 @@
         <v>62</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5296,25 +5266,25 @@
         <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>321</v>
+        <v>229</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>63</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5328,13 +5298,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>61</v>
@@ -5346,7 +5316,7 @@
         <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5360,25 +5330,25 @@
         <v>92</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5392,25 +5362,25 @@
         <v>96</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5424,25 +5394,25 @@
         <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5456,25 +5426,25 @@
         <v>107</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5488,25 +5458,25 @@
         <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>321</v>
+        <v>217</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5520,25 +5490,25 @@
         <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>90</v>
+        <v>229</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>99</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5549,16 +5519,16 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>61</v>
@@ -5570,7 +5540,7 @@
         <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5584,13 +5554,13 @@
         <v>125</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>61</v>
@@ -5602,7 +5572,7 @@
         <v>99</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5616,13 +5586,13 @@
         <v>129</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>61</v>
@@ -5634,7 +5604,7 @@
         <v>99</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5648,13 +5618,13 @@
         <v>133</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>61</v>
@@ -5666,7 +5636,7 @@
         <v>105</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5680,13 +5650,13 @@
         <v>137</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>61</v>
@@ -5698,7 +5668,7 @@
         <v>99</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5712,25 +5682,25 @@
         <v>141</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5744,13 +5714,13 @@
         <v>145</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>61</v>
@@ -5762,7 +5732,7 @@
         <v>99</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5776,13 +5746,13 @@
         <v>149</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>61</v>
@@ -5794,7 +5764,7 @@
         <v>194</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5808,13 +5778,13 @@
         <v>153</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>61</v>
@@ -5826,7 +5796,7 @@
         <v>172</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5840,13 +5810,13 @@
         <v>157</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>61</v>
@@ -5858,7 +5828,7 @@
         <v>105</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5872,13 +5842,13 @@
         <v>161</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>61</v>
@@ -5890,7 +5860,7 @@
         <v>105</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5904,13 +5874,13 @@
         <v>165</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>61</v>
@@ -5922,7 +5892,7 @@
         <v>99</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5936,13 +5906,13 @@
         <v>169</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>61</v>
@@ -5954,7 +5924,7 @@
         <v>105</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5968,25 +5938,25 @@
         <v>174</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6000,25 +5970,25 @@
         <v>178</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6032,25 +6002,25 @@
         <v>182</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>61</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>105</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6064,13 +6034,13 @@
         <v>186</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>61</v>
@@ -6079,10 +6049,10 @@
         <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>172</v>
+        <v>105</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6096,32 +6066,64 @@
         <v>191</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H31" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="J31" s="2" t="s">
+      <c r="H32" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J32"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6153,6 +6155,7 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
+    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -8,24 +8,26 @@
   </bookViews>
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
-    <sheet name="지존길드" sheetId="2" r:id="rId2"/>
-    <sheet name="빅딜" sheetId="3" r:id="rId3"/>
-    <sheet name="TopOfTop" sheetId="4" r:id="rId4"/>
-    <sheet name="눈별" sheetId="5" r:id="rId5"/>
+    <sheet name="개포동" sheetId="2" r:id="rId2"/>
+    <sheet name="멀랑" sheetId="3" r:id="rId3"/>
+    <sheet name="빅딜" sheetId="4" r:id="rId4"/>
+    <sheet name="GDRAGON" sheetId="5" r:id="rId5"/>
+    <sheet name="띵똥이" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">TopOfTop!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">눈별!$A$1:$J$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">빅딜!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">지존길드!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">GDRAGON!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">개포동!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">띵똥이!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">멀랑!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">빅딜!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="565">
   <si>
     <t>guild_name</t>
   </si>
@@ -66,22 +68,22 @@
     <t>data_date</t>
   </si>
   <si>
-    <t>지존길드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%A7%80%EC%A1%B4%EA%B8%B8%EB%93%9C</t>
+    <t>개포동</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EA%B0%9C%ED%8F%AC%EB%8F%99</t>
   </si>
   <si>
     <t>Scania</t>
   </si>
   <si>
-    <t>Scania 4</t>
-  </si>
-  <si>
-    <t>883</t>
-  </si>
-  <si>
-    <t>30위</t>
+    <t>Scania 1</t>
+  </si>
+  <si>
+    <t>728</t>
+  </si>
+  <si>
+    <t>34위</t>
   </si>
   <si>
     <t>Lv.9</t>
@@ -90,91 +92,121 @@
     <t>30명</t>
   </si>
   <si>
-    <t>4경 9428조 9087억 197만</t>
-  </si>
-  <si>
-    <t>지존길드 공지용 오픈채팅 필수참여입니다.</t>
-  </si>
-  <si>
-    <t>지존순찌</t>
+    <t>7경 2806조 1846억 5135만</t>
+  </si>
+  <si>
+    <t>오래 재밌게 하실분들 오셔욜</t>
+  </si>
+  <si>
+    <t>진이찬우</t>
+  </si>
+  <si>
+    <t>2026.10.02</t>
+  </si>
+  <si>
+    <t>멀랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%A9%80%EB%9E%91</t>
+  </si>
+  <si>
+    <t>Scania 21</t>
+  </si>
+  <si>
+    <t>828</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>27명</t>
+  </si>
+  <si>
+    <t>5경 7193조 9201억 1645만</t>
+  </si>
+  <si>
+    <t>몰랑, 멀랑, 물랑, 여러분 레쓰꼬</t>
+  </si>
+  <si>
+    <t>똥보마</t>
+  </si>
+  <si>
+    <t>2026.09.20</t>
+  </si>
+  <si>
+    <t>빅딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
+  </si>
+  <si>
+    <t>Scania 2</t>
+  </si>
+  <si>
+    <t>876</t>
+  </si>
+  <si>
+    <t>40위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>5경 985조 128억 1537만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
   </si>
   <si>
     <t>2026.09.21</t>
   </si>
   <si>
-    <t>빅딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B9%85%EB%94%9C</t>
-  </si>
-  <si>
-    <t>Scania 2</t>
-  </si>
-  <si>
-    <t>866</t>
-  </si>
-  <si>
-    <t>39위</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>5경 985조 128억 1537만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>TopOfTop</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=TopOfTop</t>
-  </si>
-  <si>
-    <t>Scania 18</t>
-  </si>
-  <si>
-    <t>919</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
-    <t>4경 4791조 9790억 3201만</t>
-  </si>
-  <si>
-    <t>길컨 1등만</t>
-  </si>
-  <si>
-    <t>복어띰</t>
-  </si>
-  <si>
-    <t>2026.09.22</t>
-  </si>
-  <si>
-    <t>눈별</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%88%88%EB%B3%84</t>
-  </si>
-  <si>
-    <t>Scania 6</t>
-  </si>
-  <si>
-    <t>907</t>
-  </si>
-  <si>
-    <t>4경 6681조 7185억 6799만</t>
-  </si>
-  <si>
-    <t>함께 성장하고 같이 즐기는 '눈별' 길드입니다. 길컨 참여 필수. 토벌전 1000억이상 신청바랍니다!</t>
-  </si>
-  <si>
-    <t>심신삐약자</t>
+    <t>GDRAGON</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=GDRAGON</t>
+  </si>
+  <si>
+    <t>Scania 3</t>
+  </si>
+  <si>
+    <t>821</t>
+  </si>
+  <si>
+    <t>32위</t>
+  </si>
+  <si>
+    <t>5경 8136조 812억 8633만</t>
+  </si>
+  <si>
+    <t>길드 컨텐츠 진심인 분 각 컨텐츠 별 점수와 함께 귓 주세요</t>
+  </si>
+  <si>
+    <t>법칙교주</t>
+  </si>
+  <si>
+    <t>띵똥이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%9D%B5%EB%98%A5%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>Scania 7</t>
+  </si>
+  <si>
+    <t>955</t>
+  </si>
+  <si>
+    <t>4경 2235조 5692억 2681만</t>
+  </si>
+  <si>
+    <t>띵똥이 세계로 초대한다</t>
+  </si>
+  <si>
+    <t>승띵똥이</t>
   </si>
   <si>
     <t>member_rank_in_guild</t>
@@ -204,610 +236,871 @@
     <t>1</t>
   </si>
   <si>
-    <t>지존쫀파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%AB%80%ED%8C%8C</t>
+    <t>네네핫쵸킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%84%A4%ED%95%AB%EC%B5%B8%ED%82%B9</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>1경 4769조 6032억 5127만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9D%B4%EC%B0%AC%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>1경 2428조 4547억 7500만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>테더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%85%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>캡틴</t>
+  </si>
+  <si>
+    <t>8072조 4200억 2179만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>진이이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9D%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>5528조 8552억 2176만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>불꽃기둥성휘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%BD%83%EA%B8%B0%EB%91%A5%EC%84%B1%ED%9C%98</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>4856조 2350억 5796만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>만쥬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%A5%AC</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>3356조 9275억 3654만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>네생각</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EC%83%9D%EA%B0%81</t>
+  </si>
+  <si>
+    <t>2768조 9866억 617만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>요미삐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EB%AF%B8%EC%82%90</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>2556조 5972억 5788만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>토뭉찡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AD%89%EC%B0%A1</t>
+  </si>
+  <si>
+    <t>2409조 4916억 4513만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>최창주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%B0%BD%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>2035조 9532억 9350만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>헤아핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%A4%EC%95%84%ED%95%91</t>
+  </si>
+  <si>
+    <t>1722조 9577억 9838만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>쿠키아빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%A0%ED%82%A4%EC%95%84%EB%B9%A0</t>
+  </si>
+  <si>
     <t>나이트로드</t>
   </si>
   <si>
-    <t>115</t>
-  </si>
-  <si>
-    <t>9888조 9654억 14만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>수텍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%ED%85%8D</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>7731조 8382억 7567만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>포항엄석대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EC%97%84%EC%84%9D%EB%8C%80</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>114</t>
-  </si>
-  <si>
-    <t>4544조 7861억 2132만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>협의</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%91%EC%9D%98</t>
+    <t>111</t>
+  </si>
+  <si>
+    <t>1506조 3744억 2344만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>드노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%85%B8</t>
+  </si>
+  <si>
+    <t>1482조 8199억 9404만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>강대리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%8C%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>1150조 3366억 5799만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>명예가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%85%EC%98%88%EA%B0%80</t>
+  </si>
+  <si>
+    <t>987조 3320억 9052만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>금쿵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%88%EC%BF%B5</t>
+  </si>
+  <si>
+    <t>884조 2593억 6763만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>핑크해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%ED%81%AC%ED%95%B4</t>
+  </si>
+  <si>
+    <t>838조 7068억 5594만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>재형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%ED%98%95</t>
+  </si>
+  <si>
+    <t>679조 6265억 6957만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>왕스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>628조 1006억 2002만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>개천박한이름</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EC%B2%9C%EB%B0%95%ED%95%9C%EC%9D%B4%EB%A6%84</t>
+  </si>
+  <si>
+    <t>551조 1430억 2090만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>rrr000rrr</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=rrr000rrr</t>
+  </si>
+  <si>
+    <t>531조 1387억 7963만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>진이시온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%84%EC%9D%B4%EC%8B%9C%EC%98%A8</t>
+  </si>
+  <si>
+    <t>489조 4840억 2311만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>웅히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%85%ED%9E%88</t>
+  </si>
+  <si>
+    <t>488조 529억 1773만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>청양한태훈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%96%91%ED%95%9C%ED%83%9C%ED%9B%88</t>
+  </si>
+  <si>
+    <t>452조 8265억 5392만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>배퉁퉁방구삑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%ED%89%81%ED%89%81%EB%B0%A9%EA%B5%AC%EC%82%91</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>392조 6072억 40만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>불금</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B8%88</t>
+  </si>
+  <si>
+    <t>373조 5939억 6363만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>천사비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%82%AC%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>356조 9346억 9448만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>엇박찌르기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%87%EB%B0%95%EC%B0%8C%EB%A5%B4%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>238조 3095억 5527만</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>웽잠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9B%BD%EC%9E%A0</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>238조 1169억 9036만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>페옥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%98%EC%98%A5</t>
   </si>
   <si>
     <t>바이퍼</t>
   </si>
   <si>
-    <t>4402조 1032억 4015만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>타개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%80%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>113</t>
-  </si>
-  <si>
-    <t>3694조 4730억 5673만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>기뽐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%BD%90</t>
+    <t>104</t>
+  </si>
+  <si>
+    <t>29조 9379억 726만</t>
+  </si>
+  <si>
+    <t>상남자호소인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EB%82%A8%EC%9E%90%ED%98%B8%EC%86%8C%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>6774조 1238억 3581만</t>
+  </si>
+  <si>
+    <t>야스무새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%8A%A4%EB%AC%B4%EC%83%88</t>
+  </si>
+  <si>
+    <t>5769조 8688억 6846만</t>
+  </si>
+  <si>
+    <t>치즈냥봄이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%EC%A6%88%EB%83%A5%EB%B4%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5062조 9488억 1435만</t>
+  </si>
+  <si>
+    <t>꿀유자맛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EC%9C%A0%EC%9E%90%EB%A7%9B</t>
+  </si>
+  <si>
+    <t>4286조 3750억 9093만</t>
+  </si>
+  <si>
+    <t>꿀밤이요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BF%80%EB%B0%A4%EC%9D%B4%EC%9A%94</t>
+  </si>
+  <si>
+    <t>4221조 8365억 1645만</t>
+  </si>
+  <si>
+    <t>따효기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B0%ED%9A%A8%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>4104조 5842억 8341만</t>
+  </si>
+  <si>
+    <t>맨발청춘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%EB%B0%9C%EC%B2%AD%EC%B6%98</t>
+  </si>
+  <si>
+    <t>3828조 1724억 2699만</t>
+  </si>
+  <si>
+    <t>겨울몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>3513조 57억 4934만</t>
+  </si>
+  <si>
+    <t>dlxxals</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=dlxxals</t>
+  </si>
+  <si>
+    <t>3270조 8464억 6469만</t>
+  </si>
+  <si>
+    <t>또뚜룸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%90%EB%9A%9C%EB%A3%B8</t>
+  </si>
+  <si>
+    <t>3110조 349억 2179만</t>
+  </si>
+  <si>
+    <t>야스오부시</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%8A%A4%EC%98%A4%EB%B6%80%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>2873조 4066억 9858만</t>
+  </si>
+  <si>
+    <t>벨뱃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A8%EB%B1%83</t>
+  </si>
+  <si>
+    <t>2752조 7670억 1586만</t>
+  </si>
+  <si>
+    <t>슝기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%9D%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>2529조 7120억 1765만</t>
+  </si>
+  <si>
+    <t>Citizen07</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Citizen07</t>
+  </si>
+  <si>
+    <t>2514조 3967억 2004만</t>
+  </si>
+  <si>
+    <t>듀여이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%80%EC%97%AC%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2209조 275억 8874만</t>
+  </si>
+  <si>
+    <t>독깨깨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B9%A8%EA%B9%A8</t>
+  </si>
+  <si>
+    <t>2008조 3512억 9074만</t>
+  </si>
+  <si>
+    <t>경차리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%BD%EC%B0%A8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1800조 6660억 6904만</t>
+  </si>
+  <si>
+    <t>루시X</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%8B%9CX</t>
+  </si>
+  <si>
+    <t>1748조 8434억 4202만</t>
+  </si>
+  <si>
+    <t>매화려인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%ED%99%94%EB%A0%A4%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>1728조 8206억 7575만</t>
+  </si>
+  <si>
+    <t>짝꿍31</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%9D%EA%BF%8D31</t>
+  </si>
+  <si>
+    <t>1464조 858억 7715만</t>
+  </si>
+  <si>
+    <t>최강태온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EA%B0%95%ED%83%9C%EC%98%A8</t>
+  </si>
+  <si>
+    <t>1418조 9709억 4333만</t>
+  </si>
+  <si>
+    <t>하루일과시작</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%A3%A8%EC%9D%BC%EA%B3%BC%EC%8B%9C%EC%9E%91</t>
+  </si>
+  <si>
+    <t>1329조 1447억 3676만</t>
+  </si>
+  <si>
+    <t>민힝만듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%9E%9D%EB%A7%8C%EB%93%80</t>
+  </si>
+  <si>
+    <t>1273조 3953억 4461만</t>
+  </si>
+  <si>
+    <t>wooksem</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=wooksem</t>
+  </si>
+  <si>
+    <t>1262조 4954억 1499만</t>
+  </si>
+  <si>
+    <t>크리스탈s</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%EB%A6%AC%EC%8A%A4%ED%83%88s</t>
+  </si>
+  <si>
+    <t>1075조 7251억 7289만</t>
+  </si>
+  <si>
+    <t>똥쉐도우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%89%90%EB%8F%84%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1044조 5559억 4230만</t>
+  </si>
+  <si>
+    <t>재봉보로봉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%AC%EB%B4%89%EB%B3%B4%EB%A1%9C%EB%B4%89</t>
+  </si>
+  <si>
+    <t>893조 4347억 5248만</t>
+  </si>
+  <si>
+    <t>빠제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A0%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>594조 7119억 808만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EB%B3%B4%EB%A7%88</t>
+  </si>
+  <si>
+    <t>583조 8403억 8783만</t>
+  </si>
+  <si>
+    <t>아이스꾸임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9D%B4%EC%8A%A4%EA%BE%B8%EC%9E%84</t>
+  </si>
+  <si>
+    <t>2경 374조 8201억 5764만</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>8237조 7144억 4543만</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>5067조 550억 6840만</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>4269조 1039억 8746만</t>
+  </si>
+  <si>
+    <t>대방어조아</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EB%B0%A9%EC%96%B4%EC%A1%B0%EC%95%84</t>
+  </si>
+  <si>
+    <t>4145조 5731억 3307만</t>
+  </si>
+  <si>
+    <t>서포터즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%ED%8F%AC%ED%84%B0%EC%A6%88</t>
+  </si>
+  <si>
+    <t>3109조 5410억 3413만</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>2586조 1679억 2303만</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>2486조 1038억 1649만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2422조 114억 1172만</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>2247조 5088억 7013만</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>1339조 3325억 1781만</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>1214조 8117억 7531만</t>
+  </si>
+  <si>
+    <t>호우기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%9A%B0%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>1154조 5842억 8701만</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>1139조 3354억 3997만</t>
+  </si>
+  <si>
+    <t>채무조정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%AC%B4%EC%A1%B0%EC%A0%95</t>
+  </si>
+  <si>
+    <t>1082조 2012억 4397만</t>
+  </si>
+  <si>
+    <t>뽀송히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EC%86%A1%ED%9E%88</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>1065조 4129억 9767만</t>
+  </si>
+  <si>
+    <t>좀치는형님</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%80%EC%B9%98%EB%8A%94%ED%98%95%EB%8B%98</t>
+  </si>
+  <si>
+    <t>1044조 7501억 1470만</t>
+  </si>
+  <si>
+    <t>정태준</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%ED%83%9C%EC%A4%80</t>
+  </si>
+  <si>
+    <t>974조 8229억 1308만</t>
+  </si>
+  <si>
+    <t>라탱호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%ED%83%B1%ED%98%B8</t>
+  </si>
+  <si>
+    <t>924조 4741억 2884만</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>792조 9853억 5939만</t>
+  </si>
+  <si>
+    <t>짤똘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%A4%EB%98%98</t>
   </si>
   <si>
     <t>팔라딘</t>
   </si>
   <si>
-    <t>3303조 6174억 3840만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>댜니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2884조 3838억 7409만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>포항가자미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%ED%95%AD%EA%B0%80%EC%9E%90%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>112</t>
-  </si>
-  <si>
-    <t>2585조 8424억 4496만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>뿡쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%A1%EC%93%B0</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>2533조 6647억 4576만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>지존빼앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EB%B9%BC%EC%95%99</t>
-  </si>
-  <si>
-    <t>캡틴</t>
-  </si>
-  <si>
-    <t>2515조 2382억 6614만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>변신술사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%80%EC%8B%A0%EC%88%A0%EC%82%AC</t>
-  </si>
-  <si>
-    <t>2465조 3877억 3257만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>온백</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A8%EB%B0%B1</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>2338조 5666억 805만</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>엘르가든</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%A5%B4%EA%B0%80%EB%93%A0</t>
-  </si>
-  <si>
-    <t>2313조 7071억 7362만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>파울</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9A%B8</t>
-  </si>
-  <si>
-    <t>1901조 6768억 6078만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>마카롱롱</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%B9%B4%EB%A1%B1%EB%A1%B1</t>
-  </si>
-  <si>
-    <t>1889조 8524억 3410만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>대좀이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8C%80%EC%A2%80%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1488조 1251억 1121만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>오옹나이스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%B9%EB%82%98%EC%9D%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1379조 1810억 4031만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>모짜리코베르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%A7%9C%EB%A6%AC%EC%BD%94%EB%B2%A0%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>1378조 9632억 3810만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%A1%B4%EC%88%9C%EC%B0%8C</t>
-  </si>
-  <si>
-    <t>